--- a/lang/da/headTags.xlsx
+++ b/lang/da/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1205</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1206</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1699">
   <si>
     <t>en</t>
   </si>
@@ -4705,316 +4705,319 @@
     <t>Twisted Wonderland</t>
   </si>
   <si>
+    <t>ULTRAKILL</t>
+  </si>
+  <si>
+    <t>Umineko - When They Cry</t>
+  </si>
+  <si>
+    <t>Umineko - Når de græder</t>
+  </si>
+  <si>
+    <t>Undertale</t>
+  </si>
+  <si>
+    <t>Undertale AU</t>
+  </si>
+  <si>
+    <t>Undertale Yellow</t>
+  </si>
+  <si>
+    <t>Undertale Gul</t>
+  </si>
+  <si>
+    <t>Universal Symbol</t>
+  </si>
+  <si>
+    <t>Up</t>
+  </si>
+  <si>
+    <t>Urban Wildlife</t>
+  </si>
+  <si>
+    <t>V for Vendetta</t>
+  </si>
+  <si>
+    <t>Valentines</t>
+  </si>
+  <si>
+    <t>Valorant</t>
+  </si>
+  <si>
+    <t>Vanilla (removed)</t>
+  </si>
+  <si>
+    <t>Vanilla (fjernet)</t>
+  </si>
+  <si>
+    <t>Vanilla Block</t>
+  </si>
+  <si>
+    <t>Vanilla Food</t>
+  </si>
+  <si>
+    <t>Vanilla Helmet</t>
+  </si>
+  <si>
+    <t>Vaniljehjelm</t>
+  </si>
+  <si>
+    <t>Vanilla Item</t>
+  </si>
+  <si>
+    <t>Vanilje-genstand</t>
+  </si>
+  <si>
+    <t>Vanilla Mob</t>
+  </si>
+  <si>
+    <t>Vault Hunters</t>
+  </si>
+  <si>
+    <t>Vegetable</t>
+  </si>
+  <si>
+    <t>Grøntsag</t>
+  </si>
+  <si>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Køretøj</t>
+  </si>
+  <si>
+    <t>Vikings</t>
+  </si>
+  <si>
+    <t>Vikinger</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Landsbyboer</t>
+  </si>
+  <si>
+    <t>Villager (Desert)</t>
+  </si>
+  <si>
+    <t>Landsbyboer (ørken)</t>
+  </si>
+  <si>
+    <t>Villager (Jungle)</t>
+  </si>
+  <si>
+    <t>Landsbyboer (jungle)</t>
+  </si>
+  <si>
+    <t>Villager (Plains)</t>
+  </si>
+  <si>
+    <t>Landsbyboer (Sletter)</t>
+  </si>
+  <si>
+    <t>Villager (Savanna)</t>
+  </si>
+  <si>
+    <t>Landsbyboer (Savanne)</t>
+  </si>
+  <si>
+    <t>Villager (Snowy Tundra)</t>
+  </si>
+  <si>
+    <t>Landsbyboer (snedækket tundra)</t>
+  </si>
+  <si>
+    <t>Villager (Swamp)</t>
+  </si>
+  <si>
+    <t>Landsbyboer (Sump)</t>
+  </si>
+  <si>
+    <t>Villager (Taiga)</t>
+  </si>
+  <si>
+    <t>Landsbyboer (Taiga)</t>
+  </si>
+  <si>
+    <t>Virtual Youtuber</t>
+  </si>
+  <si>
+    <t>Virtuel youtuber</t>
+  </si>
+  <si>
+    <t>Vocaloid</t>
+  </si>
+  <si>
+    <t>Voltron</t>
+  </si>
+  <si>
+    <t>Wakfu</t>
+  </si>
+  <si>
+    <t>Walking Dead</t>
+  </si>
+  <si>
+    <t>Wall-E</t>
+  </si>
+  <si>
+    <t>Wallace and Gromit</t>
+  </si>
+  <si>
+    <t>Wallace og Gromit</t>
+  </si>
+  <si>
+    <t>War of the Worlds</t>
+  </si>
+  <si>
+    <t>Verdenernes krig</t>
+  </si>
+  <si>
+    <t>Warcraft</t>
+  </si>
+  <si>
+    <t>Warframe</t>
+  </si>
+  <si>
+    <t>Warhammer</t>
+  </si>
+  <si>
+    <t>Warrior Cats</t>
+  </si>
+  <si>
+    <t>We Bear Bears</t>
+  </si>
+  <si>
+    <t>Vi bærer bjørne</t>
+  </si>
+  <si>
+    <t>We Happy Few</t>
+  </si>
+  <si>
+    <t>Weather</t>
+  </si>
+  <si>
+    <t>Welcome Home</t>
+  </si>
+  <si>
+    <t>Velkommen hjem</t>
+  </si>
+  <si>
+    <t>Who is this?</t>
+  </si>
+  <si>
+    <t>Hvem er det her?</t>
+  </si>
+  <si>
+    <t>Wild Update</t>
+  </si>
+  <si>
+    <t>Vild opdatering</t>
+  </si>
+  <si>
+    <t>Wings of Fire</t>
+  </si>
+  <si>
+    <t>Ildens vinger</t>
+  </si>
+  <si>
+    <t>Winnie the Pooh</t>
+  </si>
+  <si>
+    <t>Winter</t>
+  </si>
+  <si>
+    <t>Vinter</t>
+  </si>
+  <si>
+    <t>Witcher</t>
+  </si>
+  <si>
+    <t>Hekseren</t>
+  </si>
+  <si>
+    <t>Wonderful Wonder World</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>Træ</t>
+  </si>
+  <si>
+    <t>Wool</t>
+  </si>
+  <si>
+    <t>Uld</t>
+  </si>
+  <si>
+    <t>Work Safety Helmet</t>
+  </si>
+  <si>
+    <t>Sikkerhedshjelm til arbejde</t>
+  </si>
+  <si>
+    <t>Wreck It Ralph</t>
+  </si>
+  <si>
+    <t>Wybel</t>
+  </si>
+  <si>
+    <t>Wynncraft</t>
+  </si>
+  <si>
+    <t>X-Men</t>
+  </si>
+  <si>
+    <t>Xenoblade Chronicles</t>
+  </si>
+  <si>
+    <t>Yandere Simulator</t>
+  </si>
+  <si>
+    <t>Yellow Submarine</t>
+  </si>
+  <si>
+    <t>Yokai</t>
+  </si>
+  <si>
+    <t>Yooka Laylee</t>
+  </si>
+  <si>
+    <t>Young</t>
+  </si>
+  <si>
+    <t>Youtube</t>
+  </si>
+  <si>
+    <t>Yu-Gi-Oh</t>
+  </si>
+  <si>
+    <t>Yume Nikki</t>
+  </si>
+  <si>
+    <t>Zero no Tsukaima</t>
+  </si>
+  <si>
+    <t>Zero Wing</t>
+  </si>
+  <si>
+    <t>Zodiac Sign</t>
+  </si>
+  <si>
+    <t>Stjernetegn</t>
+  </si>
+  <si>
+    <t>Zombie</t>
+  </si>
+  <si>
+    <t>Zombie (Vanilla)</t>
+  </si>
+  <si>
+    <t>Zootopia</t>
+  </si>
+  <si>
     <t>Ultrakill</t>
-  </si>
-  <si>
-    <t>Umineko - When They Cry</t>
-  </si>
-  <si>
-    <t>Umineko - Når de græder</t>
-  </si>
-  <si>
-    <t>Undertale</t>
-  </si>
-  <si>
-    <t>Undertale AU</t>
-  </si>
-  <si>
-    <t>Undertale Yellow</t>
-  </si>
-  <si>
-    <t>Undertale Gul</t>
-  </si>
-  <si>
-    <t>Universal Symbol</t>
-  </si>
-  <si>
-    <t>Up</t>
-  </si>
-  <si>
-    <t>Urban Wildlife</t>
-  </si>
-  <si>
-    <t>V for Vendetta</t>
-  </si>
-  <si>
-    <t>Valentines</t>
-  </si>
-  <si>
-    <t>Valorant</t>
-  </si>
-  <si>
-    <t>Vanilla (removed)</t>
-  </si>
-  <si>
-    <t>Vanilla (fjernet)</t>
-  </si>
-  <si>
-    <t>Vanilla Block</t>
-  </si>
-  <si>
-    <t>Vanilla Food</t>
-  </si>
-  <si>
-    <t>Vanilla Helmet</t>
-  </si>
-  <si>
-    <t>Vaniljehjelm</t>
-  </si>
-  <si>
-    <t>Vanilla Item</t>
-  </si>
-  <si>
-    <t>Vanilje-genstand</t>
-  </si>
-  <si>
-    <t>Vanilla Mob</t>
-  </si>
-  <si>
-    <t>Vault Hunters</t>
-  </si>
-  <si>
-    <t>Vegetable</t>
-  </si>
-  <si>
-    <t>Grøntsag</t>
-  </si>
-  <si>
-    <t>Vehicle</t>
-  </si>
-  <si>
-    <t>Køretøj</t>
-  </si>
-  <si>
-    <t>Vikings</t>
-  </si>
-  <si>
-    <t>Vikinger</t>
-  </si>
-  <si>
-    <t>Villager</t>
-  </si>
-  <si>
-    <t>Landsbyboer</t>
-  </si>
-  <si>
-    <t>Villager (Desert)</t>
-  </si>
-  <si>
-    <t>Landsbyboer (ørken)</t>
-  </si>
-  <si>
-    <t>Villager (Jungle)</t>
-  </si>
-  <si>
-    <t>Landsbyboer (jungle)</t>
-  </si>
-  <si>
-    <t>Villager (Plains)</t>
-  </si>
-  <si>
-    <t>Landsbyboer (Sletter)</t>
-  </si>
-  <si>
-    <t>Villager (Savanna)</t>
-  </si>
-  <si>
-    <t>Landsbyboer (Savanne)</t>
-  </si>
-  <si>
-    <t>Villager (Snowy Tundra)</t>
-  </si>
-  <si>
-    <t>Landsbyboer (snedækket tundra)</t>
-  </si>
-  <si>
-    <t>Villager (Swamp)</t>
-  </si>
-  <si>
-    <t>Landsbyboer (Sump)</t>
-  </si>
-  <si>
-    <t>Villager (Taiga)</t>
-  </si>
-  <si>
-    <t>Landsbyboer (Taiga)</t>
-  </si>
-  <si>
-    <t>Virtual Youtuber</t>
-  </si>
-  <si>
-    <t>Virtuel youtuber</t>
-  </si>
-  <si>
-    <t>Vocaloid</t>
-  </si>
-  <si>
-    <t>Voltron</t>
-  </si>
-  <si>
-    <t>Wakfu</t>
-  </si>
-  <si>
-    <t>Walking Dead</t>
-  </si>
-  <si>
-    <t>Wall-E</t>
-  </si>
-  <si>
-    <t>Wallace and Gromit</t>
-  </si>
-  <si>
-    <t>Wallace og Gromit</t>
-  </si>
-  <si>
-    <t>War of the Worlds</t>
-  </si>
-  <si>
-    <t>Verdenernes krig</t>
-  </si>
-  <si>
-    <t>Warcraft</t>
-  </si>
-  <si>
-    <t>Warframe</t>
-  </si>
-  <si>
-    <t>Warhammer</t>
-  </si>
-  <si>
-    <t>Warrior Cats</t>
-  </si>
-  <si>
-    <t>We Bear Bears</t>
-  </si>
-  <si>
-    <t>Vi bærer bjørne</t>
-  </si>
-  <si>
-    <t>We Happy Few</t>
-  </si>
-  <si>
-    <t>Weather</t>
-  </si>
-  <si>
-    <t>Welcome Home</t>
-  </si>
-  <si>
-    <t>Velkommen hjem</t>
-  </si>
-  <si>
-    <t>Who is this?</t>
-  </si>
-  <si>
-    <t>Hvem er det her?</t>
-  </si>
-  <si>
-    <t>Wild Update</t>
-  </si>
-  <si>
-    <t>Vild opdatering</t>
-  </si>
-  <si>
-    <t>Wings of Fire</t>
-  </si>
-  <si>
-    <t>Ildens vinger</t>
-  </si>
-  <si>
-    <t>Winnie the Pooh</t>
-  </si>
-  <si>
-    <t>Winter</t>
-  </si>
-  <si>
-    <t>Vinter</t>
-  </si>
-  <si>
-    <t>Witcher</t>
-  </si>
-  <si>
-    <t>Hekseren</t>
-  </si>
-  <si>
-    <t>Wonderful Wonder World</t>
-  </si>
-  <si>
-    <t>Wood</t>
-  </si>
-  <si>
-    <t>Træ</t>
-  </si>
-  <si>
-    <t>Wool</t>
-  </si>
-  <si>
-    <t>Uld</t>
-  </si>
-  <si>
-    <t>Work Safety Helmet</t>
-  </si>
-  <si>
-    <t>Sikkerhedshjelm til arbejde</t>
-  </si>
-  <si>
-    <t>Wreck It Ralph</t>
-  </si>
-  <si>
-    <t>Wybel</t>
-  </si>
-  <si>
-    <t>Wynncraft</t>
-  </si>
-  <si>
-    <t>X-Men</t>
-  </si>
-  <si>
-    <t>Xenoblade Chronicles</t>
-  </si>
-  <si>
-    <t>Yandere Simulator</t>
-  </si>
-  <si>
-    <t>Yellow Submarine</t>
-  </si>
-  <si>
-    <t>Yokai</t>
-  </si>
-  <si>
-    <t>Yooka Laylee</t>
-  </si>
-  <si>
-    <t>Young</t>
-  </si>
-  <si>
-    <t>Youtube</t>
-  </si>
-  <si>
-    <t>Yu-Gi-Oh</t>
-  </si>
-  <si>
-    <t>Yume Nikki</t>
-  </si>
-  <si>
-    <t>Zero no Tsukaima</t>
-  </si>
-  <si>
-    <t>Zero Wing</t>
-  </si>
-  <si>
-    <t>Zodiac Sign</t>
-  </si>
-  <si>
-    <t>Stjernetegn</t>
-  </si>
-  <si>
-    <t>Zombie</t>
-  </si>
-  <si>
-    <t>Zombie (Vanilla)</t>
-  </si>
-  <si>
-    <t>Zootopia</t>
   </si>
   <si>
     <t>Hypixel (Mutations) Tag</t>
@@ -5457,7 +5460,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1205"/>
+  <dimension ref="A1:B1206"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14869,12 +14872,12 @@
         <v>1666</v>
       </c>
       <c r="B1176" t="s">
-        <v>1667</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="B1177" t="s">
         <v>1668</v>
@@ -14885,12 +14888,12 @@
         <v>1669</v>
       </c>
       <c r="B1178" t="s">
-        <v>1670</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="B1179" t="s">
         <v>1671</v>
@@ -14917,7 +14920,7 @@
         <v>1674</v>
       </c>
       <c r="B1182" t="s">
-        <v>381</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
@@ -14925,7 +14928,7 @@
         <v>1675</v>
       </c>
       <c r="B1183" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
@@ -14933,7 +14936,7 @@
         <v>1676</v>
       </c>
       <c r="B1184" t="s">
-        <v>1676</v>
+        <v>383</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
@@ -14949,7 +14952,7 @@
         <v>1678</v>
       </c>
       <c r="B1186" t="s">
-        <v>641</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
@@ -14957,7 +14960,7 @@
         <v>1679</v>
       </c>
       <c r="B1187" t="s">
-        <v>1679</v>
+        <v>641</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
@@ -14973,7 +14976,7 @@
         <v>1681</v>
       </c>
       <c r="B1189" t="s">
-        <v>915</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
@@ -14981,7 +14984,7 @@
         <v>1682</v>
       </c>
       <c r="B1190" t="s">
-        <v>1682</v>
+        <v>915</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
@@ -14997,7 +15000,7 @@
         <v>1684</v>
       </c>
       <c r="B1192" t="s">
-        <v>991</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
@@ -15005,7 +15008,7 @@
         <v>1685</v>
       </c>
       <c r="B1193" t="s">
-        <v>1685</v>
+        <v>991</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
@@ -15021,7 +15024,7 @@
         <v>1687</v>
       </c>
       <c r="B1195" t="s">
-        <v>1059</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
@@ -15029,7 +15032,7 @@
         <v>1688</v>
       </c>
       <c r="B1196" t="s">
-        <v>1114</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
@@ -15037,7 +15040,7 @@
         <v>1689</v>
       </c>
       <c r="B1197" t="s">
-        <v>1689</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
@@ -15069,7 +15072,7 @@
         <v>1693</v>
       </c>
       <c r="B1201" t="s">
-        <v>1414</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
@@ -15077,7 +15080,7 @@
         <v>1694</v>
       </c>
       <c r="B1202" t="s">
-        <v>1694</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="1203" spans="1:2">
@@ -15101,11 +15104,19 @@
         <v>1697</v>
       </c>
       <c r="B1205" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:2">
+      <c r="A1206" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B1206" t="s">
         <v>1531</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1205"/>
+  <autoFilter ref="A1:B1206"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/da/headTags.xlsx
+++ b/lang/da/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1206</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1207</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1700">
   <si>
     <t>en</t>
   </si>
@@ -3470,6 +3470,9 @@
   </si>
   <si>
     <t>Open Source Objects</t>
+  </si>
+  <si>
+    <t>Opus Magnum</t>
   </si>
   <si>
     <t>Orb</t>
@@ -5460,7 +5463,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1206"/>
+  <dimension ref="A1:B1207"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -11872,36 +11875,36 @@
         <v>1154</v>
       </c>
       <c r="B801" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B802" t="s">
         <v>1156</v>
-      </c>
-      <c r="B802" t="s">
-        <v>1157</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B803" t="s">
         <v>1158</v>
-      </c>
-      <c r="B803" t="s">
-        <v>1159</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B804" t="s">
         <v>1160</v>
-      </c>
-      <c r="B804" t="s">
-        <v>1161</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="B805" t="s">
         <v>1162</v>
@@ -11944,36 +11947,36 @@
         <v>1167</v>
       </c>
       <c r="B810" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B811" t="s">
         <v>1169</v>
-      </c>
-      <c r="B811" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B812" t="s">
         <v>1171</v>
-      </c>
-      <c r="B812" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B813" t="s">
         <v>1173</v>
-      </c>
-      <c r="B813" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="814" spans="1:2">
       <c r="A814" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="B814" t="s">
         <v>1175</v>
@@ -12008,12 +12011,12 @@
         <v>1179</v>
       </c>
       <c r="B818" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="B819" t="s">
         <v>1181</v>
@@ -12040,28 +12043,28 @@
         <v>1184</v>
       </c>
       <c r="B822" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B823" t="s">
         <v>1186</v>
-      </c>
-      <c r="B823" t="s">
-        <v>1187</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B824" t="s">
         <v>1188</v>
-      </c>
-      <c r="B824" t="s">
-        <v>1189</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="B825" t="s">
         <v>1190</v>
@@ -12072,12 +12075,12 @@
         <v>1191</v>
       </c>
       <c r="B826" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="B827" t="s">
         <v>1193</v>
@@ -12104,12 +12107,12 @@
         <v>1196</v>
       </c>
       <c r="B830" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="B831" t="s">
         <v>1198</v>
@@ -12152,12 +12155,12 @@
         <v>1203</v>
       </c>
       <c r="B836" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="B837" t="s">
         <v>1205</v>
@@ -12304,36 +12307,36 @@
         <v>1223</v>
       </c>
       <c r="B855" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B856" t="s">
         <v>1225</v>
-      </c>
-      <c r="B856" t="s">
-        <v>1226</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B857" t="s">
         <v>1227</v>
-      </c>
-      <c r="B857" t="s">
-        <v>1228</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B858" t="s">
         <v>1229</v>
-      </c>
-      <c r="B858" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B859" t="s">
         <v>1231</v>
@@ -12448,12 +12451,12 @@
         <v>1245</v>
       </c>
       <c r="B873" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B874" t="s">
         <v>1247</v>
@@ -12472,20 +12475,20 @@
         <v>1249</v>
       </c>
       <c r="B876" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B877" t="s">
         <v>1251</v>
-      </c>
-      <c r="B877" t="s">
-        <v>1252</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B878" t="s">
         <v>1253</v>
@@ -12504,20 +12507,20 @@
         <v>1255</v>
       </c>
       <c r="B880" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B881" t="s">
         <v>1257</v>
-      </c>
-      <c r="B881" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B882" t="s">
         <v>1259</v>
@@ -12560,12 +12563,12 @@
         <v>1264</v>
       </c>
       <c r="B887" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B888" t="s">
         <v>1266</v>
@@ -12608,12 +12611,12 @@
         <v>1271</v>
       </c>
       <c r="B893" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B894" t="s">
         <v>1273</v>
@@ -12624,12 +12627,12 @@
         <v>1274</v>
       </c>
       <c r="B895" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
       <c r="B896" t="s">
         <v>1276</v>
@@ -12664,28 +12667,28 @@
         <v>1280</v>
       </c>
       <c r="B900" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B901" t="s">
         <v>1282</v>
-      </c>
-      <c r="B901" t="s">
-        <v>1283</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B902" t="s">
         <v>1284</v>
-      </c>
-      <c r="B902" t="s">
-        <v>1285</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="B903" t="s">
         <v>1286</v>
@@ -12752,28 +12755,28 @@
         <v>1294</v>
       </c>
       <c r="B911" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B912" t="s">
         <v>1296</v>
-      </c>
-      <c r="B912" t="s">
-        <v>1297</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B913" t="s">
         <v>1298</v>
-      </c>
-      <c r="B913" t="s">
-        <v>1299</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="B914" t="s">
         <v>1300</v>
@@ -12800,44 +12803,44 @@
         <v>1303</v>
       </c>
       <c r="B917" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B918" t="s">
         <v>1305</v>
-      </c>
-      <c r="B918" t="s">
-        <v>1306</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
+        <v>1306</v>
+      </c>
+      <c r="B919" t="s">
         <v>1307</v>
-      </c>
-      <c r="B919" t="s">
-        <v>1308</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
+        <v>1308</v>
+      </c>
+      <c r="B920" t="s">
         <v>1309</v>
-      </c>
-      <c r="B920" t="s">
-        <v>1310</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B921" t="s">
         <v>1311</v>
-      </c>
-      <c r="B921" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B922" t="s">
         <v>1313</v>
@@ -12856,12 +12859,12 @@
         <v>1315</v>
       </c>
       <c r="B924" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="B925" t="s">
         <v>1317</v>
@@ -12872,20 +12875,20 @@
         <v>1318</v>
       </c>
       <c r="B926" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B927" t="s">
         <v>1320</v>
-      </c>
-      <c r="B927" t="s">
-        <v>1321</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="B928" t="s">
         <v>1322</v>
@@ -12896,20 +12899,20 @@
         <v>1323</v>
       </c>
       <c r="B929" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B930" t="s">
         <v>1325</v>
-      </c>
-      <c r="B930" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B931" t="s">
         <v>1327</v>
@@ -12944,52 +12947,52 @@
         <v>1331</v>
       </c>
       <c r="B935" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B936" t="s">
         <v>1333</v>
-      </c>
-      <c r="B936" t="s">
-        <v>1334</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B937" t="s">
         <v>1335</v>
-      </c>
-      <c r="B937" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B938" t="s">
         <v>1337</v>
-      </c>
-      <c r="B938" t="s">
-        <v>1338</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B939" t="s">
         <v>1339</v>
-      </c>
-      <c r="B939" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B940" t="s">
         <v>1341</v>
-      </c>
-      <c r="B940" t="s">
-        <v>1342</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="B941" t="s">
         <v>1343</v>
@@ -13016,12 +13019,12 @@
         <v>1346</v>
       </c>
       <c r="B944" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="B945" t="s">
         <v>1348</v>
@@ -13088,28 +13091,28 @@
         <v>1356</v>
       </c>
       <c r="B953" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B954" t="s">
         <v>1358</v>
-      </c>
-      <c r="B954" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B955" t="s">
         <v>1360</v>
-      </c>
-      <c r="B955" t="s">
-        <v>1361</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="B956" t="s">
         <v>1362</v>
@@ -13128,28 +13131,28 @@
         <v>1364</v>
       </c>
       <c r="B958" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
+        <v>1365</v>
+      </c>
+      <c r="B959" t="s">
         <v>1366</v>
-      </c>
-      <c r="B959" t="s">
-        <v>1367</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B960" t="s">
         <v>1368</v>
-      </c>
-      <c r="B960" t="s">
-        <v>1369</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="B961" t="s">
         <v>1370</v>
@@ -13168,12 +13171,12 @@
         <v>1372</v>
       </c>
       <c r="B963" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="B964" t="s">
         <v>1374</v>
@@ -13216,44 +13219,44 @@
         <v>1379</v>
       </c>
       <c r="B969" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B970" t="s">
         <v>1381</v>
-      </c>
-      <c r="B970" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B971" t="s">
         <v>1383</v>
-      </c>
-      <c r="B971" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B972" t="s">
         <v>1385</v>
-      </c>
-      <c r="B972" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B973" t="s">
         <v>1387</v>
-      </c>
-      <c r="B973" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="B974" t="s">
         <v>1389</v>
@@ -13320,12 +13323,12 @@
         <v>1397</v>
       </c>
       <c r="B982" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
       <c r="B983" t="s">
         <v>1399</v>
@@ -13352,12 +13355,12 @@
         <v>1402</v>
       </c>
       <c r="B986" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="B987" t="s">
         <v>1404</v>
@@ -13416,20 +13419,20 @@
         <v>1411</v>
       </c>
       <c r="B994" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B995" t="s">
         <v>1413</v>
-      </c>
-      <c r="B995" t="s">
-        <v>1414</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="B996" t="s">
         <v>1415</v>
@@ -13456,12 +13459,12 @@
         <v>1418</v>
       </c>
       <c r="B999" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="B1000" t="s">
         <v>1420</v>
@@ -13472,20 +13475,20 @@
         <v>1421</v>
       </c>
       <c r="B1001" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B1002" t="s">
         <v>1423</v>
-      </c>
-      <c r="B1002" t="s">
-        <v>1424</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="B1003" t="s">
         <v>1425</v>
@@ -13520,12 +13523,12 @@
         <v>1429</v>
       </c>
       <c r="B1007" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="B1008" t="s">
         <v>1431</v>
@@ -13560,20 +13563,20 @@
         <v>1435</v>
       </c>
       <c r="B1012" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B1013" t="s">
         <v>1437</v>
-      </c>
-      <c r="B1013" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B1014" t="s">
         <v>1439</v>
@@ -13608,20 +13611,20 @@
         <v>1443</v>
       </c>
       <c r="B1018" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B1019" t="s">
         <v>1445</v>
-      </c>
-      <c r="B1019" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B1020" t="s">
         <v>1447</v>
@@ -13640,20 +13643,20 @@
         <v>1449</v>
       </c>
       <c r="B1022" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B1023" t="s">
         <v>1451</v>
-      </c>
-      <c r="B1023" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B1024" t="s">
         <v>1453</v>
@@ -13664,12 +13667,12 @@
         <v>1454</v>
       </c>
       <c r="B1025" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="B1026" t="s">
         <v>1456</v>
@@ -13752,12 +13755,12 @@
         <v>1466</v>
       </c>
       <c r="B1036" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="B1037" t="s">
         <v>1468</v>
@@ -13768,28 +13771,28 @@
         <v>1469</v>
       </c>
       <c r="B1038" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B1039" t="s">
         <v>1471</v>
-      </c>
-      <c r="B1039" t="s">
-        <v>1472</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B1040" t="s">
         <v>1473</v>
-      </c>
-      <c r="B1040" t="s">
-        <v>1474</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B1041" t="s">
         <v>1475</v>
@@ -13808,12 +13811,12 @@
         <v>1477</v>
       </c>
       <c r="B1043" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B1044" t="s">
         <v>1479</v>
@@ -13824,12 +13827,12 @@
         <v>1480</v>
       </c>
       <c r="B1045" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B1046" t="s">
         <v>1482</v>
@@ -13880,68 +13883,68 @@
         <v>1488</v>
       </c>
       <c r="B1052" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B1053" t="s">
         <v>1490</v>
-      </c>
-      <c r="B1053" t="s">
-        <v>1491</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
+        <v>1491</v>
+      </c>
+      <c r="B1054" t="s">
         <v>1492</v>
-      </c>
-      <c r="B1054" t="s">
-        <v>1493</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B1055" t="s">
         <v>1494</v>
-      </c>
-      <c r="B1055" t="s">
-        <v>1495</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
+        <v>1495</v>
+      </c>
+      <c r="B1056" t="s">
         <v>1496</v>
-      </c>
-      <c r="B1056" t="s">
-        <v>1497</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B1057" t="s">
         <v>1498</v>
-      </c>
-      <c r="B1057" t="s">
-        <v>1499</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
+        <v>1499</v>
+      </c>
+      <c r="B1058" t="s">
         <v>1500</v>
-      </c>
-      <c r="B1058" t="s">
-        <v>1501</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B1059" t="s">
         <v>1502</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>1503</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1504</v>
+        <v>1503</v>
       </c>
       <c r="B1060" t="s">
         <v>1504</v>
@@ -13952,12 +13955,12 @@
         <v>1505</v>
       </c>
       <c r="B1061" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1507</v>
+        <v>1506</v>
       </c>
       <c r="B1062" t="s">
         <v>1507</v>
@@ -13984,12 +13987,12 @@
         <v>1510</v>
       </c>
       <c r="B1065" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="B1066" t="s">
         <v>1512</v>
@@ -14000,20 +14003,20 @@
         <v>1513</v>
       </c>
       <c r="B1067" t="s">
-        <v>1514</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B1068" t="s">
         <v>1515</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>1516</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="B1069" t="s">
         <v>1517</v>
@@ -14040,12 +14043,12 @@
         <v>1520</v>
       </c>
       <c r="B1072" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B1073" t="s">
         <v>1522</v>
@@ -14088,12 +14091,12 @@
         <v>1527</v>
       </c>
       <c r="B1078" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B1079" t="s">
         <v>1529</v>
@@ -14104,12 +14107,12 @@
         <v>1530</v>
       </c>
       <c r="B1080" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
       <c r="B1081" t="s">
         <v>1532</v>
@@ -14136,12 +14139,12 @@
         <v>1535</v>
       </c>
       <c r="B1084" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
       <c r="B1085" t="s">
         <v>1537</v>
@@ -14160,36 +14163,36 @@
         <v>1539</v>
       </c>
       <c r="B1087" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B1088" t="s">
         <v>1541</v>
-      </c>
-      <c r="B1088" t="s">
-        <v>1542</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
+        <v>1542</v>
+      </c>
+      <c r="B1089" t="s">
         <v>1543</v>
-      </c>
-      <c r="B1089" t="s">
-        <v>1544</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
+        <v>1544</v>
+      </c>
+      <c r="B1090" t="s">
         <v>1545</v>
-      </c>
-      <c r="B1090" t="s">
-        <v>1546</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
       <c r="B1091" t="s">
         <v>1547</v>
@@ -14208,36 +14211,36 @@
         <v>1549</v>
       </c>
       <c r="B1093" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B1094" t="s">
         <v>1551</v>
-      </c>
-      <c r="B1094" t="s">
-        <v>1552</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B1095" t="s">
         <v>1553</v>
-      </c>
-      <c r="B1095" t="s">
-        <v>1554</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B1096" t="s">
         <v>1555</v>
-      </c>
-      <c r="B1096" t="s">
-        <v>1556</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="B1097" t="s">
         <v>1557</v>
@@ -14288,12 +14291,12 @@
         <v>1563</v>
       </c>
       <c r="B1103" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="B1104" t="s">
         <v>1565</v>
@@ -14312,12 +14315,12 @@
         <v>1567</v>
       </c>
       <c r="B1106" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B1107" t="s">
         <v>1569</v>
@@ -14368,12 +14371,12 @@
         <v>1575</v>
       </c>
       <c r="B1113" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1577</v>
+        <v>1576</v>
       </c>
       <c r="B1114" t="s">
         <v>1577</v>
@@ -14392,20 +14395,20 @@
         <v>1579</v>
       </c>
       <c r="B1116" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B1117" t="s">
         <v>1581</v>
-      </c>
-      <c r="B1117" t="s">
-        <v>1582</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="B1118" t="s">
         <v>1583</v>
@@ -14424,100 +14427,100 @@
         <v>1585</v>
       </c>
       <c r="B1120" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B1121" t="s">
         <v>1587</v>
-      </c>
-      <c r="B1121" t="s">
-        <v>1588</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B1122" t="s">
         <v>1589</v>
-      </c>
-      <c r="B1122" t="s">
-        <v>1590</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B1123" t="s">
         <v>1591</v>
-      </c>
-      <c r="B1123" t="s">
-        <v>1592</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B1124" t="s">
         <v>1593</v>
-      </c>
-      <c r="B1124" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B1125" t="s">
         <v>1595</v>
-      </c>
-      <c r="B1125" t="s">
-        <v>1596</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B1126" t="s">
         <v>1597</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>1598</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B1127" t="s">
         <v>1599</v>
-      </c>
-      <c r="B1127" t="s">
-        <v>1600</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B1128" t="s">
         <v>1601</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>1602</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B1129" t="s">
         <v>1603</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>1604</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B1130" t="s">
         <v>1605</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>1606</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1607</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1608</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
-        <v>1609</v>
+        <v>1608</v>
       </c>
       <c r="B1132" t="s">
         <v>1609</v>
@@ -14560,20 +14563,20 @@
         <v>1614</v>
       </c>
       <c r="B1137" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B1138" t="s">
         <v>1616</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>1617</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>1618</v>
+        <v>1617</v>
       </c>
       <c r="B1139" t="s">
         <v>1618</v>
@@ -14608,12 +14611,12 @@
         <v>1622</v>
       </c>
       <c r="B1143" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1624</v>
+        <v>1623</v>
       </c>
       <c r="B1144" t="s">
         <v>1624</v>
@@ -14632,36 +14635,36 @@
         <v>1626</v>
       </c>
       <c r="B1146" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B1147" t="s">
         <v>1628</v>
-      </c>
-      <c r="B1147" t="s">
-        <v>1629</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B1148" t="s">
         <v>1630</v>
-      </c>
-      <c r="B1148" t="s">
-        <v>1631</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B1149" t="s">
         <v>1632</v>
-      </c>
-      <c r="B1149" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="B1150" t="s">
         <v>1634</v>
@@ -14672,20 +14675,20 @@
         <v>1635</v>
       </c>
       <c r="B1151" t="s">
-        <v>1636</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B1152" t="s">
         <v>1637</v>
-      </c>
-      <c r="B1152" t="s">
-        <v>1638</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
       <c r="B1153" t="s">
         <v>1639</v>
@@ -14696,28 +14699,28 @@
         <v>1640</v>
       </c>
       <c r="B1154" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B1155" t="s">
         <v>1642</v>
-      </c>
-      <c r="B1155" t="s">
-        <v>1643</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B1156" t="s">
         <v>1644</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>1645</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
       <c r="B1157" t="s">
         <v>1646</v>
@@ -14840,12 +14843,12 @@
         <v>1661</v>
       </c>
       <c r="B1172" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="B1173" t="s">
         <v>1663</v>
@@ -14880,12 +14883,12 @@
         <v>1667</v>
       </c>
       <c r="B1177" t="s">
-        <v>1668</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="B1178" t="s">
         <v>1669</v>
@@ -14896,12 +14899,12 @@
         <v>1670</v>
       </c>
       <c r="B1179" t="s">
-        <v>1671</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="B1180" t="s">
         <v>1672</v>
@@ -14928,7 +14931,7 @@
         <v>1675</v>
       </c>
       <c r="B1183" t="s">
-        <v>381</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
@@ -14936,7 +14939,7 @@
         <v>1676</v>
       </c>
       <c r="B1184" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
@@ -14944,7 +14947,7 @@
         <v>1677</v>
       </c>
       <c r="B1185" t="s">
-        <v>1677</v>
+        <v>383</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
@@ -14960,7 +14963,7 @@
         <v>1679</v>
       </c>
       <c r="B1187" t="s">
-        <v>641</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
@@ -14968,7 +14971,7 @@
         <v>1680</v>
       </c>
       <c r="B1188" t="s">
-        <v>1680</v>
+        <v>641</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
@@ -14984,7 +14987,7 @@
         <v>1682</v>
       </c>
       <c r="B1190" t="s">
-        <v>915</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
@@ -14992,7 +14995,7 @@
         <v>1683</v>
       </c>
       <c r="B1191" t="s">
-        <v>1683</v>
+        <v>915</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
@@ -15008,7 +15011,7 @@
         <v>1685</v>
       </c>
       <c r="B1193" t="s">
-        <v>991</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
@@ -15016,7 +15019,7 @@
         <v>1686</v>
       </c>
       <c r="B1194" t="s">
-        <v>1686</v>
+        <v>991</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
@@ -15032,7 +15035,7 @@
         <v>1688</v>
       </c>
       <c r="B1196" t="s">
-        <v>1059</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
@@ -15040,7 +15043,7 @@
         <v>1689</v>
       </c>
       <c r="B1197" t="s">
-        <v>1114</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
@@ -15048,7 +15051,7 @@
         <v>1690</v>
       </c>
       <c r="B1198" t="s">
-        <v>1690</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
@@ -15080,7 +15083,7 @@
         <v>1694</v>
       </c>
       <c r="B1202" t="s">
-        <v>1414</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1203" spans="1:2">
@@ -15088,7 +15091,7 @@
         <v>1695</v>
       </c>
       <c r="B1203" t="s">
-        <v>1695</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="1204" spans="1:2">
@@ -15112,11 +15115,19 @@
         <v>1698</v>
       </c>
       <c r="B1206" t="s">
-        <v>1531</v>
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:2">
+      <c r="A1207" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B1207" t="s">
+        <v>1532</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1206"/>
+  <autoFilter ref="A1:B1207"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/da/headTags.xlsx
+++ b/lang/da/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1207</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1208</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1702">
   <si>
     <t>en</t>
   </si>
@@ -707,6 +707,12 @@
   </si>
   <si>
     <t>Kalk</t>
+  </si>
+  <si>
+    <t>Chaos Cubed</t>
+  </si>
+  <si>
+    <t>Kaos i kubik</t>
   </si>
   <si>
     <t>Charlie and the Chocolate Factory</t>
@@ -5463,7 +5469,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1207"/>
+  <dimension ref="A1:B1208"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -6827,12 +6833,12 @@
         <v>244</v>
       </c>
       <c r="B170" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B171" t="s">
         <v>246</v>
@@ -6859,36 +6865,36 @@
         <v>251</v>
       </c>
       <c r="B174" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B175" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="176" spans="1:2">
       <c r="A176" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B176" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B177" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B178" t="s">
         <v>256</v>
@@ -6899,20 +6905,20 @@
         <v>257</v>
       </c>
       <c r="B179" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B180" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="181" spans="1:2">
       <c r="A181" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B181" t="s">
         <v>260</v>
@@ -6923,12 +6929,12 @@
         <v>261</v>
       </c>
       <c r="B182" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B183" t="s">
         <v>262</v>
@@ -6936,7 +6942,7 @@
     </row>
     <row r="184" spans="1:2">
       <c r="A184" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B184" t="s">
         <v>264</v>
@@ -6955,20 +6961,20 @@
         <v>267</v>
       </c>
       <c r="B186" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B187" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="188" spans="1:2">
       <c r="A188" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B188" t="s">
         <v>270</v>
@@ -6995,28 +7001,28 @@
         <v>275</v>
       </c>
       <c r="B191" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B192" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="193" spans="1:2">
       <c r="A193" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B193" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B194" t="s">
         <v>279</v>
@@ -7043,36 +7049,36 @@
         <v>284</v>
       </c>
       <c r="B197" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B198" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="199" spans="1:2">
       <c r="A199" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B199" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B200" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B201" t="s">
         <v>289</v>
@@ -7091,20 +7097,20 @@
         <v>292</v>
       </c>
       <c r="B203" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B204" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="205" spans="1:2">
       <c r="A205" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B205" t="s">
         <v>295</v>
@@ -7123,20 +7129,20 @@
         <v>298</v>
       </c>
       <c r="B207" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B208" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="209" spans="1:2">
       <c r="A209" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B209" t="s">
         <v>301</v>
@@ -7203,12 +7209,12 @@
         <v>316</v>
       </c>
       <c r="B217" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B218" t="s">
         <v>318</v>
@@ -7219,36 +7225,36 @@
         <v>319</v>
       </c>
       <c r="B219" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B220" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="221" spans="1:2">
       <c r="A221" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B221" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B222" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B223" t="s">
         <v>324</v>
@@ -7259,36 +7265,36 @@
         <v>325</v>
       </c>
       <c r="B224" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B225" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="226" spans="1:2">
       <c r="A226" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B226" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B227" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B228" t="s">
         <v>330</v>
@@ -7307,52 +7313,52 @@
         <v>333</v>
       </c>
       <c r="B230" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B231" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="232" spans="1:2">
       <c r="A232" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B232" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B233" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B234" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B235" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B236" t="s">
         <v>340</v>
@@ -7395,12 +7401,12 @@
         <v>349</v>
       </c>
       <c r="B241" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B242" t="s">
         <v>351</v>
@@ -7411,12 +7417,12 @@
         <v>352</v>
       </c>
       <c r="B243" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B244" t="s">
         <v>354</v>
@@ -7443,12 +7449,12 @@
         <v>359</v>
       </c>
       <c r="B247" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B248" t="s">
         <v>361</v>
@@ -7467,68 +7473,68 @@
         <v>364</v>
       </c>
       <c r="B250" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B251" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="252" spans="1:2">
       <c r="A252" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B252" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B253" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B254" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B255" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B256" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B257" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B258" t="s">
         <v>373</v>
@@ -7579,116 +7585,116 @@
         <v>384</v>
       </c>
       <c r="B264" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B265" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="266" spans="1:2">
       <c r="A266" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B266" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B267" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B268" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B269" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B270" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B271" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B272" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B273" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B274" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B275" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B276" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B277" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B278" t="s">
         <v>399</v>
@@ -7699,92 +7705,92 @@
         <v>400</v>
       </c>
       <c r="B279" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B280" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B281" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B282" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B283" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B284" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B285" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B286" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B287" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B288" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B289" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B290" t="s">
         <v>412</v>
@@ -7819,20 +7825,20 @@
         <v>419</v>
       </c>
       <c r="B294" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B295" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="296" spans="1:2">
       <c r="A296" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B296" t="s">
         <v>422</v>
@@ -7867,12 +7873,12 @@
         <v>429</v>
       </c>
       <c r="B300" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="301" spans="1:2">
       <c r="A301" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B301" t="s">
         <v>431</v>
@@ -7883,12 +7889,12 @@
         <v>432</v>
       </c>
       <c r="B302" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B303" t="s">
         <v>434</v>
@@ -7923,28 +7929,28 @@
         <v>441</v>
       </c>
       <c r="B307" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="308" spans="1:2">
       <c r="A308" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B308" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="309" spans="1:2">
       <c r="A309" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B309" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B310" t="s">
         <v>445</v>
@@ -7963,20 +7969,20 @@
         <v>448</v>
       </c>
       <c r="B312" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B313" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="314" spans="1:2">
       <c r="A314" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B314" t="s">
         <v>451</v>
@@ -8003,20 +8009,20 @@
         <v>456</v>
       </c>
       <c r="B317" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="318" spans="1:2">
       <c r="A318" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B318" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="319" spans="1:2">
       <c r="A319" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B319" t="s">
         <v>459</v>
@@ -8027,20 +8033,20 @@
         <v>460</v>
       </c>
       <c r="B320" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B321" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B322" t="s">
         <v>463</v>
@@ -8051,84 +8057,84 @@
         <v>464</v>
       </c>
       <c r="B323" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B324" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B325" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B326" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B327" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B328" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B329" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B330" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B331" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B332" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B333" t="s">
         <v>475</v>
@@ -8179,36 +8185,36 @@
         <v>486</v>
       </c>
       <c r="B339" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B340" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="A341" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B341" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="342" spans="1:2">
       <c r="A342" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B342" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B343" t="s">
         <v>491</v>
@@ -8219,28 +8225,28 @@
         <v>492</v>
       </c>
       <c r="B344" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B345" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B346" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="347" spans="1:2">
       <c r="A347" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B347" t="s">
         <v>496</v>
@@ -8339,12 +8345,12 @@
         <v>519</v>
       </c>
       <c r="B359" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B360" t="s">
         <v>521</v>
@@ -8363,20 +8369,20 @@
         <v>524</v>
       </c>
       <c r="B362" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B363" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B364" t="s">
         <v>527</v>
@@ -8395,20 +8401,20 @@
         <v>530</v>
       </c>
       <c r="B366" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B367" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B368" t="s">
         <v>533</v>
@@ -8451,12 +8457,12 @@
         <v>542</v>
       </c>
       <c r="B373" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="374" spans="1:2">
       <c r="A374" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B374" t="s">
         <v>544</v>
@@ -8483,12 +8489,12 @@
         <v>549</v>
       </c>
       <c r="B377" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="378" spans="1:2">
       <c r="A378" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B378" t="s">
         <v>551</v>
@@ -8515,44 +8521,44 @@
         <v>556</v>
       </c>
       <c r="B381" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B382" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="383" spans="1:2">
       <c r="A383" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B383" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="384" spans="1:2">
       <c r="A384" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B384" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B385" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B386" t="s">
         <v>562</v>
@@ -8571,12 +8577,12 @@
         <v>565</v>
       </c>
       <c r="B388" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B389" t="s">
         <v>567</v>
@@ -8587,20 +8593,20 @@
         <v>568</v>
       </c>
       <c r="B390" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="391" spans="1:2">
       <c r="A391" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B391" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="392" spans="1:2">
       <c r="A392" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B392" t="s">
         <v>571</v>
@@ -8627,36 +8633,36 @@
         <v>576</v>
       </c>
       <c r="B395" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B396" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B397" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="398" spans="1:2">
       <c r="A398" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B398" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="399" spans="1:2">
       <c r="A399" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B399" t="s">
         <v>581</v>
@@ -8691,12 +8697,12 @@
         <v>588</v>
       </c>
       <c r="B403" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="404" spans="1:2">
       <c r="A404" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B404" t="s">
         <v>590</v>
@@ -8715,20 +8721,20 @@
         <v>593</v>
       </c>
       <c r="B406" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B407" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="408" spans="1:2">
       <c r="A408" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B408" t="s">
         <v>596</v>
@@ -8739,28 +8745,28 @@
         <v>597</v>
       </c>
       <c r="B409" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="410" spans="1:2">
       <c r="A410" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B410" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B411" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="412" spans="1:2">
       <c r="A412" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B412" t="s">
         <v>601</v>
@@ -8779,20 +8785,20 @@
         <v>604</v>
       </c>
       <c r="B414" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B415" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B416" t="s">
         <v>607</v>
@@ -8915,36 +8921,36 @@
         <v>636</v>
       </c>
       <c r="B431" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B432" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
     </row>
     <row r="433" spans="1:2">
       <c r="A433" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B433" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="434" spans="1:2">
       <c r="A434" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B434" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B435" t="s">
         <v>641</v>
@@ -8955,12 +8961,12 @@
         <v>642</v>
       </c>
       <c r="B436" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B437" t="s">
         <v>644</v>
@@ -8971,20 +8977,20 @@
         <v>645</v>
       </c>
       <c r="B438" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B439" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B440" t="s">
         <v>648</v>
@@ -8995,20 +9001,20 @@
         <v>649</v>
       </c>
       <c r="B441" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B442" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="443" spans="1:2">
       <c r="A443" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B443" t="s">
         <v>652</v>
@@ -9035,12 +9041,12 @@
         <v>657</v>
       </c>
       <c r="B446" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B447" t="s">
         <v>659</v>
@@ -9051,28 +9057,28 @@
         <v>660</v>
       </c>
       <c r="B448" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B449" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B450" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="451" spans="1:2">
       <c r="A451" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B451" t="s">
         <v>664</v>
@@ -9091,20 +9097,20 @@
         <v>667</v>
       </c>
       <c r="B453" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B454" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="455" spans="1:2">
       <c r="A455" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B455" t="s">
         <v>670</v>
@@ -9115,20 +9121,20 @@
         <v>671</v>
       </c>
       <c r="B456" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B457" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B458" t="s">
         <v>674</v>
@@ -9163,28 +9169,28 @@
         <v>681</v>
       </c>
       <c r="B462" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="463" spans="1:2">
       <c r="A463" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B463" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="464" spans="1:2">
       <c r="A464" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="B464" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="465" spans="1:2">
       <c r="A465" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B465" t="s">
         <v>685</v>
@@ -9195,12 +9201,12 @@
         <v>686</v>
       </c>
       <c r="B466" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B467" t="s">
         <v>688</v>
@@ -9211,20 +9217,20 @@
         <v>689</v>
       </c>
       <c r="B468" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B469" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B470" t="s">
         <v>692</v>
@@ -9235,52 +9241,52 @@
         <v>693</v>
       </c>
       <c r="B471" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B472" t="s">
-        <v>685</v>
+        <v>695</v>
       </c>
     </row>
     <row r="473" spans="1:2">
       <c r="A473" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B473" t="s">
-        <v>695</v>
+        <v>687</v>
       </c>
     </row>
     <row r="474" spans="1:2">
       <c r="A474" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B474" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B475" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B476" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B477" t="s">
         <v>700</v>
@@ -9299,12 +9305,12 @@
         <v>703</v>
       </c>
       <c r="B479" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B480" t="s">
         <v>705</v>
@@ -9315,12 +9321,12 @@
         <v>706</v>
       </c>
       <c r="B481" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B482" t="s">
         <v>708</v>
@@ -9331,20 +9337,20 @@
         <v>709</v>
       </c>
       <c r="B483" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B484" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B485" t="s">
         <v>712</v>
@@ -9355,36 +9361,36 @@
         <v>713</v>
       </c>
       <c r="B486" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B487" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B488" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B489" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B490" t="s">
         <v>718</v>
@@ -9539,12 +9545,12 @@
         <v>755</v>
       </c>
       <c r="B509" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
     </row>
     <row r="510" spans="1:2">
       <c r="A510" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B510" t="s">
         <v>757</v>
@@ -9555,12 +9561,12 @@
         <v>758</v>
       </c>
       <c r="B511" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
     </row>
     <row r="512" spans="1:2">
       <c r="A512" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="B512" t="s">
         <v>759</v>
@@ -9568,7 +9574,7 @@
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B513" t="s">
         <v>761</v>
@@ -9579,12 +9585,12 @@
         <v>762</v>
       </c>
       <c r="B514" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B515" t="s">
         <v>764</v>
@@ -9619,12 +9625,12 @@
         <v>771</v>
       </c>
       <c r="B519" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="520" spans="1:2">
       <c r="A520" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B520" t="s">
         <v>773</v>
@@ -9635,12 +9641,12 @@
         <v>774</v>
       </c>
       <c r="B521" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="A522" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B522" t="s">
         <v>776</v>
@@ -9659,12 +9665,12 @@
         <v>779</v>
       </c>
       <c r="B524" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B525" t="s">
         <v>781</v>
@@ -9715,12 +9721,12 @@
         <v>792</v>
       </c>
       <c r="B531" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B532" t="s">
         <v>794</v>
@@ -9739,84 +9745,84 @@
         <v>797</v>
       </c>
       <c r="B534" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B535" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B536" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B537" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B538" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B539" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B540" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B541" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B542" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B543" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B544" t="s">
         <v>808</v>
@@ -9827,20 +9833,20 @@
         <v>809</v>
       </c>
       <c r="B545" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B546" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B547" t="s">
         <v>812</v>
@@ -9851,68 +9857,68 @@
         <v>813</v>
       </c>
       <c r="B548" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B549" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B550" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B551" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B552" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B553" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B554" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B555" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B556" t="s">
         <v>822</v>
@@ -9963,28 +9969,28 @@
         <v>833</v>
       </c>
       <c r="B562" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B563" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
     </row>
     <row r="564" spans="1:2">
       <c r="A564" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B564" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
     </row>
     <row r="565" spans="1:2">
       <c r="A565" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B565" t="s">
         <v>837</v>
@@ -9995,20 +10001,20 @@
         <v>838</v>
       </c>
       <c r="B566" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B567" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B568" t="s">
         <v>841</v>
@@ -10019,20 +10025,20 @@
         <v>842</v>
       </c>
       <c r="B569" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B570" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B571" t="s">
         <v>845</v>
@@ -10051,52 +10057,52 @@
         <v>848</v>
       </c>
       <c r="B573" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B574" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B575" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="576" spans="1:2">
       <c r="A576" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B576" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B577" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B578" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B579" t="s">
         <v>855</v>
@@ -10115,28 +10121,28 @@
         <v>858</v>
       </c>
       <c r="B581" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B582" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B583" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B584" t="s">
         <v>862</v>
@@ -10147,12 +10153,12 @@
         <v>863</v>
       </c>
       <c r="B585" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B586" t="s">
         <v>865</v>
@@ -10163,12 +10169,12 @@
         <v>866</v>
       </c>
       <c r="B587" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B588" t="s">
         <v>868</v>
@@ -10179,12 +10185,12 @@
         <v>869</v>
       </c>
       <c r="B589" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B590" t="s">
         <v>871</v>
@@ -10211,36 +10217,36 @@
         <v>876</v>
       </c>
       <c r="B593" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B594" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B595" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B596" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B597" t="s">
         <v>881</v>
@@ -10283,20 +10289,20 @@
         <v>890</v>
       </c>
       <c r="B602" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B603" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B604" t="s">
         <v>893</v>
@@ -10307,44 +10313,44 @@
         <v>894</v>
       </c>
       <c r="B605" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B606" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B607" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
     </row>
     <row r="608" spans="1:2">
       <c r="A608" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B608" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B609" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B610" t="s">
         <v>900</v>
@@ -10355,44 +10361,44 @@
         <v>901</v>
       </c>
       <c r="B611" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B612" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B613" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B614" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B615" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B616" t="s">
         <v>907</v>
@@ -10411,12 +10417,12 @@
         <v>910</v>
       </c>
       <c r="B618" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B619" t="s">
         <v>912</v>
@@ -10427,12 +10433,12 @@
         <v>913</v>
       </c>
       <c r="B620" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B621" t="s">
         <v>915</v>
@@ -10443,188 +10449,188 @@
         <v>916</v>
       </c>
       <c r="B622" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B623" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B624" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B625" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B626" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B627" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B628" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B629" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B630" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B631" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B632" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B633" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B634" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B635" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B636" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B637" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B638" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B639" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B640" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B641" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B642" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B643" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B644" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B645" t="s">
         <v>940</v>
@@ -10659,28 +10665,28 @@
         <v>947</v>
       </c>
       <c r="B649" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B650" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B651" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B652" t="s">
         <v>951</v>
@@ -10691,20 +10697,20 @@
         <v>952</v>
       </c>
       <c r="B653" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B654" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="655" spans="1:2">
       <c r="A655" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B655" t="s">
         <v>955</v>
@@ -10715,44 +10721,44 @@
         <v>956</v>
       </c>
       <c r="B656" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B657" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B658" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B659" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B660" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B661" t="s">
         <v>962</v>
@@ -10763,52 +10769,52 @@
         <v>963</v>
       </c>
       <c r="B662" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B663" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B664" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B665" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="666" spans="1:2">
       <c r="A666" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B666" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B667" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B668" t="s">
         <v>970</v>
@@ -10819,12 +10825,12 @@
         <v>971</v>
       </c>
       <c r="B669" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="670" spans="1:2">
       <c r="A670" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B670" t="s">
         <v>973</v>
@@ -10843,68 +10849,68 @@
         <v>976</v>
       </c>
       <c r="B672" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="673" spans="1:2">
       <c r="A673" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B673" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B674" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B675" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B676" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B677" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B678" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B679" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B680" t="s">
         <v>985</v>
@@ -10923,20 +10929,20 @@
         <v>988</v>
       </c>
       <c r="B682" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B683" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B684" t="s">
         <v>991</v>
@@ -10955,12 +10961,12 @@
         <v>994</v>
       </c>
       <c r="B686" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B687" t="s">
         <v>996</v>
@@ -10995,12 +11001,12 @@
         <v>1003</v>
       </c>
       <c r="B691" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B692" t="s">
         <v>1005</v>
@@ -11019,12 +11025,12 @@
         <v>1008</v>
       </c>
       <c r="B694" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="695" spans="1:2">
       <c r="A695" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B695" t="s">
         <v>1010</v>
@@ -11067,36 +11073,36 @@
         <v>1019</v>
       </c>
       <c r="B700" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B701" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B702" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B703" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B704" t="s">
         <v>1024</v>
@@ -11107,76 +11113,76 @@
         <v>1025</v>
       </c>
       <c r="B705" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B706" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B707" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B708" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B709" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B710" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B711" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B712" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B713" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B714" t="s">
         <v>1035</v>
@@ -11195,20 +11201,20 @@
         <v>1038</v>
       </c>
       <c r="B716" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B717" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B718" t="s">
         <v>1041</v>
@@ -11219,12 +11225,12 @@
         <v>1042</v>
       </c>
       <c r="B719" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B720" t="s">
         <v>1044</v>
@@ -11235,12 +11241,12 @@
         <v>1045</v>
       </c>
       <c r="B721" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B722" t="s">
         <v>1047</v>
@@ -11251,12 +11257,12 @@
         <v>1048</v>
       </c>
       <c r="B723" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B724" t="s">
         <v>1050</v>
@@ -11267,12 +11273,12 @@
         <v>1051</v>
       </c>
       <c r="B725" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B726" t="s">
         <v>1053</v>
@@ -11291,20 +11297,20 @@
         <v>1056</v>
       </c>
       <c r="B728" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B729" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B730" t="s">
         <v>1059</v>
@@ -11315,12 +11321,12 @@
         <v>1060</v>
       </c>
       <c r="B731" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B732" t="s">
         <v>1062</v>
@@ -11331,68 +11337,68 @@
         <v>1063</v>
       </c>
       <c r="B733" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B734" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B735" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B736" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B737" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B738" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B739" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B740" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B741" t="s">
         <v>1072</v>
@@ -11403,12 +11409,12 @@
         <v>1073</v>
       </c>
       <c r="B742" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B743" t="s">
         <v>1075</v>
@@ -11427,36 +11433,36 @@
         <v>1078</v>
       </c>
       <c r="B745" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B746" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B747" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B748" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B749" t="s">
         <v>1083</v>
@@ -11467,20 +11473,20 @@
         <v>1084</v>
       </c>
       <c r="B750" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B751" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B752" t="s">
         <v>1087</v>
@@ -11515,20 +11521,20 @@
         <v>1094</v>
       </c>
       <c r="B756" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B757" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="758" spans="1:2">
       <c r="A758" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B758" t="s">
         <v>1097</v>
@@ -11547,12 +11553,12 @@
         <v>1100</v>
       </c>
       <c r="B760" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="761" spans="1:2">
       <c r="A761" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B761" t="s">
         <v>1102</v>
@@ -11563,20 +11569,20 @@
         <v>1103</v>
       </c>
       <c r="B762" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="763" spans="1:2">
       <c r="A763" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B763" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B764" t="s">
         <v>1106</v>
@@ -11619,12 +11625,12 @@
         <v>1115</v>
       </c>
       <c r="B769" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B770" t="s">
         <v>1117</v>
@@ -11643,44 +11649,44 @@
         <v>1120</v>
       </c>
       <c r="B772" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B773" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="774" spans="1:2">
       <c r="A774" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B774" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="775" spans="1:2">
       <c r="A775" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B775" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B776" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B777" t="s">
         <v>1126</v>
@@ -11691,12 +11697,12 @@
         <v>1127</v>
       </c>
       <c r="B778" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B779" t="s">
         <v>1129</v>
@@ -11723,44 +11729,44 @@
         <v>1134</v>
       </c>
       <c r="B782" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B783" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B784" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B785" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B786" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B787" t="s">
         <v>1140</v>
@@ -11771,116 +11777,116 @@
         <v>1141</v>
       </c>
       <c r="B788" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B789" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B790" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B791" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B792" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B793" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B794" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B795" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B796" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B797" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B798" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B799" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B800" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B801" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B802" t="s">
         <v>1156</v>
@@ -11915,44 +11921,44 @@
         <v>1163</v>
       </c>
       <c r="B806" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B807" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B808" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B809" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B810" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B811" t="s">
         <v>1169</v>
@@ -11987,36 +11993,36 @@
         <v>1176</v>
       </c>
       <c r="B815" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B816" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B817" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B818" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B819" t="s">
         <v>1181</v>
@@ -12027,28 +12033,28 @@
         <v>1182</v>
       </c>
       <c r="B820" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B821" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B822" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B823" t="s">
         <v>1186</v>
@@ -12075,12 +12081,12 @@
         <v>1191</v>
       </c>
       <c r="B826" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B827" t="s">
         <v>1193</v>
@@ -12091,28 +12097,28 @@
         <v>1194</v>
       </c>
       <c r="B828" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B829" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B830" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B831" t="s">
         <v>1198</v>
@@ -12123,44 +12129,44 @@
         <v>1199</v>
       </c>
       <c r="B832" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B833" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B834" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B835" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B836" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B837" t="s">
         <v>1205</v>
@@ -12171,148 +12177,148 @@
         <v>1206</v>
       </c>
       <c r="B838" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B839" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B840" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B841" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B842" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B843" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B844" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B845" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B846" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B847" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B848" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B849" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B850" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B851" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B852" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B853" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B854" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B855" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B856" t="s">
         <v>1225</v>
@@ -12347,116 +12353,116 @@
         <v>1232</v>
       </c>
       <c r="B860" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B861" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B862" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B863" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B864" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B865" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B866" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B867" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B868" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B869" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B870" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B871" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B872" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B873" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B874" t="s">
         <v>1247</v>
@@ -12467,20 +12473,20 @@
         <v>1248</v>
       </c>
       <c r="B875" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B876" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B877" t="s">
         <v>1251</v>
@@ -12499,20 +12505,20 @@
         <v>1254</v>
       </c>
       <c r="B879" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B880" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B881" t="s">
         <v>1257</v>
@@ -12531,44 +12537,44 @@
         <v>1260</v>
       </c>
       <c r="B883" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B884" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B885" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B886" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B887" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B888" t="s">
         <v>1266</v>
@@ -12579,44 +12585,44 @@
         <v>1267</v>
       </c>
       <c r="B889" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B890" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B891" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B892" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B893" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B894" t="s">
         <v>1273</v>
@@ -12627,12 +12633,12 @@
         <v>1274</v>
       </c>
       <c r="B895" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B896" t="s">
         <v>1276</v>
@@ -12643,36 +12649,36 @@
         <v>1277</v>
       </c>
       <c r="B897" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B898" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B899" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B900" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B901" t="s">
         <v>1282</v>
@@ -12699,68 +12705,68 @@
         <v>1287</v>
       </c>
       <c r="B904" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B905" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B906" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B907" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B908" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B909" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B910" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B911" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B912" t="s">
         <v>1296</v>
@@ -12787,28 +12793,28 @@
         <v>1301</v>
       </c>
       <c r="B915" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B916" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B917" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B918" t="s">
         <v>1305</v>
@@ -12851,20 +12857,20 @@
         <v>1314</v>
       </c>
       <c r="B923" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B924" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B925" t="s">
         <v>1317</v>
@@ -12875,12 +12881,12 @@
         <v>1318</v>
       </c>
       <c r="B926" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B927" t="s">
         <v>1320</v>
@@ -12899,12 +12905,12 @@
         <v>1323</v>
       </c>
       <c r="B929" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B930" t="s">
         <v>1325</v>
@@ -12923,36 +12929,36 @@
         <v>1328</v>
       </c>
       <c r="B932" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B933" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B934" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B935" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B936" t="s">
         <v>1333</v>
@@ -13003,28 +13009,28 @@
         <v>1344</v>
       </c>
       <c r="B942" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B943" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B944" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B945" t="s">
         <v>1348</v>
@@ -13035,68 +13041,68 @@
         <v>1349</v>
       </c>
       <c r="B946" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B947" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B948" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B949" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B950" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B951" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B952" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B953" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B954" t="s">
         <v>1358</v>
@@ -13123,20 +13129,20 @@
         <v>1363</v>
       </c>
       <c r="B957" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B958" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B959" t="s">
         <v>1366</v>
@@ -13163,20 +13169,20 @@
         <v>1371</v>
       </c>
       <c r="B962" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B963" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B964" t="s">
         <v>1374</v>
@@ -13187,44 +13193,44 @@
         <v>1375</v>
       </c>
       <c r="B965" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B966" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B967" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B968" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B969" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B970" t="s">
         <v>1381</v>
@@ -13267,68 +13273,68 @@
         <v>1390</v>
       </c>
       <c r="B975" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="B976" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="B977" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B978" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B979" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B980" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B981" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B982" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B983" t="s">
         <v>1399</v>
@@ -13339,28 +13345,28 @@
         <v>1400</v>
       </c>
       <c r="B984" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B985" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B986" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B987" t="s">
         <v>1404</v>
@@ -13371,60 +13377,60 @@
         <v>1405</v>
       </c>
       <c r="B988" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B989" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="B990" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B991" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B992" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B993" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="B994" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B995" t="s">
         <v>1413</v>
@@ -13443,28 +13449,28 @@
         <v>1416</v>
       </c>
       <c r="B997" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B998" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B999" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B1000" t="s">
         <v>1420</v>
@@ -13475,12 +13481,12 @@
         <v>1421</v>
       </c>
       <c r="B1001" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B1002" t="s">
         <v>1423</v>
@@ -13499,36 +13505,36 @@
         <v>1426</v>
       </c>
       <c r="B1004" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B1005" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B1006" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B1007" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B1008" t="s">
         <v>1431</v>
@@ -13539,36 +13545,36 @@
         <v>1432</v>
       </c>
       <c r="B1009" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B1010" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B1011" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B1012" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B1013" t="s">
         <v>1437</v>
@@ -13587,36 +13593,36 @@
         <v>1440</v>
       </c>
       <c r="B1015" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B1016" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B1017" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B1018" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B1019" t="s">
         <v>1445</v>
@@ -13635,20 +13641,20 @@
         <v>1448</v>
       </c>
       <c r="B1021" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B1022" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B1023" t="s">
         <v>1451</v>
@@ -13667,12 +13673,12 @@
         <v>1454</v>
       </c>
       <c r="B1025" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B1026" t="s">
         <v>1456</v>
@@ -13683,84 +13689,84 @@
         <v>1457</v>
       </c>
       <c r="B1027" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B1028" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B1029" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B1030" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B1031" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B1032" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B1033" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B1034" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B1035" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B1036" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B1037" t="s">
         <v>1468</v>
@@ -13771,12 +13777,12 @@
         <v>1469</v>
       </c>
       <c r="B1038" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B1039" t="s">
         <v>1471</v>
@@ -13803,20 +13809,20 @@
         <v>1476</v>
       </c>
       <c r="B1042" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B1043" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B1044" t="s">
         <v>1479</v>
@@ -13827,12 +13833,12 @@
         <v>1480</v>
       </c>
       <c r="B1045" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B1046" t="s">
         <v>1482</v>
@@ -13843,52 +13849,52 @@
         <v>1483</v>
       </c>
       <c r="B1047" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B1048" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B1049" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B1050" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B1051" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B1052" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B1053" t="s">
         <v>1490</v>
@@ -13955,12 +13961,12 @@
         <v>1505</v>
       </c>
       <c r="B1061" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B1062" t="s">
         <v>1507</v>
@@ -13971,28 +13977,28 @@
         <v>1508</v>
       </c>
       <c r="B1063" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B1064" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B1065" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B1066" t="s">
         <v>1512</v>
@@ -14003,12 +14009,12 @@
         <v>1513</v>
       </c>
       <c r="B1067" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="B1068" t="s">
         <v>1515</v>
@@ -14027,28 +14033,28 @@
         <v>1518</v>
       </c>
       <c r="B1070" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B1071" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B1072" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B1073" t="s">
         <v>1522</v>
@@ -14059,44 +14065,44 @@
         <v>1523</v>
       </c>
       <c r="B1074" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B1075" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B1076" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B1077" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B1078" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B1079" t="s">
         <v>1529</v>
@@ -14107,12 +14113,12 @@
         <v>1530</v>
       </c>
       <c r="B1080" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B1081" t="s">
         <v>1532</v>
@@ -14123,28 +14129,28 @@
         <v>1533</v>
       </c>
       <c r="B1082" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B1083" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B1084" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B1085" t="s">
         <v>1537</v>
@@ -14155,20 +14161,20 @@
         <v>1538</v>
       </c>
       <c r="B1086" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B1087" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B1088" t="s">
         <v>1541</v>
@@ -14203,20 +14209,20 @@
         <v>1548</v>
       </c>
       <c r="B1092" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B1093" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B1094" t="s">
         <v>1551</v>
@@ -14251,52 +14257,52 @@
         <v>1558</v>
       </c>
       <c r="B1098" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B1099" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B1100" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B1101" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B1102" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B1103" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B1104" t="s">
         <v>1565</v>
@@ -14307,20 +14313,20 @@
         <v>1566</v>
       </c>
       <c r="B1105" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B1106" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B1107" t="s">
         <v>1569</v>
@@ -14331,52 +14337,52 @@
         <v>1570</v>
       </c>
       <c r="B1108" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B1109" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B1110" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B1111" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B1112" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B1113" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B1114" t="s">
         <v>1577</v>
@@ -14387,20 +14393,20 @@
         <v>1578</v>
       </c>
       <c r="B1115" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B1116" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B1117" t="s">
         <v>1581</v>
@@ -14419,20 +14425,20 @@
         <v>1584</v>
       </c>
       <c r="B1119" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B1120" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B1121" t="s">
         <v>1587</v>
@@ -14531,44 +14537,44 @@
         <v>1610</v>
       </c>
       <c r="B1133" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B1134" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
       <c r="B1135" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B1136" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B1137" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B1138" t="s">
         <v>1616</v>
@@ -14587,36 +14593,36 @@
         <v>1619</v>
       </c>
       <c r="B1140" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
       <c r="B1141" t="s">
-        <v>1620</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
       <c r="B1142" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B1143" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B1144" t="s">
         <v>1624</v>
@@ -14627,20 +14633,20 @@
         <v>1625</v>
       </c>
       <c r="B1145" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B1146" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B1147" t="s">
         <v>1628</v>
@@ -14675,12 +14681,12 @@
         <v>1635</v>
       </c>
       <c r="B1151" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B1152" t="s">
         <v>1637</v>
@@ -14699,12 +14705,12 @@
         <v>1640</v>
       </c>
       <c r="B1154" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B1155" t="s">
         <v>1642</v>
@@ -14731,124 +14737,124 @@
         <v>1647</v>
       </c>
       <c r="B1158" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B1159" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="B1160" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B1161" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="B1162" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B1163" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="B1164" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="B1165" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B1166" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="B1167" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B1168" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B1169" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B1170" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B1171" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B1172" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B1173" t="s">
         <v>1663</v>
@@ -14859,36 +14865,36 @@
         <v>1664</v>
       </c>
       <c r="B1174" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1175" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B1176" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B1177" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="B1178" t="s">
         <v>1669</v>
@@ -14899,12 +14905,12 @@
         <v>1670</v>
       </c>
       <c r="B1179" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B1180" t="s">
         <v>1672</v>
@@ -14915,36 +14921,36 @@
         <v>1673</v>
       </c>
       <c r="B1181" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B1182" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B1183" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B1184" t="s">
-        <v>381</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B1185" t="s">
         <v>383</v>
@@ -14952,182 +14958,190 @@
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1186" t="s">
-        <v>1678</v>
+        <v>385</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B1187" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1188" t="s">
-        <v>641</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B1189" t="s">
-        <v>1681</v>
+        <v>643</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B1190" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B1191" t="s">
-        <v>915</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B1192" t="s">
-        <v>1684</v>
+        <v>917</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B1193" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B1194" t="s">
-        <v>991</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1195" t="s">
-        <v>1687</v>
+        <v>993</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
       <c r="A1196" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1196" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
       <c r="A1197" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B1197" t="s">
-        <v>1059</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B1198" t="s">
-        <v>1114</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
       <c r="A1199" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B1199" t="s">
-        <v>1691</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="1200" spans="1:2">
       <c r="A1200" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1200" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="1201" spans="1:2">
       <c r="A1201" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B1201" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
       <c r="A1202" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B1202" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1203" spans="1:2">
       <c r="A1203" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1203" t="s">
-        <v>1415</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1204" spans="1:2">
       <c r="A1204" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1204" t="s">
-        <v>1696</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="1205" spans="1:2">
       <c r="A1205" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1205" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1206" spans="1:2">
       <c r="A1206" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1206" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1207" spans="1:2">
       <c r="A1207" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1207" t="s">
-        <v>1532</v>
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:2">
+      <c r="A1208" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B1208" t="s">
+        <v>1534</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1207"/>
+  <autoFilter ref="A1:B1208"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/da/headTags.xlsx
+++ b/lang/da/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1208</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1209</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1704">
   <si>
     <t>en</t>
   </si>
@@ -3728,6 +3728,12 @@
   </si>
   <si>
     <t>Pop Team Epic</t>
+  </si>
+  <si>
+    <t>Popee the Performer</t>
+  </si>
+  <si>
+    <t>Popee den udøvende kunstner</t>
   </si>
   <si>
     <t>POPGOES</t>
@@ -5469,7 +5475,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1208"/>
+  <dimension ref="A1:B1209"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -12385,92 +12391,92 @@
         <v>1237</v>
       </c>
       <c r="B864" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B865" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B866" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B867" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B868" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B869" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B870" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B871" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B872" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B873" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B874" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B875" t="s">
         <v>1249</v>
@@ -12481,20 +12487,20 @@
         <v>1250</v>
       </c>
       <c r="B876" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B877" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B878" t="s">
         <v>1253</v>
@@ -12513,20 +12519,20 @@
         <v>1256</v>
       </c>
       <c r="B880" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B881" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B882" t="s">
         <v>1259</v>
@@ -12545,44 +12551,44 @@
         <v>1262</v>
       </c>
       <c r="B884" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B885" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B886" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B887" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B888" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B889" t="s">
         <v>1268</v>
@@ -12593,44 +12599,44 @@
         <v>1269</v>
       </c>
       <c r="B890" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B891" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B892" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B893" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B894" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B895" t="s">
         <v>1275</v>
@@ -12641,12 +12647,12 @@
         <v>1276</v>
       </c>
       <c r="B896" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B897" t="s">
         <v>1278</v>
@@ -12657,36 +12663,36 @@
         <v>1279</v>
       </c>
       <c r="B898" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B899" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B900" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B901" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B902" t="s">
         <v>1284</v>
@@ -12713,68 +12719,68 @@
         <v>1289</v>
       </c>
       <c r="B905" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B906" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B907" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B908" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B909" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B910" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B911" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B912" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B913" t="s">
         <v>1298</v>
@@ -12801,28 +12807,28 @@
         <v>1303</v>
       </c>
       <c r="B916" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B917" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B918" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B919" t="s">
         <v>1307</v>
@@ -12865,20 +12871,20 @@
         <v>1316</v>
       </c>
       <c r="B924" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B925" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B926" t="s">
         <v>1319</v>
@@ -12889,12 +12895,12 @@
         <v>1320</v>
       </c>
       <c r="B927" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B928" t="s">
         <v>1322</v>
@@ -12913,12 +12919,12 @@
         <v>1325</v>
       </c>
       <c r="B930" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B931" t="s">
         <v>1327</v>
@@ -12937,36 +12943,36 @@
         <v>1330</v>
       </c>
       <c r="B933" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B934" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B935" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B936" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B937" t="s">
         <v>1335</v>
@@ -13017,28 +13023,28 @@
         <v>1346</v>
       </c>
       <c r="B943" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B944" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B945" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B946" t="s">
         <v>1350</v>
@@ -13049,68 +13055,68 @@
         <v>1351</v>
       </c>
       <c r="B947" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B948" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B949" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="B950" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B951" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B952" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B953" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B954" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B955" t="s">
         <v>1360</v>
@@ -13137,20 +13143,20 @@
         <v>1365</v>
       </c>
       <c r="B958" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B959" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B960" t="s">
         <v>1368</v>
@@ -13177,20 +13183,20 @@
         <v>1373</v>
       </c>
       <c r="B963" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B964" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B965" t="s">
         <v>1376</v>
@@ -13201,44 +13207,44 @@
         <v>1377</v>
       </c>
       <c r="B966" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B967" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B968" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B969" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B970" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B971" t="s">
         <v>1383</v>
@@ -13281,68 +13287,68 @@
         <v>1392</v>
       </c>
       <c r="B976" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B977" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B978" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B979" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B980" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B981" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B982" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B983" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B984" t="s">
         <v>1401</v>
@@ -13353,28 +13359,28 @@
         <v>1402</v>
       </c>
       <c r="B985" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B986" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B987" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="B988" t="s">
         <v>1406</v>
@@ -13385,60 +13391,60 @@
         <v>1407</v>
       </c>
       <c r="B989" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B990" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B991" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B992" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="B993" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B994" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B995" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B996" t="s">
         <v>1415</v>
@@ -13457,28 +13463,28 @@
         <v>1418</v>
       </c>
       <c r="B998" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B999" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B1000" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B1001" t="s">
         <v>1422</v>
@@ -13489,12 +13495,12 @@
         <v>1423</v>
       </c>
       <c r="B1002" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B1003" t="s">
         <v>1425</v>
@@ -13513,36 +13519,36 @@
         <v>1428</v>
       </c>
       <c r="B1005" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B1006" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B1007" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B1008" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B1009" t="s">
         <v>1433</v>
@@ -13553,36 +13559,36 @@
         <v>1434</v>
       </c>
       <c r="B1010" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B1011" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B1012" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B1013" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B1014" t="s">
         <v>1439</v>
@@ -13601,36 +13607,36 @@
         <v>1442</v>
       </c>
       <c r="B1016" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B1017" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B1018" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B1019" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B1020" t="s">
         <v>1447</v>
@@ -13649,20 +13655,20 @@
         <v>1450</v>
       </c>
       <c r="B1022" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B1023" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B1024" t="s">
         <v>1453</v>
@@ -13681,12 +13687,12 @@
         <v>1456</v>
       </c>
       <c r="B1026" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B1027" t="s">
         <v>1458</v>
@@ -13697,84 +13703,84 @@
         <v>1459</v>
       </c>
       <c r="B1028" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B1029" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B1030" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B1031" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B1032" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B1033" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B1034" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B1035" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B1036" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B1037" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B1038" t="s">
         <v>1470</v>
@@ -13785,12 +13791,12 @@
         <v>1471</v>
       </c>
       <c r="B1039" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B1040" t="s">
         <v>1473</v>
@@ -13817,20 +13823,20 @@
         <v>1478</v>
       </c>
       <c r="B1043" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B1044" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B1045" t="s">
         <v>1481</v>
@@ -13841,12 +13847,12 @@
         <v>1482</v>
       </c>
       <c r="B1046" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B1047" t="s">
         <v>1484</v>
@@ -13857,52 +13863,52 @@
         <v>1485</v>
       </c>
       <c r="B1048" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B1049" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B1050" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B1051" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B1052" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B1053" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B1054" t="s">
         <v>1492</v>
@@ -13969,12 +13975,12 @@
         <v>1507</v>
       </c>
       <c r="B1062" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B1063" t="s">
         <v>1509</v>
@@ -13985,28 +13991,28 @@
         <v>1510</v>
       </c>
       <c r="B1064" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B1065" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B1066" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B1067" t="s">
         <v>1514</v>
@@ -14017,12 +14023,12 @@
         <v>1515</v>
       </c>
       <c r="B1068" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B1069" t="s">
         <v>1517</v>
@@ -14041,28 +14047,28 @@
         <v>1520</v>
       </c>
       <c r="B1071" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B1072" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B1073" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B1074" t="s">
         <v>1524</v>
@@ -14073,44 +14079,44 @@
         <v>1525</v>
       </c>
       <c r="B1075" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B1076" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B1077" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B1078" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B1079" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B1080" t="s">
         <v>1531</v>
@@ -14121,12 +14127,12 @@
         <v>1532</v>
       </c>
       <c r="B1081" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B1082" t="s">
         <v>1534</v>
@@ -14137,28 +14143,28 @@
         <v>1535</v>
       </c>
       <c r="B1083" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B1084" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B1085" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B1086" t="s">
         <v>1539</v>
@@ -14169,20 +14175,20 @@
         <v>1540</v>
       </c>
       <c r="B1087" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B1088" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B1089" t="s">
         <v>1543</v>
@@ -14217,20 +14223,20 @@
         <v>1550</v>
       </c>
       <c r="B1093" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B1094" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B1095" t="s">
         <v>1553</v>
@@ -14265,52 +14271,52 @@
         <v>1560</v>
       </c>
       <c r="B1099" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B1100" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B1101" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B1102" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B1103" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B1104" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B1105" t="s">
         <v>1567</v>
@@ -14321,20 +14327,20 @@
         <v>1568</v>
       </c>
       <c r="B1106" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B1107" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B1108" t="s">
         <v>1571</v>
@@ -14345,52 +14351,52 @@
         <v>1572</v>
       </c>
       <c r="B1109" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B1110" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B1111" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B1112" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B1113" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B1114" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B1115" t="s">
         <v>1579</v>
@@ -14401,20 +14407,20 @@
         <v>1580</v>
       </c>
       <c r="B1116" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B1117" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B1118" t="s">
         <v>1583</v>
@@ -14433,20 +14439,20 @@
         <v>1586</v>
       </c>
       <c r="B1120" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B1121" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B1122" t="s">
         <v>1589</v>
@@ -14545,44 +14551,44 @@
         <v>1612</v>
       </c>
       <c r="B1134" t="s">
-        <v>1612</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
       <c r="B1135" t="s">
-        <v>1613</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
       <c r="B1136" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B1137" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B1138" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B1139" t="s">
         <v>1618</v>
@@ -14601,36 +14607,36 @@
         <v>1621</v>
       </c>
       <c r="B1141" t="s">
-        <v>1621</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
       <c r="B1142" t="s">
-        <v>1622</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
       <c r="B1143" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B1144" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B1145" t="s">
         <v>1626</v>
@@ -14641,20 +14647,20 @@
         <v>1627</v>
       </c>
       <c r="B1146" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B1147" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B1148" t="s">
         <v>1630</v>
@@ -14689,12 +14695,12 @@
         <v>1637</v>
       </c>
       <c r="B1152" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B1153" t="s">
         <v>1639</v>
@@ -14713,12 +14719,12 @@
         <v>1642</v>
       </c>
       <c r="B1155" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1156" t="s">
         <v>1644</v>
@@ -14745,124 +14751,124 @@
         <v>1649</v>
       </c>
       <c r="B1159" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B1160" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="B1161" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B1162" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="B1163" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="B1164" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B1165" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="B1166" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B1167" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B1168" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B1169" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B1170" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B1171" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B1172" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="B1173" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="B1174" t="s">
         <v>1665</v>
@@ -14873,36 +14879,36 @@
         <v>1666</v>
       </c>
       <c r="B1175" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B1176" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="B1177" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B1178" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B1179" t="s">
         <v>1671</v>
@@ -14913,12 +14919,12 @@
         <v>1672</v>
       </c>
       <c r="B1180" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B1181" t="s">
         <v>1674</v>
@@ -14929,219 +14935,227 @@
         <v>1675</v>
       </c>
       <c r="B1182" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B1183" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B1184" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1185" t="s">
-        <v>383</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B1186" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1187" t="s">
-        <v>1680</v>
+        <v>385</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B1188" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B1189" t="s">
-        <v>643</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B1190" t="s">
-        <v>1683</v>
+        <v>643</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B1191" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B1192" t="s">
-        <v>917</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B1193" t="s">
-        <v>1686</v>
+        <v>917</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1194" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1195" t="s">
-        <v>993</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
       <c r="A1196" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B1196" t="s">
-        <v>1689</v>
+        <v>993</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
       <c r="A1197" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B1197" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B1198" t="s">
-        <v>1061</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
       <c r="A1199" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1199" t="s">
-        <v>1116</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="1200" spans="1:2">
       <c r="A1200" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B1200" t="s">
-        <v>1693</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="1201" spans="1:2">
       <c r="A1201" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B1201" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
       <c r="A1202" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1202" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1203" spans="1:2">
       <c r="A1203" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1203" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1204" spans="1:2">
       <c r="A1204" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1204" t="s">
-        <v>1417</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1205" spans="1:2">
       <c r="A1205" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1205" t="s">
-        <v>1698</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="1206" spans="1:2">
       <c r="A1206" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1206" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1207" spans="1:2">
       <c r="A1207" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1207" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1208" spans="1:2">
       <c r="A1208" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1208" t="s">
-        <v>1534</v>
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:2">
+      <c r="A1209" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B1209" t="s">
+        <v>1536</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1208"/>
+  <autoFilter ref="A1:B1209"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/da/headTags.xlsx
+++ b/lang/da/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1209</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1210</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1704">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1706">
   <si>
     <t>en</t>
   </si>
@@ -4607,6 +4607,12 @@
   </si>
   <si>
     <t>Tinker's Construct</t>
+  </si>
+  <si>
+    <t>Tiny Takeover</t>
+  </si>
+  <si>
+    <t>Lille overtagelse</t>
   </si>
   <si>
     <t>Titanfall</t>
@@ -5475,7 +5481,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1209"/>
+  <dimension ref="A1:B1210"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -14111,20 +14117,20 @@
         <v>1530</v>
       </c>
       <c r="B1079" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B1080" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B1081" t="s">
         <v>1533</v>
@@ -14135,12 +14141,12 @@
         <v>1534</v>
       </c>
       <c r="B1082" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B1083" t="s">
         <v>1536</v>
@@ -14151,28 +14157,28 @@
         <v>1537</v>
       </c>
       <c r="B1084" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B1085" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B1086" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B1087" t="s">
         <v>1541</v>
@@ -14183,20 +14189,20 @@
         <v>1542</v>
       </c>
       <c r="B1088" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B1089" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B1090" t="s">
         <v>1545</v>
@@ -14231,20 +14237,20 @@
         <v>1552</v>
       </c>
       <c r="B1094" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B1095" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B1096" t="s">
         <v>1555</v>
@@ -14279,52 +14285,52 @@
         <v>1562</v>
       </c>
       <c r="B1100" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B1101" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B1102" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B1103" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B1104" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B1105" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B1106" t="s">
         <v>1569</v>
@@ -14335,20 +14341,20 @@
         <v>1570</v>
       </c>
       <c r="B1107" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B1108" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B1109" t="s">
         <v>1573</v>
@@ -14359,52 +14365,52 @@
         <v>1574</v>
       </c>
       <c r="B1110" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B1111" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B1112" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B1113" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B1114" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B1115" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B1116" t="s">
         <v>1581</v>
@@ -14415,20 +14421,20 @@
         <v>1582</v>
       </c>
       <c r="B1117" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B1118" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B1119" t="s">
         <v>1585</v>
@@ -14447,20 +14453,20 @@
         <v>1588</v>
       </c>
       <c r="B1121" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B1122" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B1123" t="s">
         <v>1591</v>
@@ -14559,44 +14565,44 @@
         <v>1614</v>
       </c>
       <c r="B1135" t="s">
-        <v>1614</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
       <c r="B1136" t="s">
-        <v>1615</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
       <c r="B1137" t="s">
-        <v>1616</v>
+        <v>1617</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
       <c r="B1138" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B1139" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
-        <v>1619</v>
+        <v>1620</v>
       </c>
       <c r="B1140" t="s">
         <v>1620</v>
@@ -14615,36 +14621,36 @@
         <v>1623</v>
       </c>
       <c r="B1142" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B1143" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B1144" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B1145" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B1146" t="s">
         <v>1628</v>
@@ -14655,20 +14661,20 @@
         <v>1629</v>
       </c>
       <c r="B1147" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B1148" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B1149" t="s">
         <v>1632</v>
@@ -14703,12 +14709,12 @@
         <v>1639</v>
       </c>
       <c r="B1153" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B1154" t="s">
         <v>1641</v>
@@ -14727,12 +14733,12 @@
         <v>1644</v>
       </c>
       <c r="B1156" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B1157" t="s">
         <v>1646</v>
@@ -14759,124 +14765,124 @@
         <v>1651</v>
       </c>
       <c r="B1160" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B1161" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="B1162" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="B1163" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B1164" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="B1165" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B1166" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="B1167" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B1168" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B1169" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B1170" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B1171" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="B1172" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="B1173" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1174" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B1175" t="s">
         <v>1667</v>
@@ -14887,36 +14893,36 @@
         <v>1668</v>
       </c>
       <c r="B1176" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B1177" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B1178" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B1179" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B1180" t="s">
         <v>1673</v>
@@ -14927,12 +14933,12 @@
         <v>1674</v>
       </c>
       <c r="B1181" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B1182" t="s">
         <v>1676</v>
@@ -14943,219 +14949,227 @@
         <v>1677</v>
       </c>
       <c r="B1183" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1184" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B1185" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1186" t="s">
-        <v>383</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B1187" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B1188" t="s">
-        <v>1682</v>
+        <v>385</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B1189" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B1190" t="s">
-        <v>643</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B1191" t="s">
-        <v>1685</v>
+        <v>643</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B1192" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1193" t="s">
-        <v>917</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1194" t="s">
-        <v>1688</v>
+        <v>917</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B1195" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
       <c r="A1196" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B1196" t="s">
-        <v>993</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
       <c r="A1197" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B1197" t="s">
-        <v>1691</v>
+        <v>993</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1198" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
       <c r="A1199" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B1199" t="s">
-        <v>1061</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1200" spans="1:2">
       <c r="A1200" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B1200" t="s">
-        <v>1116</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="1201" spans="1:2">
       <c r="A1201" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1201" t="s">
-        <v>1695</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
       <c r="A1202" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1202" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1203" spans="1:2">
       <c r="A1203" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1203" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1204" spans="1:2">
       <c r="A1204" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1204" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1205" spans="1:2">
       <c r="A1205" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1205" t="s">
-        <v>1419</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1206" spans="1:2">
       <c r="A1206" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1206" t="s">
-        <v>1700</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="1207" spans="1:2">
       <c r="A1207" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1207" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1208" spans="1:2">
       <c r="A1208" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B1208" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1209" spans="1:2">
       <c r="A1209" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B1209" t="s">
-        <v>1536</v>
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:2">
+      <c r="A1210" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B1210" t="s">
+        <v>1538</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1209"/>
+  <autoFilter ref="A1:B1210"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/da/headTags.xlsx
+++ b/lang/da/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1210</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1214</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1713">
   <si>
     <t>en</t>
   </si>
@@ -2587,6 +2587,9 @@
     <t>Hypixel</t>
   </si>
   <si>
+    <t>Hypixel (Abiphone)</t>
+  </si>
+  <si>
     <t>Hypixel (Attribute Shard)</t>
   </si>
   <si>
@@ -2605,6 +2608,12 @@
     <t>Hypixel (Gear)</t>
   </si>
   <si>
+    <t>Hypixel (Gemstone)</t>
+  </si>
+  <si>
+    <t>Hypixel (ædelsten)</t>
+  </si>
+  <si>
     <t>Hypixel (Minion)</t>
   </si>
   <si>
@@ -2617,6 +2626,12 @@
     <t>Hypixel (NPC)</t>
   </si>
   <si>
+    <t>Hypixel (Pet Items)</t>
+  </si>
+  <si>
+    <t>Hypixel (kæledyrsartikler)</t>
+  </si>
+  <si>
     <t>Hypixel (Pets)</t>
   </si>
   <si>
@@ -2624,6 +2639,12 @@
   </si>
   <si>
     <t>Hypixel (Reforge Stone)</t>
+  </si>
+  <si>
+    <t>Hypixel (Runes)</t>
+  </si>
+  <si>
+    <t>Hypixel (runer)</t>
   </si>
   <si>
     <t>Hypixel (Sacks)</t>
@@ -5481,7 +5502,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1210"/>
+  <dimension ref="A1:B1214"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -10125,20 +10146,20 @@
         <v>856</v>
       </c>
       <c r="B580" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
+        <v>857</v>
+      </c>
+      <c r="B581" t="s">
         <v>858</v>
-      </c>
-      <c r="B581" t="s">
-        <v>859</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B582" t="s">
         <v>860</v>
@@ -10205,12 +10226,12 @@
         <v>871</v>
       </c>
       <c r="B590" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B591" t="s">
         <v>873</v>
@@ -10245,44 +10266,44 @@
         <v>879</v>
       </c>
       <c r="B595" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B596" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B597" t="s">
-        <v>881</v>
+        <v>884</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="B598" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B599" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
     </row>
     <row r="600" spans="1:2">
       <c r="A600" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B600" t="s">
         <v>887</v>
@@ -10293,20 +10314,20 @@
         <v>888</v>
       </c>
       <c r="B601" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
+        <v>889</v>
+      </c>
+      <c r="B602" t="s">
         <v>890</v>
-      </c>
-      <c r="B602" t="s">
-        <v>891</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B603" t="s">
         <v>892</v>
@@ -10317,132 +10338,132 @@
         <v>893</v>
       </c>
       <c r="B604" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B605" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B606" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="B607" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
     </row>
     <row r="608" spans="1:2">
       <c r="A608" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B608" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
     </row>
     <row r="609" spans="1:2">
       <c r="A609" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="B609" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="B610" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="B611" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="B612" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B613" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="B614" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B615" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="B616" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="B617" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
     </row>
     <row r="618" spans="1:2">
       <c r="A618" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B618" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B619" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B620" t="s">
         <v>914</v>
@@ -10453,220 +10474,220 @@
         <v>915</v>
       </c>
       <c r="B621" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B622" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B623" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B624" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B625" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="B626" t="s">
-        <v>921</v>
+        <v>924</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
       <c r="B627" t="s">
-        <v>922</v>
+        <v>925</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="B628" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
       <c r="B629" t="s">
-        <v>924</v>
+        <v>927</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
       <c r="B630" t="s">
-        <v>925</v>
+        <v>928</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
       <c r="B631" t="s">
-        <v>926</v>
+        <v>929</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
       <c r="B632" t="s">
-        <v>927</v>
+        <v>930</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
       <c r="B633" t="s">
-        <v>928</v>
+        <v>931</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="B634" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
       <c r="B635" t="s">
-        <v>930</v>
+        <v>933</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
       <c r="B636" t="s">
-        <v>931</v>
+        <v>934</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
       <c r="B637" t="s">
-        <v>932</v>
+        <v>935</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
       <c r="B638" t="s">
-        <v>933</v>
+        <v>936</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
       <c r="B639" t="s">
-        <v>934</v>
+        <v>937</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
       <c r="B640" t="s">
-        <v>935</v>
+        <v>938</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
       <c r="B641" t="s">
-        <v>936</v>
+        <v>939</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
       <c r="B642" t="s">
-        <v>937</v>
+        <v>940</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
       <c r="B643" t="s">
-        <v>938</v>
+        <v>941</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
       <c r="B644" t="s">
-        <v>939</v>
+        <v>942</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
       <c r="B645" t="s">
-        <v>940</v>
+        <v>943</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>941</v>
+        <v>944</v>
       </c>
       <c r="B646" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="B647" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B648" t="s">
         <v>946</v>
@@ -10677,12 +10698,12 @@
         <v>947</v>
       </c>
       <c r="B649" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="B650" t="s">
         <v>949</v>
@@ -10693,172 +10714,172 @@
         <v>950</v>
       </c>
       <c r="B651" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B652" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B653" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B654" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
     </row>
     <row r="655" spans="1:2">
       <c r="A655" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="B655" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
     </row>
     <row r="656" spans="1:2">
       <c r="A656" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B656" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B657" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="B658" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="B659" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="B660" t="s">
-        <v>961</v>
+        <v>964</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
       <c r="B661" t="s">
-        <v>962</v>
+        <v>965</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
-        <v>963</v>
+        <v>966</v>
       </c>
       <c r="B662" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="B663" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B664" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="B665" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
     </row>
     <row r="666" spans="1:2">
       <c r="A666" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B666" t="s">
-        <v>968</v>
+        <v>971</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="B667" t="s">
-        <v>969</v>
+        <v>972</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="B668" t="s">
-        <v>970</v>
+        <v>973</v>
       </c>
     </row>
     <row r="669" spans="1:2">
       <c r="A669" t="s">
-        <v>971</v>
+        <v>974</v>
       </c>
       <c r="B669" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
     </row>
     <row r="670" spans="1:2">
       <c r="A670" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="B670" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
     </row>
     <row r="671" spans="1:2">
       <c r="A671" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="B671" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="672" spans="1:2">
       <c r="A672" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B672" t="s">
         <v>977</v>
@@ -10869,124 +10890,124 @@
         <v>978</v>
       </c>
       <c r="B673" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B674" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B675" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="B676" t="s">
-        <v>981</v>
+        <v>984</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
       <c r="B677" t="s">
-        <v>982</v>
+        <v>985</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
       <c r="B678" t="s">
-        <v>983</v>
+        <v>986</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
       <c r="B679" t="s">
-        <v>984</v>
+        <v>987</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="B680" t="s">
-        <v>985</v>
+        <v>988</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" t="s">
-        <v>986</v>
+        <v>989</v>
       </c>
       <c r="B681" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B682" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B683" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B684" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B685" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B686" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B687" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="688" spans="1:2">
       <c r="A688" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B688" t="s">
         <v>998</v>
@@ -11013,12 +11034,12 @@
         <v>1003</v>
       </c>
       <c r="B691" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B692" t="s">
         <v>1005</v>
@@ -11045,12 +11066,12 @@
         <v>1010</v>
       </c>
       <c r="B695" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="696" spans="1:2">
       <c r="A696" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B696" t="s">
         <v>1012</v>
@@ -11077,20 +11098,20 @@
         <v>1017</v>
       </c>
       <c r="B699" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="700" spans="1:2">
       <c r="A700" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B700" t="s">
         <v>1019</v>
-      </c>
-      <c r="B700" t="s">
-        <v>1020</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="B701" t="s">
         <v>1021</v>
@@ -11101,212 +11122,212 @@
         <v>1022</v>
       </c>
       <c r="B702" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="B703" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="B704" t="s">
-        <v>1024</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" t="s">
-        <v>1025</v>
+        <v>1028</v>
       </c>
       <c r="B705" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="B706" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="707" spans="1:2">
       <c r="A707" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="B707" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B708" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="B709" t="s">
-        <v>1030</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
       <c r="B710" t="s">
-        <v>1031</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
       <c r="B711" t="s">
-        <v>1032</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
       <c r="B712" t="s">
-        <v>1033</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
       <c r="B713" t="s">
-        <v>1034</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
       <c r="B714" t="s">
-        <v>1035</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1036</v>
+        <v>1039</v>
       </c>
       <c r="B715" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="B716" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B717" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B718" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B719" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B720" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="B721" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B722" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B723" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B724" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B725" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B726" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B727" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B728" t="s">
         <v>1057</v>
@@ -11317,132 +11338,132 @@
         <v>1058</v>
       </c>
       <c r="B729" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B730" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B731" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B732" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="B733" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B734" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B735" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="B736" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B737" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="B738" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="B739" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="B740" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="B741" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="742" spans="1:2">
       <c r="A742" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="B742" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="B743" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B744" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B745" t="s">
         <v>1079</v>
@@ -11453,76 +11474,76 @@
         <v>1080</v>
       </c>
       <c r="B746" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B747" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B748" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="B749" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="B750" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="B751" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B752" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="753" spans="1:2">
       <c r="A753" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="B753" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B754" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B755" t="s">
         <v>1093</v>
@@ -11533,12 +11554,12 @@
         <v>1094</v>
       </c>
       <c r="B756" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B757" t="s">
         <v>1096</v>
@@ -11549,36 +11570,36 @@
         <v>1097</v>
       </c>
       <c r="B758" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="759" spans="1:2">
       <c r="A759" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B759" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="760" spans="1:2">
       <c r="A760" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B760" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="761" spans="1:2">
       <c r="A761" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B761" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="762" spans="1:2">
       <c r="A762" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B762" t="s">
         <v>1104</v>
@@ -11589,36 +11610,36 @@
         <v>1105</v>
       </c>
       <c r="B763" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B764" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B765" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="766" spans="1:2">
       <c r="A766" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B766" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B767" t="s">
         <v>1112</v>
@@ -11629,20 +11650,20 @@
         <v>1113</v>
       </c>
       <c r="B768" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B769" t="s">
         <v>1115</v>
-      </c>
-      <c r="B769" t="s">
-        <v>1116</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B770" t="s">
         <v>1117</v>
@@ -11669,68 +11690,68 @@
         <v>1122</v>
       </c>
       <c r="B773" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="774" spans="1:2">
       <c r="A774" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B774" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="775" spans="1:2">
       <c r="A775" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B775" t="s">
-        <v>1124</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="B776" t="s">
-        <v>1125</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="B777" t="s">
-        <v>1126</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="B778" t="s">
-        <v>1128</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="B779" t="s">
-        <v>1129</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="780" spans="1:2">
       <c r="A780" t="s">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="B780" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="781" spans="1:2">
       <c r="A781" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B781" t="s">
         <v>1133</v>
@@ -11757,172 +11778,172 @@
         <v>1137</v>
       </c>
       <c r="B784" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B785" t="s">
-        <v>1138</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="B786" t="s">
-        <v>1139</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
       <c r="B787" t="s">
-        <v>1140</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="788" spans="1:2">
       <c r="A788" t="s">
-        <v>1141</v>
+        <v>1144</v>
       </c>
       <c r="B788" t="s">
-        <v>1142</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="789" spans="1:2">
       <c r="A789" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="B789" t="s">
-        <v>1143</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="B790" t="s">
-        <v>1144</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="B791" t="s">
-        <v>1145</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="B792" t="s">
-        <v>1146</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
       <c r="B793" t="s">
-        <v>1147</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
       <c r="B794" t="s">
-        <v>1148</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="B795" t="s">
-        <v>1149</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
       <c r="B796" t="s">
-        <v>1150</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="B797" t="s">
-        <v>1151</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
       <c r="B798" t="s">
-        <v>1152</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="B799" t="s">
-        <v>1153</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
       <c r="B800" t="s">
-        <v>1154</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
       <c r="B801" t="s">
-        <v>1155</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
       <c r="B802" t="s">
-        <v>1156</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="B803" t="s">
-        <v>1158</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B804" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B805" t="s">
         <v>1162</v>
@@ -11933,12 +11954,12 @@
         <v>1163</v>
       </c>
       <c r="B806" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="B807" t="s">
         <v>1165</v>
@@ -11949,52 +11970,52 @@
         <v>1166</v>
       </c>
       <c r="B808" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B809" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="B810" t="s">
-        <v>1168</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
       <c r="B811" t="s">
-        <v>1169</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="B812" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="813" spans="1:2">
       <c r="A813" t="s">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B813" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="814" spans="1:2">
       <c r="A814" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B814" t="s">
         <v>1175</v>
@@ -12005,12 +12026,12 @@
         <v>1176</v>
       </c>
       <c r="B815" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="B816" t="s">
         <v>1178</v>
@@ -12021,76 +12042,76 @@
         <v>1179</v>
       </c>
       <c r="B817" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B818" t="s">
-        <v>1180</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="B819" t="s">
-        <v>1181</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" t="s">
-        <v>1182</v>
+        <v>1185</v>
       </c>
       <c r="B820" t="s">
-        <v>1183</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="B821" t="s">
-        <v>1184</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="822" spans="1:2">
       <c r="A822" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="B822" t="s">
-        <v>1185</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="B823" t="s">
-        <v>1186</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="B824" t="s">
-        <v>1188</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="B825" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B826" t="s">
         <v>1192</v>
@@ -12117,244 +12138,244 @@
         <v>1196</v>
       </c>
       <c r="B829" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B830" t="s">
-        <v>1197</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="B831" t="s">
-        <v>1198</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="B832" t="s">
-        <v>1200</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="B833" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="B834" t="s">
-        <v>1202</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="B835" t="s">
-        <v>1203</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="B836" t="s">
-        <v>1204</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
       <c r="B837" t="s">
-        <v>1205</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1206</v>
+        <v>1209</v>
       </c>
       <c r="B838" t="s">
-        <v>1207</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="B839" t="s">
-        <v>1208</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B840" t="s">
-        <v>1209</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="B841" t="s">
-        <v>1210</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="B842" t="s">
-        <v>1211</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
       <c r="B843" t="s">
-        <v>1212</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
       <c r="B844" t="s">
-        <v>1213</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
       <c r="B845" t="s">
-        <v>1214</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="B846" t="s">
-        <v>1215</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="B847" t="s">
-        <v>1216</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="B848" t="s">
-        <v>1217</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
       <c r="B849" t="s">
-        <v>1218</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
       <c r="B850" t="s">
-        <v>1219</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
       <c r="B851" t="s">
-        <v>1220</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
       <c r="B852" t="s">
-        <v>1221</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="B853" t="s">
-        <v>1222</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
       <c r="B854" t="s">
-        <v>1223</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
       <c r="B855" t="s">
-        <v>1224</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="B856" t="s">
-        <v>1225</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="B857" t="s">
-        <v>1227</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="B858" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B859" t="s">
         <v>1231</v>
@@ -12365,12 +12386,12 @@
         <v>1232</v>
       </c>
       <c r="B860" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B861" t="s">
         <v>1234</v>
@@ -12381,348 +12402,348 @@
         <v>1235</v>
       </c>
       <c r="B862" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B863" t="s">
-        <v>1236</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="B864" t="s">
-        <v>1238</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="B865" t="s">
-        <v>1239</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="B866" t="s">
-        <v>1240</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="867" spans="1:2">
       <c r="A867" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="B867" t="s">
-        <v>1241</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="B868" t="s">
-        <v>1242</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
       <c r="B869" t="s">
-        <v>1243</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
       <c r="B870" t="s">
-        <v>1244</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="B871" t="s">
-        <v>1245</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
       <c r="B872" t="s">
-        <v>1246</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
       <c r="B873" t="s">
-        <v>1247</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
       <c r="B874" t="s">
-        <v>1248</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
       <c r="B875" t="s">
-        <v>1249</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1250</v>
+        <v>1253</v>
       </c>
       <c r="B876" t="s">
-        <v>1251</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="B877" t="s">
-        <v>1252</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="B878" t="s">
-        <v>1253</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="B879" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B880" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B881" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B882" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B883" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B884" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B885" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B886" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B887" t="s">
-        <v>1266</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="B888" t="s">
-        <v>1267</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
       <c r="B889" t="s">
-        <v>1268</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1269</v>
+        <v>1272</v>
       </c>
       <c r="B890" t="s">
-        <v>1270</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="B891" t="s">
-        <v>1271</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="B892" t="s">
-        <v>1272</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="B893" t="s">
-        <v>1273</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="B894" t="s">
-        <v>1274</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
       <c r="B895" t="s">
-        <v>1275</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1276</v>
+        <v>1279</v>
       </c>
       <c r="B896" t="s">
-        <v>1277</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="B897" t="s">
-        <v>1278</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="B898" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B899" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B900" t="s">
-        <v>1282</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="B901" t="s">
-        <v>1283</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="B902" t="s">
-        <v>1284</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1285</v>
+        <v>1288</v>
       </c>
       <c r="B903" t="s">
-        <v>1286</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="B904" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B905" t="s">
         <v>1290</v>
@@ -12741,76 +12762,76 @@
         <v>1292</v>
       </c>
       <c r="B907" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B908" t="s">
-        <v>1293</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="B909" t="s">
-        <v>1294</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
       <c r="B910" t="s">
-        <v>1295</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
       <c r="B911" t="s">
-        <v>1296</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
       <c r="B912" t="s">
-        <v>1297</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
       <c r="B913" t="s">
-        <v>1298</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1299</v>
+        <v>1302</v>
       </c>
       <c r="B914" t="s">
-        <v>1300</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="B915" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B916" t="s">
         <v>1304</v>
@@ -12829,36 +12850,36 @@
         <v>1306</v>
       </c>
       <c r="B918" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B919" t="s">
-        <v>1307</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="B920" t="s">
-        <v>1309</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="B921" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B922" t="s">
         <v>1313</v>
@@ -12869,20 +12890,20 @@
         <v>1314</v>
       </c>
       <c r="B923" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B924" t="s">
         <v>1316</v>
-      </c>
-      <c r="B924" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B925" t="s">
         <v>1318</v>
@@ -12893,36 +12914,36 @@
         <v>1319</v>
       </c>
       <c r="B926" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B927" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B928" t="s">
-        <v>1322</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="B929" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B930" t="s">
         <v>1326</v>
@@ -12933,12 +12954,12 @@
         <v>1327</v>
       </c>
       <c r="B931" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="932" spans="1:2">
       <c r="A932" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B932" t="s">
         <v>1329</v>
@@ -12957,52 +12978,52 @@
         <v>1332</v>
       </c>
       <c r="B934" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B935" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B936" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="B937" t="s">
-        <v>1335</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
-        <v>1336</v>
+        <v>1339</v>
       </c>
       <c r="B938" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="B939" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B940" t="s">
         <v>1341</v>
@@ -13013,28 +13034,28 @@
         <v>1342</v>
       </c>
       <c r="B941" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B942" t="s">
         <v>1344</v>
-      </c>
-      <c r="B942" t="s">
-        <v>1345</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B943" t="s">
         <v>1346</v>
-      </c>
-      <c r="B943" t="s">
-        <v>1347</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="B944" t="s">
         <v>1348</v>
@@ -13045,108 +13066,108 @@
         <v>1349</v>
       </c>
       <c r="B945" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B946" t="s">
-        <v>1350</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="B947" t="s">
-        <v>1352</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="B948" t="s">
-        <v>1353</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
       <c r="B949" t="s">
-        <v>1354</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
       <c r="B950" t="s">
-        <v>1355</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1356</v>
+        <v>1358</v>
       </c>
       <c r="B951" t="s">
-        <v>1356</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
       <c r="B952" t="s">
-        <v>1357</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
       <c r="B953" t="s">
-        <v>1358</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
       <c r="B954" t="s">
-        <v>1359</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
       <c r="B955" t="s">
-        <v>1360</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1361</v>
+        <v>1364</v>
       </c>
       <c r="B956" t="s">
-        <v>1362</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1363</v>
+        <v>1365</v>
       </c>
       <c r="B957" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B958" t="s">
         <v>1366</v>
@@ -13165,28 +13186,28 @@
         <v>1368</v>
       </c>
       <c r="B960" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B961" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B962" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B963" t="s">
         <v>1374</v>
@@ -13205,76 +13226,76 @@
         <v>1376</v>
       </c>
       <c r="B965" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B966" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B967" t="s">
-        <v>1379</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
       <c r="B968" t="s">
-        <v>1380</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
       <c r="B969" t="s">
-        <v>1381</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1382</v>
+        <v>1384</v>
       </c>
       <c r="B970" t="s">
-        <v>1382</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
       <c r="B971" t="s">
-        <v>1383</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1384</v>
+        <v>1387</v>
       </c>
       <c r="B972" t="s">
-        <v>1385</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1386</v>
+        <v>1388</v>
       </c>
       <c r="B973" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B974" t="s">
         <v>1389</v>
@@ -13285,20 +13306,20 @@
         <v>1390</v>
       </c>
       <c r="B975" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B976" t="s">
         <v>1392</v>
-      </c>
-      <c r="B976" t="s">
-        <v>1393</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
       <c r="B977" t="s">
         <v>1394</v>
@@ -13309,220 +13330,220 @@
         <v>1395</v>
       </c>
       <c r="B978" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B979" t="s">
-        <v>1396</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1397</v>
+        <v>1399</v>
       </c>
       <c r="B980" t="s">
-        <v>1397</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
       <c r="B981" t="s">
-        <v>1398</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
       <c r="B982" t="s">
-        <v>1399</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
       <c r="B983" t="s">
-        <v>1400</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
       <c r="B984" t="s">
-        <v>1401</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1402</v>
+        <v>1405</v>
       </c>
       <c r="B985" t="s">
-        <v>1403</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
       <c r="B986" t="s">
-        <v>1404</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
       <c r="B987" t="s">
-        <v>1405</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
       <c r="B988" t="s">
-        <v>1406</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1407</v>
+        <v>1409</v>
       </c>
       <c r="B989" t="s">
-        <v>1408</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
       <c r="B990" t="s">
-        <v>1409</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
       <c r="B991" t="s">
-        <v>1410</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
       <c r="B992" t="s">
-        <v>1411</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1412</v>
+        <v>1414</v>
       </c>
       <c r="B993" t="s">
-        <v>1412</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
       <c r="B994" t="s">
-        <v>1413</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
       <c r="B995" t="s">
-        <v>1414</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
       <c r="B996" t="s">
-        <v>1415</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1416</v>
+        <v>1419</v>
       </c>
       <c r="B997" t="s">
-        <v>1417</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1418</v>
+        <v>1420</v>
       </c>
       <c r="B998" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B999" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B1000" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B1001" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="B1002" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="B1003" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="B1004" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B1005" t="s">
         <v>1429</v>
@@ -13533,180 +13554,180 @@
         <v>1430</v>
       </c>
       <c r="B1006" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B1007" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B1008" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="B1009" t="s">
-        <v>1433</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1434</v>
+        <v>1437</v>
       </c>
       <c r="B1010" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="B1011" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="B1012" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="B1013" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="B1014" t="s">
-        <v>1439</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1440</v>
+        <v>1443</v>
       </c>
       <c r="B1015" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="B1016" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B1017" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B1018" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B1019" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="B1020" t="s">
-        <v>1447</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1448</v>
+        <v>1451</v>
       </c>
       <c r="B1021" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="B1022" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B1023" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B1024" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B1025" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B1026" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B1027" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B1028" t="s">
         <v>1460</v>
@@ -13717,108 +13738,108 @@
         <v>1461</v>
       </c>
       <c r="B1029" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B1030" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="B1031" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="B1032" t="s">
-        <v>1464</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1465</v>
+        <v>1468</v>
       </c>
       <c r="B1033" t="s">
-        <v>1465</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1466</v>
+        <v>1469</v>
       </c>
       <c r="B1034" t="s">
-        <v>1466</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
       <c r="B1035" t="s">
-        <v>1467</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1468</v>
+        <v>1471</v>
       </c>
       <c r="B1036" t="s">
-        <v>1468</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="B1037" t="s">
-        <v>1469</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
       <c r="B1038" t="s">
-        <v>1470</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1471</v>
+        <v>1474</v>
       </c>
       <c r="B1039" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="B1040" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="B1041" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B1042" t="s">
         <v>1477</v>
@@ -13845,100 +13866,100 @@
         <v>1481</v>
       </c>
       <c r="B1045" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B1046" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B1047" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="B1048" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B1049" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B1050" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="B1051" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="B1052" t="s">
-        <v>1490</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
       <c r="B1053" t="s">
-        <v>1491</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
       <c r="B1054" t="s">
-        <v>1492</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1493</v>
+        <v>1496</v>
       </c>
       <c r="B1055" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="B1056" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B1057" t="s">
         <v>1498</v>
@@ -13949,44 +13970,44 @@
         <v>1499</v>
       </c>
       <c r="B1058" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B1059" t="s">
         <v>1501</v>
-      </c>
-      <c r="B1059" t="s">
-        <v>1502</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B1060" t="s">
         <v>1503</v>
-      </c>
-      <c r="B1060" t="s">
-        <v>1504</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B1061" t="s">
         <v>1505</v>
-      </c>
-      <c r="B1061" t="s">
-        <v>1506</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B1062" t="s">
         <v>1507</v>
-      </c>
-      <c r="B1062" t="s">
-        <v>1508</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="B1063" t="s">
         <v>1509</v>
@@ -14005,52 +14026,52 @@
         <v>1512</v>
       </c>
       <c r="B1065" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B1066" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="B1067" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="B1068" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="B1069" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="B1070" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B1071" t="s">
         <v>1521</v>
@@ -14061,172 +14082,172 @@
         <v>1522</v>
       </c>
       <c r="B1072" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B1073" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B1074" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="B1075" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="B1076" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="B1077" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="B1078" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="B1079" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="B1080" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="B1081" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B1082" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B1083" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="B1084" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B1085" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B1086" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="B1087" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="B1088" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="B1089" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="B1090" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B1091" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B1092" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B1093" t="s">
         <v>1551</v>
@@ -14237,12 +14258,12 @@
         <v>1552</v>
       </c>
       <c r="B1094" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B1095" t="s">
         <v>1554</v>
@@ -14253,28 +14274,28 @@
         <v>1555</v>
       </c>
       <c r="B1096" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B1097" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B1098" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B1099" t="s">
         <v>1561</v>
@@ -14285,12 +14306,12 @@
         <v>1562</v>
       </c>
       <c r="B1100" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1564</v>
+        <v>1563</v>
       </c>
       <c r="B1101" t="s">
         <v>1564</v>
@@ -14301,196 +14322,196 @@
         <v>1565</v>
       </c>
       <c r="B1102" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B1103" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="B1104" t="s">
-        <v>1567</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1568</v>
+        <v>1571</v>
       </c>
       <c r="B1105" t="s">
-        <v>1568</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1569</v>
+        <v>1572</v>
       </c>
       <c r="B1106" t="s">
-        <v>1569</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1570</v>
+        <v>1573</v>
       </c>
       <c r="B1107" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="B1108" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B1109" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="B1110" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B1111" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="B1112" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="B1113" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="B1114" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="B1115" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1581</v>
+        <v>1584</v>
       </c>
       <c r="B1116" t="s">
-        <v>1581</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1582</v>
+        <v>1585</v>
       </c>
       <c r="B1117" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="B1118" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="B1119" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="B1120" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B1121" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B1122" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B1123" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B1124" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B1125" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B1126" t="s">
         <v>1597</v>
@@ -14501,76 +14522,76 @@
         <v>1598</v>
       </c>
       <c r="B1127" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B1128" t="s">
         <v>1600</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>1601</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
+        <v>1601</v>
+      </c>
+      <c r="B1129" t="s">
         <v>1602</v>
-      </c>
-      <c r="B1129" t="s">
-        <v>1603</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B1130" t="s">
         <v>1604</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>1605</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1606</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1607</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1608</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1609</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B1133" t="s">
         <v>1610</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>1611</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B1134" t="s">
         <v>1612</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>1613</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B1135" t="s">
         <v>1614</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>1615</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="B1136" t="s">
         <v>1616</v>
@@ -14581,124 +14602,124 @@
         <v>1617</v>
       </c>
       <c r="B1137" t="s">
-        <v>1617</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
-        <v>1618</v>
+        <v>1619</v>
       </c>
       <c r="B1138" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="B1139" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="B1140" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="B1141" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="B1142" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B1143" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B1144" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B1145" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="B1146" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="B1147" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="B1148" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="B1149" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="B1150" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B1151" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B1152" t="s">
         <v>1638</v>
@@ -14709,12 +14730,12 @@
         <v>1639</v>
       </c>
       <c r="B1153" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1641</v>
+        <v>1640</v>
       </c>
       <c r="B1154" t="s">
         <v>1641</v>
@@ -14741,12 +14762,12 @@
         <v>1646</v>
       </c>
       <c r="B1157" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B1158" t="s">
         <v>1648</v>
@@ -14781,395 +14802,427 @@
         <v>1654</v>
       </c>
       <c r="B1162" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B1163" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="B1164" t="s">
-        <v>1656</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1657</v>
+        <v>1660</v>
       </c>
       <c r="B1165" t="s">
-        <v>1657</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1658</v>
+        <v>1661</v>
       </c>
       <c r="B1166" t="s">
-        <v>1658</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1659</v>
+        <v>1662</v>
       </c>
       <c r="B1167" t="s">
-        <v>1659</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
       <c r="B1168" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1661</v>
+        <v>1664</v>
       </c>
       <c r="B1169" t="s">
-        <v>1661</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
       <c r="B1170" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
       <c r="B1171" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1664</v>
+        <v>1667</v>
       </c>
       <c r="B1172" t="s">
-        <v>1664</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
       <c r="B1173" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
       <c r="B1174" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1667</v>
+        <v>1670</v>
       </c>
       <c r="B1175" t="s">
-        <v>1667</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
       <c r="B1176" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="B1177" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="B1178" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="B1179" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="B1180" t="s">
-        <v>1673</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1674</v>
+        <v>1677</v>
       </c>
       <c r="B1181" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="B1182" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="B1183" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B1184" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1185" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
       <c r="B1186" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="B1187" t="s">
-        <v>383</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1683</v>
+        <v>1686</v>
       </c>
       <c r="B1188" t="s">
-        <v>385</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1684</v>
+        <v>1687</v>
       </c>
       <c r="B1189" t="s">
-        <v>1684</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1685</v>
+        <v>1688</v>
       </c>
       <c r="B1190" t="s">
-        <v>1685</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1686</v>
+        <v>1689</v>
       </c>
       <c r="B1191" t="s">
-        <v>643</v>
+        <v>383</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1687</v>
+        <v>1690</v>
       </c>
       <c r="B1192" t="s">
-        <v>1687</v>
+        <v>385</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="B1193" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1689</v>
+        <v>1692</v>
       </c>
       <c r="B1194" t="s">
-        <v>917</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1690</v>
+        <v>1693</v>
       </c>
       <c r="B1195" t="s">
-        <v>1690</v>
+        <v>643</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
       <c r="A1196" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
       <c r="B1196" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
       <c r="A1197" t="s">
-        <v>1692</v>
+        <v>1695</v>
       </c>
       <c r="B1197" t="s">
-        <v>993</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>1693</v>
+        <v>1696</v>
       </c>
       <c r="B1198" t="s">
-        <v>1693</v>
+        <v>924</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
       <c r="A1199" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="B1199" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1200" spans="1:2">
       <c r="A1200" t="s">
-        <v>1695</v>
+        <v>1698</v>
       </c>
       <c r="B1200" t="s">
-        <v>1061</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1201" spans="1:2">
       <c r="A1201" t="s">
-        <v>1696</v>
+        <v>1699</v>
       </c>
       <c r="B1201" t="s">
-        <v>1116</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
       <c r="A1202" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="B1202" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1203" spans="1:2">
       <c r="A1203" t="s">
-        <v>1698</v>
+        <v>1701</v>
       </c>
       <c r="B1203" t="s">
-        <v>1698</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1204" spans="1:2">
       <c r="A1204" t="s">
-        <v>1699</v>
+        <v>1702</v>
       </c>
       <c r="B1204" t="s">
-        <v>1699</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="1205" spans="1:2">
       <c r="A1205" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="B1205" t="s">
-        <v>1700</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="1206" spans="1:2">
       <c r="A1206" t="s">
-        <v>1701</v>
+        <v>1704</v>
       </c>
       <c r="B1206" t="s">
-        <v>1419</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="1207" spans="1:2">
       <c r="A1207" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
       <c r="B1207" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1208" spans="1:2">
       <c r="A1208" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="B1208" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1209" spans="1:2">
       <c r="A1209" t="s">
-        <v>1704</v>
+        <v>1707</v>
       </c>
       <c r="B1209" t="s">
-        <v>1704</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="1210" spans="1:2">
       <c r="A1210" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
       <c r="B1210" t="s">
-        <v>1538</v>
+        <v>1426</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:2">
+      <c r="A1211" t="s">
+        <v>1709</v>
+      </c>
+      <c r="B1211" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:2">
+      <c r="A1212" t="s">
+        <v>1710</v>
+      </c>
+      <c r="B1212" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:2">
+      <c r="A1213" t="s">
+        <v>1711</v>
+      </c>
+      <c r="B1213" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:2">
+      <c r="A1214" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B1214" t="s">
+        <v>1545</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1210"/>
+  <autoFilter ref="A1:B1214"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/da/headTags.xlsx
+++ b/lang/da/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1215</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1715">
   <si>
     <t>en</t>
   </si>
@@ -3797,6 +3797,12 @@
   </si>
   <si>
     <t>Prof Layton</t>
+  </si>
+  <si>
+    <t>Project Zomboid</t>
+  </si>
+  <si>
+    <t>Projekt Zomboid</t>
   </si>
   <si>
     <t>Pumpkin</t>
@@ -5502,7 +5508,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1214"/>
+  <dimension ref="A1:B1215"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -12562,12 +12568,12 @@
         <v>1260</v>
       </c>
       <c r="B882" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B883" t="s">
         <v>1262</v>
@@ -12586,20 +12592,20 @@
         <v>1265</v>
       </c>
       <c r="B885" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B886" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B887" t="s">
         <v>1268</v>
@@ -12618,44 +12624,44 @@
         <v>1271</v>
       </c>
       <c r="B889" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B890" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B891" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B892" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B893" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B894" t="s">
         <v>1277</v>
@@ -12666,44 +12672,44 @@
         <v>1278</v>
       </c>
       <c r="B895" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B896" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B897" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B898" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B899" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B900" t="s">
         <v>1284</v>
@@ -12714,12 +12720,12 @@
         <v>1285</v>
       </c>
       <c r="B901" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B902" t="s">
         <v>1287</v>
@@ -12730,36 +12736,36 @@
         <v>1288</v>
       </c>
       <c r="B903" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B904" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B905" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B906" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B907" t="s">
         <v>1293</v>
@@ -12786,68 +12792,68 @@
         <v>1298</v>
       </c>
       <c r="B910" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B911" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B912" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B913" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B914" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B915" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B916" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B917" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B918" t="s">
         <v>1307</v>
@@ -12874,28 +12880,28 @@
         <v>1312</v>
       </c>
       <c r="B921" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B922" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B923" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B924" t="s">
         <v>1316</v>
@@ -12938,20 +12944,20 @@
         <v>1325</v>
       </c>
       <c r="B929" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B930" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B931" t="s">
         <v>1328</v>
@@ -12962,12 +12968,12 @@
         <v>1329</v>
       </c>
       <c r="B932" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B933" t="s">
         <v>1331</v>
@@ -12986,12 +12992,12 @@
         <v>1334</v>
       </c>
       <c r="B935" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B936" t="s">
         <v>1336</v>
@@ -13010,36 +13016,36 @@
         <v>1339</v>
       </c>
       <c r="B938" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B939" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B940" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="B941" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B942" t="s">
         <v>1344</v>
@@ -13090,28 +13096,28 @@
         <v>1355</v>
       </c>
       <c r="B948" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="B949" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B950" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="B951" t="s">
         <v>1359</v>
@@ -13122,68 +13128,68 @@
         <v>1360</v>
       </c>
       <c r="B952" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B953" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B954" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B955" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B956" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B957" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B958" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B959" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B960" t="s">
         <v>1369</v>
@@ -13210,20 +13216,20 @@
         <v>1374</v>
       </c>
       <c r="B963" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B964" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B965" t="s">
         <v>1377</v>
@@ -13250,20 +13256,20 @@
         <v>1382</v>
       </c>
       <c r="B968" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="B969" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B970" t="s">
         <v>1385</v>
@@ -13274,44 +13280,44 @@
         <v>1386</v>
       </c>
       <c r="B971" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="B972" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B973" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="B974" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B975" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="B976" t="s">
         <v>1392</v>
@@ -13354,68 +13360,68 @@
         <v>1401</v>
       </c>
       <c r="B981" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B982" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B983" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B984" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="B985" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B986" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="B987" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B988" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B989" t="s">
         <v>1410</v>
@@ -13426,28 +13432,28 @@
         <v>1411</v>
       </c>
       <c r="B990" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B991" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B992" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B993" t="s">
         <v>1415</v>
@@ -13458,60 +13464,60 @@
         <v>1416</v>
       </c>
       <c r="B994" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B995" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B996" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B997" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B998" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B999" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B1000" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B1001" t="s">
         <v>1424</v>
@@ -13530,28 +13536,28 @@
         <v>1427</v>
       </c>
       <c r="B1003" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B1004" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B1005" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B1006" t="s">
         <v>1431</v>
@@ -13562,12 +13568,12 @@
         <v>1432</v>
       </c>
       <c r="B1007" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B1008" t="s">
         <v>1434</v>
@@ -13586,36 +13592,36 @@
         <v>1437</v>
       </c>
       <c r="B1010" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B1011" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B1012" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B1013" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B1014" t="s">
         <v>1442</v>
@@ -13626,36 +13632,36 @@
         <v>1443</v>
       </c>
       <c r="B1015" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B1016" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B1017" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B1018" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="B1019" t="s">
         <v>1448</v>
@@ -13674,36 +13680,36 @@
         <v>1451</v>
       </c>
       <c r="B1021" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B1022" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B1023" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B1024" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B1025" t="s">
         <v>1456</v>
@@ -13722,20 +13728,20 @@
         <v>1459</v>
       </c>
       <c r="B1027" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B1028" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B1029" t="s">
         <v>1462</v>
@@ -13754,12 +13760,12 @@
         <v>1465</v>
       </c>
       <c r="B1031" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B1032" t="s">
         <v>1467</v>
@@ -13770,84 +13776,84 @@
         <v>1468</v>
       </c>
       <c r="B1033" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B1034" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B1035" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B1036" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B1037" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B1038" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B1039" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B1040" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B1041" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B1042" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B1043" t="s">
         <v>1479</v>
@@ -13858,12 +13864,12 @@
         <v>1480</v>
       </c>
       <c r="B1044" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B1045" t="s">
         <v>1482</v>
@@ -13890,20 +13896,20 @@
         <v>1487</v>
       </c>
       <c r="B1048" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B1049" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B1050" t="s">
         <v>1490</v>
@@ -13914,12 +13920,12 @@
         <v>1491</v>
       </c>
       <c r="B1051" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B1052" t="s">
         <v>1493</v>
@@ -13930,52 +13936,52 @@
         <v>1494</v>
       </c>
       <c r="B1053" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B1054" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B1055" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B1056" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B1057" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B1058" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B1059" t="s">
         <v>1501</v>
@@ -14042,12 +14048,12 @@
         <v>1516</v>
       </c>
       <c r="B1067" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B1068" t="s">
         <v>1518</v>
@@ -14058,28 +14064,28 @@
         <v>1519</v>
       </c>
       <c r="B1069" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B1070" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
     </row>
     <row r="1071" spans="1:2">
       <c r="A1071" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B1071" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B1072" t="s">
         <v>1523</v>
@@ -14090,12 +14096,12 @@
         <v>1524</v>
       </c>
       <c r="B1073" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B1074" t="s">
         <v>1526</v>
@@ -14114,28 +14120,28 @@
         <v>1529</v>
       </c>
       <c r="B1076" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B1077" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B1078" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B1079" t="s">
         <v>1533</v>
@@ -14146,28 +14152,28 @@
         <v>1534</v>
       </c>
       <c r="B1080" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B1081" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B1082" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B1083" t="s">
         <v>1538</v>
@@ -14178,20 +14184,20 @@
         <v>1539</v>
       </c>
       <c r="B1084" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B1085" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B1086" t="s">
         <v>1542</v>
@@ -14202,12 +14208,12 @@
         <v>1543</v>
       </c>
       <c r="B1087" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B1088" t="s">
         <v>1545</v>
@@ -14218,28 +14224,28 @@
         <v>1546</v>
       </c>
       <c r="B1089" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B1090" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B1091" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B1092" t="s">
         <v>1550</v>
@@ -14250,20 +14256,20 @@
         <v>1551</v>
       </c>
       <c r="B1093" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B1094" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B1095" t="s">
         <v>1554</v>
@@ -14298,20 +14304,20 @@
         <v>1561</v>
       </c>
       <c r="B1099" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B1100" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B1101" t="s">
         <v>1564</v>
@@ -14346,52 +14352,52 @@
         <v>1571</v>
       </c>
       <c r="B1105" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B1106" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B1107" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B1108" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B1109" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B1110" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B1111" t="s">
         <v>1578</v>
@@ -14402,20 +14408,20 @@
         <v>1579</v>
       </c>
       <c r="B1112" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B1113" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B1114" t="s">
         <v>1582</v>
@@ -14426,52 +14432,52 @@
         <v>1583</v>
       </c>
       <c r="B1115" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B1116" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B1117" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B1118" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B1119" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B1120" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B1121" t="s">
         <v>1590</v>
@@ -14482,20 +14488,20 @@
         <v>1591</v>
       </c>
       <c r="B1122" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B1123" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B1124" t="s">
         <v>1594</v>
@@ -14514,20 +14520,20 @@
         <v>1597</v>
       </c>
       <c r="B1126" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1127" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B1128" t="s">
         <v>1600</v>
@@ -14626,44 +14632,44 @@
         <v>1623</v>
       </c>
       <c r="B1140" t="s">
-        <v>1623</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="B1141" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
       <c r="B1142" t="s">
-        <v>1625</v>
+        <v>1626</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
       <c r="B1143" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B1144" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B1145" t="s">
         <v>1629</v>
@@ -14682,36 +14688,36 @@
         <v>1632</v>
       </c>
       <c r="B1147" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B1148" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B1149" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B1150" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B1151" t="s">
         <v>1637</v>
@@ -14722,20 +14728,20 @@
         <v>1638</v>
       </c>
       <c r="B1152" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B1153" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B1154" t="s">
         <v>1641</v>
@@ -14770,12 +14776,12 @@
         <v>1648</v>
       </c>
       <c r="B1158" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="B1159" t="s">
         <v>1650</v>
@@ -14794,12 +14800,12 @@
         <v>1653</v>
       </c>
       <c r="B1161" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="B1162" t="s">
         <v>1655</v>
@@ -14826,124 +14832,124 @@
         <v>1660</v>
       </c>
       <c r="B1165" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B1166" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B1167" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="B1168" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="B1169" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1170" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B1171" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B1172" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="B1173" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B1174" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B1175" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B1176" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B1177" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B1178" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B1179" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B1180" t="s">
         <v>1676</v>
@@ -14954,36 +14960,36 @@
         <v>1677</v>
       </c>
       <c r="B1181" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1182" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B1183" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1184" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B1185" t="s">
         <v>1682</v>
@@ -14994,12 +15000,12 @@
         <v>1683</v>
       </c>
       <c r="B1186" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B1187" t="s">
         <v>1685</v>
@@ -15010,219 +15016,227 @@
         <v>1686</v>
       </c>
       <c r="B1188" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1189" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1190" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B1191" t="s">
-        <v>383</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B1192" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B1193" t="s">
-        <v>1691</v>
+        <v>385</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1194" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B1195" t="s">
-        <v>643</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
       <c r="A1196" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B1196" t="s">
-        <v>1694</v>
+        <v>643</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
       <c r="A1197" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1197" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1198" t="s">
-        <v>924</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
       <c r="A1199" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1199" t="s">
-        <v>1697</v>
+        <v>924</v>
       </c>
     </row>
     <row r="1200" spans="1:2">
       <c r="A1200" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1200" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1201" spans="1:2">
       <c r="A1201" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1201" t="s">
-        <v>1000</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
       <c r="A1202" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1202" t="s">
-        <v>1700</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="1203" spans="1:2">
       <c r="A1203" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1203" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1204" spans="1:2">
       <c r="A1204" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B1204" t="s">
-        <v>1068</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1205" spans="1:2">
       <c r="A1205" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B1205" t="s">
-        <v>1123</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="1206" spans="1:2">
       <c r="A1206" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B1206" t="s">
-        <v>1704</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="1207" spans="1:2">
       <c r="A1207" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B1207" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1208" spans="1:2">
       <c r="A1208" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1208" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="1209" spans="1:2">
       <c r="A1209" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1209" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1210" spans="1:2">
       <c r="A1210" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B1210" t="s">
-        <v>1426</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1211" spans="1:2">
       <c r="A1211" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B1211" t="s">
-        <v>1709</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="1212" spans="1:2">
       <c r="A1212" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B1212" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="1213" spans="1:2">
       <c r="A1213" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B1213" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1214" spans="1:2">
       <c r="A1214" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1214" t="s">
-        <v>1545</v>
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:2">
+      <c r="A1215" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B1215" t="s">
+        <v>1547</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1214"/>
+  <autoFilter ref="A1:B1215"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/da/headTags.xlsx
+++ b/lang/da/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1215</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1216</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1716">
   <si>
     <t>en</t>
   </si>
@@ -311,6 +311,9 @@
   </si>
   <si>
     <t>Baka og Test</t>
+  </si>
+  <si>
+    <t>Bakugan</t>
   </si>
   <si>
     <t>Baldi's Basics</t>
@@ -5508,7 +5511,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1215"/>
+  <dimension ref="A1:B1216"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -6072,12 +6075,12 @@
         <v>99</v>
       </c>
       <c r="B70" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B71" t="s">
         <v>101</v>
@@ -6112,12 +6115,12 @@
         <v>105</v>
       </c>
       <c r="B75" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B76" t="s">
         <v>107</v>
@@ -6128,20 +6131,20 @@
         <v>108</v>
       </c>
       <c r="B77" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
+        <v>109</v>
+      </c>
+      <c r="B78" t="s">
         <v>110</v>
-      </c>
-      <c r="B78" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B79" t="s">
         <v>112</v>
@@ -6152,12 +6155,12 @@
         <v>113</v>
       </c>
       <c r="B80" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B81" t="s">
         <v>115</v>
@@ -6168,28 +6171,28 @@
         <v>116</v>
       </c>
       <c r="B82" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
+        <v>117</v>
+      </c>
+      <c r="B83" t="s">
         <v>118</v>
-      </c>
-      <c r="B83" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" t="s">
+        <v>119</v>
+      </c>
+      <c r="B84" t="s">
         <v>120</v>
-      </c>
-      <c r="B84" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B85" t="s">
         <v>122</v>
@@ -6200,20 +6203,20 @@
         <v>123</v>
       </c>
       <c r="B86" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
+        <v>124</v>
+      </c>
+      <c r="B87" t="s">
         <v>125</v>
-      </c>
-      <c r="B87" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B88" t="s">
         <v>127</v>
@@ -6224,12 +6227,12 @@
         <v>128</v>
       </c>
       <c r="B89" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B90" t="s">
         <v>130</v>
@@ -6248,12 +6251,12 @@
         <v>132</v>
       </c>
       <c r="B92" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B93" t="s">
         <v>134</v>
@@ -6264,12 +6267,12 @@
         <v>135</v>
       </c>
       <c r="B94" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B95" t="s">
         <v>137</v>
@@ -6344,12 +6347,12 @@
         <v>146</v>
       </c>
       <c r="B104" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B105" t="s">
         <v>148</v>
@@ -6384,12 +6387,12 @@
         <v>152</v>
       </c>
       <c r="B109" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B110" t="s">
         <v>154</v>
@@ -6440,44 +6443,44 @@
         <v>160</v>
       </c>
       <c r="B116" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
+        <v>161</v>
+      </c>
+      <c r="B117" t="s">
         <v>162</v>
-      </c>
-      <c r="B117" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" t="s">
+        <v>163</v>
+      </c>
+      <c r="B118" t="s">
         <v>164</v>
-      </c>
-      <c r="B118" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" t="s">
+        <v>165</v>
+      </c>
+      <c r="B119" t="s">
         <v>166</v>
-      </c>
-      <c r="B119" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" t="s">
+        <v>167</v>
+      </c>
+      <c r="B120" t="s">
         <v>168</v>
-      </c>
-      <c r="B120" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B121" t="s">
         <v>170</v>
@@ -6584,20 +6587,20 @@
         <v>183</v>
       </c>
       <c r="B134" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
+        <v>184</v>
+      </c>
+      <c r="B135" t="s">
         <v>185</v>
-      </c>
-      <c r="B135" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="136" spans="1:2">
       <c r="A136" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B136" t="s">
         <v>187</v>
@@ -6616,12 +6619,12 @@
         <v>189</v>
       </c>
       <c r="B138" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B139" t="s">
         <v>191</v>
@@ -6640,20 +6643,20 @@
         <v>193</v>
       </c>
       <c r="B141" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
+        <v>194</v>
+      </c>
+      <c r="B142" t="s">
         <v>195</v>
-      </c>
-      <c r="B142" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="143" spans="1:2">
       <c r="A143" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B143" t="s">
         <v>197</v>
@@ -6672,36 +6675,36 @@
         <v>199</v>
       </c>
       <c r="B145" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
+        <v>200</v>
+      </c>
+      <c r="B146" t="s">
         <v>201</v>
-      </c>
-      <c r="B146" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="147" spans="1:2">
       <c r="A147" t="s">
+        <v>202</v>
+      </c>
+      <c r="B147" t="s">
         <v>203</v>
-      </c>
-      <c r="B147" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="148" spans="1:2">
       <c r="A148" t="s">
+        <v>204</v>
+      </c>
+      <c r="B148" t="s">
         <v>205</v>
-      </c>
-      <c r="B148" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="149" spans="1:2">
       <c r="A149" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B149" t="s">
         <v>207</v>
@@ -6736,52 +6739,52 @@
         <v>211</v>
       </c>
       <c r="B153" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
+        <v>212</v>
+      </c>
+      <c r="B154" t="s">
         <v>213</v>
-      </c>
-      <c r="B154" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="155" spans="1:2">
       <c r="A155" t="s">
+        <v>214</v>
+      </c>
+      <c r="B155" t="s">
         <v>215</v>
-      </c>
-      <c r="B155" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="156" spans="1:2">
       <c r="A156" t="s">
+        <v>216</v>
+      </c>
+      <c r="B156" t="s">
         <v>217</v>
-      </c>
-      <c r="B156" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="157" spans="1:2">
       <c r="A157" t="s">
+        <v>218</v>
+      </c>
+      <c r="B157" t="s">
         <v>219</v>
-      </c>
-      <c r="B157" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="158" spans="1:2">
       <c r="A158" t="s">
+        <v>220</v>
+      </c>
+      <c r="B158" t="s">
         <v>221</v>
-      </c>
-      <c r="B158" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="159" spans="1:2">
       <c r="A159" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B159" t="s">
         <v>223</v>
@@ -6792,92 +6795,92 @@
         <v>224</v>
       </c>
       <c r="B160" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
+        <v>225</v>
+      </c>
+      <c r="B161" t="s">
         <v>226</v>
-      </c>
-      <c r="B161" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="162" spans="1:2">
       <c r="A162" t="s">
+        <v>227</v>
+      </c>
+      <c r="B162" t="s">
         <v>228</v>
-      </c>
-      <c r="B162" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="163" spans="1:2">
       <c r="A163" t="s">
+        <v>229</v>
+      </c>
+      <c r="B163" t="s">
         <v>230</v>
-      </c>
-      <c r="B163" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="164" spans="1:2">
       <c r="A164" t="s">
+        <v>231</v>
+      </c>
+      <c r="B164" t="s">
         <v>232</v>
-      </c>
-      <c r="B164" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="165" spans="1:2">
       <c r="A165" t="s">
+        <v>233</v>
+      </c>
+      <c r="B165" t="s">
         <v>234</v>
-      </c>
-      <c r="B165" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="166" spans="1:2">
       <c r="A166" t="s">
+        <v>235</v>
+      </c>
+      <c r="B166" t="s">
         <v>236</v>
-      </c>
-      <c r="B166" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="167" spans="1:2">
       <c r="A167" t="s">
+        <v>237</v>
+      </c>
+      <c r="B167" t="s">
         <v>238</v>
-      </c>
-      <c r="B167" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="168" spans="1:2">
       <c r="A168" t="s">
+        <v>239</v>
+      </c>
+      <c r="B168" t="s">
         <v>240</v>
-      </c>
-      <c r="B168" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="169" spans="1:2">
       <c r="A169" t="s">
+        <v>241</v>
+      </c>
+      <c r="B169" t="s">
         <v>242</v>
-      </c>
-      <c r="B169" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="170" spans="1:2">
       <c r="A170" t="s">
+        <v>243</v>
+      </c>
+      <c r="B170" t="s">
         <v>244</v>
-      </c>
-      <c r="B170" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="171" spans="1:2">
       <c r="A171" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B171" t="s">
         <v>246</v>
@@ -6888,28 +6891,28 @@
         <v>247</v>
       </c>
       <c r="B172" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
+        <v>248</v>
+      </c>
+      <c r="B173" t="s">
         <v>249</v>
-      </c>
-      <c r="B173" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="174" spans="1:2">
       <c r="A174" t="s">
+        <v>250</v>
+      </c>
+      <c r="B174" t="s">
         <v>251</v>
-      </c>
-      <c r="B174" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="175" spans="1:2">
       <c r="A175" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B175" t="s">
         <v>253</v>
@@ -6944,12 +6947,12 @@
         <v>257</v>
       </c>
       <c r="B179" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B180" t="s">
         <v>259</v>
@@ -6968,15 +6971,15 @@
         <v>261</v>
       </c>
       <c r="B182" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
+        <v>262</v>
+      </c>
+      <c r="B183" t="s">
         <v>263</v>
-      </c>
-      <c r="B183" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="184" spans="1:2">
@@ -6984,7 +6987,7 @@
         <v>264</v>
       </c>
       <c r="B184" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="185" spans="1:2">
@@ -6992,20 +6995,20 @@
         <v>265</v>
       </c>
       <c r="B185" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
+        <v>266</v>
+      </c>
+      <c r="B186" t="s">
         <v>267</v>
-      </c>
-      <c r="B186" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="187" spans="1:2">
       <c r="A187" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B187" t="s">
         <v>269</v>
@@ -7024,28 +7027,28 @@
         <v>271</v>
       </c>
       <c r="B189" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
+        <v>272</v>
+      </c>
+      <c r="B190" t="s">
         <v>273</v>
-      </c>
-      <c r="B190" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="191" spans="1:2">
       <c r="A191" t="s">
+        <v>274</v>
+      </c>
+      <c r="B191" t="s">
         <v>275</v>
-      </c>
-      <c r="B191" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="192" spans="1:2">
       <c r="A192" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B192" t="s">
         <v>277</v>
@@ -7072,28 +7075,28 @@
         <v>280</v>
       </c>
       <c r="B195" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
+        <v>281</v>
+      </c>
+      <c r="B196" t="s">
         <v>282</v>
-      </c>
-      <c r="B196" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="197" spans="1:2">
       <c r="A197" t="s">
+        <v>283</v>
+      </c>
+      <c r="B197" t="s">
         <v>284</v>
-      </c>
-      <c r="B197" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="198" spans="1:2">
       <c r="A198" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B198" t="s">
         <v>286</v>
@@ -7128,20 +7131,20 @@
         <v>290</v>
       </c>
       <c r="B202" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
+        <v>291</v>
+      </c>
+      <c r="B203" t="s">
         <v>292</v>
-      </c>
-      <c r="B203" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="204" spans="1:2">
       <c r="A204" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B204" t="s">
         <v>294</v>
@@ -7160,20 +7163,20 @@
         <v>296</v>
       </c>
       <c r="B206" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
+        <v>297</v>
+      </c>
+      <c r="B207" t="s">
         <v>298</v>
-      </c>
-      <c r="B207" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="208" spans="1:2">
       <c r="A208" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B208" t="s">
         <v>300</v>
@@ -7192,68 +7195,68 @@
         <v>302</v>
       </c>
       <c r="B210" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
+        <v>303</v>
+      </c>
+      <c r="B211" t="s">
         <v>304</v>
-      </c>
-      <c r="B211" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="212" spans="1:2">
       <c r="A212" t="s">
+        <v>305</v>
+      </c>
+      <c r="B212" t="s">
         <v>306</v>
-      </c>
-      <c r="B212" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="213" spans="1:2">
       <c r="A213" t="s">
+        <v>307</v>
+      </c>
+      <c r="B213" t="s">
         <v>308</v>
-      </c>
-      <c r="B213" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="214" spans="1:2">
       <c r="A214" t="s">
+        <v>309</v>
+      </c>
+      <c r="B214" t="s">
         <v>310</v>
-      </c>
-      <c r="B214" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="215" spans="1:2">
       <c r="A215" t="s">
+        <v>311</v>
+      </c>
+      <c r="B215" t="s">
         <v>312</v>
-      </c>
-      <c r="B215" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="216" spans="1:2">
       <c r="A216" t="s">
+        <v>313</v>
+      </c>
+      <c r="B216" t="s">
         <v>314</v>
-      </c>
-      <c r="B216" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="217" spans="1:2">
       <c r="A217" t="s">
+        <v>315</v>
+      </c>
+      <c r="B217" t="s">
         <v>316</v>
-      </c>
-      <c r="B217" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="218" spans="1:2">
       <c r="A218" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B218" t="s">
         <v>318</v>
@@ -7264,12 +7267,12 @@
         <v>319</v>
       </c>
       <c r="B219" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B220" t="s">
         <v>321</v>
@@ -7304,12 +7307,12 @@
         <v>325</v>
       </c>
       <c r="B224" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B225" t="s">
         <v>327</v>
@@ -7344,20 +7347,20 @@
         <v>331</v>
       </c>
       <c r="B229" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
+        <v>332</v>
+      </c>
+      <c r="B230" t="s">
         <v>333</v>
-      </c>
-      <c r="B230" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="231" spans="1:2">
       <c r="A231" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B231" t="s">
         <v>335</v>
@@ -7408,44 +7411,44 @@
         <v>341</v>
       </c>
       <c r="B237" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
+        <v>342</v>
+      </c>
+      <c r="B238" t="s">
         <v>343</v>
-      </c>
-      <c r="B238" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="239" spans="1:2">
       <c r="A239" t="s">
+        <v>344</v>
+      </c>
+      <c r="B239" t="s">
         <v>345</v>
-      </c>
-      <c r="B239" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="240" spans="1:2">
       <c r="A240" t="s">
+        <v>346</v>
+      </c>
+      <c r="B240" t="s">
         <v>347</v>
-      </c>
-      <c r="B240" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="241" spans="1:2">
       <c r="A241" t="s">
+        <v>348</v>
+      </c>
+      <c r="B241" t="s">
         <v>349</v>
-      </c>
-      <c r="B241" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="242" spans="1:2">
       <c r="A242" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B242" t="s">
         <v>351</v>
@@ -7456,12 +7459,12 @@
         <v>352</v>
       </c>
       <c r="B243" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B244" t="s">
         <v>354</v>
@@ -7472,28 +7475,28 @@
         <v>355</v>
       </c>
       <c r="B245" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
+        <v>356</v>
+      </c>
+      <c r="B246" t="s">
         <v>357</v>
-      </c>
-      <c r="B246" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="247" spans="1:2">
       <c r="A247" t="s">
+        <v>358</v>
+      </c>
+      <c r="B247" t="s">
         <v>359</v>
-      </c>
-      <c r="B247" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="248" spans="1:2">
       <c r="A248" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B248" t="s">
         <v>361</v>
@@ -7504,20 +7507,20 @@
         <v>362</v>
       </c>
       <c r="B249" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
+        <v>363</v>
+      </c>
+      <c r="B250" t="s">
         <v>364</v>
-      </c>
-      <c r="B250" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="251" spans="1:2">
       <c r="A251" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B251" t="s">
         <v>366</v>
@@ -7584,52 +7587,52 @@
         <v>374</v>
       </c>
       <c r="B259" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
+        <v>375</v>
+      </c>
+      <c r="B260" t="s">
         <v>376</v>
-      </c>
-      <c r="B260" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
+        <v>377</v>
+      </c>
+      <c r="B261" t="s">
         <v>378</v>
-      </c>
-      <c r="B261" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="262" spans="1:2">
       <c r="A262" t="s">
+        <v>379</v>
+      </c>
+      <c r="B262" t="s">
         <v>380</v>
-      </c>
-      <c r="B262" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="263" spans="1:2">
       <c r="A263" t="s">
+        <v>381</v>
+      </c>
+      <c r="B263" t="s">
         <v>382</v>
-      </c>
-      <c r="B263" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="264" spans="1:2">
       <c r="A264" t="s">
+        <v>383</v>
+      </c>
+      <c r="B264" t="s">
         <v>384</v>
-      </c>
-      <c r="B264" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="265" spans="1:2">
       <c r="A265" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B265" t="s">
         <v>386</v>
@@ -7744,12 +7747,12 @@
         <v>400</v>
       </c>
       <c r="B279" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B280" t="s">
         <v>402</v>
@@ -7840,36 +7843,36 @@
         <v>413</v>
       </c>
       <c r="B291" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
+        <v>414</v>
+      </c>
+      <c r="B292" t="s">
         <v>415</v>
-      </c>
-      <c r="B292" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
+        <v>416</v>
+      </c>
+      <c r="B293" t="s">
         <v>417</v>
-      </c>
-      <c r="B293" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="294" spans="1:2">
       <c r="A294" t="s">
+        <v>418</v>
+      </c>
+      <c r="B294" t="s">
         <v>419</v>
-      </c>
-      <c r="B294" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="295" spans="1:2">
       <c r="A295" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B295" t="s">
         <v>421</v>
@@ -7888,36 +7891,36 @@
         <v>423</v>
       </c>
       <c r="B297" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
+        <v>424</v>
+      </c>
+      <c r="B298" t="s">
         <v>425</v>
-      </c>
-      <c r="B298" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
+        <v>426</v>
+      </c>
+      <c r="B299" t="s">
         <v>427</v>
-      </c>
-      <c r="B299" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="300" spans="1:2">
       <c r="A300" t="s">
+        <v>428</v>
+      </c>
+      <c r="B300" t="s">
         <v>429</v>
-      </c>
-      <c r="B300" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="301" spans="1:2">
       <c r="A301" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B301" t="s">
         <v>431</v>
@@ -7928,12 +7931,12 @@
         <v>432</v>
       </c>
       <c r="B302" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B303" t="s">
         <v>434</v>
@@ -7944,36 +7947,36 @@
         <v>435</v>
       </c>
       <c r="B304" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
+        <v>436</v>
+      </c>
+      <c r="B305" t="s">
         <v>437</v>
-      </c>
-      <c r="B305" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
+        <v>438</v>
+      </c>
+      <c r="B306" t="s">
         <v>439</v>
-      </c>
-      <c r="B306" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="307" spans="1:2">
       <c r="A307" t="s">
+        <v>440</v>
+      </c>
+      <c r="B307" t="s">
         <v>441</v>
-      </c>
-      <c r="B307" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="308" spans="1:2">
       <c r="A308" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B308" t="s">
         <v>443</v>
@@ -8000,20 +8003,20 @@
         <v>446</v>
       </c>
       <c r="B311" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
+        <v>447</v>
+      </c>
+      <c r="B312" t="s">
         <v>448</v>
-      </c>
-      <c r="B312" t="s">
-        <v>449</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B313" t="s">
         <v>450</v>
@@ -8032,28 +8035,28 @@
         <v>452</v>
       </c>
       <c r="B315" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
+        <v>453</v>
+      </c>
+      <c r="B316" t="s">
         <v>454</v>
-      </c>
-      <c r="B316" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="317" spans="1:2">
       <c r="A317" t="s">
+        <v>455</v>
+      </c>
+      <c r="B317" t="s">
         <v>456</v>
-      </c>
-      <c r="B317" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="318" spans="1:2">
       <c r="A318" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B318" t="s">
         <v>458</v>
@@ -8072,12 +8075,12 @@
         <v>460</v>
       </c>
       <c r="B320" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B321" t="s">
         <v>462</v>
@@ -8096,12 +8099,12 @@
         <v>464</v>
       </c>
       <c r="B323" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B324" t="s">
         <v>466</v>
@@ -8184,52 +8187,52 @@
         <v>476</v>
       </c>
       <c r="B334" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
+        <v>477</v>
+      </c>
+      <c r="B335" t="s">
         <v>478</v>
-      </c>
-      <c r="B335" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
+        <v>479</v>
+      </c>
+      <c r="B336" t="s">
         <v>480</v>
-      </c>
-      <c r="B336" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
+        <v>481</v>
+      </c>
+      <c r="B337" t="s">
         <v>482</v>
-      </c>
-      <c r="B337" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="A338" t="s">
+        <v>483</v>
+      </c>
+      <c r="B338" t="s">
         <v>484</v>
-      </c>
-      <c r="B338" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="A339" t="s">
+        <v>485</v>
+      </c>
+      <c r="B339" t="s">
         <v>486</v>
-      </c>
-      <c r="B339" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B340" t="s">
         <v>488</v>
@@ -8264,12 +8267,12 @@
         <v>492</v>
       </c>
       <c r="B344" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B345" t="s">
         <v>494</v>
@@ -8296,100 +8299,100 @@
         <v>497</v>
       </c>
       <c r="B348" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="349" spans="1:2">
       <c r="A349" t="s">
+        <v>498</v>
+      </c>
+      <c r="B349" t="s">
         <v>499</v>
-      </c>
-      <c r="B349" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
+        <v>500</v>
+      </c>
+      <c r="B350" t="s">
         <v>501</v>
-      </c>
-      <c r="B350" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="A351" t="s">
+        <v>502</v>
+      </c>
+      <c r="B351" t="s">
         <v>503</v>
-      </c>
-      <c r="B351" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="352" spans="1:2">
       <c r="A352" t="s">
+        <v>504</v>
+      </c>
+      <c r="B352" t="s">
         <v>505</v>
-      </c>
-      <c r="B352" t="s">
-        <v>506</v>
       </c>
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
+        <v>506</v>
+      </c>
+      <c r="B353" t="s">
         <v>507</v>
-      </c>
-      <c r="B353" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
+        <v>508</v>
+      </c>
+      <c r="B354" t="s">
         <v>509</v>
-      </c>
-      <c r="B354" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="355" spans="1:2">
       <c r="A355" t="s">
+        <v>510</v>
+      </c>
+      <c r="B355" t="s">
         <v>511</v>
-      </c>
-      <c r="B355" t="s">
-        <v>512</v>
       </c>
     </row>
     <row r="356" spans="1:2">
       <c r="A356" t="s">
+        <v>512</v>
+      </c>
+      <c r="B356" t="s">
         <v>513</v>
-      </c>
-      <c r="B356" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
+        <v>514</v>
+      </c>
+      <c r="B357" t="s">
         <v>515</v>
-      </c>
-      <c r="B357" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
+        <v>516</v>
+      </c>
+      <c r="B358" t="s">
         <v>517</v>
-      </c>
-      <c r="B358" t="s">
-        <v>518</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
+        <v>518</v>
+      </c>
+      <c r="B359" t="s">
         <v>519</v>
-      </c>
-      <c r="B359" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B360" t="s">
         <v>521</v>
@@ -8400,20 +8403,20 @@
         <v>522</v>
       </c>
       <c r="B361" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="362" spans="1:2">
       <c r="A362" t="s">
+        <v>523</v>
+      </c>
+      <c r="B362" t="s">
         <v>524</v>
-      </c>
-      <c r="B362" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B363" t="s">
         <v>526</v>
@@ -8432,20 +8435,20 @@
         <v>528</v>
       </c>
       <c r="B365" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" t="s">
+        <v>529</v>
+      </c>
+      <c r="B366" t="s">
         <v>530</v>
-      </c>
-      <c r="B366" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B367" t="s">
         <v>532</v>
@@ -8464,44 +8467,44 @@
         <v>534</v>
       </c>
       <c r="B369" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="370" spans="1:2">
       <c r="A370" t="s">
+        <v>535</v>
+      </c>
+      <c r="B370" t="s">
         <v>536</v>
-      </c>
-      <c r="B370" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" t="s">
+        <v>537</v>
+      </c>
+      <c r="B371" t="s">
         <v>538</v>
-      </c>
-      <c r="B371" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="372" spans="1:2">
       <c r="A372" t="s">
+        <v>539</v>
+      </c>
+      <c r="B372" t="s">
         <v>540</v>
-      </c>
-      <c r="B372" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="373" spans="1:2">
       <c r="A373" t="s">
+        <v>541</v>
+      </c>
+      <c r="B373" t="s">
         <v>542</v>
-      </c>
-      <c r="B373" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="374" spans="1:2">
       <c r="A374" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B374" t="s">
         <v>544</v>
@@ -8512,28 +8515,28 @@
         <v>545</v>
       </c>
       <c r="B375" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="376" spans="1:2">
       <c r="A376" t="s">
+        <v>546</v>
+      </c>
+      <c r="B376" t="s">
         <v>547</v>
-      </c>
-      <c r="B376" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="377" spans="1:2">
       <c r="A377" t="s">
+        <v>548</v>
+      </c>
+      <c r="B377" t="s">
         <v>549</v>
-      </c>
-      <c r="B377" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="378" spans="1:2">
       <c r="A378" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B378" t="s">
         <v>551</v>
@@ -8544,28 +8547,28 @@
         <v>552</v>
       </c>
       <c r="B379" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="380" spans="1:2">
       <c r="A380" t="s">
+        <v>553</v>
+      </c>
+      <c r="B380" t="s">
         <v>554</v>
-      </c>
-      <c r="B380" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" t="s">
+        <v>555</v>
+      </c>
+      <c r="B381" t="s">
         <v>556</v>
-      </c>
-      <c r="B381" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B382" t="s">
         <v>558</v>
@@ -8608,20 +8611,20 @@
         <v>563</v>
       </c>
       <c r="B387" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="388" spans="1:2">
       <c r="A388" t="s">
+        <v>564</v>
+      </c>
+      <c r="B388" t="s">
         <v>565</v>
-      </c>
-      <c r="B388" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B389" t="s">
         <v>567</v>
@@ -8632,12 +8635,12 @@
         <v>568</v>
       </c>
       <c r="B390" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="391" spans="1:2">
       <c r="A391" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B391" t="s">
         <v>570</v>
@@ -8656,28 +8659,28 @@
         <v>572</v>
       </c>
       <c r="B393" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="394" spans="1:2">
       <c r="A394" t="s">
+        <v>573</v>
+      </c>
+      <c r="B394" t="s">
         <v>574</v>
-      </c>
-      <c r="B394" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
+        <v>575</v>
+      </c>
+      <c r="B395" t="s">
         <v>576</v>
-      </c>
-      <c r="B395" t="s">
-        <v>577</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B396" t="s">
         <v>578</v>
@@ -8712,36 +8715,36 @@
         <v>582</v>
       </c>
       <c r="B400" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" t="s">
+        <v>583</v>
+      </c>
+      <c r="B401" t="s">
         <v>584</v>
-      </c>
-      <c r="B401" t="s">
-        <v>585</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
+        <v>585</v>
+      </c>
+      <c r="B402" t="s">
         <v>586</v>
-      </c>
-      <c r="B402" t="s">
-        <v>587</v>
       </c>
     </row>
     <row r="403" spans="1:2">
       <c r="A403" t="s">
+        <v>587</v>
+      </c>
+      <c r="B403" t="s">
         <v>588</v>
-      </c>
-      <c r="B403" t="s">
-        <v>589</v>
       </c>
     </row>
     <row r="404" spans="1:2">
       <c r="A404" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B404" t="s">
         <v>590</v>
@@ -8752,20 +8755,20 @@
         <v>591</v>
       </c>
       <c r="B405" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="406" spans="1:2">
       <c r="A406" t="s">
+        <v>592</v>
+      </c>
+      <c r="B406" t="s">
         <v>593</v>
-      </c>
-      <c r="B406" t="s">
-        <v>594</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B407" t="s">
         <v>595</v>
@@ -8784,12 +8787,12 @@
         <v>597</v>
       </c>
       <c r="B409" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="410" spans="1:2">
       <c r="A410" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B410" t="s">
         <v>599</v>
@@ -8816,20 +8819,20 @@
         <v>602</v>
       </c>
       <c r="B413" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
     </row>
     <row r="414" spans="1:2">
       <c r="A414" t="s">
+        <v>603</v>
+      </c>
+      <c r="B414" t="s">
         <v>604</v>
-      </c>
-      <c r="B414" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B415" t="s">
         <v>606</v>
@@ -8848,124 +8851,124 @@
         <v>608</v>
       </c>
       <c r="B417" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" t="s">
+        <v>609</v>
+      </c>
+      <c r="B418" t="s">
         <v>610</v>
-      </c>
-      <c r="B418" t="s">
-        <v>611</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" t="s">
+        <v>611</v>
+      </c>
+      <c r="B419" t="s">
         <v>612</v>
-      </c>
-      <c r="B419" t="s">
-        <v>613</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" t="s">
+        <v>613</v>
+      </c>
+      <c r="B420" t="s">
         <v>614</v>
-      </c>
-      <c r="B420" t="s">
-        <v>615</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" t="s">
+        <v>615</v>
+      </c>
+      <c r="B421" t="s">
         <v>616</v>
-      </c>
-      <c r="B421" t="s">
-        <v>617</v>
       </c>
     </row>
     <row r="422" spans="1:2">
       <c r="A422" t="s">
+        <v>617</v>
+      </c>
+      <c r="B422" t="s">
         <v>618</v>
-      </c>
-      <c r="B422" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="423" spans="1:2">
       <c r="A423" t="s">
+        <v>619</v>
+      </c>
+      <c r="B423" t="s">
         <v>620</v>
-      </c>
-      <c r="B423" t="s">
-        <v>621</v>
       </c>
     </row>
     <row r="424" spans="1:2">
       <c r="A424" t="s">
+        <v>621</v>
+      </c>
+      <c r="B424" t="s">
         <v>622</v>
-      </c>
-      <c r="B424" t="s">
-        <v>623</v>
       </c>
     </row>
     <row r="425" spans="1:2">
       <c r="A425" t="s">
+        <v>623</v>
+      </c>
+      <c r="B425" t="s">
         <v>624</v>
-      </c>
-      <c r="B425" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="426" spans="1:2">
       <c r="A426" t="s">
+        <v>625</v>
+      </c>
+      <c r="B426" t="s">
         <v>626</v>
-      </c>
-      <c r="B426" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="427" spans="1:2">
       <c r="A427" t="s">
+        <v>627</v>
+      </c>
+      <c r="B427" t="s">
         <v>628</v>
-      </c>
-      <c r="B427" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="428" spans="1:2">
       <c r="A428" t="s">
+        <v>629</v>
+      </c>
+      <c r="B428" t="s">
         <v>630</v>
-      </c>
-      <c r="B428" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="429" spans="1:2">
       <c r="A429" t="s">
+        <v>631</v>
+      </c>
+      <c r="B429" t="s">
         <v>632</v>
-      </c>
-      <c r="B429" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="430" spans="1:2">
       <c r="A430" t="s">
+        <v>633</v>
+      </c>
+      <c r="B430" t="s">
         <v>634</v>
-      </c>
-      <c r="B430" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="431" spans="1:2">
       <c r="A431" t="s">
+        <v>635</v>
+      </c>
+      <c r="B431" t="s">
         <v>636</v>
-      </c>
-      <c r="B431" t="s">
-        <v>637</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B432" t="s">
         <v>638</v>
@@ -9000,12 +9003,12 @@
         <v>642</v>
       </c>
       <c r="B436" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B437" t="s">
         <v>644</v>
@@ -9016,12 +9019,12 @@
         <v>645</v>
       </c>
       <c r="B438" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="B439" t="s">
         <v>647</v>
@@ -9040,12 +9043,12 @@
         <v>649</v>
       </c>
       <c r="B441" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B442" t="s">
         <v>651</v>
@@ -9064,28 +9067,28 @@
         <v>653</v>
       </c>
       <c r="B444" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
     </row>
     <row r="445" spans="1:2">
       <c r="A445" t="s">
+        <v>654</v>
+      </c>
+      <c r="B445" t="s">
         <v>655</v>
-      </c>
-      <c r="B445" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="446" spans="1:2">
       <c r="A446" t="s">
+        <v>656</v>
+      </c>
+      <c r="B446" t="s">
         <v>657</v>
-      </c>
-      <c r="B446" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B447" t="s">
         <v>659</v>
@@ -9096,12 +9099,12 @@
         <v>660</v>
       </c>
       <c r="B448" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
     </row>
     <row r="449" spans="1:2">
       <c r="A449" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B449" t="s">
         <v>662</v>
@@ -9128,20 +9131,20 @@
         <v>665</v>
       </c>
       <c r="B452" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="453" spans="1:2">
       <c r="A453" t="s">
+        <v>666</v>
+      </c>
+      <c r="B453" t="s">
         <v>667</v>
-      </c>
-      <c r="B453" t="s">
-        <v>668</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="B454" t="s">
         <v>669</v>
@@ -9160,12 +9163,12 @@
         <v>671</v>
       </c>
       <c r="B456" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B457" t="s">
         <v>673</v>
@@ -9184,36 +9187,36 @@
         <v>675</v>
       </c>
       <c r="B459" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="460" spans="1:2">
       <c r="A460" t="s">
+        <v>676</v>
+      </c>
+      <c r="B460" t="s">
         <v>677</v>
-      </c>
-      <c r="B460" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="461" spans="1:2">
       <c r="A461" t="s">
+        <v>678</v>
+      </c>
+      <c r="B461" t="s">
         <v>679</v>
-      </c>
-      <c r="B461" t="s">
-        <v>680</v>
       </c>
     </row>
     <row r="462" spans="1:2">
       <c r="A462" t="s">
+        <v>680</v>
+      </c>
+      <c r="B462" t="s">
         <v>681</v>
-      </c>
-      <c r="B462" t="s">
-        <v>682</v>
       </c>
     </row>
     <row r="463" spans="1:2">
       <c r="A463" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B463" t="s">
         <v>683</v>
@@ -9240,12 +9243,12 @@
         <v>686</v>
       </c>
       <c r="B466" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B467" t="s">
         <v>688</v>
@@ -9256,12 +9259,12 @@
         <v>689</v>
       </c>
       <c r="B468" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B469" t="s">
         <v>691</v>
@@ -9280,12 +9283,12 @@
         <v>693</v>
       </c>
       <c r="B471" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B472" t="s">
         <v>695</v>
@@ -9296,7 +9299,7 @@
         <v>696</v>
       </c>
       <c r="B473" t="s">
-        <v>687</v>
+        <v>696</v>
       </c>
     </row>
     <row r="474" spans="1:2">
@@ -9304,7 +9307,7 @@
         <v>697</v>
       </c>
       <c r="B474" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -9336,20 +9339,20 @@
         <v>701</v>
       </c>
       <c r="B478" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
+        <v>702</v>
+      </c>
+      <c r="B479" t="s">
         <v>703</v>
-      </c>
-      <c r="B479" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B480" t="s">
         <v>705</v>
@@ -9360,12 +9363,12 @@
         <v>706</v>
       </c>
       <c r="B481" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B482" t="s">
         <v>708</v>
@@ -9376,12 +9379,12 @@
         <v>709</v>
       </c>
       <c r="B483" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B484" t="s">
         <v>711</v>
@@ -9400,12 +9403,12 @@
         <v>713</v>
       </c>
       <c r="B486" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B487" t="s">
         <v>715</v>
@@ -9440,156 +9443,156 @@
         <v>719</v>
       </c>
       <c r="B491" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
+        <v>720</v>
+      </c>
+      <c r="B492" t="s">
         <v>721</v>
-      </c>
-      <c r="B492" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
+        <v>722</v>
+      </c>
+      <c r="B493" t="s">
         <v>723</v>
-      </c>
-      <c r="B493" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
+        <v>724</v>
+      </c>
+      <c r="B494" t="s">
         <v>725</v>
-      </c>
-      <c r="B494" t="s">
-        <v>726</v>
       </c>
     </row>
     <row r="495" spans="1:2">
       <c r="A495" t="s">
+        <v>726</v>
+      </c>
+      <c r="B495" t="s">
         <v>727</v>
-      </c>
-      <c r="B495" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="496" spans="1:2">
       <c r="A496" t="s">
+        <v>728</v>
+      </c>
+      <c r="B496" t="s">
         <v>729</v>
-      </c>
-      <c r="B496" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="497" spans="1:2">
       <c r="A497" t="s">
+        <v>730</v>
+      </c>
+      <c r="B497" t="s">
         <v>731</v>
-      </c>
-      <c r="B497" t="s">
-        <v>732</v>
       </c>
     </row>
     <row r="498" spans="1:2">
       <c r="A498" t="s">
+        <v>732</v>
+      </c>
+      <c r="B498" t="s">
         <v>733</v>
-      </c>
-      <c r="B498" t="s">
-        <v>734</v>
       </c>
     </row>
     <row r="499" spans="1:2">
       <c r="A499" t="s">
+        <v>734</v>
+      </c>
+      <c r="B499" t="s">
         <v>735</v>
-      </c>
-      <c r="B499" t="s">
-        <v>736</v>
       </c>
     </row>
     <row r="500" spans="1:2">
       <c r="A500" t="s">
+        <v>736</v>
+      </c>
+      <c r="B500" t="s">
         <v>737</v>
-      </c>
-      <c r="B500" t="s">
-        <v>738</v>
       </c>
     </row>
     <row r="501" spans="1:2">
       <c r="A501" t="s">
+        <v>738</v>
+      </c>
+      <c r="B501" t="s">
         <v>739</v>
-      </c>
-      <c r="B501" t="s">
-        <v>740</v>
       </c>
     </row>
     <row r="502" spans="1:2">
       <c r="A502" t="s">
+        <v>740</v>
+      </c>
+      <c r="B502" t="s">
         <v>741</v>
-      </c>
-      <c r="B502" t="s">
-        <v>742</v>
       </c>
     </row>
     <row r="503" spans="1:2">
       <c r="A503" t="s">
+        <v>742</v>
+      </c>
+      <c r="B503" t="s">
         <v>743</v>
-      </c>
-      <c r="B503" t="s">
-        <v>744</v>
       </c>
     </row>
     <row r="504" spans="1:2">
       <c r="A504" t="s">
+        <v>744</v>
+      </c>
+      <c r="B504" t="s">
         <v>745</v>
-      </c>
-      <c r="B504" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="505" spans="1:2">
       <c r="A505" t="s">
+        <v>746</v>
+      </c>
+      <c r="B505" t="s">
         <v>747</v>
-      </c>
-      <c r="B505" t="s">
-        <v>748</v>
       </c>
     </row>
     <row r="506" spans="1:2">
       <c r="A506" t="s">
+        <v>748</v>
+      </c>
+      <c r="B506" t="s">
         <v>749</v>
-      </c>
-      <c r="B506" t="s">
-        <v>750</v>
       </c>
     </row>
     <row r="507" spans="1:2">
       <c r="A507" t="s">
+        <v>750</v>
+      </c>
+      <c r="B507" t="s">
         <v>751</v>
-      </c>
-      <c r="B507" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="508" spans="1:2">
       <c r="A508" t="s">
+        <v>752</v>
+      </c>
+      <c r="B508" t="s">
         <v>753</v>
-      </c>
-      <c r="B508" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="509" spans="1:2">
       <c r="A509" t="s">
+        <v>754</v>
+      </c>
+      <c r="B509" t="s">
         <v>755</v>
-      </c>
-      <c r="B509" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="510" spans="1:2">
       <c r="A510" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B510" t="s">
         <v>757</v>
@@ -9600,15 +9603,15 @@
         <v>758</v>
       </c>
       <c r="B511" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="512" spans="1:2">
       <c r="A512" t="s">
+        <v>759</v>
+      </c>
+      <c r="B512" t="s">
         <v>760</v>
-      </c>
-      <c r="B512" t="s">
-        <v>759</v>
       </c>
     </row>
     <row r="513" spans="1:2">
@@ -9616,7 +9619,7 @@
         <v>761</v>
       </c>
       <c r="B513" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -9624,12 +9627,12 @@
         <v>762</v>
       </c>
       <c r="B514" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B515" t="s">
         <v>764</v>
@@ -9640,36 +9643,36 @@
         <v>765</v>
       </c>
       <c r="B516" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
+        <v>766</v>
+      </c>
+      <c r="B517" t="s">
         <v>767</v>
-      </c>
-      <c r="B517" t="s">
-        <v>768</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
+        <v>768</v>
+      </c>
+      <c r="B518" t="s">
         <v>769</v>
-      </c>
-      <c r="B518" t="s">
-        <v>770</v>
       </c>
     </row>
     <row r="519" spans="1:2">
       <c r="A519" t="s">
+        <v>770</v>
+      </c>
+      <c r="B519" t="s">
         <v>771</v>
-      </c>
-      <c r="B519" t="s">
-        <v>772</v>
       </c>
     </row>
     <row r="520" spans="1:2">
       <c r="A520" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B520" t="s">
         <v>773</v>
@@ -9680,12 +9683,12 @@
         <v>774</v>
       </c>
       <c r="B521" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="522" spans="1:2">
       <c r="A522" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B522" t="s">
         <v>776</v>
@@ -9696,20 +9699,20 @@
         <v>777</v>
       </c>
       <c r="B523" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
+        <v>778</v>
+      </c>
+      <c r="B524" t="s">
         <v>779</v>
-      </c>
-      <c r="B524" t="s">
-        <v>780</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B525" t="s">
         <v>781</v>
@@ -9720,52 +9723,52 @@
         <v>782</v>
       </c>
       <c r="B526" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="527" spans="1:2">
       <c r="A527" t="s">
+        <v>783</v>
+      </c>
+      <c r="B527" t="s">
         <v>784</v>
-      </c>
-      <c r="B527" t="s">
-        <v>785</v>
       </c>
     </row>
     <row r="528" spans="1:2">
       <c r="A528" t="s">
+        <v>785</v>
+      </c>
+      <c r="B528" t="s">
         <v>786</v>
-      </c>
-      <c r="B528" t="s">
-        <v>787</v>
       </c>
     </row>
     <row r="529" spans="1:2">
       <c r="A529" t="s">
+        <v>787</v>
+      </c>
+      <c r="B529" t="s">
         <v>788</v>
-      </c>
-      <c r="B529" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" t="s">
+        <v>789</v>
+      </c>
+      <c r="B530" t="s">
         <v>790</v>
-      </c>
-      <c r="B530" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="531" spans="1:2">
       <c r="A531" t="s">
+        <v>791</v>
+      </c>
+      <c r="B531" t="s">
         <v>792</v>
-      </c>
-      <c r="B531" t="s">
-        <v>793</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="B532" t="s">
         <v>794</v>
@@ -9776,20 +9779,20 @@
         <v>795</v>
       </c>
       <c r="B533" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="534" spans="1:2">
       <c r="A534" t="s">
+        <v>796</v>
+      </c>
+      <c r="B534" t="s">
         <v>797</v>
-      </c>
-      <c r="B534" t="s">
-        <v>798</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B535" t="s">
         <v>799</v>
@@ -9872,12 +9875,12 @@
         <v>809</v>
       </c>
       <c r="B545" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B546" t="s">
         <v>811</v>
@@ -9896,12 +9899,12 @@
         <v>813</v>
       </c>
       <c r="B548" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B549" t="s">
         <v>815</v>
@@ -9968,52 +9971,52 @@
         <v>823</v>
       </c>
       <c r="B557" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
+        <v>824</v>
+      </c>
+      <c r="B558" t="s">
         <v>825</v>
-      </c>
-      <c r="B558" t="s">
-        <v>826</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
+        <v>826</v>
+      </c>
+      <c r="B559" t="s">
         <v>827</v>
-      </c>
-      <c r="B559" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
+        <v>828</v>
+      </c>
+      <c r="B560" t="s">
         <v>829</v>
-      </c>
-      <c r="B560" t="s">
-        <v>830</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" t="s">
+        <v>830</v>
+      </c>
+      <c r="B561" t="s">
         <v>831</v>
-      </c>
-      <c r="B561" t="s">
-        <v>832</v>
       </c>
     </row>
     <row r="562" spans="1:2">
       <c r="A562" t="s">
+        <v>832</v>
+      </c>
+      <c r="B562" t="s">
         <v>833</v>
-      </c>
-      <c r="B562" t="s">
-        <v>834</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B563" t="s">
         <v>835</v>
@@ -10040,12 +10043,12 @@
         <v>838</v>
       </c>
       <c r="B566" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B567" t="s">
         <v>840</v>
@@ -10064,12 +10067,12 @@
         <v>842</v>
       </c>
       <c r="B569" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="B570" t="s">
         <v>844</v>
@@ -10088,20 +10091,20 @@
         <v>846</v>
       </c>
       <c r="B572" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
+        <v>847</v>
+      </c>
+      <c r="B573" t="s">
         <v>848</v>
-      </c>
-      <c r="B573" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B574" t="s">
         <v>850</v>
@@ -10160,20 +10163,20 @@
         <v>857</v>
       </c>
       <c r="B581" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
+        <v>858</v>
+      </c>
+      <c r="B582" t="s">
         <v>859</v>
-      </c>
-      <c r="B582" t="s">
-        <v>860</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B583" t="s">
         <v>861</v>
@@ -10192,12 +10195,12 @@
         <v>863</v>
       </c>
       <c r="B585" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="B586" t="s">
         <v>865</v>
@@ -10208,12 +10211,12 @@
         <v>866</v>
       </c>
       <c r="B587" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B588" t="s">
         <v>868</v>
@@ -10224,20 +10227,20 @@
         <v>869</v>
       </c>
       <c r="B589" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
+        <v>870</v>
+      </c>
+      <c r="B590" t="s">
         <v>871</v>
-      </c>
-      <c r="B590" t="s">
-        <v>872</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B591" t="s">
         <v>873</v>
@@ -10248,20 +10251,20 @@
         <v>874</v>
       </c>
       <c r="B592" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
+        <v>875</v>
+      </c>
+      <c r="B593" t="s">
         <v>876</v>
-      </c>
-      <c r="B593" t="s">
-        <v>877</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B594" t="s">
         <v>878</v>
@@ -10272,28 +10275,28 @@
         <v>879</v>
       </c>
       <c r="B595" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
+        <v>880</v>
+      </c>
+      <c r="B596" t="s">
         <v>881</v>
-      </c>
-      <c r="B596" t="s">
-        <v>882</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
+        <v>882</v>
+      </c>
+      <c r="B597" t="s">
         <v>883</v>
-      </c>
-      <c r="B597" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B598" t="s">
         <v>885</v>
@@ -10328,44 +10331,44 @@
         <v>889</v>
       </c>
       <c r="B602" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
+        <v>890</v>
+      </c>
+      <c r="B603" t="s">
         <v>891</v>
-      </c>
-      <c r="B603" t="s">
-        <v>892</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
+        <v>892</v>
+      </c>
+      <c r="B604" t="s">
         <v>893</v>
-      </c>
-      <c r="B604" t="s">
-        <v>894</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
+        <v>894</v>
+      </c>
+      <c r="B605" t="s">
         <v>895</v>
-      </c>
-      <c r="B605" t="s">
-        <v>896</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
+        <v>896</v>
+      </c>
+      <c r="B606" t="s">
         <v>897</v>
-      </c>
-      <c r="B606" t="s">
-        <v>898</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B607" t="s">
         <v>899</v>
@@ -10384,12 +10387,12 @@
         <v>901</v>
       </c>
       <c r="B609" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B610" t="s">
         <v>903</v>
@@ -10432,12 +10435,12 @@
         <v>908</v>
       </c>
       <c r="B615" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="B616" t="s">
         <v>910</v>
@@ -10480,20 +10483,20 @@
         <v>915</v>
       </c>
       <c r="B621" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
+        <v>916</v>
+      </c>
+      <c r="B622" t="s">
         <v>917</v>
-      </c>
-      <c r="B622" t="s">
-        <v>918</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B623" t="s">
         <v>919</v>
@@ -10504,12 +10507,12 @@
         <v>920</v>
       </c>
       <c r="B624" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B625" t="s">
         <v>922</v>
@@ -10520,12 +10523,12 @@
         <v>923</v>
       </c>
       <c r="B626" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B627" t="s">
         <v>925</v>
@@ -10712,36 +10715,36 @@
         <v>948</v>
       </c>
       <c r="B650" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
+        <v>949</v>
+      </c>
+      <c r="B651" t="s">
         <v>950</v>
-      </c>
-      <c r="B651" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
+        <v>951</v>
+      </c>
+      <c r="B652" t="s">
         <v>952</v>
-      </c>
-      <c r="B652" t="s">
-        <v>953</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
+        <v>953</v>
+      </c>
+      <c r="B653" t="s">
         <v>954</v>
-      </c>
-      <c r="B653" t="s">
-        <v>955</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B654" t="s">
         <v>956</v>
@@ -10768,12 +10771,12 @@
         <v>959</v>
       </c>
       <c r="B657" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="B658" t="s">
         <v>961</v>
@@ -10792,12 +10795,12 @@
         <v>963</v>
       </c>
       <c r="B660" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="B661" t="s">
         <v>965</v>
@@ -10840,12 +10843,12 @@
         <v>970</v>
       </c>
       <c r="B666" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="B667" t="s">
         <v>972</v>
@@ -10896,12 +10899,12 @@
         <v>978</v>
       </c>
       <c r="B673" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="B674" t="s">
         <v>980</v>
@@ -10912,20 +10915,20 @@
         <v>981</v>
       </c>
       <c r="B675" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
+        <v>982</v>
+      </c>
+      <c r="B676" t="s">
         <v>983</v>
-      </c>
-      <c r="B676" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="B677" t="s">
         <v>985</v>
@@ -10992,20 +10995,20 @@
         <v>993</v>
       </c>
       <c r="B685" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
+        <v>994</v>
+      </c>
+      <c r="B686" t="s">
         <v>995</v>
-      </c>
-      <c r="B686" t="s">
-        <v>996</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="B687" t="s">
         <v>997</v>
@@ -11024,20 +11027,20 @@
         <v>999</v>
       </c>
       <c r="B689" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B690" t="s">
         <v>1001</v>
-      </c>
-      <c r="B690" t="s">
-        <v>1002</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="B691" t="s">
         <v>1003</v>
@@ -11048,36 +11051,36 @@
         <v>1004</v>
       </c>
       <c r="B692" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B693" t="s">
         <v>1006</v>
-      </c>
-      <c r="B693" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="694" spans="1:2">
       <c r="A694" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B694" t="s">
         <v>1008</v>
-      </c>
-      <c r="B694" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="695" spans="1:2">
       <c r="A695" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B695" t="s">
         <v>1010</v>
-      </c>
-      <c r="B695" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="696" spans="1:2">
       <c r="A696" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="B696" t="s">
         <v>1012</v>
@@ -11088,20 +11091,20 @@
         <v>1013</v>
       </c>
       <c r="B697" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="698" spans="1:2">
       <c r="A698" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B698" t="s">
         <v>1015</v>
-      </c>
-      <c r="B698" t="s">
-        <v>1016</v>
       </c>
     </row>
     <row r="699" spans="1:2">
       <c r="A699" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="B699" t="s">
         <v>1017</v>
@@ -11112,44 +11115,44 @@
         <v>1018</v>
       </c>
       <c r="B700" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B701" t="s">
         <v>1020</v>
-      </c>
-      <c r="B701" t="s">
-        <v>1021</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B702" t="s">
         <v>1022</v>
-      </c>
-      <c r="B702" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B703" t="s">
         <v>1024</v>
-      </c>
-      <c r="B703" t="s">
-        <v>1025</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B704" t="s">
         <v>1026</v>
-      </c>
-      <c r="B704" t="s">
-        <v>1027</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="B705" t="s">
         <v>1028</v>
@@ -11184,12 +11187,12 @@
         <v>1032</v>
       </c>
       <c r="B709" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="B710" t="s">
         <v>1034</v>
@@ -11264,20 +11267,20 @@
         <v>1043</v>
       </c>
       <c r="B719" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B720" t="s">
         <v>1045</v>
-      </c>
-      <c r="B720" t="s">
-        <v>1046</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="B721" t="s">
         <v>1047</v>
@@ -11296,12 +11299,12 @@
         <v>1049</v>
       </c>
       <c r="B723" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="B724" t="s">
         <v>1051</v>
@@ -11312,12 +11315,12 @@
         <v>1052</v>
       </c>
       <c r="B725" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="B726" t="s">
         <v>1054</v>
@@ -11328,12 +11331,12 @@
         <v>1055</v>
       </c>
       <c r="B727" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B728" t="s">
         <v>1057</v>
@@ -11344,12 +11347,12 @@
         <v>1058</v>
       </c>
       <c r="B729" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="B730" t="s">
         <v>1060</v>
@@ -11360,20 +11363,20 @@
         <v>1061</v>
       </c>
       <c r="B731" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B732" t="s">
         <v>1063</v>
-      </c>
-      <c r="B732" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="B733" t="s">
         <v>1065</v>
@@ -11392,12 +11395,12 @@
         <v>1067</v>
       </c>
       <c r="B735" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B736" t="s">
         <v>1069</v>
@@ -11408,12 +11411,12 @@
         <v>1070</v>
       </c>
       <c r="B737" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B738" t="s">
         <v>1072</v>
@@ -11480,12 +11483,12 @@
         <v>1080</v>
       </c>
       <c r="B746" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B747" t="s">
         <v>1082</v>
@@ -11496,20 +11499,20 @@
         <v>1083</v>
       </c>
       <c r="B748" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B749" t="s">
         <v>1085</v>
-      </c>
-      <c r="B749" t="s">
-        <v>1086</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B750" t="s">
         <v>1087</v>
@@ -11544,12 +11547,12 @@
         <v>1091</v>
       </c>
       <c r="B754" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B755" t="s">
         <v>1093</v>
@@ -11568,36 +11571,36 @@
         <v>1095</v>
       </c>
       <c r="B757" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="758" spans="1:2">
       <c r="A758" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B758" t="s">
         <v>1097</v>
-      </c>
-      <c r="B758" t="s">
-        <v>1098</v>
       </c>
     </row>
     <row r="759" spans="1:2">
       <c r="A759" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B759" t="s">
         <v>1099</v>
-      </c>
-      <c r="B759" t="s">
-        <v>1100</v>
       </c>
     </row>
     <row r="760" spans="1:2">
       <c r="A760" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B760" t="s">
         <v>1101</v>
-      </c>
-      <c r="B760" t="s">
-        <v>1102</v>
       </c>
     </row>
     <row r="761" spans="1:2">
       <c r="A761" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B761" t="s">
         <v>1103</v>
@@ -11616,20 +11619,20 @@
         <v>1105</v>
       </c>
       <c r="B763" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B764" t="s">
         <v>1107</v>
-      </c>
-      <c r="B764" t="s">
-        <v>1108</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B765" t="s">
         <v>1109</v>
@@ -11640,12 +11643,12 @@
         <v>1110</v>
       </c>
       <c r="B766" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B767" t="s">
         <v>1112</v>
@@ -11664,44 +11667,44 @@
         <v>1114</v>
       </c>
       <c r="B769" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B770" t="s">
         <v>1116</v>
-      </c>
-      <c r="B770" t="s">
-        <v>1117</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B771" t="s">
         <v>1118</v>
-      </c>
-      <c r="B771" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B772" t="s">
         <v>1120</v>
-      </c>
-      <c r="B772" t="s">
-        <v>1121</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B773" t="s">
         <v>1122</v>
-      </c>
-      <c r="B773" t="s">
-        <v>1123</v>
       </c>
     </row>
     <row r="774" spans="1:2">
       <c r="A774" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B774" t="s">
         <v>1124</v>
@@ -11712,20 +11715,20 @@
         <v>1125</v>
       </c>
       <c r="B775" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="776" spans="1:2">
       <c r="A776" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B776" t="s">
         <v>1127</v>
-      </c>
-      <c r="B776" t="s">
-        <v>1128</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B777" t="s">
         <v>1129</v>
@@ -11768,12 +11771,12 @@
         <v>1134</v>
       </c>
       <c r="B782" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B783" t="s">
         <v>1136</v>
@@ -11784,28 +11787,28 @@
         <v>1137</v>
       </c>
       <c r="B784" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B785" t="s">
         <v>1139</v>
-      </c>
-      <c r="B785" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B786" t="s">
         <v>1141</v>
-      </c>
-      <c r="B786" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="B787" t="s">
         <v>1143</v>
@@ -11848,12 +11851,12 @@
         <v>1148</v>
       </c>
       <c r="B792" t="s">
-        <v>1149</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="B793" t="s">
         <v>1150</v>
@@ -11968,36 +11971,36 @@
         <v>1164</v>
       </c>
       <c r="B807" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B808" t="s">
         <v>1166</v>
-      </c>
-      <c r="B808" t="s">
-        <v>1167</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B809" t="s">
         <v>1168</v>
-      </c>
-      <c r="B809" t="s">
-        <v>1169</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B810" t="s">
         <v>1170</v>
-      </c>
-      <c r="B810" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="B811" t="s">
         <v>1172</v>
@@ -12040,36 +12043,36 @@
         <v>1177</v>
       </c>
       <c r="B816" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B817" t="s">
         <v>1179</v>
-      </c>
-      <c r="B817" t="s">
-        <v>1180</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B818" t="s">
         <v>1181</v>
-      </c>
-      <c r="B818" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B819" t="s">
         <v>1183</v>
-      </c>
-      <c r="B819" t="s">
-        <v>1184</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="B820" t="s">
         <v>1185</v>
@@ -12104,12 +12107,12 @@
         <v>1189</v>
       </c>
       <c r="B824" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="B825" t="s">
         <v>1191</v>
@@ -12136,28 +12139,28 @@
         <v>1194</v>
       </c>
       <c r="B828" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B829" t="s">
         <v>1196</v>
-      </c>
-      <c r="B829" t="s">
-        <v>1197</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B830" t="s">
         <v>1198</v>
-      </c>
-      <c r="B830" t="s">
-        <v>1199</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="B831" t="s">
         <v>1200</v>
@@ -12168,12 +12171,12 @@
         <v>1201</v>
       </c>
       <c r="B832" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="833" spans="1:2">
       <c r="A833" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="B833" t="s">
         <v>1203</v>
@@ -12200,12 +12203,12 @@
         <v>1206</v>
       </c>
       <c r="B836" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="B837" t="s">
         <v>1208</v>
@@ -12248,12 +12251,12 @@
         <v>1213</v>
       </c>
       <c r="B842" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
       <c r="B843" t="s">
         <v>1215</v>
@@ -12400,36 +12403,36 @@
         <v>1233</v>
       </c>
       <c r="B861" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B862" t="s">
         <v>1235</v>
-      </c>
-      <c r="B862" t="s">
-        <v>1236</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B863" t="s">
         <v>1237</v>
-      </c>
-      <c r="B863" t="s">
-        <v>1238</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B864" t="s">
         <v>1239</v>
-      </c>
-      <c r="B864" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B865" t="s">
         <v>1241</v>
@@ -12456,12 +12459,12 @@
         <v>1244</v>
       </c>
       <c r="B868" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="B869" t="s">
         <v>1246</v>
@@ -12552,12 +12555,12 @@
         <v>1257</v>
       </c>
       <c r="B880" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B881" t="s">
         <v>1259</v>
@@ -12568,12 +12571,12 @@
         <v>1260</v>
       </c>
       <c r="B882" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B883" t="s">
         <v>1262</v>
@@ -12584,20 +12587,20 @@
         <v>1263</v>
       </c>
       <c r="B884" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B885" t="s">
         <v>1265</v>
-      </c>
-      <c r="B885" t="s">
-        <v>1266</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B886" t="s">
         <v>1267</v>
@@ -12616,20 +12619,20 @@
         <v>1269</v>
       </c>
       <c r="B888" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B889" t="s">
         <v>1271</v>
-      </c>
-      <c r="B889" t="s">
-        <v>1272</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="B890" t="s">
         <v>1273</v>
@@ -12672,12 +12675,12 @@
         <v>1278</v>
       </c>
       <c r="B895" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="B896" t="s">
         <v>1280</v>
@@ -12720,12 +12723,12 @@
         <v>1285</v>
       </c>
       <c r="B901" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="B902" t="s">
         <v>1287</v>
@@ -12736,12 +12739,12 @@
         <v>1288</v>
       </c>
       <c r="B903" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="B904" t="s">
         <v>1290</v>
@@ -12776,28 +12779,28 @@
         <v>1294</v>
       </c>
       <c r="B908" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B909" t="s">
         <v>1296</v>
-      </c>
-      <c r="B909" t="s">
-        <v>1297</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B910" t="s">
         <v>1298</v>
-      </c>
-      <c r="B910" t="s">
-        <v>1299</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="B911" t="s">
         <v>1300</v>
@@ -12864,28 +12867,28 @@
         <v>1308</v>
       </c>
       <c r="B919" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B920" t="s">
         <v>1310</v>
-      </c>
-      <c r="B920" t="s">
-        <v>1311</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B921" t="s">
         <v>1312</v>
-      </c>
-      <c r="B921" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="B922" t="s">
         <v>1314</v>
@@ -12912,44 +12915,44 @@
         <v>1317</v>
       </c>
       <c r="B925" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B926" t="s">
         <v>1319</v>
-      </c>
-      <c r="B926" t="s">
-        <v>1320</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B927" t="s">
         <v>1321</v>
-      </c>
-      <c r="B927" t="s">
-        <v>1322</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B928" t="s">
         <v>1323</v>
-      </c>
-      <c r="B928" t="s">
-        <v>1324</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B929" t="s">
         <v>1325</v>
-      </c>
-      <c r="B929" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B930" t="s">
         <v>1327</v>
@@ -12968,12 +12971,12 @@
         <v>1329</v>
       </c>
       <c r="B932" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="B933" t="s">
         <v>1331</v>
@@ -12984,20 +12987,20 @@
         <v>1332</v>
       </c>
       <c r="B934" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B935" t="s">
         <v>1334</v>
-      </c>
-      <c r="B935" t="s">
-        <v>1335</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="B936" t="s">
         <v>1336</v>
@@ -13008,20 +13011,20 @@
         <v>1337</v>
       </c>
       <c r="B937" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B938" t="s">
         <v>1339</v>
-      </c>
-      <c r="B938" t="s">
-        <v>1340</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B939" t="s">
         <v>1341</v>
@@ -13056,52 +13059,52 @@
         <v>1345</v>
       </c>
       <c r="B943" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B944" t="s">
         <v>1347</v>
-      </c>
-      <c r="B944" t="s">
-        <v>1348</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B945" t="s">
         <v>1349</v>
-      </c>
-      <c r="B945" t="s">
-        <v>1350</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B946" t="s">
         <v>1351</v>
-      </c>
-      <c r="B946" t="s">
-        <v>1352</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B947" t="s">
         <v>1353</v>
-      </c>
-      <c r="B947" t="s">
-        <v>1354</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B948" t="s">
         <v>1355</v>
-      </c>
-      <c r="B948" t="s">
-        <v>1356</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="B949" t="s">
         <v>1357</v>
@@ -13128,12 +13131,12 @@
         <v>1360</v>
       </c>
       <c r="B952" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
       <c r="B953" t="s">
         <v>1362</v>
@@ -13200,28 +13203,28 @@
         <v>1370</v>
       </c>
       <c r="B961" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B962" t="s">
         <v>1372</v>
-      </c>
-      <c r="B962" t="s">
-        <v>1373</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B963" t="s">
         <v>1374</v>
-      </c>
-      <c r="B963" t="s">
-        <v>1375</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="B964" t="s">
         <v>1376</v>
@@ -13240,28 +13243,28 @@
         <v>1378</v>
       </c>
       <c r="B966" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B967" t="s">
         <v>1380</v>
-      </c>
-      <c r="B967" t="s">
-        <v>1381</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B968" t="s">
         <v>1382</v>
-      </c>
-      <c r="B968" t="s">
-        <v>1383</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="B969" t="s">
         <v>1384</v>
@@ -13280,12 +13283,12 @@
         <v>1386</v>
       </c>
       <c r="B971" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1388</v>
+        <v>1387</v>
       </c>
       <c r="B972" t="s">
         <v>1388</v>
@@ -13328,44 +13331,44 @@
         <v>1393</v>
       </c>
       <c r="B977" t="s">
-        <v>1394</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B978" t="s">
         <v>1395</v>
-      </c>
-      <c r="B978" t="s">
-        <v>1396</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B979" t="s">
         <v>1397</v>
-      </c>
-      <c r="B979" t="s">
-        <v>1398</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B980" t="s">
         <v>1399</v>
-      </c>
-      <c r="B980" t="s">
-        <v>1400</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B981" t="s">
         <v>1401</v>
-      </c>
-      <c r="B981" t="s">
-        <v>1402</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="B982" t="s">
         <v>1403</v>
@@ -13432,12 +13435,12 @@
         <v>1411</v>
       </c>
       <c r="B990" t="s">
-        <v>1412</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="B991" t="s">
         <v>1413</v>
@@ -13464,12 +13467,12 @@
         <v>1416</v>
       </c>
       <c r="B994" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="B995" t="s">
         <v>1418</v>
@@ -13528,20 +13531,20 @@
         <v>1425</v>
       </c>
       <c r="B1002" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B1003" t="s">
         <v>1427</v>
-      </c>
-      <c r="B1003" t="s">
-        <v>1428</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="B1004" t="s">
         <v>1429</v>
@@ -13568,12 +13571,12 @@
         <v>1432</v>
       </c>
       <c r="B1007" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B1008" t="s">
         <v>1434</v>
@@ -13584,20 +13587,20 @@
         <v>1435</v>
       </c>
       <c r="B1009" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B1010" t="s">
         <v>1437</v>
-      </c>
-      <c r="B1010" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B1011" t="s">
         <v>1439</v>
@@ -13632,12 +13635,12 @@
         <v>1443</v>
       </c>
       <c r="B1015" t="s">
-        <v>1444</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B1016" t="s">
         <v>1445</v>
@@ -13672,20 +13675,20 @@
         <v>1449</v>
       </c>
       <c r="B1020" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B1021" t="s">
         <v>1451</v>
-      </c>
-      <c r="B1021" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B1022" t="s">
         <v>1453</v>
@@ -13720,20 +13723,20 @@
         <v>1457</v>
       </c>
       <c r="B1026" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B1027" t="s">
         <v>1459</v>
-      </c>
-      <c r="B1027" t="s">
-        <v>1460</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B1028" t="s">
         <v>1461</v>
@@ -13752,20 +13755,20 @@
         <v>1463</v>
       </c>
       <c r="B1030" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B1031" t="s">
         <v>1465</v>
-      </c>
-      <c r="B1031" t="s">
-        <v>1466</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="B1032" t="s">
         <v>1467</v>
@@ -13776,12 +13779,12 @@
         <v>1468</v>
       </c>
       <c r="B1033" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B1034" t="s">
         <v>1470</v>
@@ -13864,12 +13867,12 @@
         <v>1480</v>
       </c>
       <c r="B1044" t="s">
-        <v>1481</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="B1045" t="s">
         <v>1482</v>
@@ -13880,28 +13883,28 @@
         <v>1483</v>
       </c>
       <c r="B1046" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B1047" t="s">
         <v>1485</v>
-      </c>
-      <c r="B1047" t="s">
-        <v>1486</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B1048" t="s">
         <v>1487</v>
-      </c>
-      <c r="B1048" t="s">
-        <v>1488</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="B1049" t="s">
         <v>1489</v>
@@ -13920,12 +13923,12 @@
         <v>1491</v>
       </c>
       <c r="B1051" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="B1052" t="s">
         <v>1493</v>
@@ -13936,12 +13939,12 @@
         <v>1494</v>
       </c>
       <c r="B1053" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="B1054" t="s">
         <v>1496</v>
@@ -13992,68 +13995,68 @@
         <v>1502</v>
       </c>
       <c r="B1060" t="s">
-        <v>1503</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B1061" t="s">
         <v>1504</v>
-      </c>
-      <c r="B1061" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B1062" t="s">
         <v>1506</v>
-      </c>
-      <c r="B1062" t="s">
-        <v>1507</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B1063" t="s">
         <v>1508</v>
-      </c>
-      <c r="B1063" t="s">
-        <v>1509</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B1064" t="s">
         <v>1510</v>
-      </c>
-      <c r="B1064" t="s">
-        <v>1511</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B1065" t="s">
         <v>1512</v>
-      </c>
-      <c r="B1065" t="s">
-        <v>1513</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B1066" t="s">
         <v>1514</v>
-      </c>
-      <c r="B1066" t="s">
-        <v>1515</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
+        <v>1515</v>
+      </c>
+      <c r="B1067" t="s">
         <v>1516</v>
-      </c>
-      <c r="B1067" t="s">
-        <v>1517</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="B1068" t="s">
         <v>1518</v>
@@ -14064,12 +14067,12 @@
         <v>1519</v>
       </c>
       <c r="B1069" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="B1070" t="s">
         <v>1521</v>
@@ -14096,12 +14099,12 @@
         <v>1524</v>
       </c>
       <c r="B1073" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B1074" t="s">
         <v>1526</v>
@@ -14112,20 +14115,20 @@
         <v>1527</v>
       </c>
       <c r="B1075" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B1076" t="s">
         <v>1529</v>
-      </c>
-      <c r="B1076" t="s">
-        <v>1530</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
       <c r="B1077" t="s">
         <v>1531</v>
@@ -14152,12 +14155,12 @@
         <v>1534</v>
       </c>
       <c r="B1080" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B1081" t="s">
         <v>1536</v>
@@ -14184,12 +14187,12 @@
         <v>1539</v>
       </c>
       <c r="B1084" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
       <c r="B1085" t="s">
         <v>1541</v>
@@ -14208,12 +14211,12 @@
         <v>1543</v>
       </c>
       <c r="B1087" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="B1088" t="s">
         <v>1545</v>
@@ -14224,12 +14227,12 @@
         <v>1546</v>
       </c>
       <c r="B1089" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="B1090" t="s">
         <v>1548</v>
@@ -14256,12 +14259,12 @@
         <v>1551</v>
       </c>
       <c r="B1093" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B1094" t="s">
         <v>1553</v>
@@ -14280,36 +14283,36 @@
         <v>1555</v>
       </c>
       <c r="B1096" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
+        <v>1556</v>
+      </c>
+      <c r="B1097" t="s">
         <v>1557</v>
-      </c>
-      <c r="B1097" t="s">
-        <v>1558</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B1098" t="s">
         <v>1559</v>
-      </c>
-      <c r="B1098" t="s">
-        <v>1560</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
+        <v>1560</v>
+      </c>
+      <c r="B1099" t="s">
         <v>1561</v>
-      </c>
-      <c r="B1099" t="s">
-        <v>1562</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1563</v>
+        <v>1562</v>
       </c>
       <c r="B1100" t="s">
         <v>1563</v>
@@ -14328,36 +14331,36 @@
         <v>1565</v>
       </c>
       <c r="B1102" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B1103" t="s">
         <v>1567</v>
-      </c>
-      <c r="B1103" t="s">
-        <v>1568</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B1104" t="s">
         <v>1569</v>
-      </c>
-      <c r="B1104" t="s">
-        <v>1570</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B1105" t="s">
         <v>1571</v>
-      </c>
-      <c r="B1105" t="s">
-        <v>1572</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1573</v>
+        <v>1572</v>
       </c>
       <c r="B1106" t="s">
         <v>1573</v>
@@ -14408,12 +14411,12 @@
         <v>1579</v>
       </c>
       <c r="B1112" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="B1113" t="s">
         <v>1581</v>
@@ -14432,12 +14435,12 @@
         <v>1583</v>
       </c>
       <c r="B1115" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1585</v>
+        <v>1584</v>
       </c>
       <c r="B1116" t="s">
         <v>1585</v>
@@ -14488,12 +14491,12 @@
         <v>1591</v>
       </c>
       <c r="B1122" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="B1123" t="s">
         <v>1593</v>
@@ -14512,20 +14515,20 @@
         <v>1595</v>
       </c>
       <c r="B1125" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B1126" t="s">
         <v>1597</v>
-      </c>
-      <c r="B1126" t="s">
-        <v>1598</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="B1127" t="s">
         <v>1599</v>
@@ -14544,100 +14547,100 @@
         <v>1601</v>
       </c>
       <c r="B1129" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B1130" t="s">
         <v>1603</v>
-      </c>
-      <c r="B1130" t="s">
-        <v>1604</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
+        <v>1604</v>
+      </c>
+      <c r="B1131" t="s">
         <v>1605</v>
-      </c>
-      <c r="B1131" t="s">
-        <v>1606</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1607</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1608</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B1133" t="s">
         <v>1609</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>1610</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B1134" t="s">
         <v>1611</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>1612</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B1135" t="s">
         <v>1613</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>1614</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B1136" t="s">
         <v>1615</v>
-      </c>
-      <c r="B1136" t="s">
-        <v>1616</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B1137" t="s">
         <v>1617</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>1618</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B1138" t="s">
         <v>1619</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>1620</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B1139" t="s">
         <v>1621</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>1622</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B1140" t="s">
         <v>1623</v>
-      </c>
-      <c r="B1140" t="s">
-        <v>1624</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
-        <v>1625</v>
+        <v>1624</v>
       </c>
       <c r="B1141" t="s">
         <v>1625</v>
@@ -14680,20 +14683,20 @@
         <v>1630</v>
       </c>
       <c r="B1146" t="s">
-        <v>1631</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B1147" t="s">
         <v>1632</v>
-      </c>
-      <c r="B1147" t="s">
-        <v>1633</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
       <c r="B1148" t="s">
         <v>1634</v>
@@ -14728,12 +14731,12 @@
         <v>1638</v>
       </c>
       <c r="B1152" t="s">
-        <v>1639</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1640</v>
+        <v>1639</v>
       </c>
       <c r="B1153" t="s">
         <v>1640</v>
@@ -14752,36 +14755,36 @@
         <v>1642</v>
       </c>
       <c r="B1155" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B1156" t="s">
         <v>1644</v>
-      </c>
-      <c r="B1156" t="s">
-        <v>1645</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B1157" t="s">
         <v>1646</v>
-      </c>
-      <c r="B1157" t="s">
-        <v>1647</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B1158" t="s">
         <v>1648</v>
-      </c>
-      <c r="B1158" t="s">
-        <v>1649</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>1650</v>
+        <v>1649</v>
       </c>
       <c r="B1159" t="s">
         <v>1650</v>
@@ -14792,20 +14795,20 @@
         <v>1651</v>
       </c>
       <c r="B1160" t="s">
-        <v>1652</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B1161" t="s">
         <v>1653</v>
-      </c>
-      <c r="B1161" t="s">
-        <v>1654</v>
       </c>
     </row>
     <row r="1162" spans="1:2">
       <c r="A1162" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
       <c r="B1162" t="s">
         <v>1655</v>
@@ -14816,28 +14819,28 @@
         <v>1656</v>
       </c>
       <c r="B1163" t="s">
-        <v>1657</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B1164" t="s">
         <v>1658</v>
-      </c>
-      <c r="B1164" t="s">
-        <v>1659</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B1165" t="s">
         <v>1660</v>
-      </c>
-      <c r="B1165" t="s">
-        <v>1661</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="B1166" t="s">
         <v>1662</v>
@@ -14960,12 +14963,12 @@
         <v>1677</v>
       </c>
       <c r="B1181" t="s">
-        <v>1678</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="B1182" t="s">
         <v>1679</v>
@@ -15000,12 +15003,12 @@
         <v>1683</v>
       </c>
       <c r="B1186" t="s">
-        <v>1684</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="B1187" t="s">
         <v>1685</v>
@@ -15016,12 +15019,12 @@
         <v>1686</v>
       </c>
       <c r="B1188" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="B1189" t="s">
         <v>1688</v>
@@ -15048,7 +15051,7 @@
         <v>1691</v>
       </c>
       <c r="B1192" t="s">
-        <v>383</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
@@ -15056,7 +15059,7 @@
         <v>1692</v>
       </c>
       <c r="B1193" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
@@ -15064,7 +15067,7 @@
         <v>1693</v>
       </c>
       <c r="B1194" t="s">
-        <v>1693</v>
+        <v>386</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
@@ -15080,7 +15083,7 @@
         <v>1695</v>
       </c>
       <c r="B1196" t="s">
-        <v>643</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
@@ -15088,7 +15091,7 @@
         <v>1696</v>
       </c>
       <c r="B1197" t="s">
-        <v>1696</v>
+        <v>644</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
@@ -15104,7 +15107,7 @@
         <v>1698</v>
       </c>
       <c r="B1199" t="s">
-        <v>924</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1200" spans="1:2">
@@ -15112,7 +15115,7 @@
         <v>1699</v>
       </c>
       <c r="B1200" t="s">
-        <v>1699</v>
+        <v>925</v>
       </c>
     </row>
     <row r="1201" spans="1:2">
@@ -15128,7 +15131,7 @@
         <v>1701</v>
       </c>
       <c r="B1202" t="s">
-        <v>1000</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1203" spans="1:2">
@@ -15136,7 +15139,7 @@
         <v>1702</v>
       </c>
       <c r="B1203" t="s">
-        <v>1702</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="1204" spans="1:2">
@@ -15152,7 +15155,7 @@
         <v>1704</v>
       </c>
       <c r="B1205" t="s">
-        <v>1068</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="1206" spans="1:2">
@@ -15160,7 +15163,7 @@
         <v>1705</v>
       </c>
       <c r="B1206" t="s">
-        <v>1123</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="1207" spans="1:2">
@@ -15168,7 +15171,7 @@
         <v>1706</v>
       </c>
       <c r="B1207" t="s">
-        <v>1706</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="1208" spans="1:2">
@@ -15200,7 +15203,7 @@
         <v>1710</v>
       </c>
       <c r="B1211" t="s">
-        <v>1428</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1212" spans="1:2">
@@ -15208,7 +15211,7 @@
         <v>1711</v>
       </c>
       <c r="B1212" t="s">
-        <v>1711</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="1213" spans="1:2">
@@ -15232,11 +15235,19 @@
         <v>1714</v>
       </c>
       <c r="B1215" t="s">
-        <v>1547</v>
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:2">
+      <c r="A1216" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B1216" t="s">
+        <v>1548</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1215"/>
+  <autoFilter ref="A1:B1216"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/da/headTags.xlsx
+++ b/lang/da/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1217</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1716">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1718">
   <si>
     <t>en</t>
   </si>
@@ -4085,6 +4085,12 @@
   </si>
   <si>
     <t>Mordors skygger</t>
+  </si>
+  <si>
+    <t>Shark</t>
+  </si>
+  <si>
+    <t>Haj</t>
   </si>
   <si>
     <t>Sheep</t>
@@ -5511,7 +5517,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1216"/>
+  <dimension ref="A1:B1217"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -13115,28 +13121,28 @@
         <v>1358</v>
       </c>
       <c r="B950" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B951" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="952" spans="1:2">
       <c r="A952" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="B952" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B953" t="s">
         <v>1362</v>
@@ -13147,68 +13153,68 @@
         <v>1363</v>
       </c>
       <c r="B954" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B955" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B956" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B957" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B958" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B959" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B960" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B961" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B962" t="s">
         <v>1372</v>
@@ -13235,20 +13241,20 @@
         <v>1377</v>
       </c>
       <c r="B965" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B966" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B967" t="s">
         <v>1380</v>
@@ -13275,20 +13281,20 @@
         <v>1385</v>
       </c>
       <c r="B970" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B971" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="B972" t="s">
         <v>1388</v>
@@ -13299,44 +13305,44 @@
         <v>1389</v>
       </c>
       <c r="B973" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B974" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="B975" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="B976" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B977" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B978" t="s">
         <v>1395</v>
@@ -13379,68 +13385,68 @@
         <v>1404</v>
       </c>
       <c r="B983" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="B984" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="985" spans="1:2">
       <c r="A985" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B985" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="B986" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B987" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B988" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B989" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="B990" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B991" t="s">
         <v>1413</v>
@@ -13451,28 +13457,28 @@
         <v>1414</v>
       </c>
       <c r="B992" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B993" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B994" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B995" t="s">
         <v>1418</v>
@@ -13483,60 +13489,60 @@
         <v>1419</v>
       </c>
       <c r="B996" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B997" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B998" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B999" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B1000" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B1001" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B1002" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B1003" t="s">
         <v>1427</v>
@@ -13555,28 +13561,28 @@
         <v>1430</v>
       </c>
       <c r="B1005" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B1006" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B1007" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B1008" t="s">
         <v>1434</v>
@@ -13587,12 +13593,12 @@
         <v>1435</v>
       </c>
       <c r="B1009" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B1010" t="s">
         <v>1437</v>
@@ -13611,36 +13617,36 @@
         <v>1440</v>
       </c>
       <c r="B1012" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B1013" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B1014" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B1015" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B1016" t="s">
         <v>1445</v>
@@ -13651,36 +13657,36 @@
         <v>1446</v>
       </c>
       <c r="B1017" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="B1018" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B1019" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B1020" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B1021" t="s">
         <v>1451</v>
@@ -13699,36 +13705,36 @@
         <v>1454</v>
       </c>
       <c r="B1023" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B1024" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B1025" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B1026" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B1027" t="s">
         <v>1459</v>
@@ -13747,20 +13753,20 @@
         <v>1462</v>
       </c>
       <c r="B1029" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B1030" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B1031" t="s">
         <v>1465</v>
@@ -13779,12 +13785,12 @@
         <v>1468</v>
       </c>
       <c r="B1033" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B1034" t="s">
         <v>1470</v>
@@ -13795,84 +13801,84 @@
         <v>1471</v>
       </c>
       <c r="B1035" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B1036" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B1037" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B1038" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B1039" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B1040" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B1041" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B1042" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B1043" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B1044" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B1045" t="s">
         <v>1482</v>
@@ -13883,12 +13889,12 @@
         <v>1483</v>
       </c>
       <c r="B1046" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B1047" t="s">
         <v>1485</v>
@@ -13915,20 +13921,20 @@
         <v>1490</v>
       </c>
       <c r="B1050" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B1051" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B1052" t="s">
         <v>1493</v>
@@ -13939,12 +13945,12 @@
         <v>1494</v>
       </c>
       <c r="B1053" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B1054" t="s">
         <v>1496</v>
@@ -13955,52 +13961,52 @@
         <v>1497</v>
       </c>
       <c r="B1055" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B1056" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B1057" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B1058" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B1059" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B1060" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B1061" t="s">
         <v>1504</v>
@@ -14067,12 +14073,12 @@
         <v>1519</v>
       </c>
       <c r="B1069" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B1070" t="s">
         <v>1521</v>
@@ -14083,28 +14089,28 @@
         <v>1522</v>
       </c>
       <c r="B1071" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B1072" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B1073" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B1074" t="s">
         <v>1526</v>
@@ -14115,12 +14121,12 @@
         <v>1527</v>
       </c>
       <c r="B1075" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B1076" t="s">
         <v>1529</v>
@@ -14139,28 +14145,28 @@
         <v>1532</v>
       </c>
       <c r="B1078" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B1079" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B1080" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B1081" t="s">
         <v>1536</v>
@@ -14171,28 +14177,28 @@
         <v>1537</v>
       </c>
       <c r="B1082" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B1083" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B1084" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B1085" t="s">
         <v>1541</v>
@@ -14203,20 +14209,20 @@
         <v>1542</v>
       </c>
       <c r="B1086" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B1087" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B1088" t="s">
         <v>1545</v>
@@ -14227,12 +14233,12 @@
         <v>1546</v>
       </c>
       <c r="B1089" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B1090" t="s">
         <v>1548</v>
@@ -14243,28 +14249,28 @@
         <v>1549</v>
       </c>
       <c r="B1091" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B1092" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B1093" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B1094" t="s">
         <v>1553</v>
@@ -14275,20 +14281,20 @@
         <v>1554</v>
       </c>
       <c r="B1095" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B1096" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B1097" t="s">
         <v>1557</v>
@@ -14323,20 +14329,20 @@
         <v>1564</v>
       </c>
       <c r="B1101" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B1102" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="1103" spans="1:2">
       <c r="A1103" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="B1103" t="s">
         <v>1567</v>
@@ -14371,52 +14377,52 @@
         <v>1574</v>
       </c>
       <c r="B1107" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B1108" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="1109" spans="1:2">
       <c r="A1109" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B1109" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
       <c r="B1110" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B1111" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B1112" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B1113" t="s">
         <v>1581</v>
@@ -14427,20 +14433,20 @@
         <v>1582</v>
       </c>
       <c r="B1114" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B1115" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B1116" t="s">
         <v>1585</v>
@@ -14451,52 +14457,52 @@
         <v>1586</v>
       </c>
       <c r="B1117" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B1118" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B1119" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B1120" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B1121" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B1122" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B1123" t="s">
         <v>1593</v>
@@ -14507,20 +14513,20 @@
         <v>1594</v>
       </c>
       <c r="B1124" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B1125" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B1126" t="s">
         <v>1597</v>
@@ -14539,20 +14545,20 @@
         <v>1600</v>
       </c>
       <c r="B1128" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B1129" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B1130" t="s">
         <v>1603</v>
@@ -14651,44 +14657,44 @@
         <v>1626</v>
       </c>
       <c r="B1142" t="s">
-        <v>1626</v>
+        <v>1627</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
       <c r="B1143" t="s">
-        <v>1627</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="1144" spans="1:2">
       <c r="A1144" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
       <c r="B1144" t="s">
-        <v>1628</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
       <c r="B1145" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B1146" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B1147" t="s">
         <v>1632</v>
@@ -14707,36 +14713,36 @@
         <v>1635</v>
       </c>
       <c r="B1149" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B1150" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B1151" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B1152" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B1153" t="s">
         <v>1640</v>
@@ -14747,20 +14753,20 @@
         <v>1641</v>
       </c>
       <c r="B1154" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B1155" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1156" t="s">
         <v>1644</v>
@@ -14795,12 +14801,12 @@
         <v>1651</v>
       </c>
       <c r="B1160" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B1161" t="s">
         <v>1653</v>
@@ -14819,12 +14825,12 @@
         <v>1656</v>
       </c>
       <c r="B1163" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B1164" t="s">
         <v>1658</v>
@@ -14851,124 +14857,124 @@
         <v>1663</v>
       </c>
       <c r="B1167" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="B1168" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="B1169" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B1170" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B1171" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="B1172" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B1173" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B1174" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B1175" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B1176" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B1177" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B1178" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B1179" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B1180" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B1181" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1182" t="s">
         <v>1679</v>
@@ -14979,36 +14985,36 @@
         <v>1680</v>
       </c>
       <c r="B1183" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B1184" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B1185" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B1186" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B1187" t="s">
         <v>1685</v>
@@ -15019,12 +15025,12 @@
         <v>1686</v>
       </c>
       <c r="B1188" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1189" t="s">
         <v>1688</v>
@@ -15035,219 +15041,227 @@
         <v>1689</v>
       </c>
       <c r="B1190" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B1191" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B1192" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1193" t="s">
-        <v>384</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B1194" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B1195" t="s">
-        <v>1694</v>
+        <v>386</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
       <c r="A1196" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1196" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
       <c r="A1197" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1197" t="s">
-        <v>644</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1198" t="s">
-        <v>1697</v>
+        <v>644</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
       <c r="A1199" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1199" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1200" spans="1:2">
       <c r="A1200" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1200" t="s">
-        <v>925</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1201" spans="1:2">
       <c r="A1201" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1201" t="s">
-        <v>1700</v>
+        <v>925</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
       <c r="A1202" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1202" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1203" spans="1:2">
       <c r="A1203" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B1203" t="s">
-        <v>1001</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1204" spans="1:2">
       <c r="A1204" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B1204" t="s">
-        <v>1703</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="1205" spans="1:2">
       <c r="A1205" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B1205" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1206" spans="1:2">
       <c r="A1206" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B1206" t="s">
-        <v>1069</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1207" spans="1:2">
       <c r="A1207" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1207" t="s">
-        <v>1124</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="1208" spans="1:2">
       <c r="A1208" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1208" t="s">
-        <v>1707</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="1209" spans="1:2">
       <c r="A1209" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B1209" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1210" spans="1:2">
       <c r="A1210" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B1210" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1211" spans="1:2">
       <c r="A1211" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B1211" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="1212" spans="1:2">
       <c r="A1212" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B1212" t="s">
-        <v>1429</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1213" spans="1:2">
       <c r="A1213" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1213" t="s">
-        <v>1712</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1214" spans="1:2">
       <c r="A1214" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="B1214" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1215" spans="1:2">
       <c r="A1215" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B1215" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="1216" spans="1:2">
       <c r="A1216" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B1216" t="s">
-        <v>1548</v>
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:2">
+      <c r="A1217" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B1217" t="s">
+        <v>1550</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1216"/>
+  <autoFilter ref="A1:B1217"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/da/headTags.xlsx
+++ b/lang/da/headTags.xlsx
@@ -1420,6 +1420,9 @@
     <t>Eventyrlige fortællinger</t>
   </si>
   <si>
+    <t>Fall Drop</t>
+  </si>
+  <si>
     <t>Fall Guys</t>
   </si>
   <si>
@@ -5081,9 +5084,6 @@
   </si>
   <si>
     <t>Hypixel (mutationer) Tag</t>
-  </si>
-  <si>
-    <t>Fall Drop</t>
   </si>
   <si>
     <t>Summer Drop 2025</t>
@@ -8201,52 +8201,52 @@
         <v>477</v>
       </c>
       <c r="B335" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
+        <v>478</v>
+      </c>
+      <c r="B336" t="s">
         <v>479</v>
-      </c>
-      <c r="B336" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
+        <v>480</v>
+      </c>
+      <c r="B337" t="s">
         <v>481</v>
-      </c>
-      <c r="B337" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="338" spans="1:2">
       <c r="A338" t="s">
+        <v>482</v>
+      </c>
+      <c r="B338" t="s">
         <v>483</v>
-      </c>
-      <c r="B338" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="339" spans="1:2">
       <c r="A339" t="s">
+        <v>484</v>
+      </c>
+      <c r="B339" t="s">
         <v>485</v>
-      </c>
-      <c r="B339" t="s">
-        <v>486</v>
       </c>
     </row>
     <row r="340" spans="1:2">
       <c r="A340" t="s">
+        <v>486</v>
+      </c>
+      <c r="B340" t="s">
         <v>487</v>
-      </c>
-      <c r="B340" t="s">
-        <v>488</v>
       </c>
     </row>
     <row r="341" spans="1:2">
       <c r="A341" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B341" t="s">
         <v>489</v>
@@ -8281,12 +8281,12 @@
         <v>493</v>
       </c>
       <c r="B345" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B346" t="s">
         <v>495</v>
@@ -8313,100 +8313,100 @@
         <v>498</v>
       </c>
       <c r="B349" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
+        <v>499</v>
+      </c>
+      <c r="B350" t="s">
         <v>500</v>
-      </c>
-      <c r="B350" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="A351" t="s">
+        <v>501</v>
+      </c>
+      <c r="B351" t="s">
         <v>502</v>
-      </c>
-      <c r="B351" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="352" spans="1:2">
       <c r="A352" t="s">
+        <v>503</v>
+      </c>
+      <c r="B352" t="s">
         <v>504</v>
-      </c>
-      <c r="B352" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="353" spans="1:2">
       <c r="A353" t="s">
+        <v>505</v>
+      </c>
+      <c r="B353" t="s">
         <v>506</v>
-      </c>
-      <c r="B353" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="354" spans="1:2">
       <c r="A354" t="s">
+        <v>507</v>
+      </c>
+      <c r="B354" t="s">
         <v>508</v>
-      </c>
-      <c r="B354" t="s">
-        <v>509</v>
       </c>
     </row>
     <row r="355" spans="1:2">
       <c r="A355" t="s">
+        <v>509</v>
+      </c>
+      <c r="B355" t="s">
         <v>510</v>
-      </c>
-      <c r="B355" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="356" spans="1:2">
       <c r="A356" t="s">
+        <v>511</v>
+      </c>
+      <c r="B356" t="s">
         <v>512</v>
-      </c>
-      <c r="B356" t="s">
-        <v>513</v>
       </c>
     </row>
     <row r="357" spans="1:2">
       <c r="A357" t="s">
+        <v>513</v>
+      </c>
+      <c r="B357" t="s">
         <v>514</v>
-      </c>
-      <c r="B357" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="358" spans="1:2">
       <c r="A358" t="s">
+        <v>515</v>
+      </c>
+      <c r="B358" t="s">
         <v>516</v>
-      </c>
-      <c r="B358" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="359" spans="1:2">
       <c r="A359" t="s">
+        <v>517</v>
+      </c>
+      <c r="B359" t="s">
         <v>518</v>
-      </c>
-      <c r="B359" t="s">
-        <v>519</v>
       </c>
     </row>
     <row r="360" spans="1:2">
       <c r="A360" t="s">
+        <v>519</v>
+      </c>
+      <c r="B360" t="s">
         <v>520</v>
-      </c>
-      <c r="B360" t="s">
-        <v>521</v>
       </c>
     </row>
     <row r="361" spans="1:2">
       <c r="A361" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B361" t="s">
         <v>522</v>
@@ -8417,20 +8417,20 @@
         <v>523</v>
       </c>
       <c r="B362" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
+        <v>524</v>
+      </c>
+      <c r="B363" t="s">
         <v>525</v>
-      </c>
-      <c r="B363" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B364" t="s">
         <v>527</v>
@@ -8449,20 +8449,20 @@
         <v>529</v>
       </c>
       <c r="B366" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
+        <v>530</v>
+      </c>
+      <c r="B367" t="s">
         <v>531</v>
-      </c>
-      <c r="B367" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B368" t="s">
         <v>533</v>
@@ -8481,44 +8481,44 @@
         <v>535</v>
       </c>
       <c r="B370" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" t="s">
+        <v>536</v>
+      </c>
+      <c r="B371" t="s">
         <v>537</v>
-      </c>
-      <c r="B371" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="372" spans="1:2">
       <c r="A372" t="s">
+        <v>538</v>
+      </c>
+      <c r="B372" t="s">
         <v>539</v>
-      </c>
-      <c r="B372" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="373" spans="1:2">
       <c r="A373" t="s">
+        <v>540</v>
+      </c>
+      <c r="B373" t="s">
         <v>541</v>
-      </c>
-      <c r="B373" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="374" spans="1:2">
       <c r="A374" t="s">
+        <v>542</v>
+      </c>
+      <c r="B374" t="s">
         <v>543</v>
-      </c>
-      <c r="B374" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="375" spans="1:2">
       <c r="A375" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B375" t="s">
         <v>545</v>
@@ -8529,28 +8529,28 @@
         <v>546</v>
       </c>
       <c r="B376" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="377" spans="1:2">
       <c r="A377" t="s">
+        <v>547</v>
+      </c>
+      <c r="B377" t="s">
         <v>548</v>
-      </c>
-      <c r="B377" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="378" spans="1:2">
       <c r="A378" t="s">
+        <v>549</v>
+      </c>
+      <c r="B378" t="s">
         <v>550</v>
-      </c>
-      <c r="B378" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="379" spans="1:2">
       <c r="A379" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B379" t="s">
         <v>552</v>
@@ -8561,28 +8561,28 @@
         <v>553</v>
       </c>
       <c r="B380" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" t="s">
+        <v>554</v>
+      </c>
+      <c r="B381" t="s">
         <v>555</v>
-      </c>
-      <c r="B381" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" t="s">
+        <v>556</v>
+      </c>
+      <c r="B382" t="s">
         <v>557</v>
-      </c>
-      <c r="B382" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="383" spans="1:2">
       <c r="A383" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B383" t="s">
         <v>559</v>
@@ -8625,20 +8625,20 @@
         <v>564</v>
       </c>
       <c r="B388" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" t="s">
+        <v>565</v>
+      </c>
+      <c r="B389" t="s">
         <v>566</v>
-      </c>
-      <c r="B389" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B390" t="s">
         <v>568</v>
@@ -8649,12 +8649,12 @@
         <v>569</v>
       </c>
       <c r="B391" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="392" spans="1:2">
       <c r="A392" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B392" t="s">
         <v>571</v>
@@ -8673,28 +8673,28 @@
         <v>573</v>
       </c>
       <c r="B394" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
+        <v>574</v>
+      </c>
+      <c r="B395" t="s">
         <v>575</v>
-      </c>
-      <c r="B395" t="s">
-        <v>576</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" t="s">
+        <v>576</v>
+      </c>
+      <c r="B396" t="s">
         <v>577</v>
-      </c>
-      <c r="B396" t="s">
-        <v>578</v>
       </c>
     </row>
     <row r="397" spans="1:2">
       <c r="A397" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B397" t="s">
         <v>579</v>
@@ -8729,36 +8729,36 @@
         <v>583</v>
       </c>
       <c r="B401" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
+        <v>584</v>
+      </c>
+      <c r="B402" t="s">
         <v>585</v>
-      </c>
-      <c r="B402" t="s">
-        <v>586</v>
       </c>
     </row>
     <row r="403" spans="1:2">
       <c r="A403" t="s">
+        <v>586</v>
+      </c>
+      <c r="B403" t="s">
         <v>587</v>
-      </c>
-      <c r="B403" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="404" spans="1:2">
       <c r="A404" t="s">
+        <v>588</v>
+      </c>
+      <c r="B404" t="s">
         <v>589</v>
-      </c>
-      <c r="B404" t="s">
-        <v>590</v>
       </c>
     </row>
     <row r="405" spans="1:2">
       <c r="A405" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B405" t="s">
         <v>591</v>
@@ -8769,20 +8769,20 @@
         <v>592</v>
       </c>
       <c r="B406" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" t="s">
+        <v>593</v>
+      </c>
+      <c r="B407" t="s">
         <v>594</v>
-      </c>
-      <c r="B407" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="408" spans="1:2">
       <c r="A408" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B408" t="s">
         <v>596</v>
@@ -8801,12 +8801,12 @@
         <v>598</v>
       </c>
       <c r="B410" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B411" t="s">
         <v>600</v>
@@ -8833,20 +8833,20 @@
         <v>603</v>
       </c>
       <c r="B414" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
+        <v>604</v>
+      </c>
+      <c r="B415" t="s">
         <v>605</v>
-      </c>
-      <c r="B415" t="s">
-        <v>606</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B416" t="s">
         <v>607</v>
@@ -8865,124 +8865,124 @@
         <v>609</v>
       </c>
       <c r="B418" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" t="s">
+        <v>610</v>
+      </c>
+      <c r="B419" t="s">
         <v>611</v>
-      </c>
-      <c r="B419" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" t="s">
+        <v>612</v>
+      </c>
+      <c r="B420" t="s">
         <v>613</v>
-      </c>
-      <c r="B420" t="s">
-        <v>614</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" t="s">
+        <v>614</v>
+      </c>
+      <c r="B421" t="s">
         <v>615</v>
-      </c>
-      <c r="B421" t="s">
-        <v>616</v>
       </c>
     </row>
     <row r="422" spans="1:2">
       <c r="A422" t="s">
+        <v>616</v>
+      </c>
+      <c r="B422" t="s">
         <v>617</v>
-      </c>
-      <c r="B422" t="s">
-        <v>618</v>
       </c>
     </row>
     <row r="423" spans="1:2">
       <c r="A423" t="s">
+        <v>618</v>
+      </c>
+      <c r="B423" t="s">
         <v>619</v>
-      </c>
-      <c r="B423" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="424" spans="1:2">
       <c r="A424" t="s">
+        <v>620</v>
+      </c>
+      <c r="B424" t="s">
         <v>621</v>
-      </c>
-      <c r="B424" t="s">
-        <v>622</v>
       </c>
     </row>
     <row r="425" spans="1:2">
       <c r="A425" t="s">
+        <v>622</v>
+      </c>
+      <c r="B425" t="s">
         <v>623</v>
-      </c>
-      <c r="B425" t="s">
-        <v>624</v>
       </c>
     </row>
     <row r="426" spans="1:2">
       <c r="A426" t="s">
+        <v>624</v>
+      </c>
+      <c r="B426" t="s">
         <v>625</v>
-      </c>
-      <c r="B426" t="s">
-        <v>626</v>
       </c>
     </row>
     <row r="427" spans="1:2">
       <c r="A427" t="s">
+        <v>626</v>
+      </c>
+      <c r="B427" t="s">
         <v>627</v>
-      </c>
-      <c r="B427" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="428" spans="1:2">
       <c r="A428" t="s">
+        <v>628</v>
+      </c>
+      <c r="B428" t="s">
         <v>629</v>
-      </c>
-      <c r="B428" t="s">
-        <v>630</v>
       </c>
     </row>
     <row r="429" spans="1:2">
       <c r="A429" t="s">
+        <v>630</v>
+      </c>
+      <c r="B429" t="s">
         <v>631</v>
-      </c>
-      <c r="B429" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="430" spans="1:2">
       <c r="A430" t="s">
+        <v>632</v>
+      </c>
+      <c r="B430" t="s">
         <v>633</v>
-      </c>
-      <c r="B430" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="431" spans="1:2">
       <c r="A431" t="s">
+        <v>634</v>
+      </c>
+      <c r="B431" t="s">
         <v>635</v>
-      </c>
-      <c r="B431" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="432" spans="1:2">
       <c r="A432" t="s">
+        <v>636</v>
+      </c>
+      <c r="B432" t="s">
         <v>637</v>
-      </c>
-      <c r="B432" t="s">
-        <v>638</v>
       </c>
     </row>
     <row r="433" spans="1:2">
       <c r="A433" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B433" t="s">
         <v>639</v>
@@ -9017,12 +9017,12 @@
         <v>643</v>
       </c>
       <c r="B437" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B438" t="s">
         <v>645</v>
@@ -9033,12 +9033,12 @@
         <v>646</v>
       </c>
       <c r="B439" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="B440" t="s">
         <v>648</v>
@@ -9057,12 +9057,12 @@
         <v>650</v>
       </c>
       <c r="B442" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="443" spans="1:2">
       <c r="A443" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B443" t="s">
         <v>652</v>
@@ -9081,28 +9081,28 @@
         <v>654</v>
       </c>
       <c r="B445" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="446" spans="1:2">
       <c r="A446" t="s">
+        <v>655</v>
+      </c>
+      <c r="B446" t="s">
         <v>656</v>
-      </c>
-      <c r="B446" t="s">
-        <v>657</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" t="s">
+        <v>657</v>
+      </c>
+      <c r="B447" t="s">
         <v>658</v>
-      </c>
-      <c r="B447" t="s">
-        <v>659</v>
       </c>
     </row>
     <row r="448" spans="1:2">
       <c r="A448" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B448" t="s">
         <v>660</v>
@@ -9113,12 +9113,12 @@
         <v>661</v>
       </c>
       <c r="B449" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B450" t="s">
         <v>663</v>
@@ -9145,20 +9145,20 @@
         <v>666</v>
       </c>
       <c r="B453" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
+        <v>667</v>
+      </c>
+      <c r="B454" t="s">
         <v>668</v>
-      </c>
-      <c r="B454" t="s">
-        <v>669</v>
       </c>
     </row>
     <row r="455" spans="1:2">
       <c r="A455" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B455" t="s">
         <v>670</v>
@@ -9177,12 +9177,12 @@
         <v>672</v>
       </c>
       <c r="B457" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B458" t="s">
         <v>674</v>
@@ -9201,36 +9201,36 @@
         <v>676</v>
       </c>
       <c r="B460" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="461" spans="1:2">
       <c r="A461" t="s">
+        <v>677</v>
+      </c>
+      <c r="B461" t="s">
         <v>678</v>
-      </c>
-      <c r="B461" t="s">
-        <v>679</v>
       </c>
     </row>
     <row r="462" spans="1:2">
       <c r="A462" t="s">
+        <v>679</v>
+      </c>
+      <c r="B462" t="s">
         <v>680</v>
-      </c>
-      <c r="B462" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="463" spans="1:2">
       <c r="A463" t="s">
+        <v>681</v>
+      </c>
+      <c r="B463" t="s">
         <v>682</v>
-      </c>
-      <c r="B463" t="s">
-        <v>683</v>
       </c>
     </row>
     <row r="464" spans="1:2">
       <c r="A464" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B464" t="s">
         <v>684</v>
@@ -9257,12 +9257,12 @@
         <v>687</v>
       </c>
       <c r="B467" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B468" t="s">
         <v>689</v>
@@ -9273,12 +9273,12 @@
         <v>690</v>
       </c>
       <c r="B469" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B470" t="s">
         <v>692</v>
@@ -9297,12 +9297,12 @@
         <v>694</v>
       </c>
       <c r="B472" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="473" spans="1:2">
       <c r="A473" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B473" t="s">
         <v>696</v>
@@ -9313,7 +9313,7 @@
         <v>697</v>
       </c>
       <c r="B474" t="s">
-        <v>688</v>
+        <v>697</v>
       </c>
     </row>
     <row r="475" spans="1:2">
@@ -9321,7 +9321,7 @@
         <v>698</v>
       </c>
       <c r="B475" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
     </row>
     <row r="476" spans="1:2">
@@ -9353,20 +9353,20 @@
         <v>702</v>
       </c>
       <c r="B479" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
+        <v>703</v>
+      </c>
+      <c r="B480" t="s">
         <v>704</v>
-      </c>
-      <c r="B480" t="s">
-        <v>705</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B481" t="s">
         <v>706</v>
@@ -9377,12 +9377,12 @@
         <v>707</v>
       </c>
       <c r="B482" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B483" t="s">
         <v>709</v>
@@ -9393,12 +9393,12 @@
         <v>710</v>
       </c>
       <c r="B484" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B485" t="s">
         <v>712</v>
@@ -9417,12 +9417,12 @@
         <v>714</v>
       </c>
       <c r="B487" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B488" t="s">
         <v>716</v>
@@ -9457,156 +9457,156 @@
         <v>720</v>
       </c>
       <c r="B492" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
+        <v>721</v>
+      </c>
+      <c r="B493" t="s">
         <v>722</v>
-      </c>
-      <c r="B493" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
+        <v>723</v>
+      </c>
+      <c r="B494" t="s">
         <v>724</v>
-      </c>
-      <c r="B494" t="s">
-        <v>725</v>
       </c>
     </row>
     <row r="495" spans="1:2">
       <c r="A495" t="s">
+        <v>725</v>
+      </c>
+      <c r="B495" t="s">
         <v>726</v>
-      </c>
-      <c r="B495" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="496" spans="1:2">
       <c r="A496" t="s">
+        <v>727</v>
+      </c>
+      <c r="B496" t="s">
         <v>728</v>
-      </c>
-      <c r="B496" t="s">
-        <v>729</v>
       </c>
     </row>
     <row r="497" spans="1:2">
       <c r="A497" t="s">
+        <v>729</v>
+      </c>
+      <c r="B497" t="s">
         <v>730</v>
-      </c>
-      <c r="B497" t="s">
-        <v>731</v>
       </c>
     </row>
     <row r="498" spans="1:2">
       <c r="A498" t="s">
+        <v>731</v>
+      </c>
+      <c r="B498" t="s">
         <v>732</v>
-      </c>
-      <c r="B498" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="499" spans="1:2">
       <c r="A499" t="s">
+        <v>733</v>
+      </c>
+      <c r="B499" t="s">
         <v>734</v>
-      </c>
-      <c r="B499" t="s">
-        <v>735</v>
       </c>
     </row>
     <row r="500" spans="1:2">
       <c r="A500" t="s">
+        <v>735</v>
+      </c>
+      <c r="B500" t="s">
         <v>736</v>
-      </c>
-      <c r="B500" t="s">
-        <v>737</v>
       </c>
     </row>
     <row r="501" spans="1:2">
       <c r="A501" t="s">
+        <v>737</v>
+      </c>
+      <c r="B501" t="s">
         <v>738</v>
-      </c>
-      <c r="B501" t="s">
-        <v>739</v>
       </c>
     </row>
     <row r="502" spans="1:2">
       <c r="A502" t="s">
+        <v>739</v>
+      </c>
+      <c r="B502" t="s">
         <v>740</v>
-      </c>
-      <c r="B502" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="503" spans="1:2">
       <c r="A503" t="s">
+        <v>741</v>
+      </c>
+      <c r="B503" t="s">
         <v>742</v>
-      </c>
-      <c r="B503" t="s">
-        <v>743</v>
       </c>
     </row>
     <row r="504" spans="1:2">
       <c r="A504" t="s">
+        <v>743</v>
+      </c>
+      <c r="B504" t="s">
         <v>744</v>
-      </c>
-      <c r="B504" t="s">
-        <v>745</v>
       </c>
     </row>
     <row r="505" spans="1:2">
       <c r="A505" t="s">
+        <v>745</v>
+      </c>
+      <c r="B505" t="s">
         <v>746</v>
-      </c>
-      <c r="B505" t="s">
-        <v>747</v>
       </c>
     </row>
     <row r="506" spans="1:2">
       <c r="A506" t="s">
+        <v>747</v>
+      </c>
+      <c r="B506" t="s">
         <v>748</v>
-      </c>
-      <c r="B506" t="s">
-        <v>749</v>
       </c>
     </row>
     <row r="507" spans="1:2">
       <c r="A507" t="s">
+        <v>749</v>
+      </c>
+      <c r="B507" t="s">
         <v>750</v>
-      </c>
-      <c r="B507" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="508" spans="1:2">
       <c r="A508" t="s">
+        <v>751</v>
+      </c>
+      <c r="B508" t="s">
         <v>752</v>
-      </c>
-      <c r="B508" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="509" spans="1:2">
       <c r="A509" t="s">
+        <v>753</v>
+      </c>
+      <c r="B509" t="s">
         <v>754</v>
-      </c>
-      <c r="B509" t="s">
-        <v>755</v>
       </c>
     </row>
     <row r="510" spans="1:2">
       <c r="A510" t="s">
+        <v>755</v>
+      </c>
+      <c r="B510" t="s">
         <v>756</v>
-      </c>
-      <c r="B510" t="s">
-        <v>757</v>
       </c>
     </row>
     <row r="511" spans="1:2">
       <c r="A511" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B511" t="s">
         <v>758</v>
@@ -9617,15 +9617,15 @@
         <v>759</v>
       </c>
       <c r="B512" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
+        <v>760</v>
+      </c>
+      <c r="B513" t="s">
         <v>761</v>
-      </c>
-      <c r="B513" t="s">
-        <v>760</v>
       </c>
     </row>
     <row r="514" spans="1:2">
@@ -9633,7 +9633,7 @@
         <v>762</v>
       </c>
       <c r="B514" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
     </row>
     <row r="515" spans="1:2">
@@ -9641,12 +9641,12 @@
         <v>763</v>
       </c>
       <c r="B515" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="A516" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B516" t="s">
         <v>765</v>
@@ -9657,36 +9657,36 @@
         <v>766</v>
       </c>
       <c r="B517" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
+        <v>767</v>
+      </c>
+      <c r="B518" t="s">
         <v>768</v>
-      </c>
-      <c r="B518" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="519" spans="1:2">
       <c r="A519" t="s">
+        <v>769</v>
+      </c>
+      <c r="B519" t="s">
         <v>770</v>
-      </c>
-      <c r="B519" t="s">
-        <v>771</v>
       </c>
     </row>
     <row r="520" spans="1:2">
       <c r="A520" t="s">
+        <v>771</v>
+      </c>
+      <c r="B520" t="s">
         <v>772</v>
-      </c>
-      <c r="B520" t="s">
-        <v>773</v>
       </c>
     </row>
     <row r="521" spans="1:2">
       <c r="A521" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B521" t="s">
         <v>774</v>
@@ -9697,12 +9697,12 @@
         <v>775</v>
       </c>
       <c r="B522" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B523" t="s">
         <v>777</v>
@@ -9713,20 +9713,20 @@
         <v>778</v>
       </c>
       <c r="B524" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" t="s">
+        <v>779</v>
+      </c>
+      <c r="B525" t="s">
         <v>780</v>
-      </c>
-      <c r="B525" t="s">
-        <v>781</v>
       </c>
     </row>
     <row r="526" spans="1:2">
       <c r="A526" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B526" t="s">
         <v>782</v>
@@ -9737,52 +9737,52 @@
         <v>783</v>
       </c>
       <c r="B527" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="528" spans="1:2">
       <c r="A528" t="s">
+        <v>784</v>
+      </c>
+      <c r="B528" t="s">
         <v>785</v>
-      </c>
-      <c r="B528" t="s">
-        <v>786</v>
       </c>
     </row>
     <row r="529" spans="1:2">
       <c r="A529" t="s">
+        <v>786</v>
+      </c>
+      <c r="B529" t="s">
         <v>787</v>
-      </c>
-      <c r="B529" t="s">
-        <v>788</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" t="s">
+        <v>788</v>
+      </c>
+      <c r="B530" t="s">
         <v>789</v>
-      </c>
-      <c r="B530" t="s">
-        <v>790</v>
       </c>
     </row>
     <row r="531" spans="1:2">
       <c r="A531" t="s">
+        <v>790</v>
+      </c>
+      <c r="B531" t="s">
         <v>791</v>
-      </c>
-      <c r="B531" t="s">
-        <v>792</v>
       </c>
     </row>
     <row r="532" spans="1:2">
       <c r="A532" t="s">
+        <v>792</v>
+      </c>
+      <c r="B532" t="s">
         <v>793</v>
-      </c>
-      <c r="B532" t="s">
-        <v>794</v>
       </c>
     </row>
     <row r="533" spans="1:2">
       <c r="A533" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B533" t="s">
         <v>795</v>
@@ -9793,20 +9793,20 @@
         <v>796</v>
       </c>
       <c r="B534" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
+        <v>797</v>
+      </c>
+      <c r="B535" t="s">
         <v>798</v>
-      </c>
-      <c r="B535" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B536" t="s">
         <v>800</v>
@@ -9889,12 +9889,12 @@
         <v>810</v>
       </c>
       <c r="B546" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B547" t="s">
         <v>812</v>
@@ -9913,12 +9913,12 @@
         <v>814</v>
       </c>
       <c r="B549" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B550" t="s">
         <v>816</v>
@@ -9985,52 +9985,52 @@
         <v>824</v>
       </c>
       <c r="B558" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
+        <v>825</v>
+      </c>
+      <c r="B559" t="s">
         <v>826</v>
-      </c>
-      <c r="B559" t="s">
-        <v>827</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
+        <v>827</v>
+      </c>
+      <c r="B560" t="s">
         <v>828</v>
-      </c>
-      <c r="B560" t="s">
-        <v>829</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" t="s">
+        <v>829</v>
+      </c>
+      <c r="B561" t="s">
         <v>830</v>
-      </c>
-      <c r="B561" t="s">
-        <v>831</v>
       </c>
     </row>
     <row r="562" spans="1:2">
       <c r="A562" t="s">
+        <v>831</v>
+      </c>
+      <c r="B562" t="s">
         <v>832</v>
-      </c>
-      <c r="B562" t="s">
-        <v>833</v>
       </c>
     </row>
     <row r="563" spans="1:2">
       <c r="A563" t="s">
+        <v>833</v>
+      </c>
+      <c r="B563" t="s">
         <v>834</v>
-      </c>
-      <c r="B563" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="564" spans="1:2">
       <c r="A564" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B564" t="s">
         <v>836</v>
@@ -10057,12 +10057,12 @@
         <v>839</v>
       </c>
       <c r="B567" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="B568" t="s">
         <v>841</v>
@@ -10081,12 +10081,12 @@
         <v>843</v>
       </c>
       <c r="B570" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B571" t="s">
         <v>845</v>
@@ -10105,20 +10105,20 @@
         <v>847</v>
       </c>
       <c r="B573" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
+        <v>848</v>
+      </c>
+      <c r="B574" t="s">
         <v>849</v>
-      </c>
-      <c r="B574" t="s">
-        <v>850</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B575" t="s">
         <v>851</v>
@@ -10177,20 +10177,20 @@
         <v>858</v>
       </c>
       <c r="B582" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
+        <v>859</v>
+      </c>
+      <c r="B583" t="s">
         <v>860</v>
-      </c>
-      <c r="B583" t="s">
-        <v>861</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B584" t="s">
         <v>862</v>
@@ -10209,12 +10209,12 @@
         <v>864</v>
       </c>
       <c r="B586" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B587" t="s">
         <v>866</v>
@@ -10225,12 +10225,12 @@
         <v>867</v>
       </c>
       <c r="B588" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B589" t="s">
         <v>869</v>
@@ -10241,20 +10241,20 @@
         <v>870</v>
       </c>
       <c r="B590" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
+        <v>871</v>
+      </c>
+      <c r="B591" t="s">
         <v>872</v>
-      </c>
-      <c r="B591" t="s">
-        <v>873</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="B592" t="s">
         <v>874</v>
@@ -10265,20 +10265,20 @@
         <v>875</v>
       </c>
       <c r="B593" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
+        <v>876</v>
+      </c>
+      <c r="B594" t="s">
         <v>877</v>
-      </c>
-      <c r="B594" t="s">
-        <v>878</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B595" t="s">
         <v>879</v>
@@ -10289,28 +10289,28 @@
         <v>880</v>
       </c>
       <c r="B596" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
+        <v>881</v>
+      </c>
+      <c r="B597" t="s">
         <v>882</v>
-      </c>
-      <c r="B597" t="s">
-        <v>883</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
+        <v>883</v>
+      </c>
+      <c r="B598" t="s">
         <v>884</v>
-      </c>
-      <c r="B598" t="s">
-        <v>885</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B599" t="s">
         <v>886</v>
@@ -10345,44 +10345,44 @@
         <v>890</v>
       </c>
       <c r="B603" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
+        <v>891</v>
+      </c>
+      <c r="B604" t="s">
         <v>892</v>
-      </c>
-      <c r="B604" t="s">
-        <v>893</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
+        <v>893</v>
+      </c>
+      <c r="B605" t="s">
         <v>894</v>
-      </c>
-      <c r="B605" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
+        <v>895</v>
+      </c>
+      <c r="B606" t="s">
         <v>896</v>
-      </c>
-      <c r="B606" t="s">
-        <v>897</v>
       </c>
     </row>
     <row r="607" spans="1:2">
       <c r="A607" t="s">
+        <v>897</v>
+      </c>
+      <c r="B607" t="s">
         <v>898</v>
-      </c>
-      <c r="B607" t="s">
-        <v>899</v>
       </c>
     </row>
     <row r="608" spans="1:2">
       <c r="A608" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B608" t="s">
         <v>900</v>
@@ -10401,12 +10401,12 @@
         <v>902</v>
       </c>
       <c r="B610" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B611" t="s">
         <v>904</v>
@@ -10449,12 +10449,12 @@
         <v>909</v>
       </c>
       <c r="B616" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B617" t="s">
         <v>911</v>
@@ -10497,20 +10497,20 @@
         <v>916</v>
       </c>
       <c r="B622" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
+        <v>917</v>
+      </c>
+      <c r="B623" t="s">
         <v>918</v>
-      </c>
-      <c r="B623" t="s">
-        <v>919</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B624" t="s">
         <v>920</v>
@@ -10521,12 +10521,12 @@
         <v>921</v>
       </c>
       <c r="B625" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B626" t="s">
         <v>923</v>
@@ -10537,12 +10537,12 @@
         <v>924</v>
       </c>
       <c r="B627" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B628" t="s">
         <v>926</v>
@@ -10729,36 +10729,36 @@
         <v>949</v>
       </c>
       <c r="B651" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
+        <v>950</v>
+      </c>
+      <c r="B652" t="s">
         <v>951</v>
-      </c>
-      <c r="B652" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
+        <v>952</v>
+      </c>
+      <c r="B653" t="s">
         <v>953</v>
-      </c>
-      <c r="B653" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
+        <v>954</v>
+      </c>
+      <c r="B654" t="s">
         <v>955</v>
-      </c>
-      <c r="B654" t="s">
-        <v>956</v>
       </c>
     </row>
     <row r="655" spans="1:2">
       <c r="A655" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B655" t="s">
         <v>957</v>
@@ -10785,12 +10785,12 @@
         <v>960</v>
       </c>
       <c r="B658" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B659" t="s">
         <v>962</v>
@@ -10809,12 +10809,12 @@
         <v>964</v>
       </c>
       <c r="B661" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="B662" t="s">
         <v>966</v>
@@ -10857,12 +10857,12 @@
         <v>971</v>
       </c>
       <c r="B667" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="B668" t="s">
         <v>973</v>
@@ -10913,12 +10913,12 @@
         <v>979</v>
       </c>
       <c r="B674" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="B675" t="s">
         <v>981</v>
@@ -10929,20 +10929,20 @@
         <v>982</v>
       </c>
       <c r="B676" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
+        <v>983</v>
+      </c>
+      <c r="B677" t="s">
         <v>984</v>
-      </c>
-      <c r="B677" t="s">
-        <v>985</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="B678" t="s">
         <v>986</v>
@@ -11009,20 +11009,20 @@
         <v>994</v>
       </c>
       <c r="B686" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
+        <v>995</v>
+      </c>
+      <c r="B687" t="s">
         <v>996</v>
-      </c>
-      <c r="B687" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="688" spans="1:2">
       <c r="A688" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="B688" t="s">
         <v>998</v>
@@ -11041,20 +11041,20 @@
         <v>1000</v>
       </c>
       <c r="B690" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B691" t="s">
         <v>1002</v>
-      </c>
-      <c r="B691" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B692" t="s">
         <v>1004</v>
@@ -11065,36 +11065,36 @@
         <v>1005</v>
       </c>
       <c r="B693" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="694" spans="1:2">
       <c r="A694" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B694" t="s">
         <v>1007</v>
-      </c>
-      <c r="B694" t="s">
-        <v>1008</v>
       </c>
     </row>
     <row r="695" spans="1:2">
       <c r="A695" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B695" t="s">
         <v>1009</v>
-      </c>
-      <c r="B695" t="s">
-        <v>1010</v>
       </c>
     </row>
     <row r="696" spans="1:2">
       <c r="A696" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B696" t="s">
         <v>1011</v>
-      </c>
-      <c r="B696" t="s">
-        <v>1012</v>
       </c>
     </row>
     <row r="697" spans="1:2">
       <c r="A697" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="B697" t="s">
         <v>1013</v>
@@ -11105,20 +11105,20 @@
         <v>1014</v>
       </c>
       <c r="B698" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="699" spans="1:2">
       <c r="A699" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B699" t="s">
         <v>1016</v>
-      </c>
-      <c r="B699" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="700" spans="1:2">
       <c r="A700" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="B700" t="s">
         <v>1018</v>
@@ -11129,44 +11129,44 @@
         <v>1019</v>
       </c>
       <c r="B701" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B702" t="s">
         <v>1021</v>
-      </c>
-      <c r="B702" t="s">
-        <v>1022</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B703" t="s">
         <v>1023</v>
-      </c>
-      <c r="B703" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B704" t="s">
         <v>1025</v>
-      </c>
-      <c r="B704" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="705" spans="1:2">
       <c r="A705" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B705" t="s">
         <v>1027</v>
-      </c>
-      <c r="B705" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="706" spans="1:2">
       <c r="A706" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="B706" t="s">
         <v>1029</v>
@@ -11201,12 +11201,12 @@
         <v>1033</v>
       </c>
       <c r="B710" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="B711" t="s">
         <v>1035</v>
@@ -11281,20 +11281,20 @@
         <v>1044</v>
       </c>
       <c r="B720" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B721" t="s">
         <v>1046</v>
-      </c>
-      <c r="B721" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="B722" t="s">
         <v>1048</v>
@@ -11313,12 +11313,12 @@
         <v>1050</v>
       </c>
       <c r="B724" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="B725" t="s">
         <v>1052</v>
@@ -11329,12 +11329,12 @@
         <v>1053</v>
       </c>
       <c r="B726" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="B727" t="s">
         <v>1055</v>
@@ -11345,12 +11345,12 @@
         <v>1056</v>
       </c>
       <c r="B728" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B729" t="s">
         <v>1058</v>
@@ -11361,12 +11361,12 @@
         <v>1059</v>
       </c>
       <c r="B730" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="B731" t="s">
         <v>1061</v>
@@ -11377,20 +11377,20 @@
         <v>1062</v>
       </c>
       <c r="B732" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B733" t="s">
         <v>1064</v>
-      </c>
-      <c r="B733" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
       <c r="B734" t="s">
         <v>1066</v>
@@ -11409,12 +11409,12 @@
         <v>1068</v>
       </c>
       <c r="B736" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B737" t="s">
         <v>1070</v>
@@ -11425,12 +11425,12 @@
         <v>1071</v>
       </c>
       <c r="B738" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B739" t="s">
         <v>1073</v>
@@ -11497,12 +11497,12 @@
         <v>1081</v>
       </c>
       <c r="B747" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B748" t="s">
         <v>1083</v>
@@ -11513,20 +11513,20 @@
         <v>1084</v>
       </c>
       <c r="B749" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B750" t="s">
         <v>1086</v>
-      </c>
-      <c r="B750" t="s">
-        <v>1087</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B751" t="s">
         <v>1088</v>
@@ -11561,12 +11561,12 @@
         <v>1092</v>
       </c>
       <c r="B755" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B756" t="s">
         <v>1094</v>
@@ -11585,36 +11585,36 @@
         <v>1096</v>
       </c>
       <c r="B758" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="759" spans="1:2">
       <c r="A759" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B759" t="s">
         <v>1098</v>
-      </c>
-      <c r="B759" t="s">
-        <v>1099</v>
       </c>
     </row>
     <row r="760" spans="1:2">
       <c r="A760" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B760" t="s">
         <v>1100</v>
-      </c>
-      <c r="B760" t="s">
-        <v>1101</v>
       </c>
     </row>
     <row r="761" spans="1:2">
       <c r="A761" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B761" t="s">
         <v>1102</v>
-      </c>
-      <c r="B761" t="s">
-        <v>1103</v>
       </c>
     </row>
     <row r="762" spans="1:2">
       <c r="A762" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B762" t="s">
         <v>1104</v>
@@ -11633,20 +11633,20 @@
         <v>1106</v>
       </c>
       <c r="B764" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B765" t="s">
         <v>1108</v>
-      </c>
-      <c r="B765" t="s">
-        <v>1109</v>
       </c>
     </row>
     <row r="766" spans="1:2">
       <c r="A766" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B766" t="s">
         <v>1110</v>
@@ -11657,12 +11657,12 @@
         <v>1111</v>
       </c>
       <c r="B767" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="768" spans="1:2">
       <c r="A768" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B768" t="s">
         <v>1113</v>
@@ -11681,44 +11681,44 @@
         <v>1115</v>
       </c>
       <c r="B770" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B771" t="s">
         <v>1117</v>
-      </c>
-      <c r="B771" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B772" t="s">
         <v>1119</v>
-      </c>
-      <c r="B772" t="s">
-        <v>1120</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B773" t="s">
         <v>1121</v>
-      </c>
-      <c r="B773" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="774" spans="1:2">
       <c r="A774" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B774" t="s">
         <v>1123</v>
-      </c>
-      <c r="B774" t="s">
-        <v>1124</v>
       </c>
     </row>
     <row r="775" spans="1:2">
       <c r="A775" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B775" t="s">
         <v>1125</v>
@@ -11729,20 +11729,20 @@
         <v>1126</v>
       </c>
       <c r="B776" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B777" t="s">
         <v>1128</v>
-      </c>
-      <c r="B777" t="s">
-        <v>1129</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B778" t="s">
         <v>1130</v>
@@ -11785,12 +11785,12 @@
         <v>1135</v>
       </c>
       <c r="B783" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B784" t="s">
         <v>1137</v>
@@ -11801,28 +11801,28 @@
         <v>1138</v>
       </c>
       <c r="B785" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B786" t="s">
         <v>1140</v>
-      </c>
-      <c r="B786" t="s">
-        <v>1141</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B787" t="s">
         <v>1142</v>
-      </c>
-      <c r="B787" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="788" spans="1:2">
       <c r="A788" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="B788" t="s">
         <v>1144</v>
@@ -11865,12 +11865,12 @@
         <v>1149</v>
       </c>
       <c r="B793" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="B794" t="s">
         <v>1151</v>
@@ -11985,36 +11985,36 @@
         <v>1165</v>
       </c>
       <c r="B808" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B809" t="s">
         <v>1167</v>
-      </c>
-      <c r="B809" t="s">
-        <v>1168</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B810" t="s">
         <v>1169</v>
-      </c>
-      <c r="B810" t="s">
-        <v>1170</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B811" t="s">
         <v>1171</v>
-      </c>
-      <c r="B811" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="812" spans="1:2">
       <c r="A812" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="B812" t="s">
         <v>1173</v>
@@ -12057,36 +12057,36 @@
         <v>1178</v>
       </c>
       <c r="B817" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B818" t="s">
         <v>1180</v>
-      </c>
-      <c r="B818" t="s">
-        <v>1181</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B819" t="s">
         <v>1182</v>
-      </c>
-      <c r="B819" t="s">
-        <v>1183</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B820" t="s">
         <v>1184</v>
-      </c>
-      <c r="B820" t="s">
-        <v>1185</v>
       </c>
     </row>
     <row r="821" spans="1:2">
       <c r="A821" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="B821" t="s">
         <v>1186</v>
@@ -12121,12 +12121,12 @@
         <v>1190</v>
       </c>
       <c r="B825" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="B826" t="s">
         <v>1192</v>
@@ -12153,28 +12153,28 @@
         <v>1195</v>
       </c>
       <c r="B829" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B830" t="s">
         <v>1197</v>
-      </c>
-      <c r="B830" t="s">
-        <v>1198</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B831" t="s">
         <v>1199</v>
-      </c>
-      <c r="B831" t="s">
-        <v>1200</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="B832" t="s">
         <v>1201</v>
@@ -12185,12 +12185,12 @@
         <v>1202</v>
       </c>
       <c r="B833" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="B834" t="s">
         <v>1204</v>
@@ -12217,12 +12217,12 @@
         <v>1207</v>
       </c>
       <c r="B837" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
       <c r="B838" t="s">
         <v>1209</v>
@@ -12265,12 +12265,12 @@
         <v>1214</v>
       </c>
       <c r="B843" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
       <c r="B844" t="s">
         <v>1216</v>
@@ -12417,36 +12417,36 @@
         <v>1234</v>
       </c>
       <c r="B862" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B863" t="s">
         <v>1236</v>
-      </c>
-      <c r="B863" t="s">
-        <v>1237</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B864" t="s">
         <v>1238</v>
-      </c>
-      <c r="B864" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B865" t="s">
         <v>1240</v>
-      </c>
-      <c r="B865" t="s">
-        <v>1241</v>
       </c>
     </row>
     <row r="866" spans="1:2">
       <c r="A866" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B866" t="s">
         <v>1242</v>
@@ -12473,12 +12473,12 @@
         <v>1245</v>
       </c>
       <c r="B869" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B870" t="s">
         <v>1247</v>
@@ -12569,12 +12569,12 @@
         <v>1258</v>
       </c>
       <c r="B881" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="B882" t="s">
         <v>1260</v>
@@ -12585,12 +12585,12 @@
         <v>1261</v>
       </c>
       <c r="B883" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="B884" t="s">
         <v>1263</v>
@@ -12601,20 +12601,20 @@
         <v>1264</v>
       </c>
       <c r="B885" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B886" t="s">
         <v>1266</v>
-      </c>
-      <c r="B886" t="s">
-        <v>1267</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B887" t="s">
         <v>1268</v>
@@ -12633,20 +12633,20 @@
         <v>1270</v>
       </c>
       <c r="B889" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B890" t="s">
         <v>1272</v>
-      </c>
-      <c r="B890" t="s">
-        <v>1273</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="B891" t="s">
         <v>1274</v>
@@ -12689,12 +12689,12 @@
         <v>1279</v>
       </c>
       <c r="B896" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="B897" t="s">
         <v>1281</v>
@@ -12737,12 +12737,12 @@
         <v>1286</v>
       </c>
       <c r="B902" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
       <c r="B903" t="s">
         <v>1288</v>
@@ -12753,12 +12753,12 @@
         <v>1289</v>
       </c>
       <c r="B904" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="B905" t="s">
         <v>1291</v>
@@ -12793,28 +12793,28 @@
         <v>1295</v>
       </c>
       <c r="B909" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B910" t="s">
         <v>1297</v>
-      </c>
-      <c r="B910" t="s">
-        <v>1298</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B911" t="s">
         <v>1299</v>
-      </c>
-      <c r="B911" t="s">
-        <v>1300</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
       <c r="B912" t="s">
         <v>1301</v>
@@ -12881,28 +12881,28 @@
         <v>1309</v>
       </c>
       <c r="B920" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
+        <v>1310</v>
+      </c>
+      <c r="B921" t="s">
         <v>1311</v>
-      </c>
-      <c r="B921" t="s">
-        <v>1312</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
+        <v>1312</v>
+      </c>
+      <c r="B922" t="s">
         <v>1313</v>
-      </c>
-      <c r="B922" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="B923" t="s">
         <v>1315</v>
@@ -12929,44 +12929,44 @@
         <v>1318</v>
       </c>
       <c r="B926" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B927" t="s">
         <v>1320</v>
-      </c>
-      <c r="B927" t="s">
-        <v>1321</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B928" t="s">
         <v>1322</v>
-      </c>
-      <c r="B928" t="s">
-        <v>1323</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B929" t="s">
         <v>1324</v>
-      </c>
-      <c r="B929" t="s">
-        <v>1325</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B930" t="s">
         <v>1326</v>
-      </c>
-      <c r="B930" t="s">
-        <v>1327</v>
       </c>
     </row>
     <row r="931" spans="1:2">
       <c r="A931" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B931" t="s">
         <v>1328</v>
@@ -12985,12 +12985,12 @@
         <v>1330</v>
       </c>
       <c r="B933" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="B934" t="s">
         <v>1332</v>
@@ -13001,20 +13001,20 @@
         <v>1333</v>
       </c>
       <c r="B935" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B936" t="s">
         <v>1335</v>
-      </c>
-      <c r="B936" t="s">
-        <v>1336</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="B937" t="s">
         <v>1337</v>
@@ -13025,20 +13025,20 @@
         <v>1338</v>
       </c>
       <c r="B938" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B939" t="s">
         <v>1340</v>
-      </c>
-      <c r="B939" t="s">
-        <v>1341</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="B940" t="s">
         <v>1342</v>
@@ -13073,60 +13073,60 @@
         <v>1346</v>
       </c>
       <c r="B944" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B945" t="s">
         <v>1348</v>
-      </c>
-      <c r="B945" t="s">
-        <v>1349</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B946" t="s">
         <v>1350</v>
-      </c>
-      <c r="B946" t="s">
-        <v>1351</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B947" t="s">
         <v>1352</v>
-      </c>
-      <c r="B947" t="s">
-        <v>1353</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B948" t="s">
         <v>1354</v>
-      </c>
-      <c r="B948" t="s">
-        <v>1355</v>
       </c>
     </row>
     <row r="949" spans="1:2">
       <c r="A949" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B949" t="s">
         <v>1356</v>
-      </c>
-      <c r="B949" t="s">
-        <v>1357</v>
       </c>
     </row>
     <row r="950" spans="1:2">
       <c r="A950" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B950" t="s">
         <v>1358</v>
-      </c>
-      <c r="B950" t="s">
-        <v>1359</v>
       </c>
     </row>
     <row r="951" spans="1:2">
       <c r="A951" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="B951" t="s">
         <v>1360</v>
@@ -13153,12 +13153,12 @@
         <v>1363</v>
       </c>
       <c r="B954" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
       <c r="B955" t="s">
         <v>1365</v>
@@ -13225,28 +13225,28 @@
         <v>1373</v>
       </c>
       <c r="B963" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B964" t="s">
         <v>1375</v>
-      </c>
-      <c r="B964" t="s">
-        <v>1376</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B965" t="s">
         <v>1377</v>
-      </c>
-      <c r="B965" t="s">
-        <v>1378</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="B966" t="s">
         <v>1379</v>
@@ -13265,28 +13265,28 @@
         <v>1381</v>
       </c>
       <c r="B968" t="s">
-        <v>1382</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B969" t="s">
         <v>1383</v>
-      </c>
-      <c r="B969" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B970" t="s">
         <v>1385</v>
-      </c>
-      <c r="B970" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="B971" t="s">
         <v>1387</v>
@@ -13305,12 +13305,12 @@
         <v>1389</v>
       </c>
       <c r="B973" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1391</v>
+        <v>1390</v>
       </c>
       <c r="B974" t="s">
         <v>1391</v>
@@ -13353,44 +13353,44 @@
         <v>1396</v>
       </c>
       <c r="B979" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B980" t="s">
         <v>1398</v>
-      </c>
-      <c r="B980" t="s">
-        <v>1399</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B981" t="s">
         <v>1400</v>
-      </c>
-      <c r="B981" t="s">
-        <v>1401</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B982" t="s">
         <v>1402</v>
-      </c>
-      <c r="B982" t="s">
-        <v>1403</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B983" t="s">
         <v>1404</v>
-      </c>
-      <c r="B983" t="s">
-        <v>1405</v>
       </c>
     </row>
     <row r="984" spans="1:2">
       <c r="A984" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="B984" t="s">
         <v>1406</v>
@@ -13457,12 +13457,12 @@
         <v>1414</v>
       </c>
       <c r="B992" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="B993" t="s">
         <v>1416</v>
@@ -13489,12 +13489,12 @@
         <v>1419</v>
       </c>
       <c r="B996" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="B997" t="s">
         <v>1421</v>
@@ -13553,20 +13553,20 @@
         <v>1428</v>
       </c>
       <c r="B1004" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B1005" t="s">
         <v>1430</v>
-      </c>
-      <c r="B1005" t="s">
-        <v>1431</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="B1006" t="s">
         <v>1432</v>
@@ -13593,12 +13593,12 @@
         <v>1435</v>
       </c>
       <c r="B1009" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B1010" t="s">
         <v>1437</v>
@@ -13609,20 +13609,20 @@
         <v>1438</v>
       </c>
       <c r="B1011" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B1012" t="s">
         <v>1440</v>
-      </c>
-      <c r="B1012" t="s">
-        <v>1441</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B1013" t="s">
         <v>1442</v>
@@ -13657,12 +13657,12 @@
         <v>1446</v>
       </c>
       <c r="B1017" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="B1018" t="s">
         <v>1448</v>
@@ -13697,20 +13697,20 @@
         <v>1452</v>
       </c>
       <c r="B1022" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B1023" t="s">
         <v>1454</v>
-      </c>
-      <c r="B1023" t="s">
-        <v>1455</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="B1024" t="s">
         <v>1456</v>
@@ -13745,20 +13745,20 @@
         <v>1460</v>
       </c>
       <c r="B1028" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B1029" t="s">
         <v>1462</v>
-      </c>
-      <c r="B1029" t="s">
-        <v>1463</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B1030" t="s">
         <v>1464</v>
@@ -13777,20 +13777,20 @@
         <v>1466</v>
       </c>
       <c r="B1032" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B1033" t="s">
         <v>1468</v>
-      </c>
-      <c r="B1033" t="s">
-        <v>1469</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B1034" t="s">
         <v>1470</v>
@@ -13801,12 +13801,12 @@
         <v>1471</v>
       </c>
       <c r="B1035" t="s">
-        <v>1472</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="B1036" t="s">
         <v>1473</v>
@@ -13889,12 +13889,12 @@
         <v>1483</v>
       </c>
       <c r="B1046" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1485</v>
+        <v>1484</v>
       </c>
       <c r="B1047" t="s">
         <v>1485</v>
@@ -13905,28 +13905,28 @@
         <v>1486</v>
       </c>
       <c r="B1048" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
+        <v>1487</v>
+      </c>
+      <c r="B1049" t="s">
         <v>1488</v>
-      </c>
-      <c r="B1049" t="s">
-        <v>1489</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B1050" t="s">
         <v>1490</v>
-      </c>
-      <c r="B1050" t="s">
-        <v>1491</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="B1051" t="s">
         <v>1492</v>
@@ -13945,12 +13945,12 @@
         <v>1494</v>
       </c>
       <c r="B1053" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1496</v>
+        <v>1495</v>
       </c>
       <c r="B1054" t="s">
         <v>1496</v>
@@ -13961,12 +13961,12 @@
         <v>1497</v>
       </c>
       <c r="B1055" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
       <c r="B1056" t="s">
         <v>1499</v>
@@ -14017,68 +14017,68 @@
         <v>1505</v>
       </c>
       <c r="B1062" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B1063" t="s">
         <v>1507</v>
-      </c>
-      <c r="B1063" t="s">
-        <v>1508</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B1064" t="s">
         <v>1509</v>
-      </c>
-      <c r="B1064" t="s">
-        <v>1510</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
+        <v>1510</v>
+      </c>
+      <c r="B1065" t="s">
         <v>1511</v>
-      </c>
-      <c r="B1065" t="s">
-        <v>1512</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B1066" t="s">
         <v>1513</v>
-      </c>
-      <c r="B1066" t="s">
-        <v>1514</v>
       </c>
     </row>
     <row r="1067" spans="1:2">
       <c r="A1067" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B1067" t="s">
         <v>1515</v>
-      </c>
-      <c r="B1067" t="s">
-        <v>1516</v>
       </c>
     </row>
     <row r="1068" spans="1:2">
       <c r="A1068" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B1068" t="s">
         <v>1517</v>
-      </c>
-      <c r="B1068" t="s">
-        <v>1518</v>
       </c>
     </row>
     <row r="1069" spans="1:2">
       <c r="A1069" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B1069" t="s">
         <v>1519</v>
-      </c>
-      <c r="B1069" t="s">
-        <v>1520</v>
       </c>
     </row>
     <row r="1070" spans="1:2">
       <c r="A1070" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="B1070" t="s">
         <v>1521</v>
@@ -14089,12 +14089,12 @@
         <v>1522</v>
       </c>
       <c r="B1071" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="B1072" t="s">
         <v>1524</v>
@@ -14121,12 +14121,12 @@
         <v>1527</v>
       </c>
       <c r="B1075" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B1076" t="s">
         <v>1529</v>
@@ -14137,20 +14137,20 @@
         <v>1530</v>
       </c>
       <c r="B1077" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B1078" t="s">
         <v>1532</v>
-      </c>
-      <c r="B1078" t="s">
-        <v>1533</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
       <c r="B1079" t="s">
         <v>1534</v>
@@ -14177,12 +14177,12 @@
         <v>1537</v>
       </c>
       <c r="B1082" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="B1083" t="s">
         <v>1539</v>
@@ -14209,12 +14209,12 @@
         <v>1542</v>
       </c>
       <c r="B1086" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="B1087" t="s">
         <v>1544</v>
@@ -14233,12 +14233,12 @@
         <v>1546</v>
       </c>
       <c r="B1089" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="B1090" t="s">
         <v>1548</v>
@@ -14249,12 +14249,12 @@
         <v>1549</v>
       </c>
       <c r="B1091" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
       <c r="B1092" t="s">
         <v>1551</v>
@@ -14281,12 +14281,12 @@
         <v>1554</v>
       </c>
       <c r="B1095" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B1096" t="s">
         <v>1556</v>
@@ -14305,36 +14305,36 @@
         <v>1558</v>
       </c>
       <c r="B1098" t="s">
-        <v>1559</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
+        <v>1559</v>
+      </c>
+      <c r="B1099" t="s">
         <v>1560</v>
-      </c>
-      <c r="B1099" t="s">
-        <v>1561</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B1100" t="s">
         <v>1562</v>
-      </c>
-      <c r="B1100" t="s">
-        <v>1563</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B1101" t="s">
         <v>1564</v>
-      </c>
-      <c r="B1101" t="s">
-        <v>1565</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="B1102" t="s">
         <v>1566</v>
@@ -14353,36 +14353,36 @@
         <v>1568</v>
       </c>
       <c r="B1104" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B1105" t="s">
         <v>1570</v>
-      </c>
-      <c r="B1105" t="s">
-        <v>1571</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B1106" t="s">
         <v>1572</v>
-      </c>
-      <c r="B1106" t="s">
-        <v>1573</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B1107" t="s">
         <v>1574</v>
-      </c>
-      <c r="B1107" t="s">
-        <v>1575</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B1108" t="s">
         <v>1576</v>
@@ -14433,12 +14433,12 @@
         <v>1582</v>
       </c>
       <c r="B1114" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1584</v>
+        <v>1583</v>
       </c>
       <c r="B1115" t="s">
         <v>1584</v>
@@ -14457,12 +14457,12 @@
         <v>1586</v>
       </c>
       <c r="B1117" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="B1118" t="s">
         <v>1588</v>
@@ -14513,12 +14513,12 @@
         <v>1594</v>
       </c>
       <c r="B1124" t="s">
-        <v>1595</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="B1125" t="s">
         <v>1596</v>
@@ -14537,20 +14537,20 @@
         <v>1598</v>
       </c>
       <c r="B1127" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B1128" t="s">
         <v>1600</v>
-      </c>
-      <c r="B1128" t="s">
-        <v>1601</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B1129" t="s">
         <v>1602</v>
@@ -14569,100 +14569,100 @@
         <v>1604</v>
       </c>
       <c r="B1131" t="s">
-        <v>1605</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B1132" t="s">
         <v>1606</v>
-      </c>
-      <c r="B1132" t="s">
-        <v>1607</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B1133" t="s">
         <v>1608</v>
-      </c>
-      <c r="B1133" t="s">
-        <v>1609</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B1134" t="s">
         <v>1610</v>
-      </c>
-      <c r="B1134" t="s">
-        <v>1611</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B1135" t="s">
         <v>1612</v>
-      </c>
-      <c r="B1135" t="s">
-        <v>1613</v>
       </c>
     </row>
     <row r="1136" spans="1:2">
       <c r="A1136" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B1136" t="s">
         <v>1614</v>
-      </c>
-      <c r="B1136" t="s">
-        <v>1615</v>
       </c>
     </row>
     <row r="1137" spans="1:2">
       <c r="A1137" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B1137" t="s">
         <v>1616</v>
-      </c>
-      <c r="B1137" t="s">
-        <v>1617</v>
       </c>
     </row>
     <row r="1138" spans="1:2">
       <c r="A1138" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B1138" t="s">
         <v>1618</v>
-      </c>
-      <c r="B1138" t="s">
-        <v>1619</v>
       </c>
     </row>
     <row r="1139" spans="1:2">
       <c r="A1139" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B1139" t="s">
         <v>1620</v>
-      </c>
-      <c r="B1139" t="s">
-        <v>1621</v>
       </c>
     </row>
     <row r="1140" spans="1:2">
       <c r="A1140" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B1140" t="s">
         <v>1622</v>
-      </c>
-      <c r="B1140" t="s">
-        <v>1623</v>
       </c>
     </row>
     <row r="1141" spans="1:2">
       <c r="A1141" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B1141" t="s">
         <v>1624</v>
-      </c>
-      <c r="B1141" t="s">
-        <v>1625</v>
       </c>
     </row>
     <row r="1142" spans="1:2">
       <c r="A1142" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B1142" t="s">
         <v>1626</v>
-      </c>
-      <c r="B1142" t="s">
-        <v>1627</v>
       </c>
     </row>
     <row r="1143" spans="1:2">
       <c r="A1143" t="s">
-        <v>1628</v>
+        <v>1627</v>
       </c>
       <c r="B1143" t="s">
         <v>1628</v>
@@ -14705,20 +14705,20 @@
         <v>1633</v>
       </c>
       <c r="B1148" t="s">
-        <v>1634</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B1149" t="s">
         <v>1635</v>
-      </c>
-      <c r="B1149" t="s">
-        <v>1636</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1637</v>
+        <v>1636</v>
       </c>
       <c r="B1150" t="s">
         <v>1637</v>
@@ -14753,12 +14753,12 @@
         <v>1641</v>
       </c>
       <c r="B1154" t="s">
-        <v>1642</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="B1155" t="s">
         <v>1643</v>
@@ -14777,36 +14777,36 @@
         <v>1645</v>
       </c>
       <c r="B1157" t="s">
-        <v>1646</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B1158" t="s">
         <v>1647</v>
-      </c>
-      <c r="B1158" t="s">
-        <v>1648</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B1159" t="s">
         <v>1649</v>
-      </c>
-      <c r="B1159" t="s">
-        <v>1650</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B1160" t="s">
         <v>1651</v>
-      </c>
-      <c r="B1160" t="s">
-        <v>1652</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="B1161" t="s">
         <v>1653</v>
@@ -14817,20 +14817,20 @@
         <v>1654</v>
       </c>
       <c r="B1162" t="s">
-        <v>1655</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B1163" t="s">
         <v>1656</v>
-      </c>
-      <c r="B1163" t="s">
-        <v>1657</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="B1164" t="s">
         <v>1658</v>
@@ -14841,28 +14841,28 @@
         <v>1659</v>
       </c>
       <c r="B1165" t="s">
-        <v>1660</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B1166" t="s">
         <v>1661</v>
-      </c>
-      <c r="B1166" t="s">
-        <v>1662</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B1167" t="s">
         <v>1663</v>
-      </c>
-      <c r="B1167" t="s">
-        <v>1664</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="B1168" t="s">
         <v>1665</v>
@@ -14985,12 +14985,12 @@
         <v>1680</v>
       </c>
       <c r="B1183" t="s">
-        <v>1681</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="B1184" t="s">
         <v>1682</v>
@@ -15025,12 +15025,12 @@
         <v>1686</v>
       </c>
       <c r="B1188" t="s">
-        <v>1687</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="B1189" t="s">
         <v>1688</v>
@@ -15105,7 +15105,7 @@
         <v>1698</v>
       </c>
       <c r="B1198" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
@@ -15129,7 +15129,7 @@
         <v>1701</v>
       </c>
       <c r="B1201" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
@@ -15153,7 +15153,7 @@
         <v>1704</v>
       </c>
       <c r="B1204" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="1205" spans="1:2">
@@ -15177,7 +15177,7 @@
         <v>1707</v>
       </c>
       <c r="B1207" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="1208" spans="1:2">
@@ -15185,7 +15185,7 @@
         <v>1708</v>
       </c>
       <c r="B1208" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="1209" spans="1:2">
@@ -15225,7 +15225,7 @@
         <v>1713</v>
       </c>
       <c r="B1213" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="1214" spans="1:2">
@@ -15257,7 +15257,7 @@
         <v>1717</v>
       </c>
       <c r="B1217" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
   </sheetData>

--- a/lang/da/headTags.xlsx
+++ b/lang/da/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1217</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1218</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1720">
   <si>
     <t>en</t>
   </si>
@@ -3785,6 +3785,12 @@
   </si>
   <si>
     <t>Predator</t>
+  </si>
+  <si>
+    <t>Prehistoric Creature</t>
+  </si>
+  <si>
+    <t>Forhistorisk væsen</t>
   </si>
   <si>
     <t>Present</t>
@@ -5517,7 +5523,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1217"/>
+  <dimension ref="A1:B1218"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -12553,28 +12559,28 @@
         <v>1256</v>
       </c>
       <c r="B879" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B880" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B881" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B882" t="s">
         <v>1260</v>
@@ -12585,12 +12591,12 @@
         <v>1261</v>
       </c>
       <c r="B883" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B884" t="s">
         <v>1263</v>
@@ -12601,12 +12607,12 @@
         <v>1264</v>
       </c>
       <c r="B885" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B886" t="s">
         <v>1266</v>
@@ -12625,20 +12631,20 @@
         <v>1269</v>
       </c>
       <c r="B888" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B889" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B890" t="s">
         <v>1272</v>
@@ -12657,44 +12663,44 @@
         <v>1275</v>
       </c>
       <c r="B892" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B893" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B894" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B895" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B896" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B897" t="s">
         <v>1281</v>
@@ -12705,44 +12711,44 @@
         <v>1282</v>
       </c>
       <c r="B898" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B899" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B900" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B901" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B902" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B903" t="s">
         <v>1288</v>
@@ -12753,12 +12759,12 @@
         <v>1289</v>
       </c>
       <c r="B904" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B905" t="s">
         <v>1291</v>
@@ -12769,36 +12775,36 @@
         <v>1292</v>
       </c>
       <c r="B906" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B907" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B908" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B909" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B910" t="s">
         <v>1297</v>
@@ -12825,68 +12831,68 @@
         <v>1302</v>
       </c>
       <c r="B913" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="914" spans="1:2">
       <c r="A914" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="B914" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="B915" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B916" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B917" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B918" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B919" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B920" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B921" t="s">
         <v>1311</v>
@@ -12913,28 +12919,28 @@
         <v>1316</v>
       </c>
       <c r="B924" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="925" spans="1:2">
       <c r="A925" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B925" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="B926" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B927" t="s">
         <v>1320</v>
@@ -12977,20 +12983,20 @@
         <v>1329</v>
       </c>
       <c r="B932" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="933" spans="1:2">
       <c r="A933" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B933" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B934" t="s">
         <v>1332</v>
@@ -13001,12 +13007,12 @@
         <v>1333</v>
       </c>
       <c r="B935" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B936" t="s">
         <v>1335</v>
@@ -13025,12 +13031,12 @@
         <v>1338</v>
       </c>
       <c r="B938" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B939" t="s">
         <v>1340</v>
@@ -13049,36 +13055,36 @@
         <v>1343</v>
       </c>
       <c r="B941" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="B942" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B943" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B944" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B945" t="s">
         <v>1348</v>
@@ -13137,28 +13143,28 @@
         <v>1361</v>
       </c>
       <c r="B952" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="953" spans="1:2">
       <c r="A953" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B953" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B954" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B955" t="s">
         <v>1365</v>
@@ -13169,68 +13175,68 @@
         <v>1366</v>
       </c>
       <c r="B956" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B957" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B958" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B959" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B960" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B961" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B962" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B963" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B964" t="s">
         <v>1375</v>
@@ -13257,20 +13263,20 @@
         <v>1380</v>
       </c>
       <c r="B967" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
     </row>
     <row r="968" spans="1:2">
       <c r="A968" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="B968" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B969" t="s">
         <v>1383</v>
@@ -13297,20 +13303,20 @@
         <v>1388</v>
       </c>
       <c r="B972" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="973" spans="1:2">
       <c r="A973" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="B973" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B974" t="s">
         <v>1391</v>
@@ -13321,44 +13327,44 @@
         <v>1392</v>
       </c>
       <c r="B975" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B976" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B977" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B978" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B979" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B980" t="s">
         <v>1398</v>
@@ -13401,68 +13407,68 @@
         <v>1407</v>
       </c>
       <c r="B985" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="986" spans="1:2">
       <c r="A986" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B986" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="B987" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B988" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="B989" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B990" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B991" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B992" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B993" t="s">
         <v>1416</v>
@@ -13473,28 +13479,28 @@
         <v>1417</v>
       </c>
       <c r="B994" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B995" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B996" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B997" t="s">
         <v>1421</v>
@@ -13505,60 +13511,60 @@
         <v>1422</v>
       </c>
       <c r="B998" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B999" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B1000" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B1001" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B1002" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B1003" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B1004" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B1005" t="s">
         <v>1430</v>
@@ -13577,28 +13583,28 @@
         <v>1433</v>
       </c>
       <c r="B1007" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B1008" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B1009" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B1010" t="s">
         <v>1437</v>
@@ -13609,12 +13615,12 @@
         <v>1438</v>
       </c>
       <c r="B1011" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B1012" t="s">
         <v>1440</v>
@@ -13633,36 +13639,36 @@
         <v>1443</v>
       </c>
       <c r="B1014" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B1015" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B1016" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B1017" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="B1018" t="s">
         <v>1448</v>
@@ -13673,36 +13679,36 @@
         <v>1449</v>
       </c>
       <c r="B1019" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B1020" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B1021" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B1022" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B1023" t="s">
         <v>1454</v>
@@ -13721,36 +13727,36 @@
         <v>1457</v>
       </c>
       <c r="B1025" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B1026" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B1027" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B1028" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B1029" t="s">
         <v>1462</v>
@@ -13769,20 +13775,20 @@
         <v>1465</v>
       </c>
       <c r="B1031" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B1032" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B1033" t="s">
         <v>1468</v>
@@ -13801,12 +13807,12 @@
         <v>1471</v>
       </c>
       <c r="B1035" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B1036" t="s">
         <v>1473</v>
@@ -13817,84 +13823,84 @@
         <v>1474</v>
       </c>
       <c r="B1037" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="B1038" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B1039" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B1040" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B1041" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B1042" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B1043" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B1044" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B1045" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B1046" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B1047" t="s">
         <v>1485</v>
@@ -13905,12 +13911,12 @@
         <v>1486</v>
       </c>
       <c r="B1048" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B1049" t="s">
         <v>1488</v>
@@ -13937,20 +13943,20 @@
         <v>1493</v>
       </c>
       <c r="B1052" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="1053" spans="1:2">
       <c r="A1053" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B1053" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="B1054" t="s">
         <v>1496</v>
@@ -13961,12 +13967,12 @@
         <v>1497</v>
       </c>
       <c r="B1055" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B1056" t="s">
         <v>1499</v>
@@ -13977,52 +13983,52 @@
         <v>1500</v>
       </c>
       <c r="B1057" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B1058" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B1059" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B1060" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B1061" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B1062" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B1063" t="s">
         <v>1507</v>
@@ -14089,12 +14095,12 @@
         <v>1522</v>
       </c>
       <c r="B1071" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="1072" spans="1:2">
       <c r="A1072" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B1072" t="s">
         <v>1524</v>
@@ -14105,28 +14111,28 @@
         <v>1525</v>
       </c>
       <c r="B1073" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B1074" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B1075" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B1076" t="s">
         <v>1529</v>
@@ -14137,12 +14143,12 @@
         <v>1530</v>
       </c>
       <c r="B1077" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B1078" t="s">
         <v>1532</v>
@@ -14161,28 +14167,28 @@
         <v>1535</v>
       </c>
       <c r="B1080" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="B1081" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B1082" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B1083" t="s">
         <v>1539</v>
@@ -14193,28 +14199,28 @@
         <v>1540</v>
       </c>
       <c r="B1084" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B1085" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B1086" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B1087" t="s">
         <v>1544</v>
@@ -14225,20 +14231,20 @@
         <v>1545</v>
       </c>
       <c r="B1088" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B1089" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B1090" t="s">
         <v>1548</v>
@@ -14249,12 +14255,12 @@
         <v>1549</v>
       </c>
       <c r="B1091" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B1092" t="s">
         <v>1551</v>
@@ -14265,28 +14271,28 @@
         <v>1552</v>
       </c>
       <c r="B1093" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B1094" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B1095" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B1096" t="s">
         <v>1556</v>
@@ -14297,20 +14303,20 @@
         <v>1557</v>
       </c>
       <c r="B1097" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B1098" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B1099" t="s">
         <v>1560</v>
@@ -14345,20 +14351,20 @@
         <v>1567</v>
       </c>
       <c r="B1103" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="1104" spans="1:2">
       <c r="A1104" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B1104" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="B1105" t="s">
         <v>1570</v>
@@ -14393,52 +14399,52 @@
         <v>1577</v>
       </c>
       <c r="B1109" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="1110" spans="1:2">
       <c r="A1110" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B1110" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B1111" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B1112" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B1113" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B1114" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B1115" t="s">
         <v>1584</v>
@@ -14449,20 +14455,20 @@
         <v>1585</v>
       </c>
       <c r="B1116" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B1117" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B1118" t="s">
         <v>1588</v>
@@ -14473,52 +14479,52 @@
         <v>1589</v>
       </c>
       <c r="B1119" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B1120" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B1121" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B1122" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B1123" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B1124" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B1125" t="s">
         <v>1596</v>
@@ -14529,20 +14535,20 @@
         <v>1597</v>
       </c>
       <c r="B1126" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1127" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B1128" t="s">
         <v>1600</v>
@@ -14561,20 +14567,20 @@
         <v>1603</v>
       </c>
       <c r="B1130" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B1131" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B1132" t="s">
         <v>1606</v>
@@ -14673,44 +14679,44 @@
         <v>1629</v>
       </c>
       <c r="B1144" t="s">
-        <v>1629</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="1145" spans="1:2">
       <c r="A1145" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
       <c r="B1145" t="s">
-        <v>1630</v>
+        <v>1631</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
       <c r="B1146" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B1147" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B1148" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B1149" t="s">
         <v>1635</v>
@@ -14729,36 +14735,36 @@
         <v>1638</v>
       </c>
       <c r="B1151" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B1152" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B1153" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B1154" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B1155" t="s">
         <v>1643</v>
@@ -14769,20 +14775,20 @@
         <v>1644</v>
       </c>
       <c r="B1156" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B1157" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B1158" t="s">
         <v>1647</v>
@@ -14817,12 +14823,12 @@
         <v>1654</v>
       </c>
       <c r="B1162" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
     </row>
     <row r="1163" spans="1:2">
       <c r="A1163" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B1163" t="s">
         <v>1656</v>
@@ -14841,12 +14847,12 @@
         <v>1659</v>
       </c>
       <c r="B1165" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="B1166" t="s">
         <v>1661</v>
@@ -14873,124 +14879,124 @@
         <v>1666</v>
       </c>
       <c r="B1169" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="1170" spans="1:2">
       <c r="A1170" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="B1170" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="B1171" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B1172" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B1173" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B1174" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B1175" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B1176" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B1177" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B1178" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B1179" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B1180" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1181" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B1182" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1183" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B1184" t="s">
         <v>1682</v>
@@ -15001,36 +15007,36 @@
         <v>1683</v>
       </c>
       <c r="B1185" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B1186" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B1187" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B1188" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1189" t="s">
         <v>1688</v>
@@ -15049,219 +15055,227 @@
         <v>1691</v>
       </c>
       <c r="B1191" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1192" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B1193" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B1194" t="s">
-        <v>384</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1195" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
       <c r="A1196" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1196" t="s">
-        <v>1696</v>
+        <v>386</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
       <c r="A1197" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1197" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1198" t="s">
-        <v>645</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
       <c r="A1199" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1199" t="s">
-        <v>1699</v>
+        <v>645</v>
       </c>
     </row>
     <row r="1200" spans="1:2">
       <c r="A1200" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1200" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1201" spans="1:2">
       <c r="A1201" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1201" t="s">
-        <v>926</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
       <c r="A1202" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B1202" t="s">
-        <v>1702</v>
+        <v>926</v>
       </c>
     </row>
     <row r="1203" spans="1:2">
       <c r="A1203" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B1203" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="1204" spans="1:2">
       <c r="A1204" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B1204" t="s">
-        <v>1002</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1205" spans="1:2">
       <c r="A1205" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B1205" t="s">
-        <v>1705</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="1206" spans="1:2">
       <c r="A1206" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1206" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="1207" spans="1:2">
       <c r="A1207" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1207" t="s">
-        <v>1070</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1208" spans="1:2">
       <c r="A1208" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B1208" t="s">
-        <v>1125</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="1209" spans="1:2">
       <c r="A1209" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B1209" t="s">
-        <v>1709</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="1210" spans="1:2">
       <c r="A1210" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B1210" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="1211" spans="1:2">
       <c r="A1211" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B1211" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1212" spans="1:2">
       <c r="A1212" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1212" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="1213" spans="1:2">
       <c r="A1213" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="B1213" t="s">
-        <v>1432</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1214" spans="1:2">
       <c r="A1214" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B1214" t="s">
-        <v>1714</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="1215" spans="1:2">
       <c r="A1215" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B1215" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="1216" spans="1:2">
       <c r="A1216" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B1216" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="1217" spans="1:2">
       <c r="A1217" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B1217" t="s">
-        <v>1551</v>
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:2">
+      <c r="A1218" t="s">
+        <v>1719</v>
+      </c>
+      <c r="B1218" t="s">
+        <v>1553</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1217"/>
+  <autoFilter ref="A1:B1218"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/da/headTags.xlsx
+++ b/lang/da/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1218</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1219</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1722">
   <si>
     <t>en</t>
   </si>
@@ -299,6 +299,12 @@
   </si>
   <si>
     <t>Tilbage til fremtiden</t>
+  </si>
+  <si>
+    <t>Backrooms (Movie)</t>
+  </si>
+  <si>
+    <t>Backrooms (film)</t>
   </si>
   <si>
     <t>Bag</t>
@@ -5523,7 +5529,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1218"/>
+  <dimension ref="A1:B1219"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -6079,20 +6085,20 @@
         <v>98</v>
       </c>
       <c r="B69" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B70" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B71" t="s">
         <v>101</v>
@@ -6103,36 +6109,36 @@
         <v>102</v>
       </c>
       <c r="B72" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B73" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B74" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B75" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B76" t="s">
         <v>107</v>
@@ -6143,12 +6149,12 @@
         <v>108</v>
       </c>
       <c r="B77" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B78" t="s">
         <v>110</v>
@@ -6167,12 +6173,12 @@
         <v>113</v>
       </c>
       <c r="B80" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B81" t="s">
         <v>115</v>
@@ -6183,12 +6189,12 @@
         <v>116</v>
       </c>
       <c r="B82" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B83" t="s">
         <v>118</v>
@@ -6215,12 +6221,12 @@
         <v>123</v>
       </c>
       <c r="B86" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B87" t="s">
         <v>125</v>
@@ -6239,12 +6245,12 @@
         <v>128</v>
       </c>
       <c r="B89" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B90" t="s">
         <v>130</v>
@@ -6255,20 +6261,20 @@
         <v>131</v>
       </c>
       <c r="B91" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B92" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B93" t="s">
         <v>134</v>
@@ -6279,12 +6285,12 @@
         <v>135</v>
       </c>
       <c r="B94" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B95" t="s">
         <v>137</v>
@@ -6295,76 +6301,76 @@
         <v>138</v>
       </c>
       <c r="B96" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B97" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B98" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B99" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B100" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B101" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B102" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B103" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B104" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B105" t="s">
         <v>148</v>
@@ -6375,36 +6381,36 @@
         <v>149</v>
       </c>
       <c r="B106" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B107" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B108" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B109" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B110" t="s">
         <v>154</v>
@@ -6415,52 +6421,52 @@
         <v>155</v>
       </c>
       <c r="B111" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B112" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B113" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B114" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B115" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B116" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B117" t="s">
         <v>162</v>
@@ -6503,108 +6509,108 @@
         <v>171</v>
       </c>
       <c r="B122" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B123" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="124" spans="1:2">
       <c r="A124" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B124" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="125" spans="1:2">
       <c r="A125" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B125" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="126" spans="1:2">
       <c r="A126" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B126" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="127" spans="1:2">
       <c r="A127" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B127" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="128" spans="1:2">
       <c r="A128" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B128" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="129" spans="1:2">
       <c r="A129" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B129" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="130" spans="1:2">
       <c r="A130" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B130" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="131" spans="1:2">
       <c r="A131" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B131" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="132" spans="1:2">
       <c r="A132" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B132" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="133" spans="1:2">
       <c r="A133" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B133" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="134" spans="1:2">
       <c r="A134" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B134" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="135" spans="1:2">
       <c r="A135" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B135" t="s">
         <v>185</v>
@@ -6623,20 +6629,20 @@
         <v>188</v>
       </c>
       <c r="B137" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="138" spans="1:2">
       <c r="A138" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B138" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="139" spans="1:2">
       <c r="A139" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B139" t="s">
         <v>191</v>
@@ -6647,20 +6653,20 @@
         <v>192</v>
       </c>
       <c r="B140" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="141" spans="1:2">
       <c r="A141" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B141" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="142" spans="1:2">
       <c r="A142" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B142" t="s">
         <v>195</v>
@@ -6679,20 +6685,20 @@
         <v>198</v>
       </c>
       <c r="B144" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="145" spans="1:2">
       <c r="A145" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B145" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="146" spans="1:2">
       <c r="A146" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B146" t="s">
         <v>201</v>
@@ -6727,36 +6733,36 @@
         <v>208</v>
       </c>
       <c r="B150" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="151" spans="1:2">
       <c r="A151" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B151" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="152" spans="1:2">
       <c r="A152" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B152" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="153" spans="1:2">
       <c r="A153" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B153" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="154" spans="1:2">
       <c r="A154" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B154" t="s">
         <v>213</v>
@@ -6807,12 +6813,12 @@
         <v>224</v>
       </c>
       <c r="B160" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="161" spans="1:2">
       <c r="A161" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B161" t="s">
         <v>226</v>
@@ -6903,12 +6909,12 @@
         <v>247</v>
       </c>
       <c r="B172" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="173" spans="1:2">
       <c r="A173" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B173" t="s">
         <v>249</v>
@@ -6935,36 +6941,36 @@
         <v>254</v>
       </c>
       <c r="B176" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="177" spans="1:2">
       <c r="A177" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B177" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="178" spans="1:2">
       <c r="A178" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B178" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="179" spans="1:2">
       <c r="A179" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B179" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
     </row>
     <row r="180" spans="1:2">
       <c r="A180" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B180" t="s">
         <v>259</v>
@@ -6975,20 +6981,20 @@
         <v>260</v>
       </c>
       <c r="B181" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
     </row>
     <row r="182" spans="1:2">
       <c r="A182" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B182" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="183" spans="1:2">
       <c r="A183" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B183" t="s">
         <v>263</v>
@@ -6999,12 +7005,12 @@
         <v>264</v>
       </c>
       <c r="B184" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="185" spans="1:2">
       <c r="A185" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B185" t="s">
         <v>265</v>
@@ -7012,7 +7018,7 @@
     </row>
     <row r="186" spans="1:2">
       <c r="A186" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B186" t="s">
         <v>267</v>
@@ -7031,20 +7037,20 @@
         <v>270</v>
       </c>
       <c r="B188" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="189" spans="1:2">
       <c r="A189" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B189" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="190" spans="1:2">
       <c r="A190" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B190" t="s">
         <v>273</v>
@@ -7071,28 +7077,28 @@
         <v>278</v>
       </c>
       <c r="B193" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="194" spans="1:2">
       <c r="A194" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B194" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="195" spans="1:2">
       <c r="A195" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B195" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="196" spans="1:2">
       <c r="A196" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B196" t="s">
         <v>282</v>
@@ -7119,36 +7125,36 @@
         <v>287</v>
       </c>
       <c r="B199" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="200" spans="1:2">
       <c r="A200" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B200" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="201" spans="1:2">
       <c r="A201" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B201" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="202" spans="1:2">
       <c r="A202" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B202" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="203" spans="1:2">
       <c r="A203" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B203" t="s">
         <v>292</v>
@@ -7167,20 +7173,20 @@
         <v>295</v>
       </c>
       <c r="B205" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="206" spans="1:2">
       <c r="A206" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B206" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="207" spans="1:2">
       <c r="A207" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B207" t="s">
         <v>298</v>
@@ -7199,20 +7205,20 @@
         <v>301</v>
       </c>
       <c r="B209" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="210" spans="1:2">
       <c r="A210" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B210" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="211" spans="1:2">
       <c r="A211" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B211" t="s">
         <v>304</v>
@@ -7279,12 +7285,12 @@
         <v>319</v>
       </c>
       <c r="B219" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="220" spans="1:2">
       <c r="A220" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B220" t="s">
         <v>321</v>
@@ -7295,36 +7301,36 @@
         <v>322</v>
       </c>
       <c r="B221" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="222" spans="1:2">
       <c r="A222" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B222" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="223" spans="1:2">
       <c r="A223" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B223" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="224" spans="1:2">
       <c r="A224" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B224" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="225" spans="1:2">
       <c r="A225" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B225" t="s">
         <v>327</v>
@@ -7335,36 +7341,36 @@
         <v>328</v>
       </c>
       <c r="B226" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="227" spans="1:2">
       <c r="A227" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B227" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="228" spans="1:2">
       <c r="A228" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B228" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="229" spans="1:2">
       <c r="A229" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B229" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="230" spans="1:2">
       <c r="A230" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B230" t="s">
         <v>333</v>
@@ -7383,52 +7389,52 @@
         <v>336</v>
       </c>
       <c r="B232" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="233" spans="1:2">
       <c r="A233" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B233" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="234" spans="1:2">
       <c r="A234" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B234" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="235" spans="1:2">
       <c r="A235" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B235" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="236" spans="1:2">
       <c r="A236" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B236" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="237" spans="1:2">
       <c r="A237" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B237" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="238" spans="1:2">
       <c r="A238" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B238" t="s">
         <v>343</v>
@@ -7471,12 +7477,12 @@
         <v>352</v>
       </c>
       <c r="B243" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="244" spans="1:2">
       <c r="A244" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B244" t="s">
         <v>354</v>
@@ -7487,12 +7493,12 @@
         <v>355</v>
       </c>
       <c r="B245" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="246" spans="1:2">
       <c r="A246" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B246" t="s">
         <v>357</v>
@@ -7519,12 +7525,12 @@
         <v>362</v>
       </c>
       <c r="B249" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="250" spans="1:2">
       <c r="A250" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B250" t="s">
         <v>364</v>
@@ -7543,68 +7549,68 @@
         <v>367</v>
       </c>
       <c r="B252" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="253" spans="1:2">
       <c r="A253" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B253" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="254" spans="1:2">
       <c r="A254" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B254" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="255" spans="1:2">
       <c r="A255" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B255" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="256" spans="1:2">
       <c r="A256" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B256" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B257" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B258" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B259" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B260" t="s">
         <v>376</v>
@@ -7655,116 +7661,116 @@
         <v>387</v>
       </c>
       <c r="B266" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="267" spans="1:2">
       <c r="A267" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B267" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B268" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B269" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B270" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B271" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B272" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B273" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B274" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B275" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B276" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B277" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B278" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B279" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B280" t="s">
         <v>402</v>
@@ -7775,92 +7781,92 @@
         <v>403</v>
       </c>
       <c r="B281" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="282" spans="1:2">
       <c r="A282" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B282" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B283" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B284" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B285" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B286" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B287" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B288" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B289" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B290" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="291" spans="1:2">
       <c r="A291" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B291" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B292" t="s">
         <v>415</v>
@@ -7895,20 +7901,20 @@
         <v>422</v>
       </c>
       <c r="B296" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="297" spans="1:2">
       <c r="A297" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B297" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B298" t="s">
         <v>425</v>
@@ -7943,12 +7949,12 @@
         <v>432</v>
       </c>
       <c r="B302" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="303" spans="1:2">
       <c r="A303" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B303" t="s">
         <v>434</v>
@@ -7959,12 +7965,12 @@
         <v>435</v>
       </c>
       <c r="B304" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B305" t="s">
         <v>437</v>
@@ -7999,28 +8005,28 @@
         <v>444</v>
       </c>
       <c r="B309" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="310" spans="1:2">
       <c r="A310" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B310" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="311" spans="1:2">
       <c r="A311" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B311" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B312" t="s">
         <v>448</v>
@@ -8039,20 +8045,20 @@
         <v>451</v>
       </c>
       <c r="B314" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="315" spans="1:2">
       <c r="A315" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B315" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B316" t="s">
         <v>454</v>
@@ -8079,20 +8085,20 @@
         <v>459</v>
       </c>
       <c r="B319" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="320" spans="1:2">
       <c r="A320" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B320" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B321" t="s">
         <v>462</v>
@@ -8103,20 +8109,20 @@
         <v>463</v>
       </c>
       <c r="B322" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="323" spans="1:2">
       <c r="A323" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B323" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B324" t="s">
         <v>466</v>
@@ -8127,92 +8133,92 @@
         <v>467</v>
       </c>
       <c r="B325" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="326" spans="1:2">
       <c r="A326" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B326" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B327" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B328" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B329" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B330" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B331" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B332" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B333" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B334" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B335" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B336" t="s">
         <v>479</v>
@@ -8263,36 +8269,36 @@
         <v>490</v>
       </c>
       <c r="B342" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="343" spans="1:2">
       <c r="A343" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B343" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B344" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B345" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B346" t="s">
         <v>495</v>
@@ -8303,28 +8309,28 @@
         <v>496</v>
       </c>
       <c r="B347" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="348" spans="1:2">
       <c r="A348" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B348" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="349" spans="1:2">
       <c r="A349" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B349" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B350" t="s">
         <v>500</v>
@@ -8423,12 +8429,12 @@
         <v>523</v>
       </c>
       <c r="B362" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="363" spans="1:2">
       <c r="A363" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B363" t="s">
         <v>525</v>
@@ -8447,20 +8453,20 @@
         <v>528</v>
       </c>
       <c r="B365" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="366" spans="1:2">
       <c r="A366" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B366" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B367" t="s">
         <v>531</v>
@@ -8479,20 +8485,20 @@
         <v>534</v>
       </c>
       <c r="B369" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="370" spans="1:2">
       <c r="A370" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B370" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B371" t="s">
         <v>537</v>
@@ -8535,12 +8541,12 @@
         <v>546</v>
       </c>
       <c r="B376" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="377" spans="1:2">
       <c r="A377" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B377" t="s">
         <v>548</v>
@@ -8567,12 +8573,12 @@
         <v>553</v>
       </c>
       <c r="B380" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="381" spans="1:2">
       <c r="A381" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B381" t="s">
         <v>555</v>
@@ -8599,44 +8605,44 @@
         <v>560</v>
       </c>
       <c r="B384" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="385" spans="1:2">
       <c r="A385" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B385" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B386" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="387" spans="1:2">
       <c r="A387" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B387" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="388" spans="1:2">
       <c r="A388" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B388" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B389" t="s">
         <v>566</v>
@@ -8655,12 +8661,12 @@
         <v>569</v>
       </c>
       <c r="B391" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="392" spans="1:2">
       <c r="A392" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B392" t="s">
         <v>571</v>
@@ -8671,20 +8677,20 @@
         <v>572</v>
       </c>
       <c r="B393" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="394" spans="1:2">
       <c r="A394" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B394" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B395" t="s">
         <v>575</v>
@@ -8711,36 +8717,36 @@
         <v>580</v>
       </c>
       <c r="B398" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="399" spans="1:2">
       <c r="A399" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B399" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="400" spans="1:2">
       <c r="A400" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B400" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B401" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B402" t="s">
         <v>585</v>
@@ -8775,12 +8781,12 @@
         <v>592</v>
       </c>
       <c r="B406" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="407" spans="1:2">
       <c r="A407" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B407" t="s">
         <v>594</v>
@@ -8799,20 +8805,20 @@
         <v>597</v>
       </c>
       <c r="B409" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="410" spans="1:2">
       <c r="A410" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B410" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B411" t="s">
         <v>600</v>
@@ -8823,28 +8829,28 @@
         <v>601</v>
       </c>
       <c r="B412" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="413" spans="1:2">
       <c r="A413" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B413" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="414" spans="1:2">
       <c r="A414" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B414" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B415" t="s">
         <v>605</v>
@@ -8863,20 +8869,20 @@
         <v>608</v>
       </c>
       <c r="B417" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="418" spans="1:2">
       <c r="A418" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B418" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B419" t="s">
         <v>611</v>
@@ -8999,36 +9005,36 @@
         <v>640</v>
       </c>
       <c r="B434" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="435" spans="1:2">
       <c r="A435" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B435" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B436" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B437" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B438" t="s">
         <v>645</v>
@@ -9039,12 +9045,12 @@
         <v>646</v>
       </c>
       <c r="B439" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B440" t="s">
         <v>648</v>
@@ -9055,20 +9061,20 @@
         <v>649</v>
       </c>
       <c r="B441" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B442" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="443" spans="1:2">
       <c r="A443" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B443" t="s">
         <v>652</v>
@@ -9079,20 +9085,20 @@
         <v>653</v>
       </c>
       <c r="B444" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="445" spans="1:2">
       <c r="A445" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B445" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="446" spans="1:2">
       <c r="A446" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B446" t="s">
         <v>656</v>
@@ -9119,12 +9125,12 @@
         <v>661</v>
       </c>
       <c r="B449" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="450" spans="1:2">
       <c r="A450" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B450" t="s">
         <v>663</v>
@@ -9135,28 +9141,28 @@
         <v>664</v>
       </c>
       <c r="B451" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B452" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="453" spans="1:2">
       <c r="A453" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B453" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B454" t="s">
         <v>668</v>
@@ -9175,20 +9181,20 @@
         <v>671</v>
       </c>
       <c r="B456" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="457" spans="1:2">
       <c r="A457" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B457" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B458" t="s">
         <v>674</v>
@@ -9199,20 +9205,20 @@
         <v>675</v>
       </c>
       <c r="B459" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="460" spans="1:2">
       <c r="A460" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B460" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="461" spans="1:2">
       <c r="A461" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B461" t="s">
         <v>678</v>
@@ -9247,28 +9253,28 @@
         <v>685</v>
       </c>
       <c r="B465" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="466" spans="1:2">
       <c r="A466" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B466" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="B467" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B468" t="s">
         <v>689</v>
@@ -9279,12 +9285,12 @@
         <v>690</v>
       </c>
       <c r="B469" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B470" t="s">
         <v>692</v>
@@ -9295,20 +9301,20 @@
         <v>693</v>
       </c>
       <c r="B471" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B472" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="473" spans="1:2">
       <c r="A473" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B473" t="s">
         <v>696</v>
@@ -9319,52 +9325,52 @@
         <v>697</v>
       </c>
       <c r="B474" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B475" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B476" t="s">
-        <v>699</v>
+        <v>691</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B477" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B478" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B479" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B480" t="s">
         <v>704</v>
@@ -9383,12 +9389,12 @@
         <v>707</v>
       </c>
       <c r="B482" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="483" spans="1:2">
       <c r="A483" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B483" t="s">
         <v>709</v>
@@ -9399,12 +9405,12 @@
         <v>710</v>
       </c>
       <c r="B484" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="B485" t="s">
         <v>712</v>
@@ -9415,20 +9421,20 @@
         <v>713</v>
       </c>
       <c r="B486" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B487" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B488" t="s">
         <v>716</v>
@@ -9439,36 +9445,36 @@
         <v>717</v>
       </c>
       <c r="B489" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B490" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B491" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B492" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B493" t="s">
         <v>722</v>
@@ -9623,12 +9629,12 @@
         <v>759</v>
       </c>
       <c r="B512" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
     </row>
     <row r="513" spans="1:2">
       <c r="A513" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B513" t="s">
         <v>761</v>
@@ -9639,12 +9645,12 @@
         <v>762</v>
       </c>
       <c r="B514" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="B515" t="s">
         <v>763</v>
@@ -9652,7 +9658,7 @@
     </row>
     <row r="516" spans="1:2">
       <c r="A516" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B516" t="s">
         <v>765</v>
@@ -9663,12 +9669,12 @@
         <v>766</v>
       </c>
       <c r="B517" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B518" t="s">
         <v>768</v>
@@ -9703,12 +9709,12 @@
         <v>775</v>
       </c>
       <c r="B522" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
     </row>
     <row r="523" spans="1:2">
       <c r="A523" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B523" t="s">
         <v>777</v>
@@ -9719,12 +9725,12 @@
         <v>778</v>
       </c>
       <c r="B524" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="B525" t="s">
         <v>780</v>
@@ -9743,12 +9749,12 @@
         <v>783</v>
       </c>
       <c r="B527" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
     </row>
     <row r="528" spans="1:2">
       <c r="A528" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B528" t="s">
         <v>785</v>
@@ -9799,12 +9805,12 @@
         <v>796</v>
       </c>
       <c r="B534" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="535" spans="1:2">
       <c r="A535" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B535" t="s">
         <v>798</v>
@@ -9823,84 +9829,84 @@
         <v>801</v>
       </c>
       <c r="B537" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="538" spans="1:2">
       <c r="A538" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B538" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B539" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B540" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B541" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B542" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B543" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B544" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B545" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B546" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B547" t="s">
         <v>812</v>
@@ -9911,20 +9917,20 @@
         <v>813</v>
       </c>
       <c r="B548" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B549" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B550" t="s">
         <v>816</v>
@@ -9935,68 +9941,68 @@
         <v>817</v>
       </c>
       <c r="B551" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B552" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B553" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B554" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B555" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B556" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B557" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B558" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B559" t="s">
         <v>826</v>
@@ -10047,28 +10053,28 @@
         <v>837</v>
       </c>
       <c r="B565" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="566" spans="1:2">
       <c r="A566" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B566" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B567" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B568" t="s">
         <v>841</v>
@@ -10079,20 +10085,20 @@
         <v>842</v>
       </c>
       <c r="B569" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B570" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B571" t="s">
         <v>845</v>
@@ -10103,20 +10109,20 @@
         <v>846</v>
       </c>
       <c r="B572" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B573" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B574" t="s">
         <v>849</v>
@@ -10135,60 +10141,60 @@
         <v>852</v>
       </c>
       <c r="B576" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="577" spans="1:2">
       <c r="A577" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B577" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B578" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B579" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B580" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B581" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B582" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B583" t="s">
         <v>860</v>
@@ -10207,20 +10213,20 @@
         <v>863</v>
       </c>
       <c r="B585" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="586" spans="1:2">
       <c r="A586" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B586" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B587" t="s">
         <v>866</v>
@@ -10231,12 +10237,12 @@
         <v>867</v>
       </c>
       <c r="B588" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B589" t="s">
         <v>869</v>
@@ -10247,12 +10253,12 @@
         <v>870</v>
       </c>
       <c r="B590" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B591" t="s">
         <v>872</v>
@@ -10271,12 +10277,12 @@
         <v>875</v>
       </c>
       <c r="B593" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
     </row>
     <row r="594" spans="1:2">
       <c r="A594" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B594" t="s">
         <v>877</v>
@@ -10295,12 +10301,12 @@
         <v>880</v>
       </c>
       <c r="B596" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
     </row>
     <row r="597" spans="1:2">
       <c r="A597" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B597" t="s">
         <v>882</v>
@@ -10327,36 +10333,36 @@
         <v>887</v>
       </c>
       <c r="B600" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="601" spans="1:2">
       <c r="A601" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B601" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B602" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B603" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B604" t="s">
         <v>892</v>
@@ -10399,20 +10405,20 @@
         <v>901</v>
       </c>
       <c r="B609" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="610" spans="1:2">
       <c r="A610" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B610" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B611" t="s">
         <v>904</v>
@@ -10423,44 +10429,44 @@
         <v>905</v>
       </c>
       <c r="B612" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B613" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B614" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B615" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B616" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B617" t="s">
         <v>911</v>
@@ -10471,44 +10477,44 @@
         <v>912</v>
       </c>
       <c r="B618" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B619" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B620" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B621" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B622" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B623" t="s">
         <v>918</v>
@@ -10527,12 +10533,12 @@
         <v>921</v>
       </c>
       <c r="B625" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="626" spans="1:2">
       <c r="A626" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B626" t="s">
         <v>923</v>
@@ -10543,12 +10549,12 @@
         <v>924</v>
       </c>
       <c r="B627" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B628" t="s">
         <v>926</v>
@@ -10559,188 +10565,188 @@
         <v>927</v>
       </c>
       <c r="B629" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B630" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B631" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B632" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B633" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B634" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B635" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B636" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B637" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B638" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B639" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B640" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B641" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B642" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B643" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B644" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B645" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B646" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B647" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B648" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B649" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B650" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B651" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B652" t="s">
         <v>951</v>
@@ -10775,28 +10781,28 @@
         <v>958</v>
       </c>
       <c r="B656" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="657" spans="1:2">
       <c r="A657" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B657" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B658" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B659" t="s">
         <v>962</v>
@@ -10807,20 +10813,20 @@
         <v>963</v>
       </c>
       <c r="B660" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B661" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B662" t="s">
         <v>966</v>
@@ -10831,44 +10837,44 @@
         <v>967</v>
       </c>
       <c r="B663" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B664" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B665" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="666" spans="1:2">
       <c r="A666" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B666" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B667" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B668" t="s">
         <v>973</v>
@@ -10879,52 +10885,52 @@
         <v>974</v>
       </c>
       <c r="B669" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="670" spans="1:2">
       <c r="A670" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B670" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="671" spans="1:2">
       <c r="A671" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B671" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="672" spans="1:2">
       <c r="A672" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B672" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="673" spans="1:2">
       <c r="A673" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B673" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B674" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B675" t="s">
         <v>981</v>
@@ -10935,12 +10941,12 @@
         <v>982</v>
       </c>
       <c r="B676" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B677" t="s">
         <v>984</v>
@@ -10959,68 +10965,68 @@
         <v>987</v>
       </c>
       <c r="B679" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="680" spans="1:2">
       <c r="A680" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B680" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B681" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B682" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B683" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B684" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B685" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B686" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B687" t="s">
         <v>996</v>
@@ -11039,20 +11045,20 @@
         <v>999</v>
       </c>
       <c r="B689" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="690" spans="1:2">
       <c r="A690" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B690" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B691" t="s">
         <v>1002</v>
@@ -11071,12 +11077,12 @@
         <v>1005</v>
       </c>
       <c r="B693" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="694" spans="1:2">
       <c r="A694" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B694" t="s">
         <v>1007</v>
@@ -11111,12 +11117,12 @@
         <v>1014</v>
       </c>
       <c r="B698" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="699" spans="1:2">
       <c r="A699" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B699" t="s">
         <v>1016</v>
@@ -11135,12 +11141,12 @@
         <v>1019</v>
       </c>
       <c r="B701" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="702" spans="1:2">
       <c r="A702" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B702" t="s">
         <v>1021</v>
@@ -11183,36 +11189,36 @@
         <v>1030</v>
       </c>
       <c r="B707" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="708" spans="1:2">
       <c r="A708" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B708" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B709" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B710" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B711" t="s">
         <v>1035</v>
@@ -11223,76 +11229,76 @@
         <v>1036</v>
       </c>
       <c r="B712" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B713" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B714" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B715" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B716" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B717" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B718" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B719" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B720" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B721" t="s">
         <v>1046</v>
@@ -11311,20 +11317,20 @@
         <v>1049</v>
       </c>
       <c r="B723" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="724" spans="1:2">
       <c r="A724" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B724" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B725" t="s">
         <v>1052</v>
@@ -11335,12 +11341,12 @@
         <v>1053</v>
       </c>
       <c r="B726" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B727" t="s">
         <v>1055</v>
@@ -11351,12 +11357,12 @@
         <v>1056</v>
       </c>
       <c r="B728" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B729" t="s">
         <v>1058</v>
@@ -11367,12 +11373,12 @@
         <v>1059</v>
       </c>
       <c r="B730" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B731" t="s">
         <v>1061</v>
@@ -11383,12 +11389,12 @@
         <v>1062</v>
       </c>
       <c r="B732" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B733" t="s">
         <v>1064</v>
@@ -11407,20 +11413,20 @@
         <v>1067</v>
       </c>
       <c r="B735" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="736" spans="1:2">
       <c r="A736" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B736" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B737" t="s">
         <v>1070</v>
@@ -11431,12 +11437,12 @@
         <v>1071</v>
       </c>
       <c r="B738" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B739" t="s">
         <v>1073</v>
@@ -11447,68 +11453,68 @@
         <v>1074</v>
       </c>
       <c r="B740" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B741" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="742" spans="1:2">
       <c r="A742" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B742" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B743" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B744" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B745" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B746" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B747" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B748" t="s">
         <v>1083</v>
@@ -11519,12 +11525,12 @@
         <v>1084</v>
       </c>
       <c r="B749" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B750" t="s">
         <v>1086</v>
@@ -11543,36 +11549,36 @@
         <v>1089</v>
       </c>
       <c r="B752" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="753" spans="1:2">
       <c r="A753" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B753" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B754" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B755" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B756" t="s">
         <v>1094</v>
@@ -11583,20 +11589,20 @@
         <v>1095</v>
       </c>
       <c r="B757" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="758" spans="1:2">
       <c r="A758" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B758" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="759" spans="1:2">
       <c r="A759" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B759" t="s">
         <v>1098</v>
@@ -11631,20 +11637,20 @@
         <v>1105</v>
       </c>
       <c r="B763" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="764" spans="1:2">
       <c r="A764" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B764" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B765" t="s">
         <v>1108</v>
@@ -11663,12 +11669,12 @@
         <v>1111</v>
       </c>
       <c r="B767" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="768" spans="1:2">
       <c r="A768" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B768" t="s">
         <v>1113</v>
@@ -11679,20 +11685,20 @@
         <v>1114</v>
       </c>
       <c r="B769" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B770" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B771" t="s">
         <v>1117</v>
@@ -11735,12 +11741,12 @@
         <v>1126</v>
       </c>
       <c r="B776" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="777" spans="1:2">
       <c r="A777" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B777" t="s">
         <v>1128</v>
@@ -11759,44 +11765,44 @@
         <v>1131</v>
       </c>
       <c r="B779" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="780" spans="1:2">
       <c r="A780" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B780" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="781" spans="1:2">
       <c r="A781" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B781" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B782" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B783" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B784" t="s">
         <v>1137</v>
@@ -11807,12 +11813,12 @@
         <v>1138</v>
       </c>
       <c r="B785" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B786" t="s">
         <v>1140</v>
@@ -11839,44 +11845,44 @@
         <v>1145</v>
       </c>
       <c r="B789" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="790" spans="1:2">
       <c r="A790" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B790" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B791" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B792" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B793" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B794" t="s">
         <v>1151</v>
@@ -11887,116 +11893,116 @@
         <v>1152</v>
       </c>
       <c r="B795" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B796" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B797" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B798" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B799" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B800" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B801" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B802" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B803" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B804" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B805" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B806" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B807" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B808" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B809" t="s">
         <v>1167</v>
@@ -12031,44 +12037,44 @@
         <v>1174</v>
       </c>
       <c r="B813" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="814" spans="1:2">
       <c r="A814" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B814" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B815" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B816" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B817" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B818" t="s">
         <v>1180</v>
@@ -12103,36 +12109,36 @@
         <v>1187</v>
       </c>
       <c r="B822" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="823" spans="1:2">
       <c r="A823" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B823" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B824" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B825" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B826" t="s">
         <v>1192</v>
@@ -12143,28 +12149,28 @@
         <v>1193</v>
       </c>
       <c r="B827" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B828" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B829" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B830" t="s">
         <v>1197</v>
@@ -12191,12 +12197,12 @@
         <v>1202</v>
       </c>
       <c r="B833" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="834" spans="1:2">
       <c r="A834" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B834" t="s">
         <v>1204</v>
@@ -12207,28 +12213,28 @@
         <v>1205</v>
       </c>
       <c r="B835" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B836" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B837" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B838" t="s">
         <v>1209</v>
@@ -12239,44 +12245,44 @@
         <v>1210</v>
       </c>
       <c r="B839" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B840" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B841" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B842" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B843" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B844" t="s">
         <v>1216</v>
@@ -12287,148 +12293,148 @@
         <v>1217</v>
       </c>
       <c r="B845" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B846" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B847" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B848" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B849" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B850" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B851" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B852" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B853" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B854" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B855" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B856" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B857" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B858" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B859" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B860" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B861" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B862" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B863" t="s">
         <v>1236</v>
@@ -12463,28 +12469,28 @@
         <v>1243</v>
       </c>
       <c r="B867" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="868" spans="1:2">
       <c r="A868" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B868" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B869" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B870" t="s">
         <v>1247</v>
@@ -12495,68 +12501,68 @@
         <v>1248</v>
       </c>
       <c r="B871" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B872" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B873" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B874" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B875" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B876" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B877" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B878" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B879" t="s">
         <v>1257</v>
@@ -12567,28 +12573,28 @@
         <v>1258</v>
       </c>
       <c r="B880" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B881" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B882" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B883" t="s">
         <v>1262</v>
@@ -12599,12 +12605,12 @@
         <v>1263</v>
       </c>
       <c r="B884" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B885" t="s">
         <v>1265</v>
@@ -12615,12 +12621,12 @@
         <v>1266</v>
       </c>
       <c r="B886" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B887" t="s">
         <v>1268</v>
@@ -12639,20 +12645,20 @@
         <v>1271</v>
       </c>
       <c r="B889" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="890" spans="1:2">
       <c r="A890" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="B890" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="B891" t="s">
         <v>1274</v>
@@ -12671,44 +12677,44 @@
         <v>1277</v>
       </c>
       <c r="B893" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="894" spans="1:2">
       <c r="A894" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B894" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="B895" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B896" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B897" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B898" t="s">
         <v>1283</v>
@@ -12719,44 +12725,44 @@
         <v>1284</v>
       </c>
       <c r="B899" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B900" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B901" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B902" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B903" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B904" t="s">
         <v>1290</v>
@@ -12767,12 +12773,12 @@
         <v>1291</v>
       </c>
       <c r="B905" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B906" t="s">
         <v>1293</v>
@@ -12783,36 +12789,36 @@
         <v>1294</v>
       </c>
       <c r="B907" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="B908" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B909" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B910" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B911" t="s">
         <v>1299</v>
@@ -12839,68 +12845,68 @@
         <v>1304</v>
       </c>
       <c r="B914" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="915" spans="1:2">
       <c r="A915" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="B915" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="B916" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B917" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B918" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B919" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B920" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B921" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B922" t="s">
         <v>1313</v>
@@ -12927,28 +12933,28 @@
         <v>1318</v>
       </c>
       <c r="B925" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="926" spans="1:2">
       <c r="A926" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B926" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B927" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B928" t="s">
         <v>1322</v>
@@ -12991,20 +12997,20 @@
         <v>1331</v>
       </c>
       <c r="B933" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="934" spans="1:2">
       <c r="A934" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B934" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B935" t="s">
         <v>1334</v>
@@ -13015,12 +13021,12 @@
         <v>1335</v>
       </c>
       <c r="B936" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B937" t="s">
         <v>1337</v>
@@ -13039,12 +13045,12 @@
         <v>1340</v>
       </c>
       <c r="B939" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
     </row>
     <row r="940" spans="1:2">
       <c r="A940" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B940" t="s">
         <v>1342</v>
@@ -13063,36 +13069,36 @@
         <v>1345</v>
       </c>
       <c r="B942" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="943" spans="1:2">
       <c r="A943" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="B943" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B944" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B945" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B946" t="s">
         <v>1350</v>
@@ -13151,28 +13157,28 @@
         <v>1363</v>
       </c>
       <c r="B953" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="954" spans="1:2">
       <c r="A954" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B954" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="B955" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B956" t="s">
         <v>1367</v>
@@ -13183,68 +13189,68 @@
         <v>1368</v>
       </c>
       <c r="B957" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B958" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B959" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B960" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B961" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B962" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B963" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B964" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B965" t="s">
         <v>1377</v>
@@ -13271,20 +13277,20 @@
         <v>1382</v>
       </c>
       <c r="B968" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="969" spans="1:2">
       <c r="A969" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="B969" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B970" t="s">
         <v>1385</v>
@@ -13311,20 +13317,20 @@
         <v>1390</v>
       </c>
       <c r="B973" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="974" spans="1:2">
       <c r="A974" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="B974" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="B975" t="s">
         <v>1393</v>
@@ -13335,44 +13341,44 @@
         <v>1394</v>
       </c>
       <c r="B976" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B977" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B978" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B979" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B980" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B981" t="s">
         <v>1400</v>
@@ -13415,68 +13421,68 @@
         <v>1409</v>
       </c>
       <c r="B986" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="987" spans="1:2">
       <c r="A987" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B987" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="B988" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B989" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B990" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B991" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B992" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B993" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B994" t="s">
         <v>1418</v>
@@ -13487,28 +13493,28 @@
         <v>1419</v>
       </c>
       <c r="B995" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B996" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B997" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B998" t="s">
         <v>1423</v>
@@ -13519,60 +13525,60 @@
         <v>1424</v>
       </c>
       <c r="B999" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B1000" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B1001" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B1002" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B1003" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B1004" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B1005" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B1006" t="s">
         <v>1432</v>
@@ -13591,28 +13597,28 @@
         <v>1435</v>
       </c>
       <c r="B1008" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="1009" spans="1:2">
       <c r="A1009" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B1009" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B1010" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B1011" t="s">
         <v>1439</v>
@@ -13623,12 +13629,12 @@
         <v>1440</v>
       </c>
       <c r="B1012" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B1013" t="s">
         <v>1442</v>
@@ -13647,36 +13653,36 @@
         <v>1445</v>
       </c>
       <c r="B1015" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="1016" spans="1:2">
       <c r="A1016" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B1016" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="B1017" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B1018" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B1019" t="s">
         <v>1450</v>
@@ -13687,36 +13693,36 @@
         <v>1451</v>
       </c>
       <c r="B1020" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B1021" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B1022" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B1023" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B1024" t="s">
         <v>1456</v>
@@ -13735,36 +13741,36 @@
         <v>1459</v>
       </c>
       <c r="B1026" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="1027" spans="1:2">
       <c r="A1027" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B1027" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B1028" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B1029" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B1030" t="s">
         <v>1464</v>
@@ -13783,20 +13789,20 @@
         <v>1467</v>
       </c>
       <c r="B1032" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="1033" spans="1:2">
       <c r="A1033" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B1033" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="B1034" t="s">
         <v>1470</v>
@@ -13815,12 +13821,12 @@
         <v>1473</v>
       </c>
       <c r="B1036" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="1037" spans="1:2">
       <c r="A1037" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B1037" t="s">
         <v>1475</v>
@@ -13831,84 +13837,84 @@
         <v>1476</v>
       </c>
       <c r="B1038" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="B1039" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B1040" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B1041" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B1042" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B1043" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B1044" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B1045" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B1046" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B1047" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B1048" t="s">
         <v>1487</v>
@@ -13919,12 +13925,12 @@
         <v>1488</v>
       </c>
       <c r="B1049" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B1050" t="s">
         <v>1490</v>
@@ -13951,20 +13957,20 @@
         <v>1495</v>
       </c>
       <c r="B1053" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="1054" spans="1:2">
       <c r="A1054" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B1054" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="B1055" t="s">
         <v>1498</v>
@@ -13975,12 +13981,12 @@
         <v>1499</v>
       </c>
       <c r="B1056" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B1057" t="s">
         <v>1501</v>
@@ -13991,52 +13997,52 @@
         <v>1502</v>
       </c>
       <c r="B1058" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B1059" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B1060" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B1061" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B1062" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B1063" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B1064" t="s">
         <v>1509</v>
@@ -14103,12 +14109,12 @@
         <v>1524</v>
       </c>
       <c r="B1072" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="1073" spans="1:2">
       <c r="A1073" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B1073" t="s">
         <v>1526</v>
@@ -14119,28 +14125,28 @@
         <v>1527</v>
       </c>
       <c r="B1074" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B1075" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B1076" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B1077" t="s">
         <v>1531</v>
@@ -14151,12 +14157,12 @@
         <v>1532</v>
       </c>
       <c r="B1078" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B1079" t="s">
         <v>1534</v>
@@ -14175,28 +14181,28 @@
         <v>1537</v>
       </c>
       <c r="B1081" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="1082" spans="1:2">
       <c r="A1082" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="B1082" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="B1083" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B1084" t="s">
         <v>1541</v>
@@ -14207,28 +14213,28 @@
         <v>1542</v>
       </c>
       <c r="B1085" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B1086" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B1087" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B1088" t="s">
         <v>1546</v>
@@ -14239,20 +14245,20 @@
         <v>1547</v>
       </c>
       <c r="B1089" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B1090" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B1091" t="s">
         <v>1550</v>
@@ -14263,12 +14269,12 @@
         <v>1551</v>
       </c>
       <c r="B1092" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B1093" t="s">
         <v>1553</v>
@@ -14279,28 +14285,28 @@
         <v>1554</v>
       </c>
       <c r="B1094" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B1095" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B1096" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B1097" t="s">
         <v>1558</v>
@@ -14311,20 +14317,20 @@
         <v>1559</v>
       </c>
       <c r="B1098" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B1099" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B1100" t="s">
         <v>1562</v>
@@ -14359,20 +14365,20 @@
         <v>1569</v>
       </c>
       <c r="B1104" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="1105" spans="1:2">
       <c r="A1105" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B1105" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="B1106" t="s">
         <v>1572</v>
@@ -14407,52 +14413,52 @@
         <v>1579</v>
       </c>
       <c r="B1110" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
     </row>
     <row r="1111" spans="1:2">
       <c r="A1111" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
       <c r="B1111" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B1112" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B1113" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B1114" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B1115" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B1116" t="s">
         <v>1586</v>
@@ -14463,20 +14469,20 @@
         <v>1587</v>
       </c>
       <c r="B1117" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B1118" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B1119" t="s">
         <v>1590</v>
@@ -14487,52 +14493,52 @@
         <v>1591</v>
       </c>
       <c r="B1120" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B1121" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B1122" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B1123" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B1124" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B1125" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B1126" t="s">
         <v>1598</v>
@@ -14543,20 +14549,20 @@
         <v>1599</v>
       </c>
       <c r="B1127" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B1128" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B1129" t="s">
         <v>1602</v>
@@ -14575,20 +14581,20 @@
         <v>1605</v>
       </c>
       <c r="B1131" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="1132" spans="1:2">
       <c r="A1132" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="B1132" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B1133" t="s">
         <v>1608</v>
@@ -14687,44 +14693,44 @@
         <v>1631</v>
       </c>
       <c r="B1145" t="s">
-        <v>1631</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="1146" spans="1:2">
       <c r="A1146" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
       <c r="B1146" t="s">
-        <v>1632</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
       <c r="B1147" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B1148" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B1149" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B1150" t="s">
         <v>1637</v>
@@ -14743,36 +14749,36 @@
         <v>1640</v>
       </c>
       <c r="B1152" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
     </row>
     <row r="1153" spans="1:2">
       <c r="A1153" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="B1153" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="B1154" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1155" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B1156" t="s">
         <v>1645</v>
@@ -14783,20 +14789,20 @@
         <v>1646</v>
       </c>
       <c r="B1157" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B1158" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B1159" t="s">
         <v>1649</v>
@@ -14831,12 +14837,12 @@
         <v>1656</v>
       </c>
       <c r="B1163" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="1164" spans="1:2">
       <c r="A1164" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B1164" t="s">
         <v>1658</v>
@@ -14855,12 +14861,12 @@
         <v>1661</v>
       </c>
       <c r="B1166" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="1167" spans="1:2">
       <c r="A1167" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="B1167" t="s">
         <v>1663</v>
@@ -14887,124 +14893,124 @@
         <v>1668</v>
       </c>
       <c r="B1170" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="1171" spans="1:2">
       <c r="A1171" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="B1171" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="B1172" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B1173" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B1174" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B1175" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B1176" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B1177" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B1178" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B1179" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1180" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B1181" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1182" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B1183" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B1184" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B1185" t="s">
         <v>1684</v>
@@ -15015,36 +15021,36 @@
         <v>1685</v>
       </c>
       <c r="B1186" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B1187" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1188" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1189" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B1190" t="s">
         <v>1690</v>
@@ -15063,36 +15069,36 @@
         <v>1693</v>
       </c>
       <c r="B1192" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="1193" spans="1:2">
       <c r="A1193" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="B1193" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="B1194" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1195" t="s">
-        <v>384</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
       <c r="A1196" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1196" t="s">
         <v>386</v>
@@ -15100,182 +15106,190 @@
     </row>
     <row r="1197" spans="1:2">
       <c r="A1197" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1197" t="s">
-        <v>1698</v>
+        <v>388</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1198" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
       <c r="A1199" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1199" t="s">
-        <v>645</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1200" spans="1:2">
       <c r="A1200" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1200" t="s">
-        <v>1701</v>
+        <v>647</v>
       </c>
     </row>
     <row r="1201" spans="1:2">
       <c r="A1201" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B1201" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
       <c r="A1202" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B1202" t="s">
-        <v>926</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="1203" spans="1:2">
       <c r="A1203" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B1203" t="s">
-        <v>1704</v>
+        <v>928</v>
       </c>
     </row>
     <row r="1204" spans="1:2">
       <c r="A1204" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B1204" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1205" spans="1:2">
       <c r="A1205" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1205" t="s">
-        <v>1002</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="1206" spans="1:2">
       <c r="A1206" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1206" t="s">
-        <v>1707</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="1207" spans="1:2">
       <c r="A1207" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B1207" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1208" spans="1:2">
       <c r="A1208" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B1208" t="s">
-        <v>1070</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1209" spans="1:2">
       <c r="A1209" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B1209" t="s">
-        <v>1125</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="1210" spans="1:2">
       <c r="A1210" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B1210" t="s">
-        <v>1711</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="1211" spans="1:2">
       <c r="A1211" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1211" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="1212" spans="1:2">
       <c r="A1212" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="B1212" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1213" spans="1:2">
       <c r="A1213" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B1213" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="1214" spans="1:2">
       <c r="A1214" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B1214" t="s">
-        <v>1434</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="1215" spans="1:2">
       <c r="A1215" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B1215" t="s">
-        <v>1716</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="1216" spans="1:2">
       <c r="A1216" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B1216" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="1217" spans="1:2">
       <c r="A1217" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B1217" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="1218" spans="1:2">
       <c r="A1218" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B1218" t="s">
-        <v>1553</v>
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:2">
+      <c r="A1219" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B1219" t="s">
+        <v>1555</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1218"/>
+  <autoFilter ref="A1:B1219"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/da/headTags.xlsx
+++ b/lang/da/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1219</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1220</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1722">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1724">
   <si>
     <t>en</t>
   </si>
@@ -1133,6 +1133,12 @@
   </si>
   <si>
     <t>Diablo</t>
+  </si>
+  <si>
+    <t>Die of Death</t>
+  </si>
+  <si>
+    <t>Dødens død</t>
   </si>
   <si>
     <t>Digimon</t>
@@ -5529,7 +5535,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1219"/>
+  <dimension ref="A1:B1220"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -7581,44 +7587,44 @@
         <v>372</v>
       </c>
       <c r="B256" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="257" spans="1:2">
       <c r="A257" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B257" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="258" spans="1:2">
       <c r="A258" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B258" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="259" spans="1:2">
       <c r="A259" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B259" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="260" spans="1:2">
       <c r="A260" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B260" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="261" spans="1:2">
       <c r="A261" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B261" t="s">
         <v>378</v>
@@ -7669,116 +7675,116 @@
         <v>389</v>
       </c>
       <c r="B267" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="268" spans="1:2">
       <c r="A268" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B268" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="269" spans="1:2">
       <c r="A269" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B269" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="270" spans="1:2">
       <c r="A270" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B270" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="271" spans="1:2">
       <c r="A271" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B271" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="272" spans="1:2">
       <c r="A272" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B272" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="273" spans="1:2">
       <c r="A273" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B273" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="274" spans="1:2">
       <c r="A274" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B274" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="275" spans="1:2">
       <c r="A275" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B275" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="276" spans="1:2">
       <c r="A276" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B276" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="277" spans="1:2">
       <c r="A277" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B277" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="278" spans="1:2">
       <c r="A278" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B278" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="279" spans="1:2">
       <c r="A279" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B279" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="280" spans="1:2">
       <c r="A280" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B280" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="281" spans="1:2">
       <c r="A281" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B281" t="s">
         <v>404</v>
@@ -7789,92 +7795,92 @@
         <v>405</v>
       </c>
       <c r="B282" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="283" spans="1:2">
       <c r="A283" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B283" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="284" spans="1:2">
       <c r="A284" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B284" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="285" spans="1:2">
       <c r="A285" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B285" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="286" spans="1:2">
       <c r="A286" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B286" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="287" spans="1:2">
       <c r="A287" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B287" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="288" spans="1:2">
       <c r="A288" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B288" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="289" spans="1:2">
       <c r="A289" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B289" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="290" spans="1:2">
       <c r="A290" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B290" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="291" spans="1:2">
       <c r="A291" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B291" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="292" spans="1:2">
       <c r="A292" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B292" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="293" spans="1:2">
       <c r="A293" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B293" t="s">
         <v>417</v>
@@ -7909,20 +7915,20 @@
         <v>424</v>
       </c>
       <c r="B297" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="298" spans="1:2">
       <c r="A298" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B298" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="299" spans="1:2">
       <c r="A299" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B299" t="s">
         <v>427</v>
@@ -7957,12 +7963,12 @@
         <v>434</v>
       </c>
       <c r="B303" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="304" spans="1:2">
       <c r="A304" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B304" t="s">
         <v>436</v>
@@ -7973,12 +7979,12 @@
         <v>437</v>
       </c>
       <c r="B305" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="306" spans="1:2">
       <c r="A306" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B306" t="s">
         <v>439</v>
@@ -8013,28 +8019,28 @@
         <v>446</v>
       </c>
       <c r="B310" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="311" spans="1:2">
       <c r="A311" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B311" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="312" spans="1:2">
       <c r="A312" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B312" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="313" spans="1:2">
       <c r="A313" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B313" t="s">
         <v>450</v>
@@ -8053,20 +8059,20 @@
         <v>453</v>
       </c>
       <c r="B315" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="316" spans="1:2">
       <c r="A316" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B316" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="317" spans="1:2">
       <c r="A317" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B317" t="s">
         <v>456</v>
@@ -8093,20 +8099,20 @@
         <v>461</v>
       </c>
       <c r="B320" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="321" spans="1:2">
       <c r="A321" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B321" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="322" spans="1:2">
       <c r="A322" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B322" t="s">
         <v>464</v>
@@ -8117,20 +8123,20 @@
         <v>465</v>
       </c>
       <c r="B323" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="324" spans="1:2">
       <c r="A324" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B324" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="325" spans="1:2">
       <c r="A325" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B325" t="s">
         <v>468</v>
@@ -8141,92 +8147,92 @@
         <v>469</v>
       </c>
       <c r="B326" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="327" spans="1:2">
       <c r="A327" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B327" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="328" spans="1:2">
       <c r="A328" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B328" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="329" spans="1:2">
       <c r="A329" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B329" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="330" spans="1:2">
       <c r="A330" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B330" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="331" spans="1:2">
       <c r="A331" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B331" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="332" spans="1:2">
       <c r="A332" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B332" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="333" spans="1:2">
       <c r="A333" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B333" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="334" spans="1:2">
       <c r="A334" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B334" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="335" spans="1:2">
       <c r="A335" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B335" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="336" spans="1:2">
       <c r="A336" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B336" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="337" spans="1:2">
       <c r="A337" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B337" t="s">
         <v>481</v>
@@ -8277,36 +8283,36 @@
         <v>492</v>
       </c>
       <c r="B343" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="344" spans="1:2">
       <c r="A344" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B344" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="345" spans="1:2">
       <c r="A345" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B345" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="346" spans="1:2">
       <c r="A346" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B346" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="347" spans="1:2">
       <c r="A347" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B347" t="s">
         <v>497</v>
@@ -8317,28 +8323,28 @@
         <v>498</v>
       </c>
       <c r="B348" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="349" spans="1:2">
       <c r="A349" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B349" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="350" spans="1:2">
       <c r="A350" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B350" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="351" spans="1:2">
       <c r="A351" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B351" t="s">
         <v>502</v>
@@ -8437,12 +8443,12 @@
         <v>525</v>
       </c>
       <c r="B363" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="364" spans="1:2">
       <c r="A364" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B364" t="s">
         <v>527</v>
@@ -8461,20 +8467,20 @@
         <v>530</v>
       </c>
       <c r="B366" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="367" spans="1:2">
       <c r="A367" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B367" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="368" spans="1:2">
       <c r="A368" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B368" t="s">
         <v>533</v>
@@ -8493,20 +8499,20 @@
         <v>536</v>
       </c>
       <c r="B370" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="371" spans="1:2">
       <c r="A371" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B371" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="372" spans="1:2">
       <c r="A372" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B372" t="s">
         <v>539</v>
@@ -8549,12 +8555,12 @@
         <v>548</v>
       </c>
       <c r="B377" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="378" spans="1:2">
       <c r="A378" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B378" t="s">
         <v>550</v>
@@ -8581,12 +8587,12 @@
         <v>555</v>
       </c>
       <c r="B381" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="382" spans="1:2">
       <c r="A382" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B382" t="s">
         <v>557</v>
@@ -8613,44 +8619,44 @@
         <v>562</v>
       </c>
       <c r="B385" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="386" spans="1:2">
       <c r="A386" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="B386" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="387" spans="1:2">
       <c r="A387" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B387" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="388" spans="1:2">
       <c r="A388" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B388" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="389" spans="1:2">
       <c r="A389" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B389" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="390" spans="1:2">
       <c r="A390" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B390" t="s">
         <v>568</v>
@@ -8669,12 +8675,12 @@
         <v>571</v>
       </c>
       <c r="B392" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="393" spans="1:2">
       <c r="A393" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B393" t="s">
         <v>573</v>
@@ -8685,20 +8691,20 @@
         <v>574</v>
       </c>
       <c r="B394" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="395" spans="1:2">
       <c r="A395" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B395" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="396" spans="1:2">
       <c r="A396" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B396" t="s">
         <v>577</v>
@@ -8725,36 +8731,36 @@
         <v>582</v>
       </c>
       <c r="B399" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="400" spans="1:2">
       <c r="A400" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B400" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="401" spans="1:2">
       <c r="A401" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B401" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="402" spans="1:2">
       <c r="A402" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B402" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="403" spans="1:2">
       <c r="A403" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B403" t="s">
         <v>587</v>
@@ -8789,12 +8795,12 @@
         <v>594</v>
       </c>
       <c r="B407" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="408" spans="1:2">
       <c r="A408" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B408" t="s">
         <v>596</v>
@@ -8813,20 +8819,20 @@
         <v>599</v>
       </c>
       <c r="B410" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="411" spans="1:2">
       <c r="A411" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B411" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="412" spans="1:2">
       <c r="A412" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B412" t="s">
         <v>602</v>
@@ -8837,28 +8843,28 @@
         <v>603</v>
       </c>
       <c r="B413" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="414" spans="1:2">
       <c r="A414" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B414" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="415" spans="1:2">
       <c r="A415" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B415" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B416" t="s">
         <v>607</v>
@@ -8877,20 +8883,20 @@
         <v>610</v>
       </c>
       <c r="B418" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="419" spans="1:2">
       <c r="A419" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B419" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B420" t="s">
         <v>613</v>
@@ -9013,36 +9019,36 @@
         <v>642</v>
       </c>
       <c r="B435" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="436" spans="1:2">
       <c r="A436" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B436" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B437" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B438" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B439" t="s">
         <v>647</v>
@@ -9053,12 +9059,12 @@
         <v>648</v>
       </c>
       <c r="B440" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="441" spans="1:2">
       <c r="A441" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B441" t="s">
         <v>650</v>
@@ -9069,20 +9075,20 @@
         <v>651</v>
       </c>
       <c r="B442" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="443" spans="1:2">
       <c r="A443" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B443" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="444" spans="1:2">
       <c r="A444" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B444" t="s">
         <v>654</v>
@@ -9093,20 +9099,20 @@
         <v>655</v>
       </c>
       <c r="B445" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="446" spans="1:2">
       <c r="A446" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B446" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B447" t="s">
         <v>658</v>
@@ -9133,12 +9139,12 @@
         <v>663</v>
       </c>
       <c r="B450" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="451" spans="1:2">
       <c r="A451" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B451" t="s">
         <v>665</v>
@@ -9149,28 +9155,28 @@
         <v>666</v>
       </c>
       <c r="B452" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="453" spans="1:2">
       <c r="A453" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B453" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B454" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="455" spans="1:2">
       <c r="A455" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B455" t="s">
         <v>670</v>
@@ -9189,20 +9195,20 @@
         <v>673</v>
       </c>
       <c r="B457" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="458" spans="1:2">
       <c r="A458" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B458" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="B459" t="s">
         <v>676</v>
@@ -9213,20 +9219,20 @@
         <v>677</v>
       </c>
       <c r="B460" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="461" spans="1:2">
       <c r="A461" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B461" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="462" spans="1:2">
       <c r="A462" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="B462" t="s">
         <v>680</v>
@@ -9261,28 +9267,28 @@
         <v>687</v>
       </c>
       <c r="B466" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="467" spans="1:2">
       <c r="A467" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B467" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="B468" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B469" t="s">
         <v>691</v>
@@ -9293,12 +9299,12 @@
         <v>692</v>
       </c>
       <c r="B470" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="471" spans="1:2">
       <c r="A471" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B471" t="s">
         <v>694</v>
@@ -9309,20 +9315,20 @@
         <v>695</v>
       </c>
       <c r="B472" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="473" spans="1:2">
       <c r="A473" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B473" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="474" spans="1:2">
       <c r="A474" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="B474" t="s">
         <v>698</v>
@@ -9333,52 +9339,52 @@
         <v>699</v>
       </c>
       <c r="B475" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="476" spans="1:2">
       <c r="A476" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B476" t="s">
-        <v>691</v>
+        <v>701</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="B477" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B478" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B479" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B480" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B481" t="s">
         <v>706</v>
@@ -9397,12 +9403,12 @@
         <v>709</v>
       </c>
       <c r="B483" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="484" spans="1:2">
       <c r="A484" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B484" t="s">
         <v>711</v>
@@ -9413,12 +9419,12 @@
         <v>712</v>
       </c>
       <c r="B485" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="486" spans="1:2">
       <c r="A486" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="B486" t="s">
         <v>714</v>
@@ -9429,20 +9435,20 @@
         <v>715</v>
       </c>
       <c r="B487" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="488" spans="1:2">
       <c r="A488" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B488" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B489" t="s">
         <v>718</v>
@@ -9453,36 +9459,36 @@
         <v>719</v>
       </c>
       <c r="B490" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
     <row r="491" spans="1:2">
       <c r="A491" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B491" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B492" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B493" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B494" t="s">
         <v>724</v>
@@ -9637,12 +9643,12 @@
         <v>761</v>
       </c>
       <c r="B513" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
     </row>
     <row r="514" spans="1:2">
       <c r="A514" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B514" t="s">
         <v>763</v>
@@ -9653,12 +9659,12 @@
         <v>764</v>
       </c>
       <c r="B515" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
     </row>
     <row r="516" spans="1:2">
       <c r="A516" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B516" t="s">
         <v>765</v>
@@ -9666,7 +9672,7 @@
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B517" t="s">
         <v>767</v>
@@ -9677,12 +9683,12 @@
         <v>768</v>
       </c>
       <c r="B518" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="519" spans="1:2">
       <c r="A519" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B519" t="s">
         <v>770</v>
@@ -9717,12 +9723,12 @@
         <v>777</v>
       </c>
       <c r="B523" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="524" spans="1:2">
       <c r="A524" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B524" t="s">
         <v>779</v>
@@ -9733,12 +9739,12 @@
         <v>780</v>
       </c>
       <c r="B525" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="526" spans="1:2">
       <c r="A526" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B526" t="s">
         <v>782</v>
@@ -9757,12 +9763,12 @@
         <v>785</v>
       </c>
       <c r="B528" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="529" spans="1:2">
       <c r="A529" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B529" t="s">
         <v>787</v>
@@ -9813,12 +9819,12 @@
         <v>798</v>
       </c>
       <c r="B535" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
     </row>
     <row r="536" spans="1:2">
       <c r="A536" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="B536" t="s">
         <v>800</v>
@@ -9837,84 +9843,84 @@
         <v>803</v>
       </c>
       <c r="B538" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
     </row>
     <row r="539" spans="1:2">
       <c r="A539" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B539" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B540" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B541" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B542" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B543" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B544" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B545" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B546" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B547" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="548" spans="1:2">
       <c r="A548" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B548" t="s">
         <v>814</v>
@@ -9925,20 +9931,20 @@
         <v>815</v>
       </c>
       <c r="B549" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="550" spans="1:2">
       <c r="A550" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B550" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B551" t="s">
         <v>818</v>
@@ -9949,68 +9955,68 @@
         <v>819</v>
       </c>
       <c r="B552" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="553" spans="1:2">
       <c r="A553" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B553" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B554" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B555" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B556" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B557" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B558" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B559" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B560" t="s">
         <v>828</v>
@@ -10061,28 +10067,28 @@
         <v>839</v>
       </c>
       <c r="B566" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
     </row>
     <row r="567" spans="1:2">
       <c r="A567" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B567" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="B568" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B569" t="s">
         <v>843</v>
@@ -10093,20 +10099,20 @@
         <v>844</v>
       </c>
       <c r="B570" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
     </row>
     <row r="571" spans="1:2">
       <c r="A571" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B571" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="572" spans="1:2">
       <c r="A572" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B572" t="s">
         <v>847</v>
@@ -10117,20 +10123,20 @@
         <v>848</v>
       </c>
       <c r="B573" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="574" spans="1:2">
       <c r="A574" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B574" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B575" t="s">
         <v>851</v>
@@ -10149,60 +10155,60 @@
         <v>854</v>
       </c>
       <c r="B577" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="578" spans="1:2">
       <c r="A578" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B578" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B579" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B580" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B581" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B582" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B583" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B584" t="s">
         <v>862</v>
@@ -10221,20 +10227,20 @@
         <v>865</v>
       </c>
       <c r="B586" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="587" spans="1:2">
       <c r="A587" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B587" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B588" t="s">
         <v>868</v>
@@ -10245,12 +10251,12 @@
         <v>869</v>
       </c>
       <c r="B589" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="590" spans="1:2">
       <c r="A590" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B590" t="s">
         <v>871</v>
@@ -10261,12 +10267,12 @@
         <v>872</v>
       </c>
       <c r="B591" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="592" spans="1:2">
       <c r="A592" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B592" t="s">
         <v>874</v>
@@ -10285,12 +10291,12 @@
         <v>877</v>
       </c>
       <c r="B594" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="595" spans="1:2">
       <c r="A595" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B595" t="s">
         <v>879</v>
@@ -10309,12 +10315,12 @@
         <v>882</v>
       </c>
       <c r="B597" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="598" spans="1:2">
       <c r="A598" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B598" t="s">
         <v>884</v>
@@ -10341,36 +10347,36 @@
         <v>889</v>
       </c>
       <c r="B601" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
     </row>
     <row r="602" spans="1:2">
       <c r="A602" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B602" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B603" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B604" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B605" t="s">
         <v>894</v>
@@ -10413,20 +10419,20 @@
         <v>903</v>
       </c>
       <c r="B610" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
     </row>
     <row r="611" spans="1:2">
       <c r="A611" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B611" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B612" t="s">
         <v>906</v>
@@ -10437,44 +10443,44 @@
         <v>907</v>
       </c>
       <c r="B613" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="614" spans="1:2">
       <c r="A614" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B614" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B615" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B616" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B617" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="618" spans="1:2">
       <c r="A618" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B618" t="s">
         <v>913</v>
@@ -10485,44 +10491,44 @@
         <v>914</v>
       </c>
       <c r="B619" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="620" spans="1:2">
       <c r="A620" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B620" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B621" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B622" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B623" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B624" t="s">
         <v>920</v>
@@ -10541,12 +10547,12 @@
         <v>923</v>
       </c>
       <c r="B626" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="627" spans="1:2">
       <c r="A627" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B627" t="s">
         <v>925</v>
@@ -10557,12 +10563,12 @@
         <v>926</v>
       </c>
       <c r="B628" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="629" spans="1:2">
       <c r="A629" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B629" t="s">
         <v>928</v>
@@ -10573,188 +10579,188 @@
         <v>929</v>
       </c>
       <c r="B630" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="631" spans="1:2">
       <c r="A631" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B631" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B632" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B633" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B634" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B635" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B636" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B637" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B638" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B639" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B640" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B641" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B642" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B643" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B644" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B645" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B646" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B647" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B648" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B649" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B650" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B651" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B652" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B653" t="s">
         <v>953</v>
@@ -10789,28 +10795,28 @@
         <v>960</v>
       </c>
       <c r="B657" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="658" spans="1:2">
       <c r="A658" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B658" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B659" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B660" t="s">
         <v>964</v>
@@ -10821,20 +10827,20 @@
         <v>965</v>
       </c>
       <c r="B661" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="662" spans="1:2">
       <c r="A662" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B662" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B663" t="s">
         <v>968</v>
@@ -10845,44 +10851,44 @@
         <v>969</v>
       </c>
       <c r="B664" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="665" spans="1:2">
       <c r="A665" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B665" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
     </row>
     <row r="666" spans="1:2">
       <c r="A666" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B666" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B667" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B668" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="669" spans="1:2">
       <c r="A669" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B669" t="s">
         <v>975</v>
@@ -10893,52 +10899,52 @@
         <v>976</v>
       </c>
       <c r="B670" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="671" spans="1:2">
       <c r="A671" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B671" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="672" spans="1:2">
       <c r="A672" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B672" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="673" spans="1:2">
       <c r="A673" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B673" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B674" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B675" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B676" t="s">
         <v>983</v>
@@ -10949,12 +10955,12 @@
         <v>984</v>
       </c>
       <c r="B677" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="678" spans="1:2">
       <c r="A678" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B678" t="s">
         <v>986</v>
@@ -10973,68 +10979,68 @@
         <v>989</v>
       </c>
       <c r="B680" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="681" spans="1:2">
       <c r="A681" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B681" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B682" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B683" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B684" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B685" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B686" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B687" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="688" spans="1:2">
       <c r="A688" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B688" t="s">
         <v>998</v>
@@ -11053,20 +11059,20 @@
         <v>1001</v>
       </c>
       <c r="B690" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="691" spans="1:2">
       <c r="A691" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B691" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B692" t="s">
         <v>1004</v>
@@ -11085,12 +11091,12 @@
         <v>1007</v>
       </c>
       <c r="B694" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="695" spans="1:2">
       <c r="A695" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B695" t="s">
         <v>1009</v>
@@ -11125,12 +11131,12 @@
         <v>1016</v>
       </c>
       <c r="B699" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="700" spans="1:2">
       <c r="A700" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B700" t="s">
         <v>1018</v>
@@ -11149,12 +11155,12 @@
         <v>1021</v>
       </c>
       <c r="B702" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="703" spans="1:2">
       <c r="A703" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B703" t="s">
         <v>1023</v>
@@ -11197,36 +11203,36 @@
         <v>1032</v>
       </c>
       <c r="B708" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="709" spans="1:2">
       <c r="A709" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B709" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B710" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B711" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B712" t="s">
         <v>1037</v>
@@ -11237,76 +11243,76 @@
         <v>1038</v>
       </c>
       <c r="B713" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="714" spans="1:2">
       <c r="A714" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B714" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B715" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B716" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B717" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B718" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B719" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B720" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B721" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B722" t="s">
         <v>1048</v>
@@ -11325,20 +11331,20 @@
         <v>1051</v>
       </c>
       <c r="B724" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="725" spans="1:2">
       <c r="A725" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B725" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B726" t="s">
         <v>1054</v>
@@ -11349,12 +11355,12 @@
         <v>1055</v>
       </c>
       <c r="B727" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="728" spans="1:2">
       <c r="A728" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B728" t="s">
         <v>1057</v>
@@ -11365,12 +11371,12 @@
         <v>1058</v>
       </c>
       <c r="B729" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="730" spans="1:2">
       <c r="A730" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B730" t="s">
         <v>1060</v>
@@ -11381,12 +11387,12 @@
         <v>1061</v>
       </c>
       <c r="B731" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="732" spans="1:2">
       <c r="A732" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B732" t="s">
         <v>1063</v>
@@ -11397,12 +11403,12 @@
         <v>1064</v>
       </c>
       <c r="B733" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="734" spans="1:2">
       <c r="A734" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B734" t="s">
         <v>1066</v>
@@ -11421,20 +11427,20 @@
         <v>1069</v>
       </c>
       <c r="B736" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="737" spans="1:2">
       <c r="A737" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B737" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B738" t="s">
         <v>1072</v>
@@ -11445,12 +11451,12 @@
         <v>1073</v>
       </c>
       <c r="B739" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="740" spans="1:2">
       <c r="A740" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B740" t="s">
         <v>1075</v>
@@ -11461,68 +11467,68 @@
         <v>1076</v>
       </c>
       <c r="B741" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="742" spans="1:2">
       <c r="A742" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B742" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B743" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B744" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B745" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B746" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B747" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B748" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B749" t="s">
         <v>1085</v>
@@ -11533,12 +11539,12 @@
         <v>1086</v>
       </c>
       <c r="B750" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="751" spans="1:2">
       <c r="A751" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B751" t="s">
         <v>1088</v>
@@ -11557,36 +11563,36 @@
         <v>1091</v>
       </c>
       <c r="B753" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="754" spans="1:2">
       <c r="A754" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B754" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B755" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B756" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B757" t="s">
         <v>1096</v>
@@ -11597,20 +11603,20 @@
         <v>1097</v>
       </c>
       <c r="B758" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="759" spans="1:2">
       <c r="A759" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B759" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="760" spans="1:2">
       <c r="A760" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B760" t="s">
         <v>1100</v>
@@ -11645,20 +11651,20 @@
         <v>1107</v>
       </c>
       <c r="B764" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="765" spans="1:2">
       <c r="A765" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B765" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="766" spans="1:2">
       <c r="A766" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B766" t="s">
         <v>1110</v>
@@ -11677,12 +11683,12 @@
         <v>1113</v>
       </c>
       <c r="B768" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="769" spans="1:2">
       <c r="A769" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B769" t="s">
         <v>1115</v>
@@ -11693,20 +11699,20 @@
         <v>1116</v>
       </c>
       <c r="B770" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="771" spans="1:2">
       <c r="A771" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B771" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B772" t="s">
         <v>1119</v>
@@ -11749,12 +11755,12 @@
         <v>1128</v>
       </c>
       <c r="B777" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="778" spans="1:2">
       <c r="A778" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B778" t="s">
         <v>1130</v>
@@ -11773,44 +11779,44 @@
         <v>1133</v>
       </c>
       <c r="B780" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="781" spans="1:2">
       <c r="A781" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B781" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B782" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B783" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B784" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B785" t="s">
         <v>1139</v>
@@ -11821,12 +11827,12 @@
         <v>1140</v>
       </c>
       <c r="B786" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="787" spans="1:2">
       <c r="A787" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B787" t="s">
         <v>1142</v>
@@ -11853,44 +11859,44 @@
         <v>1147</v>
       </c>
       <c r="B790" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="791" spans="1:2">
       <c r="A791" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B791" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B792" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B793" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B794" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B795" t="s">
         <v>1153</v>
@@ -11901,116 +11907,116 @@
         <v>1154</v>
       </c>
       <c r="B796" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="797" spans="1:2">
       <c r="A797" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B797" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B798" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B799" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B800" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B801" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B802" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B803" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B804" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B805" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B806" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B807" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B808" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B809" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B810" t="s">
         <v>1169</v>
@@ -12045,44 +12051,44 @@
         <v>1176</v>
       </c>
       <c r="B814" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="815" spans="1:2">
       <c r="A815" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B815" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B816" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B817" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B818" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B819" t="s">
         <v>1182</v>
@@ -12117,36 +12123,36 @@
         <v>1189</v>
       </c>
       <c r="B823" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="824" spans="1:2">
       <c r="A824" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B824" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B825" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B826" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B827" t="s">
         <v>1194</v>
@@ -12157,28 +12163,28 @@
         <v>1195</v>
       </c>
       <c r="B828" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="829" spans="1:2">
       <c r="A829" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B829" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B830" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B831" t="s">
         <v>1199</v>
@@ -12205,12 +12211,12 @@
         <v>1204</v>
       </c>
       <c r="B834" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="835" spans="1:2">
       <c r="A835" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B835" t="s">
         <v>1206</v>
@@ -12221,28 +12227,28 @@
         <v>1207</v>
       </c>
       <c r="B836" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="837" spans="1:2">
       <c r="A837" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B837" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B838" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B839" t="s">
         <v>1211</v>
@@ -12253,44 +12259,44 @@
         <v>1212</v>
       </c>
       <c r="B840" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="841" spans="1:2">
       <c r="A841" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B841" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B842" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B843" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B844" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B845" t="s">
         <v>1218</v>
@@ -12301,148 +12307,148 @@
         <v>1219</v>
       </c>
       <c r="B846" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="847" spans="1:2">
       <c r="A847" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B847" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B848" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B849" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B850" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B851" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B852" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B853" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B854" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B855" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B856" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B857" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B858" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B859" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B860" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B861" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B862" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B863" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B864" t="s">
         <v>1238</v>
@@ -12477,28 +12483,28 @@
         <v>1245</v>
       </c>
       <c r="B868" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="869" spans="1:2">
       <c r="A869" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B869" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B870" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B871" t="s">
         <v>1249</v>
@@ -12509,68 +12515,68 @@
         <v>1250</v>
       </c>
       <c r="B872" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="873" spans="1:2">
       <c r="A873" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B873" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B874" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B875" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B876" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B877" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B878" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B879" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B880" t="s">
         <v>1259</v>
@@ -12581,28 +12587,28 @@
         <v>1260</v>
       </c>
       <c r="B881" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="882" spans="1:2">
       <c r="A882" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B882" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B883" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B884" t="s">
         <v>1264</v>
@@ -12613,12 +12619,12 @@
         <v>1265</v>
       </c>
       <c r="B885" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="886" spans="1:2">
       <c r="A886" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B886" t="s">
         <v>1267</v>
@@ -12629,12 +12635,12 @@
         <v>1268</v>
       </c>
       <c r="B887" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
     </row>
     <row r="888" spans="1:2">
       <c r="A888" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B888" t="s">
         <v>1270</v>
@@ -12653,20 +12659,20 @@
         <v>1273</v>
       </c>
       <c r="B890" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="891" spans="1:2">
       <c r="A891" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="B891" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B892" t="s">
         <v>1276</v>
@@ -12685,44 +12691,44 @@
         <v>1279</v>
       </c>
       <c r="B894" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="895" spans="1:2">
       <c r="A895" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B895" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B896" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B897" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B898" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B899" t="s">
         <v>1285</v>
@@ -12733,44 +12739,44 @@
         <v>1286</v>
       </c>
       <c r="B900" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="901" spans="1:2">
       <c r="A901" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="B901" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="B902" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B903" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B904" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B905" t="s">
         <v>1292</v>
@@ -12781,12 +12787,12 @@
         <v>1293</v>
       </c>
       <c r="B906" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="907" spans="1:2">
       <c r="A907" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="B907" t="s">
         <v>1295</v>
@@ -12797,36 +12803,36 @@
         <v>1296</v>
       </c>
       <c r="B908" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="909" spans="1:2">
       <c r="A909" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="B909" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="B910" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B911" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B912" t="s">
         <v>1301</v>
@@ -12853,68 +12859,68 @@
         <v>1306</v>
       </c>
       <c r="B915" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="916" spans="1:2">
       <c r="A916" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="B916" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="B917" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B918" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B919" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B920" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B921" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B922" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B923" t="s">
         <v>1315</v>
@@ -12941,28 +12947,28 @@
         <v>1320</v>
       </c>
       <c r="B926" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="927" spans="1:2">
       <c r="A927" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="B927" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B928" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B929" t="s">
         <v>1324</v>
@@ -13005,20 +13011,20 @@
         <v>1333</v>
       </c>
       <c r="B934" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="935" spans="1:2">
       <c r="A935" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B935" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B936" t="s">
         <v>1336</v>
@@ -13029,12 +13035,12 @@
         <v>1337</v>
       </c>
       <c r="B937" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="938" spans="1:2">
       <c r="A938" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B938" t="s">
         <v>1339</v>
@@ -13053,12 +13059,12 @@
         <v>1342</v>
       </c>
       <c r="B940" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="941" spans="1:2">
       <c r="A941" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B941" t="s">
         <v>1344</v>
@@ -13077,36 +13083,36 @@
         <v>1347</v>
       </c>
       <c r="B943" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="944" spans="1:2">
       <c r="A944" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="B944" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B945" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B946" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B947" t="s">
         <v>1352</v>
@@ -13165,28 +13171,28 @@
         <v>1365</v>
       </c>
       <c r="B954" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="955" spans="1:2">
       <c r="A955" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="B955" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="B956" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B957" t="s">
         <v>1369</v>
@@ -13197,68 +13203,68 @@
         <v>1370</v>
       </c>
       <c r="B958" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="959" spans="1:2">
       <c r="A959" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B959" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B960" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B961" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B962" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B963" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B964" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B965" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B966" t="s">
         <v>1379</v>
@@ -13285,20 +13291,20 @@
         <v>1384</v>
       </c>
       <c r="B969" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
     </row>
     <row r="970" spans="1:2">
       <c r="A970" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="B970" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B971" t="s">
         <v>1387</v>
@@ -13325,20 +13331,20 @@
         <v>1392</v>
       </c>
       <c r="B974" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="975" spans="1:2">
       <c r="A975" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="B975" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B976" t="s">
         <v>1395</v>
@@ -13349,44 +13355,44 @@
         <v>1396</v>
       </c>
       <c r="B977" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="978" spans="1:2">
       <c r="A978" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="B978" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B979" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B980" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B981" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B982" t="s">
         <v>1402</v>
@@ -13429,68 +13435,68 @@
         <v>1411</v>
       </c>
       <c r="B987" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="988" spans="1:2">
       <c r="A988" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B988" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B989" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B990" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B991" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B992" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B993" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B994" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B995" t="s">
         <v>1420</v>
@@ -13501,28 +13507,28 @@
         <v>1421</v>
       </c>
       <c r="B996" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="997" spans="1:2">
       <c r="A997" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B997" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B998" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B999" t="s">
         <v>1425</v>
@@ -13533,60 +13539,60 @@
         <v>1426</v>
       </c>
       <c r="B1000" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="1001" spans="1:2">
       <c r="A1001" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B1001" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="B1002" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B1003" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B1004" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B1005" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B1006" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B1007" t="s">
         <v>1434</v>
@@ -13605,28 +13611,28 @@
         <v>1437</v>
       </c>
       <c r="B1009" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="1010" spans="1:2">
       <c r="A1010" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B1010" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B1011" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B1012" t="s">
         <v>1441</v>
@@ -13637,12 +13643,12 @@
         <v>1442</v>
       </c>
       <c r="B1013" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="1014" spans="1:2">
       <c r="A1014" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B1014" t="s">
         <v>1444</v>
@@ -13661,36 +13667,36 @@
         <v>1447</v>
       </c>
       <c r="B1016" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="1017" spans="1:2">
       <c r="A1017" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B1017" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="B1018" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B1019" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B1020" t="s">
         <v>1452</v>
@@ -13701,36 +13707,36 @@
         <v>1453</v>
       </c>
       <c r="B1021" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="1022" spans="1:2">
       <c r="A1022" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="B1022" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B1023" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B1024" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B1025" t="s">
         <v>1458</v>
@@ -13749,36 +13755,36 @@
         <v>1461</v>
       </c>
       <c r="B1027" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
     </row>
     <row r="1028" spans="1:2">
       <c r="A1028" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="B1028" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B1029" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B1030" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B1031" t="s">
         <v>1466</v>
@@ -13797,20 +13803,20 @@
         <v>1469</v>
       </c>
       <c r="B1033" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="1034" spans="1:2">
       <c r="A1034" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B1034" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="B1035" t="s">
         <v>1472</v>
@@ -13829,12 +13835,12 @@
         <v>1475</v>
       </c>
       <c r="B1037" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="1038" spans="1:2">
       <c r="A1038" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B1038" t="s">
         <v>1477</v>
@@ -13845,84 +13851,84 @@
         <v>1478</v>
       </c>
       <c r="B1039" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="1040" spans="1:2">
       <c r="A1040" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B1040" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="B1041" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B1042" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B1043" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B1044" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B1045" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B1046" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B1047" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B1048" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B1049" t="s">
         <v>1489</v>
@@ -13933,12 +13939,12 @@
         <v>1490</v>
       </c>
       <c r="B1050" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="1051" spans="1:2">
       <c r="A1051" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="B1051" t="s">
         <v>1492</v>
@@ -13965,20 +13971,20 @@
         <v>1497</v>
       </c>
       <c r="B1054" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="1055" spans="1:2">
       <c r="A1055" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="B1055" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="B1056" t="s">
         <v>1500</v>
@@ -13989,12 +13995,12 @@
         <v>1501</v>
       </c>
       <c r="B1057" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
     </row>
     <row r="1058" spans="1:2">
       <c r="A1058" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="B1058" t="s">
         <v>1503</v>
@@ -14005,52 +14011,52 @@
         <v>1504</v>
       </c>
       <c r="B1059" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="1060" spans="1:2">
       <c r="A1060" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B1060" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="B1061" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B1062" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B1063" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B1064" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B1065" t="s">
         <v>1511</v>
@@ -14117,12 +14123,12 @@
         <v>1526</v>
       </c>
       <c r="B1073" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="1074" spans="1:2">
       <c r="A1074" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B1074" t="s">
         <v>1528</v>
@@ -14133,28 +14139,28 @@
         <v>1529</v>
       </c>
       <c r="B1075" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="1076" spans="1:2">
       <c r="A1076" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="B1076" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="B1077" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B1078" t="s">
         <v>1533</v>
@@ -14165,12 +14171,12 @@
         <v>1534</v>
       </c>
       <c r="B1079" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="1080" spans="1:2">
       <c r="A1080" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="B1080" t="s">
         <v>1536</v>
@@ -14189,28 +14195,28 @@
         <v>1539</v>
       </c>
       <c r="B1082" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="1083" spans="1:2">
       <c r="A1083" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="B1083" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="B1084" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B1085" t="s">
         <v>1543</v>
@@ -14221,28 +14227,28 @@
         <v>1544</v>
       </c>
       <c r="B1086" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="1087" spans="1:2">
       <c r="A1087" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="B1087" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="B1088" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B1089" t="s">
         <v>1548</v>
@@ -14253,20 +14259,20 @@
         <v>1549</v>
       </c>
       <c r="B1090" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="1091" spans="1:2">
       <c r="A1091" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="B1091" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B1092" t="s">
         <v>1552</v>
@@ -14277,12 +14283,12 @@
         <v>1553</v>
       </c>
       <c r="B1093" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="1094" spans="1:2">
       <c r="A1094" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B1094" t="s">
         <v>1555</v>
@@ -14293,28 +14299,28 @@
         <v>1556</v>
       </c>
       <c r="B1095" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="1096" spans="1:2">
       <c r="A1096" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B1096" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B1097" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B1098" t="s">
         <v>1560</v>
@@ -14325,20 +14331,20 @@
         <v>1561</v>
       </c>
       <c r="B1099" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="1100" spans="1:2">
       <c r="A1100" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B1100" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="B1101" t="s">
         <v>1564</v>
@@ -14373,20 +14379,20 @@
         <v>1571</v>
       </c>
       <c r="B1105" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="1106" spans="1:2">
       <c r="A1106" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B1106" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="B1107" t="s">
         <v>1574</v>
@@ -14421,52 +14427,52 @@
         <v>1581</v>
       </c>
       <c r="B1111" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="1112" spans="1:2">
       <c r="A1112" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B1112" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
       <c r="B1113" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B1114" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B1115" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B1116" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B1117" t="s">
         <v>1588</v>
@@ -14477,20 +14483,20 @@
         <v>1589</v>
       </c>
       <c r="B1118" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="1119" spans="1:2">
       <c r="A1119" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B1119" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
       <c r="B1120" t="s">
         <v>1592</v>
@@ -14501,52 +14507,52 @@
         <v>1593</v>
       </c>
       <c r="B1121" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="1122" spans="1:2">
       <c r="A1122" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B1122" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
       <c r="B1123" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B1124" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B1125" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1126" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B1127" t="s">
         <v>1600</v>
@@ -14557,20 +14563,20 @@
         <v>1601</v>
       </c>
       <c r="B1128" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="1129" spans="1:2">
       <c r="A1129" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B1129" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B1130" t="s">
         <v>1604</v>
@@ -14589,20 +14595,20 @@
         <v>1607</v>
       </c>
       <c r="B1132" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="1133" spans="1:2">
       <c r="A1133" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
       <c r="B1133" t="s">
-        <v>1608</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
       <c r="B1134" t="s">
         <v>1610</v>
@@ -14701,44 +14707,44 @@
         <v>1633</v>
       </c>
       <c r="B1146" t="s">
-        <v>1633</v>
+        <v>1634</v>
       </c>
     </row>
     <row r="1147" spans="1:2">
       <c r="A1147" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="B1147" t="s">
-        <v>1634</v>
+        <v>1635</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
       <c r="B1148" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B1149" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B1150" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B1151" t="s">
         <v>1639</v>
@@ -14757,36 +14763,36 @@
         <v>1642</v>
       </c>
       <c r="B1153" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="1154" spans="1:2">
       <c r="A1154" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="B1154" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="B1155" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B1156" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B1157" t="s">
         <v>1647</v>
@@ -14797,20 +14803,20 @@
         <v>1648</v>
       </c>
       <c r="B1158" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="1159" spans="1:2">
       <c r="A1159" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="B1159" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="B1160" t="s">
         <v>1651</v>
@@ -14845,12 +14851,12 @@
         <v>1658</v>
       </c>
       <c r="B1164" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="1165" spans="1:2">
       <c r="A1165" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="B1165" t="s">
         <v>1660</v>
@@ -14869,12 +14875,12 @@
         <v>1663</v>
       </c>
       <c r="B1167" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="1168" spans="1:2">
       <c r="A1168" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="B1168" t="s">
         <v>1665</v>
@@ -14901,124 +14907,124 @@
         <v>1670</v>
       </c>
       <c r="B1171" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="1172" spans="1:2">
       <c r="A1172" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="B1172" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="B1173" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B1174" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B1175" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B1176" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B1177" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B1178" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1179" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B1180" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1181" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B1182" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B1183" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B1184" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B1185" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B1186" t="s">
         <v>1686</v>
@@ -15029,36 +15035,36 @@
         <v>1687</v>
       </c>
       <c r="B1187" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
     </row>
     <row r="1188" spans="1:2">
       <c r="A1188" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="B1188" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="B1189" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B1190" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B1191" t="s">
         <v>1692</v>
@@ -15077,36 +15083,36 @@
         <v>1695</v>
       </c>
       <c r="B1193" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="1194" spans="1:2">
       <c r="A1194" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="B1194" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="B1195" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
       <c r="A1196" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1196" t="s">
-        <v>386</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
       <c r="A1197" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1197" t="s">
         <v>388</v>
@@ -15114,182 +15120,190 @@
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1198" t="s">
-        <v>1700</v>
+        <v>390</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
       <c r="A1199" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1199" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="1200" spans="1:2">
       <c r="A1200" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B1200" t="s">
-        <v>647</v>
+        <v>1703</v>
       </c>
     </row>
     <row r="1201" spans="1:2">
       <c r="A1201" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B1201" t="s">
-        <v>1703</v>
+        <v>649</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
       <c r="A1202" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B1202" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1203" spans="1:2">
       <c r="A1203" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B1203" t="s">
-        <v>928</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="1204" spans="1:2">
       <c r="A1204" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1204" t="s">
-        <v>1706</v>
+        <v>930</v>
       </c>
     </row>
     <row r="1205" spans="1:2">
       <c r="A1205" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1205" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1206" spans="1:2">
       <c r="A1206" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B1206" t="s">
-        <v>1004</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="1207" spans="1:2">
       <c r="A1207" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B1207" t="s">
-        <v>1709</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="1208" spans="1:2">
       <c r="A1208" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B1208" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="1209" spans="1:2">
       <c r="A1209" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B1209" t="s">
-        <v>1072</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="1210" spans="1:2">
       <c r="A1210" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1210" t="s">
-        <v>1127</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="1211" spans="1:2">
       <c r="A1211" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="B1211" t="s">
-        <v>1713</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="1212" spans="1:2">
       <c r="A1212" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B1212" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="1213" spans="1:2">
       <c r="A1213" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B1213" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="1214" spans="1:2">
       <c r="A1214" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B1214" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="1215" spans="1:2">
       <c r="A1215" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B1215" t="s">
-        <v>1436</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="1216" spans="1:2">
       <c r="A1216" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B1216" t="s">
-        <v>1718</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="1217" spans="1:2">
       <c r="A1217" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B1217" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="1218" spans="1:2">
       <c r="A1218" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B1218" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="1219" spans="1:2">
       <c r="A1219" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B1219" t="s">
-        <v>1555</v>
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:2">
+      <c r="A1220" t="s">
+        <v>1723</v>
+      </c>
+      <c r="B1220" t="s">
+        <v>1557</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1219"/>
+  <autoFilter ref="A1:B1220"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>

--- a/lang/da/headTags.xlsx
+++ b/lang/da/headTags.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Translations" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1220</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Translations'!$A$1:$B$1221</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="1726">
   <si>
     <t>en</t>
   </si>
@@ -1835,6 +1835,12 @@
   </si>
   <si>
     <t>Font (Orange)</t>
+  </si>
+  <si>
+    <t>Font (Pale Oak)</t>
+  </si>
+  <si>
+    <t>Skrifttype (lys eg)</t>
   </si>
   <si>
     <t>Font (Pink)</t>
@@ -5535,7 +5541,7 @@
   <sheetPr filterMode="1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:B1220"/>
+  <dimension ref="A1:B1221"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="50" customWidth="true" style="0"/>
@@ -8859,20 +8865,20 @@
         <v>606</v>
       </c>
       <c r="B415" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="416" spans="1:2">
       <c r="A416" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B416" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
     </row>
     <row r="417" spans="1:2">
       <c r="A417" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B417" t="s">
         <v>609</v>
@@ -8891,20 +8897,20 @@
         <v>612</v>
       </c>
       <c r="B419" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="420" spans="1:2">
       <c r="A420" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B420" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
     </row>
     <row r="421" spans="1:2">
       <c r="A421" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B421" t="s">
         <v>615</v>
@@ -9027,36 +9033,36 @@
         <v>644</v>
       </c>
       <c r="B436" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="437" spans="1:2">
       <c r="A437" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B437" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
     </row>
     <row r="438" spans="1:2">
       <c r="A438" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B438" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="439" spans="1:2">
       <c r="A439" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B439" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
     </row>
     <row r="440" spans="1:2">
       <c r="A440" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B440" t="s">
         <v>649</v>
@@ -9067,12 +9073,12 @@
         <v>650</v>
       </c>
       <c r="B441" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="442" spans="1:2">
       <c r="A442" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B442" t="s">
         <v>652</v>
@@ -9083,20 +9089,20 @@
         <v>653</v>
       </c>
       <c r="B443" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="444" spans="1:2">
       <c r="A444" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B444" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="445" spans="1:2">
       <c r="A445" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B445" t="s">
         <v>656</v>
@@ -9107,20 +9113,20 @@
         <v>657</v>
       </c>
       <c r="B446" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="447" spans="1:2">
       <c r="A447" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B447" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="448" spans="1:2">
       <c r="A448" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B448" t="s">
         <v>660</v>
@@ -9147,12 +9153,12 @@
         <v>665</v>
       </c>
       <c r="B451" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="452" spans="1:2">
       <c r="A452" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B452" t="s">
         <v>667</v>
@@ -9163,28 +9169,28 @@
         <v>668</v>
       </c>
       <c r="B453" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="454" spans="1:2">
       <c r="A454" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B454" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="455" spans="1:2">
       <c r="A455" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B455" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="456" spans="1:2">
       <c r="A456" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B456" t="s">
         <v>672</v>
@@ -9203,20 +9209,20 @@
         <v>675</v>
       </c>
       <c r="B458" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="459" spans="1:2">
       <c r="A459" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B459" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="460" spans="1:2">
       <c r="A460" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B460" t="s">
         <v>678</v>
@@ -9227,20 +9233,20 @@
         <v>679</v>
       </c>
       <c r="B461" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="462" spans="1:2">
       <c r="A462" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B462" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="463" spans="1:2">
       <c r="A463" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B463" t="s">
         <v>682</v>
@@ -9275,28 +9281,28 @@
         <v>689</v>
       </c>
       <c r="B467" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="468" spans="1:2">
       <c r="A468" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B468" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="469" spans="1:2">
       <c r="A469" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="B469" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="470" spans="1:2">
       <c r="A470" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B470" t="s">
         <v>693</v>
@@ -9307,12 +9313,12 @@
         <v>694</v>
       </c>
       <c r="B471" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="472" spans="1:2">
       <c r="A472" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="B472" t="s">
         <v>696</v>
@@ -9323,20 +9329,20 @@
         <v>697</v>
       </c>
       <c r="B473" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="474" spans="1:2">
       <c r="A474" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B474" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="475" spans="1:2">
       <c r="A475" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="B475" t="s">
         <v>700</v>
@@ -9347,52 +9353,52 @@
         <v>701</v>
       </c>
       <c r="B476" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="477" spans="1:2">
       <c r="A477" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B477" t="s">
-        <v>693</v>
+        <v>703</v>
       </c>
     </row>
     <row r="478" spans="1:2">
       <c r="A478" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="B478" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
     </row>
     <row r="479" spans="1:2">
       <c r="A479" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B479" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="480" spans="1:2">
       <c r="A480" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="B480" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="481" spans="1:2">
       <c r="A481" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B481" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="482" spans="1:2">
       <c r="A482" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B482" t="s">
         <v>708</v>
@@ -9411,12 +9417,12 @@
         <v>711</v>
       </c>
       <c r="B484" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="485" spans="1:2">
       <c r="A485" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B485" t="s">
         <v>713</v>
@@ -9427,12 +9433,12 @@
         <v>714</v>
       </c>
       <c r="B486" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="487" spans="1:2">
       <c r="A487" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="B487" t="s">
         <v>716</v>
@@ -9443,20 +9449,20 @@
         <v>717</v>
       </c>
       <c r="B488" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="489" spans="1:2">
       <c r="A489" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B489" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="490" spans="1:2">
       <c r="A490" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B490" t="s">
         <v>720</v>
@@ -9467,36 +9473,36 @@
         <v>721</v>
       </c>
       <c r="B491" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
     </row>
     <row r="492" spans="1:2">
       <c r="A492" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B492" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
     </row>
     <row r="493" spans="1:2">
       <c r="A493" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="B493" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
     </row>
     <row r="494" spans="1:2">
       <c r="A494" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B494" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
     </row>
     <row r="495" spans="1:2">
       <c r="A495" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B495" t="s">
         <v>726</v>
@@ -9651,12 +9657,12 @@
         <v>763</v>
       </c>
       <c r="B514" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="515" spans="1:2">
       <c r="A515" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B515" t="s">
         <v>765</v>
@@ -9667,12 +9673,12 @@
         <v>766</v>
       </c>
       <c r="B516" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
     </row>
     <row r="517" spans="1:2">
       <c r="A517" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B517" t="s">
         <v>767</v>
@@ -9680,7 +9686,7 @@
     </row>
     <row r="518" spans="1:2">
       <c r="A518" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B518" t="s">
         <v>769</v>
@@ -9691,12 +9697,12 @@
         <v>770</v>
       </c>
       <c r="B519" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
     </row>
     <row r="520" spans="1:2">
       <c r="A520" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B520" t="s">
         <v>772</v>
@@ -9731,12 +9737,12 @@
         <v>779</v>
       </c>
       <c r="B524" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
     </row>
     <row r="525" spans="1:2">
       <c r="A525" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B525" t="s">
         <v>781</v>
@@ -9747,12 +9753,12 @@
         <v>782</v>
       </c>
       <c r="B526" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
     </row>
     <row r="527" spans="1:2">
       <c r="A527" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B527" t="s">
         <v>784</v>
@@ -9771,12 +9777,12 @@
         <v>787</v>
       </c>
       <c r="B529" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
     </row>
     <row r="530" spans="1:2">
       <c r="A530" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B530" t="s">
         <v>789</v>
@@ -9827,12 +9833,12 @@
         <v>800</v>
       </c>
       <c r="B536" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
     </row>
     <row r="537" spans="1:2">
       <c r="A537" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B537" t="s">
         <v>802</v>
@@ -9851,84 +9857,84 @@
         <v>805</v>
       </c>
       <c r="B539" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
     </row>
     <row r="540" spans="1:2">
       <c r="A540" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B540" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="541" spans="1:2">
       <c r="A541" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B541" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="542" spans="1:2">
       <c r="A542" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B542" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="543" spans="1:2">
       <c r="A543" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B543" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
     </row>
     <row r="544" spans="1:2">
       <c r="A544" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B544" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
     </row>
     <row r="545" spans="1:2">
       <c r="A545" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B545" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="546" spans="1:2">
       <c r="A546" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B546" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="547" spans="1:2">
       <c r="A547" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B547" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="548" spans="1:2">
       <c r="A548" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B548" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="549" spans="1:2">
       <c r="A549" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B549" t="s">
         <v>816</v>
@@ -9939,20 +9945,20 @@
         <v>817</v>
       </c>
       <c r="B550" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="551" spans="1:2">
       <c r="A551" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B551" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="552" spans="1:2">
       <c r="A552" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B552" t="s">
         <v>820</v>
@@ -9963,68 +9969,68 @@
         <v>821</v>
       </c>
       <c r="B553" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="554" spans="1:2">
       <c r="A554" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B554" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
     </row>
     <row r="555" spans="1:2">
       <c r="A555" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B555" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
     </row>
     <row r="556" spans="1:2">
       <c r="A556" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B556" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
     </row>
     <row r="557" spans="1:2">
       <c r="A557" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B557" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
     </row>
     <row r="558" spans="1:2">
       <c r="A558" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B558" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="559" spans="1:2">
       <c r="A559" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B559" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="560" spans="1:2">
       <c r="A560" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B560" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
     </row>
     <row r="561" spans="1:2">
       <c r="A561" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B561" t="s">
         <v>830</v>
@@ -10075,28 +10081,28 @@
         <v>841</v>
       </c>
       <c r="B567" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
     </row>
     <row r="568" spans="1:2">
       <c r="A568" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B568" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="569" spans="1:2">
       <c r="A569" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B569" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
     </row>
     <row r="570" spans="1:2">
       <c r="A570" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B570" t="s">
         <v>845</v>
@@ -10107,20 +10113,20 @@
         <v>846</v>
       </c>
       <c r="B571" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
     </row>
     <row r="572" spans="1:2">
       <c r="A572" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="B572" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="573" spans="1:2">
       <c r="A573" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B573" t="s">
         <v>849</v>
@@ -10131,20 +10137,20 @@
         <v>850</v>
       </c>
       <c r="B574" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
     </row>
     <row r="575" spans="1:2">
       <c r="A575" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="B575" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
     </row>
     <row r="576" spans="1:2">
       <c r="A576" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B576" t="s">
         <v>853</v>
@@ -10163,60 +10169,60 @@
         <v>856</v>
       </c>
       <c r="B578" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
     </row>
     <row r="579" spans="1:2">
       <c r="A579" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B579" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="580" spans="1:2">
       <c r="A580" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B580" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
     </row>
     <row r="581" spans="1:2">
       <c r="A581" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B581" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="582" spans="1:2">
       <c r="A582" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B582" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
     </row>
     <row r="583" spans="1:2">
       <c r="A583" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B583" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
     </row>
     <row r="584" spans="1:2">
       <c r="A584" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B584" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="585" spans="1:2">
       <c r="A585" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B585" t="s">
         <v>864</v>
@@ -10235,20 +10241,20 @@
         <v>867</v>
       </c>
       <c r="B587" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="588" spans="1:2">
       <c r="A588" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B588" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="589" spans="1:2">
       <c r="A589" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B589" t="s">
         <v>870</v>
@@ -10259,12 +10265,12 @@
         <v>871</v>
       </c>
       <c r="B590" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="591" spans="1:2">
       <c r="A591" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B591" t="s">
         <v>873</v>
@@ -10275,12 +10281,12 @@
         <v>874</v>
       </c>
       <c r="B592" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B593" t="s">
         <v>876</v>
@@ -10299,12 +10305,12 @@
         <v>879</v>
       </c>
       <c r="B595" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
     </row>
     <row r="596" spans="1:2">
       <c r="A596" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B596" t="s">
         <v>881</v>
@@ -10323,12 +10329,12 @@
         <v>884</v>
       </c>
       <c r="B598" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
     </row>
     <row r="599" spans="1:2">
       <c r="A599" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B599" t="s">
         <v>886</v>
@@ -10355,36 +10361,36 @@
         <v>891</v>
       </c>
       <c r="B602" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="603" spans="1:2">
       <c r="A603" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B603" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="604" spans="1:2">
       <c r="A604" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B604" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
     </row>
     <row r="605" spans="1:2">
       <c r="A605" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B605" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
     </row>
     <row r="606" spans="1:2">
       <c r="A606" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B606" t="s">
         <v>896</v>
@@ -10427,20 +10433,20 @@
         <v>905</v>
       </c>
       <c r="B611" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
     </row>
     <row r="612" spans="1:2">
       <c r="A612" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B612" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="613" spans="1:2">
       <c r="A613" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B613" t="s">
         <v>908</v>
@@ -10451,44 +10457,44 @@
         <v>909</v>
       </c>
       <c r="B614" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="615" spans="1:2">
       <c r="A615" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B615" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="616" spans="1:2">
       <c r="A616" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B616" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="617" spans="1:2">
       <c r="A617" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B617" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="618" spans="1:2">
       <c r="A618" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B618" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="619" spans="1:2">
       <c r="A619" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B619" t="s">
         <v>915</v>
@@ -10499,44 +10505,44 @@
         <v>916</v>
       </c>
       <c r="B620" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="621" spans="1:2">
       <c r="A621" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B621" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="622" spans="1:2">
       <c r="A622" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B622" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="623" spans="1:2">
       <c r="A623" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B623" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="624" spans="1:2">
       <c r="A624" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B624" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
     </row>
     <row r="625" spans="1:2">
       <c r="A625" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B625" t="s">
         <v>922</v>
@@ -10555,12 +10561,12 @@
         <v>925</v>
       </c>
       <c r="B627" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="628" spans="1:2">
       <c r="A628" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B628" t="s">
         <v>927</v>
@@ -10571,12 +10577,12 @@
         <v>928</v>
       </c>
       <c r="B629" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="630" spans="1:2">
       <c r="A630" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B630" t="s">
         <v>930</v>
@@ -10587,188 +10593,188 @@
         <v>931</v>
       </c>
       <c r="B631" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="632" spans="1:2">
       <c r="A632" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B632" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
     </row>
     <row r="633" spans="1:2">
       <c r="A633" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B633" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="634" spans="1:2">
       <c r="A634" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B634" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="635" spans="1:2">
       <c r="A635" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B635" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="636" spans="1:2">
       <c r="A636" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B636" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="637" spans="1:2">
       <c r="A637" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B637" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="638" spans="1:2">
       <c r="A638" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B638" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="639" spans="1:2">
       <c r="A639" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B639" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="640" spans="1:2">
       <c r="A640" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B640" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="641" spans="1:2">
       <c r="A641" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B641" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="642" spans="1:2">
       <c r="A642" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B642" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="643" spans="1:2">
       <c r="A643" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B643" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="644" spans="1:2">
       <c r="A644" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B644" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="645" spans="1:2">
       <c r="A645" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B645" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="646" spans="1:2">
       <c r="A646" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B646" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="647" spans="1:2">
       <c r="A647" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B647" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="648" spans="1:2">
       <c r="A648" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B648" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="649" spans="1:2">
       <c r="A649" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B649" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="650" spans="1:2">
       <c r="A650" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B650" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
     </row>
     <row r="651" spans="1:2">
       <c r="A651" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B651" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="652" spans="1:2">
       <c r="A652" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B652" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
     </row>
     <row r="653" spans="1:2">
       <c r="A653" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B653" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="654" spans="1:2">
       <c r="A654" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B654" t="s">
         <v>955</v>
@@ -10803,28 +10809,28 @@
         <v>962</v>
       </c>
       <c r="B658" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="659" spans="1:2">
       <c r="A659" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B659" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="660" spans="1:2">
       <c r="A660" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B660" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="661" spans="1:2">
       <c r="A661" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B661" t="s">
         <v>966</v>
@@ -10835,20 +10841,20 @@
         <v>967</v>
       </c>
       <c r="B662" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="663" spans="1:2">
       <c r="A663" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B663" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
     </row>
     <row r="664" spans="1:2">
       <c r="A664" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B664" t="s">
         <v>970</v>
@@ -10859,44 +10865,44 @@
         <v>971</v>
       </c>
       <c r="B665" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="666" spans="1:2">
       <c r="A666" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B666" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="667" spans="1:2">
       <c r="A667" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B667" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
     </row>
     <row r="668" spans="1:2">
       <c r="A668" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B668" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="669" spans="1:2">
       <c r="A669" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B669" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="670" spans="1:2">
       <c r="A670" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B670" t="s">
         <v>977</v>
@@ -10907,52 +10913,52 @@
         <v>978</v>
       </c>
       <c r="B671" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="672" spans="1:2">
       <c r="A672" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B672" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="673" spans="1:2">
       <c r="A673" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B673" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="674" spans="1:2">
       <c r="A674" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B674" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="675" spans="1:2">
       <c r="A675" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B675" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
     </row>
     <row r="676" spans="1:2">
       <c r="A676" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B676" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="677" spans="1:2">
       <c r="A677" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B677" t="s">
         <v>985</v>
@@ -10963,12 +10969,12 @@
         <v>986</v>
       </c>
       <c r="B678" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="679" spans="1:2">
       <c r="A679" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B679" t="s">
         <v>988</v>
@@ -10987,68 +10993,68 @@
         <v>991</v>
       </c>
       <c r="B681" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="682" spans="1:2">
       <c r="A682" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B682" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="683" spans="1:2">
       <c r="A683" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B683" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
     </row>
     <row r="684" spans="1:2">
       <c r="A684" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B684" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="685" spans="1:2">
       <c r="A685" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B685" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
     </row>
     <row r="686" spans="1:2">
       <c r="A686" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B686" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="687" spans="1:2">
       <c r="A687" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B687" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
     </row>
     <row r="688" spans="1:2">
       <c r="A688" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B688" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="689" spans="1:2">
       <c r="A689" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B689" t="s">
         <v>1000</v>
@@ -11067,20 +11073,20 @@
         <v>1003</v>
       </c>
       <c r="B691" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="692" spans="1:2">
       <c r="A692" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B692" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="693" spans="1:2">
       <c r="A693" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B693" t="s">
         <v>1006</v>
@@ -11099,12 +11105,12 @@
         <v>1009</v>
       </c>
       <c r="B695" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="696" spans="1:2">
       <c r="A696" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B696" t="s">
         <v>1011</v>
@@ -11139,12 +11145,12 @@
         <v>1018</v>
       </c>
       <c r="B700" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="701" spans="1:2">
       <c r="A701" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B701" t="s">
         <v>1020</v>
@@ -11163,12 +11169,12 @@
         <v>1023</v>
       </c>
       <c r="B703" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="704" spans="1:2">
       <c r="A704" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B704" t="s">
         <v>1025</v>
@@ -11211,36 +11217,36 @@
         <v>1034</v>
       </c>
       <c r="B709" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="710" spans="1:2">
       <c r="A710" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B710" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="711" spans="1:2">
       <c r="A711" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B711" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="712" spans="1:2">
       <c r="A712" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B712" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="713" spans="1:2">
       <c r="A713" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B713" t="s">
         <v>1039</v>
@@ -11251,76 +11257,76 @@
         <v>1040</v>
       </c>
       <c r="B714" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="715" spans="1:2">
       <c r="A715" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B715" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="716" spans="1:2">
       <c r="A716" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B716" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="717" spans="1:2">
       <c r="A717" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B717" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="718" spans="1:2">
       <c r="A718" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B718" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="719" spans="1:2">
       <c r="A719" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B719" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="720" spans="1:2">
       <c r="A720" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B720" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="721" spans="1:2">
       <c r="A721" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B721" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="722" spans="1:2">
       <c r="A722" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B722" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="723" spans="1:2">
       <c r="A723" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="B723" t="s">
         <v>1050</v>
@@ -11339,20 +11345,20 @@
         <v>1053</v>
       </c>
       <c r="B725" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="726" spans="1:2">
       <c r="A726" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B726" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="727" spans="1:2">
       <c r="A727" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B727" t="s">
         <v>1056</v>
@@ -11363,12 +11369,12 @@
         <v>1057</v>
       </c>
       <c r="B728" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="729" spans="1:2">
       <c r="A729" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B729" t="s">
         <v>1059</v>
@@ -11379,12 +11385,12 @@
         <v>1060</v>
       </c>
       <c r="B730" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="731" spans="1:2">
       <c r="A731" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B731" t="s">
         <v>1062</v>
@@ -11395,12 +11401,12 @@
         <v>1063</v>
       </c>
       <c r="B732" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="733" spans="1:2">
       <c r="A733" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B733" t="s">
         <v>1065</v>
@@ -11411,12 +11417,12 @@
         <v>1066</v>
       </c>
       <c r="B734" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="735" spans="1:2">
       <c r="A735" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B735" t="s">
         <v>1068</v>
@@ -11435,20 +11441,20 @@
         <v>1071</v>
       </c>
       <c r="B737" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="738" spans="1:2">
       <c r="A738" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B738" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="739" spans="1:2">
       <c r="A739" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B739" t="s">
         <v>1074</v>
@@ -11459,12 +11465,12 @@
         <v>1075</v>
       </c>
       <c r="B740" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="741" spans="1:2">
       <c r="A741" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B741" t="s">
         <v>1077</v>
@@ -11475,68 +11481,68 @@
         <v>1078</v>
       </c>
       <c r="B742" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="743" spans="1:2">
       <c r="A743" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B743" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="744" spans="1:2">
       <c r="A744" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B744" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="745" spans="1:2">
       <c r="A745" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B745" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="746" spans="1:2">
       <c r="A746" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B746" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="747" spans="1:2">
       <c r="A747" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B747" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="748" spans="1:2">
       <c r="A748" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B748" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="749" spans="1:2">
       <c r="A749" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B749" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="750" spans="1:2">
       <c r="A750" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B750" t="s">
         <v>1087</v>
@@ -11547,12 +11553,12 @@
         <v>1088</v>
       </c>
       <c r="B751" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="752" spans="1:2">
       <c r="A752" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B752" t="s">
         <v>1090</v>
@@ -11571,36 +11577,36 @@
         <v>1093</v>
       </c>
       <c r="B754" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="755" spans="1:2">
       <c r="A755" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B755" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="756" spans="1:2">
       <c r="A756" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B756" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="757" spans="1:2">
       <c r="A757" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B757" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="758" spans="1:2">
       <c r="A758" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B758" t="s">
         <v>1098</v>
@@ -11611,20 +11617,20 @@
         <v>1099</v>
       </c>
       <c r="B759" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="760" spans="1:2">
       <c r="A760" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B760" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="761" spans="1:2">
       <c r="A761" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B761" t="s">
         <v>1102</v>
@@ -11659,20 +11665,20 @@
         <v>1109</v>
       </c>
       <c r="B765" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="766" spans="1:2">
       <c r="A766" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B766" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="767" spans="1:2">
       <c r="A767" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B767" t="s">
         <v>1112</v>
@@ -11691,12 +11697,12 @@
         <v>1115</v>
       </c>
       <c r="B769" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="770" spans="1:2">
       <c r="A770" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B770" t="s">
         <v>1117</v>
@@ -11707,20 +11713,20 @@
         <v>1118</v>
       </c>
       <c r="B771" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
     </row>
     <row r="772" spans="1:2">
       <c r="A772" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B772" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="773" spans="1:2">
       <c r="A773" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B773" t="s">
         <v>1121</v>
@@ -11763,12 +11769,12 @@
         <v>1130</v>
       </c>
       <c r="B778" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="779" spans="1:2">
       <c r="A779" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B779" t="s">
         <v>1132</v>
@@ -11787,44 +11793,44 @@
         <v>1135</v>
       </c>
       <c r="B781" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="782" spans="1:2">
       <c r="A782" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B782" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="783" spans="1:2">
       <c r="A783" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B783" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="784" spans="1:2">
       <c r="A784" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B784" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="785" spans="1:2">
       <c r="A785" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B785" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="786" spans="1:2">
       <c r="A786" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B786" t="s">
         <v>1141</v>
@@ -11835,12 +11841,12 @@
         <v>1142</v>
       </c>
       <c r="B787" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="788" spans="1:2">
       <c r="A788" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B788" t="s">
         <v>1144</v>
@@ -11867,44 +11873,44 @@
         <v>1149</v>
       </c>
       <c r="B791" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="792" spans="1:2">
       <c r="A792" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B792" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="793" spans="1:2">
       <c r="A793" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B793" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="794" spans="1:2">
       <c r="A794" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B794" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="795" spans="1:2">
       <c r="A795" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B795" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="796" spans="1:2">
       <c r="A796" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B796" t="s">
         <v>1155</v>
@@ -11915,116 +11921,116 @@
         <v>1156</v>
       </c>
       <c r="B797" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="798" spans="1:2">
       <c r="A798" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B798" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="799" spans="1:2">
       <c r="A799" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B799" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="800" spans="1:2">
       <c r="A800" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B800" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="801" spans="1:2">
       <c r="A801" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B801" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="802" spans="1:2">
       <c r="A802" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B802" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="803" spans="1:2">
       <c r="A803" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B803" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="804" spans="1:2">
       <c r="A804" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B804" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="805" spans="1:2">
       <c r="A805" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B805" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="806" spans="1:2">
       <c r="A806" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B806" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="807" spans="1:2">
       <c r="A807" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B807" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="808" spans="1:2">
       <c r="A808" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B808" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="809" spans="1:2">
       <c r="A809" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B809" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="810" spans="1:2">
       <c r="A810" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B810" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="811" spans="1:2">
       <c r="A811" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B811" t="s">
         <v>1171</v>
@@ -12059,44 +12065,44 @@
         <v>1178</v>
       </c>
       <c r="B815" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="816" spans="1:2">
       <c r="A816" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B816" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="817" spans="1:2">
       <c r="A817" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B817" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="818" spans="1:2">
       <c r="A818" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B818" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="819" spans="1:2">
       <c r="A819" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B819" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="820" spans="1:2">
       <c r="A820" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B820" t="s">
         <v>1184</v>
@@ -12131,36 +12137,36 @@
         <v>1191</v>
       </c>
       <c r="B824" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="825" spans="1:2">
       <c r="A825" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B825" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="826" spans="1:2">
       <c r="A826" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B826" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="827" spans="1:2">
       <c r="A827" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B827" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="828" spans="1:2">
       <c r="A828" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B828" t="s">
         <v>1196</v>
@@ -12171,28 +12177,28 @@
         <v>1197</v>
       </c>
       <c r="B829" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="830" spans="1:2">
       <c r="A830" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B830" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="831" spans="1:2">
       <c r="A831" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B831" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="832" spans="1:2">
       <c r="A832" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B832" t="s">
         <v>1201</v>
@@ -12219,12 +12225,12 @@
         <v>1206</v>
       </c>
       <c r="B835" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="836" spans="1:2">
       <c r="A836" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B836" t="s">
         <v>1208</v>
@@ -12235,28 +12241,28 @@
         <v>1209</v>
       </c>
       <c r="B837" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="838" spans="1:2">
       <c r="A838" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B838" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="839" spans="1:2">
       <c r="A839" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B839" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="840" spans="1:2">
       <c r="A840" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B840" t="s">
         <v>1213</v>
@@ -12267,44 +12273,44 @@
         <v>1214</v>
       </c>
       <c r="B841" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="842" spans="1:2">
       <c r="A842" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B842" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="843" spans="1:2">
       <c r="A843" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B843" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="844" spans="1:2">
       <c r="A844" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B844" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="845" spans="1:2">
       <c r="A845" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B845" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="846" spans="1:2">
       <c r="A846" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B846" t="s">
         <v>1220</v>
@@ -12315,148 +12321,148 @@
         <v>1221</v>
       </c>
       <c r="B847" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="848" spans="1:2">
       <c r="A848" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B848" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="849" spans="1:2">
       <c r="A849" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B849" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="850" spans="1:2">
       <c r="A850" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B850" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="851" spans="1:2">
       <c r="A851" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B851" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="852" spans="1:2">
       <c r="A852" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B852" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
     </row>
     <row r="853" spans="1:2">
       <c r="A853" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B853" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="854" spans="1:2">
       <c r="A854" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B854" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="855" spans="1:2">
       <c r="A855" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B855" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="856" spans="1:2">
       <c r="A856" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B856" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="857" spans="1:2">
       <c r="A857" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B857" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="858" spans="1:2">
       <c r="A858" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B858" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="859" spans="1:2">
       <c r="A859" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B859" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="860" spans="1:2">
       <c r="A860" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B860" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="861" spans="1:2">
       <c r="A861" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B861" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="862" spans="1:2">
       <c r="A862" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B862" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="863" spans="1:2">
       <c r="A863" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B863" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="864" spans="1:2">
       <c r="A864" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B864" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="865" spans="1:2">
       <c r="A865" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B865" t="s">
         <v>1240</v>
@@ -12491,28 +12497,28 @@
         <v>1247</v>
       </c>
       <c r="B869" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="870" spans="1:2">
       <c r="A870" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B870" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="871" spans="1:2">
       <c r="A871" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B871" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="872" spans="1:2">
       <c r="A872" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B872" t="s">
         <v>1251</v>
@@ -12523,68 +12529,68 @@
         <v>1252</v>
       </c>
       <c r="B873" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="874" spans="1:2">
       <c r="A874" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B874" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="875" spans="1:2">
       <c r="A875" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B875" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="876" spans="1:2">
       <c r="A876" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B876" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="877" spans="1:2">
       <c r="A877" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B877" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="878" spans="1:2">
       <c r="A878" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B878" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="879" spans="1:2">
       <c r="A879" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B879" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="880" spans="1:2">
       <c r="A880" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B880" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="881" spans="1:2">
       <c r="A881" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B881" t="s">
         <v>1261</v>
@@ -12595,28 +12601,28 @@
         <v>1262</v>
       </c>
       <c r="B882" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="883" spans="1:2">
       <c r="A883" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B883" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="884" spans="1:2">
       <c r="A884" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B884" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="885" spans="1:2">
       <c r="A885" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B885" t="s">
         <v>1266</v>
@@ -12627,12 +12633,12 @@
         <v>1267</v>
       </c>
       <c r="B886" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="887" spans="1:2">
       <c r="A887" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B887" t="s">
         <v>1269</v>
@@ -12643,12 +12649,12 @@
         <v>1270</v>
       </c>
       <c r="B888" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="889" spans="1:2">
       <c r="A889" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="B889" t="s">
         <v>1272</v>
@@ -12667,20 +12673,20 @@
         <v>1275</v>
       </c>
       <c r="B891" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="892" spans="1:2">
       <c r="A892" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="B892" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="893" spans="1:2">
       <c r="A893" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="B893" t="s">
         <v>1278</v>
@@ -12699,44 +12705,44 @@
         <v>1281</v>
       </c>
       <c r="B895" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="896" spans="1:2">
       <c r="A896" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="B896" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="897" spans="1:2">
       <c r="A897" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="B897" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="898" spans="1:2">
       <c r="A898" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B898" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="899" spans="1:2">
       <c r="A899" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="B899" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="900" spans="1:2">
       <c r="A900" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B900" t="s">
         <v>1287</v>
@@ -12747,44 +12753,44 @@
         <v>1288</v>
       </c>
       <c r="B901" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="902" spans="1:2">
       <c r="A902" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B902" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="903" spans="1:2">
       <c r="A903" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="B903" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="904" spans="1:2">
       <c r="A904" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B904" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="905" spans="1:2">
       <c r="A905" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="B905" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="906" spans="1:2">
       <c r="A906" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="B906" t="s">
         <v>1294</v>
@@ -12795,12 +12801,12 @@
         <v>1295</v>
       </c>
       <c r="B907" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="908" spans="1:2">
       <c r="A908" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="B908" t="s">
         <v>1297</v>
@@ -12811,36 +12817,36 @@
         <v>1298</v>
       </c>
       <c r="B909" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="910" spans="1:2">
       <c r="A910" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="B910" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="911" spans="1:2">
       <c r="A911" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="B911" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="912" spans="1:2">
       <c r="A912" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="B912" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="913" spans="1:2">
       <c r="A913" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="B913" t="s">
         <v>1303</v>
@@ -12867,68 +12873,68 @@
         <v>1308</v>
       </c>
       <c r="B916" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="917" spans="1:2">
       <c r="A917" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="B917" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="918" spans="1:2">
       <c r="A918" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="B918" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="919" spans="1:2">
       <c r="A919" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="B919" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="920" spans="1:2">
       <c r="A920" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="B920" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="921" spans="1:2">
       <c r="A921" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="B921" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="922" spans="1:2">
       <c r="A922" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="B922" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="923" spans="1:2">
       <c r="A923" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="B923" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="924" spans="1:2">
       <c r="A924" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="B924" t="s">
         <v>1317</v>
@@ -12955,28 +12961,28 @@
         <v>1322</v>
       </c>
       <c r="B927" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="928" spans="1:2">
       <c r="A928" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B928" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="929" spans="1:2">
       <c r="A929" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B929" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="930" spans="1:2">
       <c r="A930" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B930" t="s">
         <v>1326</v>
@@ -13019,20 +13025,20 @@
         <v>1335</v>
       </c>
       <c r="B935" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="936" spans="1:2">
       <c r="A936" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B936" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
     </row>
     <row r="937" spans="1:2">
       <c r="A937" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B937" t="s">
         <v>1338</v>
@@ -13043,12 +13049,12 @@
         <v>1339</v>
       </c>
       <c r="B938" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="939" spans="1:2">
       <c r="A939" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B939" t="s">
         <v>1341</v>
@@ -13067,12 +13073,12 @@
         <v>1344</v>
       </c>
       <c r="B941" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="942" spans="1:2">
       <c r="A942" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B942" t="s">
         <v>1346</v>
@@ -13091,36 +13097,36 @@
         <v>1349</v>
       </c>
       <c r="B944" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="945" spans="1:2">
       <c r="A945" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="B945" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="946" spans="1:2">
       <c r="A946" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B946" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="947" spans="1:2">
       <c r="A947" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="B947" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="948" spans="1:2">
       <c r="A948" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B948" t="s">
         <v>1354</v>
@@ -13179,28 +13185,28 @@
         <v>1367</v>
       </c>
       <c r="B955" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="956" spans="1:2">
       <c r="A956" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="B956" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="957" spans="1:2">
       <c r="A957" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B957" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="958" spans="1:2">
       <c r="A958" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B958" t="s">
         <v>1371</v>
@@ -13211,68 +13217,68 @@
         <v>1372</v>
       </c>
       <c r="B959" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="960" spans="1:2">
       <c r="A960" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B960" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="961" spans="1:2">
       <c r="A961" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B961" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="962" spans="1:2">
       <c r="A962" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="B962" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="963" spans="1:2">
       <c r="A963" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B963" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="964" spans="1:2">
       <c r="A964" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="B964" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="965" spans="1:2">
       <c r="A965" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B965" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="966" spans="1:2">
       <c r="A966" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="B966" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="967" spans="1:2">
       <c r="A967" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B967" t="s">
         <v>1381</v>
@@ -13299,20 +13305,20 @@
         <v>1386</v>
       </c>
       <c r="B970" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
     </row>
     <row r="971" spans="1:2">
       <c r="A971" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="B971" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="972" spans="1:2">
       <c r="A972" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B972" t="s">
         <v>1389</v>
@@ -13339,20 +13345,20 @@
         <v>1394</v>
       </c>
       <c r="B975" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="976" spans="1:2">
       <c r="A976" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="B976" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="977" spans="1:2">
       <c r="A977" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="B977" t="s">
         <v>1397</v>
@@ -13363,44 +13369,44 @@
         <v>1398</v>
       </c>
       <c r="B978" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="979" spans="1:2">
       <c r="A979" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="B979" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="980" spans="1:2">
       <c r="A980" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B980" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="981" spans="1:2">
       <c r="A981" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="B981" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="982" spans="1:2">
       <c r="A982" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B982" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="983" spans="1:2">
       <c r="A983" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B983" t="s">
         <v>1404</v>
@@ -13443,68 +13449,68 @@
         <v>1413</v>
       </c>
       <c r="B988" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="989" spans="1:2">
       <c r="A989" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B989" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="990" spans="1:2">
       <c r="A990" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B990" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="991" spans="1:2">
       <c r="A991" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B991" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="992" spans="1:2">
       <c r="A992" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B992" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="993" spans="1:2">
       <c r="A993" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B993" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="994" spans="1:2">
       <c r="A994" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B994" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
     </row>
     <row r="995" spans="1:2">
       <c r="A995" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B995" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="996" spans="1:2">
       <c r="A996" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B996" t="s">
         <v>1422</v>
@@ -13515,28 +13521,28 @@
         <v>1423</v>
       </c>
       <c r="B997" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
     </row>
     <row r="998" spans="1:2">
       <c r="A998" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="B998" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="999" spans="1:2">
       <c r="A999" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B999" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="1000" spans="1:2">
       <c r="A1000" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="B1000" t="s">
         <v>1427</v>
@@ -13547,60 +13553,60 @@
         <v>1428</v>
       </c>
       <c r="B1001" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="1002" spans="1:2">
       <c r="A1002" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B1002" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="1003" spans="1:2">
       <c r="A1003" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B1003" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="1004" spans="1:2">
       <c r="A1004" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B1004" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="1005" spans="1:2">
       <c r="A1005" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B1005" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="1006" spans="1:2">
       <c r="A1006" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B1006" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="1007" spans="1:2">
       <c r="A1007" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B1007" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="1008" spans="1:2">
       <c r="A1008" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B1008" t="s">
         <v>1436</v>
@@ -13619,28 +13625,28 @@
         <v>1439</v>
       </c>
       <c r="B1010" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1011" spans="1:2">
       <c r="A1011" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B1011" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="1012" spans="1:2">
       <c r="A1012" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B1012" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="1013" spans="1:2">
       <c r="A1013" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B1013" t="s">
         <v>1443</v>
@@ -13651,12 +13657,12 @@
         <v>1444</v>
       </c>
       <c r="B1014" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="1015" spans="1:2">
       <c r="A1015" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B1015" t="s">
         <v>1446</v>
@@ -13675,36 +13681,36 @@
         <v>1449</v>
       </c>
       <c r="B1017" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="1018" spans="1:2">
       <c r="A1018" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B1018" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="1019" spans="1:2">
       <c r="A1019" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="B1019" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="1020" spans="1:2">
       <c r="A1020" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="B1020" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="1021" spans="1:2">
       <c r="A1021" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B1021" t="s">
         <v>1454</v>
@@ -13715,36 +13721,36 @@
         <v>1455</v>
       </c>
       <c r="B1022" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="1023" spans="1:2">
       <c r="A1023" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="B1023" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="1024" spans="1:2">
       <c r="A1024" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B1024" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
     </row>
     <row r="1025" spans="1:2">
       <c r="A1025" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="B1025" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="1026" spans="1:2">
       <c r="A1026" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B1026" t="s">
         <v>1460</v>
@@ -13763,36 +13769,36 @@
         <v>1463</v>
       </c>
       <c r="B1028" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
     </row>
     <row r="1029" spans="1:2">
       <c r="A1029" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B1029" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="1030" spans="1:2">
       <c r="A1030" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="B1030" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="1031" spans="1:2">
       <c r="A1031" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B1031" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="1032" spans="1:2">
       <c r="A1032" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="B1032" t="s">
         <v>1468</v>
@@ -13811,20 +13817,20 @@
         <v>1471</v>
       </c>
       <c r="B1034" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="1035" spans="1:2">
       <c r="A1035" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B1035" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="1036" spans="1:2">
       <c r="A1036" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="B1036" t="s">
         <v>1474</v>
@@ -13843,12 +13849,12 @@
         <v>1477</v>
       </c>
       <c r="B1038" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="1039" spans="1:2">
       <c r="A1039" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B1039" t="s">
         <v>1479</v>
@@ -13859,84 +13865,84 @@
         <v>1480</v>
       </c>
       <c r="B1040" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="1041" spans="1:2">
       <c r="A1041" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B1041" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="1042" spans="1:2">
       <c r="A1042" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="B1042" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="1043" spans="1:2">
       <c r="A1043" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B1043" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="1044" spans="1:2">
       <c r="A1044" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="B1044" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="1045" spans="1:2">
       <c r="A1045" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B1045" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="1046" spans="1:2">
       <c r="A1046" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B1046" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="1047" spans="1:2">
       <c r="A1047" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="B1047" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="1048" spans="1:2">
       <c r="A1048" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B1048" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="1049" spans="1:2">
       <c r="A1049" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="B1049" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="1050" spans="1:2">
       <c r="A1050" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B1050" t="s">
         <v>1491</v>
@@ -13947,12 +13953,12 @@
         <v>1492</v>
       </c>
       <c r="B1051" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="1052" spans="1:2">
       <c r="A1052" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="B1052" t="s">
         <v>1494</v>
@@ -13979,20 +13985,20 @@
         <v>1499</v>
       </c>
       <c r="B1055" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="1056" spans="1:2">
       <c r="A1056" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B1056" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="1057" spans="1:2">
       <c r="A1057" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B1057" t="s">
         <v>1502</v>
@@ -14003,12 +14009,12 @@
         <v>1503</v>
       </c>
       <c r="B1058" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="1059" spans="1:2">
       <c r="A1059" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="B1059" t="s">
         <v>1505</v>
@@ -14019,52 +14025,52 @@
         <v>1506</v>
       </c>
       <c r="B1060" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="1061" spans="1:2">
       <c r="A1061" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B1061" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="1062" spans="1:2">
       <c r="A1062" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="B1062" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="1063" spans="1:2">
       <c r="A1063" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="B1063" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="1064" spans="1:2">
       <c r="A1064" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="B1064" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="1065" spans="1:2">
       <c r="A1065" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B1065" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="1066" spans="1:2">
       <c r="A1066" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="B1066" t="s">
         <v>1513</v>
@@ -14131,12 +14137,12 @@
         <v>1528</v>
       </c>
       <c r="B1074" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="1075" spans="1:2">
       <c r="A1075" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="B1075" t="s">
         <v>1530</v>
@@ -14147,28 +14153,28 @@
         <v>1531</v>
       </c>
       <c r="B1076" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="1077" spans="1:2">
       <c r="A1077" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="B1077" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="1078" spans="1:2">
       <c r="A1078" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="B1078" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="1079" spans="1:2">
       <c r="A1079" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="B1079" t="s">
         <v>1535</v>
@@ -14179,12 +14185,12 @@
         <v>1536</v>
       </c>
       <c r="B1080" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="1081" spans="1:2">
       <c r="A1081" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="B1081" t="s">
         <v>1538</v>
@@ -14203,28 +14209,28 @@
         <v>1541</v>
       </c>
       <c r="B1083" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="1084" spans="1:2">
       <c r="A1084" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="B1084" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="1085" spans="1:2">
       <c r="A1085" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="B1085" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="1086" spans="1:2">
       <c r="A1086" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="B1086" t="s">
         <v>1545</v>
@@ -14235,28 +14241,28 @@
         <v>1546</v>
       </c>
       <c r="B1087" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="1088" spans="1:2">
       <c r="A1088" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="B1088" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="1089" spans="1:2">
       <c r="A1089" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="B1089" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="1090" spans="1:2">
       <c r="A1090" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="B1090" t="s">
         <v>1550</v>
@@ -14267,20 +14273,20 @@
         <v>1551</v>
       </c>
       <c r="B1091" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="1092" spans="1:2">
       <c r="A1092" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="B1092" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="1093" spans="1:2">
       <c r="A1093" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="B1093" t="s">
         <v>1554</v>
@@ -14291,12 +14297,12 @@
         <v>1555</v>
       </c>
       <c r="B1094" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="1095" spans="1:2">
       <c r="A1095" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="B1095" t="s">
         <v>1557</v>
@@ -14307,28 +14313,28 @@
         <v>1558</v>
       </c>
       <c r="B1096" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="1097" spans="1:2">
       <c r="A1097" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="B1097" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="1098" spans="1:2">
       <c r="A1098" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="B1098" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="1099" spans="1:2">
       <c r="A1099" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B1099" t="s">
         <v>1562</v>
@@ -14339,20 +14345,20 @@
         <v>1563</v>
       </c>
       <c r="B1100" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="1101" spans="1:2">
       <c r="A1101" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="B1101" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="1102" spans="1:2">
       <c r="A1102" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B1102" t="s">
         <v>1566</v>
@@ -14387,20 +14393,20 @@
         <v>1573</v>
       </c>
       <c r="B1106" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="1107" spans="1:2">
       <c r="A1107" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B1107" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
     </row>
     <row r="1108" spans="1:2">
       <c r="A1108" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="B1108" t="s">
         <v>1576</v>
@@ -14435,52 +14441,52 @@
         <v>1583</v>
       </c>
       <c r="B1112" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="1113" spans="1:2">
       <c r="A1113" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B1113" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="1114" spans="1:2">
       <c r="A1114" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="B1114" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="1115" spans="1:2">
       <c r="A1115" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B1115" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="1116" spans="1:2">
       <c r="A1116" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
       <c r="B1116" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="1117" spans="1:2">
       <c r="A1117" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B1117" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
     </row>
     <row r="1118" spans="1:2">
       <c r="A1118" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
       <c r="B1118" t="s">
         <v>1590</v>
@@ -14491,20 +14497,20 @@
         <v>1591</v>
       </c>
       <c r="B1119" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="1120" spans="1:2">
       <c r="A1120" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B1120" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="1121" spans="1:2">
       <c r="A1121" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
       <c r="B1121" t="s">
         <v>1594</v>
@@ -14515,52 +14521,52 @@
         <v>1595</v>
       </c>
       <c r="B1122" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="1123" spans="1:2">
       <c r="A1123" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B1123" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
     </row>
     <row r="1124" spans="1:2">
       <c r="A1124" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B1124" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="1125" spans="1:2">
       <c r="A1125" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
       <c r="B1125" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="1126" spans="1:2">
       <c r="A1126" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
       <c r="B1126" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="1127" spans="1:2">
       <c r="A1127" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
       <c r="B1127" t="s">
-        <v>1600</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="1128" spans="1:2">
       <c r="A1128" t="s">
-        <v>1601</v>
+        <v>1602</v>
       </c>
       <c r="B1128" t="s">
         <v>1602</v>
@@ -14571,20 +14577,20 @@
         <v>1603</v>
       </c>
       <c r="B1129" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="1130" spans="1:2">
       <c r="A1130" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
       <c r="B1130" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="1131" spans="1:2">
       <c r="A1131" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B1131" t="s">
         <v>1606</v>
@@ -14603,20 +14609,20 @@
         <v>1609</v>
       </c>
       <c r="B1133" t="s">
-        <v>1609</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="1134" spans="1:2">
       <c r="A1134" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
       <c r="B1134" t="s">
-        <v>1610</v>
+        <v>1611</v>
       </c>
     </row>
     <row r="1135" spans="1:2">
       <c r="A1135" t="s">
-        <v>1611</v>
+        <v>1612</v>
       </c>
       <c r="B1135" t="s">
         <v>1612</v>
@@ -14715,44 +14721,44 @@
         <v>1635</v>
       </c>
       <c r="B1147" t="s">
-        <v>1635</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="1148" spans="1:2">
       <c r="A1148" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
       <c r="B1148" t="s">
-        <v>1636</v>
+        <v>1637</v>
       </c>
     </row>
     <row r="1149" spans="1:2">
       <c r="A1149" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
       <c r="B1149" t="s">
-        <v>1637</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="1150" spans="1:2">
       <c r="A1150" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
       <c r="B1150" t="s">
-        <v>1638</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="1151" spans="1:2">
       <c r="A1151" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="B1151" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="1152" spans="1:2">
       <c r="A1152" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="B1152" t="s">
         <v>1641</v>
@@ -14771,36 +14777,36 @@
         <v>1644</v>
       </c>
       <c r="B1154" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="1155" spans="1:2">
       <c r="A1155" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="B1155" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="1156" spans="1:2">
       <c r="A1156" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="B1156" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
     </row>
     <row r="1157" spans="1:2">
       <c r="A1157" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="B1157" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="1158" spans="1:2">
       <c r="A1158" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="B1158" t="s">
         <v>1649</v>
@@ -14811,20 +14817,20 @@
         <v>1650</v>
       </c>
       <c r="B1159" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
     </row>
     <row r="1160" spans="1:2">
       <c r="A1160" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="B1160" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="1161" spans="1:2">
       <c r="A1161" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="B1161" t="s">
         <v>1653</v>
@@ -14859,12 +14865,12 @@
         <v>1660</v>
       </c>
       <c r="B1165" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="1166" spans="1:2">
       <c r="A1166" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="B1166" t="s">
         <v>1662</v>
@@ -14883,12 +14889,12 @@
         <v>1665</v>
       </c>
       <c r="B1168" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="1169" spans="1:2">
       <c r="A1169" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="B1169" t="s">
         <v>1667</v>
@@ -14915,124 +14921,124 @@
         <v>1672</v>
       </c>
       <c r="B1172" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="1173" spans="1:2">
       <c r="A1173" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="B1173" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="1174" spans="1:2">
       <c r="A1174" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="B1174" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="1175" spans="1:2">
       <c r="A1175" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="B1175" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="1176" spans="1:2">
       <c r="A1176" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="B1176" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="1177" spans="1:2">
       <c r="A1177" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="B1177" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="1178" spans="1:2">
       <c r="A1178" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="B1178" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="1179" spans="1:2">
       <c r="A1179" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="B1179" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="1180" spans="1:2">
       <c r="A1180" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="B1180" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="1181" spans="1:2">
       <c r="A1181" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="B1181" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="1182" spans="1:2">
       <c r="A1182" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="B1182" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="1183" spans="1:2">
       <c r="A1183" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="B1183" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="1184" spans="1:2">
       <c r="A1184" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="B1184" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="1185" spans="1:2">
       <c r="A1185" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="B1185" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="1186" spans="1:2">
       <c r="A1186" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="B1186" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
     </row>
     <row r="1187" spans="1:2">
       <c r="A1187" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="B1187" t="s">
         <v>1688</v>
@@ -15043,36 +15049,36 @@
         <v>1689</v>
       </c>
       <c r="B1188" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="1189" spans="1:2">
       <c r="A1189" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="B1189" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="1190" spans="1:2">
       <c r="A1190" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="B1190" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
     </row>
     <row r="1191" spans="1:2">
       <c r="A1191" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="B1191" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="1192" spans="1:2">
       <c r="A1192" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="B1192" t="s">
         <v>1694</v>
@@ -15091,219 +15097,227 @@
         <v>1697</v>
       </c>
       <c r="B1194" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="1195" spans="1:2">
       <c r="A1195" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="B1195" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="1196" spans="1:2">
       <c r="A1196" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="B1196" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="1197" spans="1:2">
       <c r="A1197" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="B1197" t="s">
-        <v>388</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="1198" spans="1:2">
       <c r="A1198" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="B1198" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
     </row>
     <row r="1199" spans="1:2">
       <c r="A1199" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="B1199" t="s">
-        <v>1702</v>
+        <v>390</v>
       </c>
     </row>
     <row r="1200" spans="1:2">
       <c r="A1200" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="B1200" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
     </row>
     <row r="1201" spans="1:2">
       <c r="A1201" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="B1201" t="s">
-        <v>649</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="1202" spans="1:2">
       <c r="A1202" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="B1202" t="s">
-        <v>1705</v>
+        <v>651</v>
       </c>
     </row>
     <row r="1203" spans="1:2">
       <c r="A1203" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="B1203" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
     </row>
     <row r="1204" spans="1:2">
       <c r="A1204" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="B1204" t="s">
-        <v>930</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="1205" spans="1:2">
       <c r="A1205" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="B1205" t="s">
-        <v>1708</v>
+        <v>932</v>
       </c>
     </row>
     <row r="1206" spans="1:2">
       <c r="A1206" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="B1206" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="1207" spans="1:2">
       <c r="A1207" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="B1207" t="s">
-        <v>1006</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="1208" spans="1:2">
       <c r="A1208" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="B1208" t="s">
-        <v>1711</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="1209" spans="1:2">
       <c r="A1209" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="B1209" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="1210" spans="1:2">
       <c r="A1210" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="B1210" t="s">
-        <v>1074</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="1211" spans="1:2">
       <c r="A1211" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="B1211" t="s">
-        <v>1129</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="1212" spans="1:2">
       <c r="A1212" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="B1212" t="s">
-        <v>1715</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="1213" spans="1:2">
       <c r="A1213" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="B1213" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="1214" spans="1:2">
       <c r="A1214" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="B1214" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="1215" spans="1:2">
       <c r="A1215" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="B1215" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
     </row>
     <row r="1216" spans="1:2">
       <c r="A1216" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="B1216" t="s">
-        <v>1438</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="1217" spans="1:2">
       <c r="A1217" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="B1217" t="s">
-        <v>1720</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="1218" spans="1:2">
       <c r="A1218" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="B1218" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="1219" spans="1:2">
       <c r="A1219" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="B1219" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="1220" spans="1:2">
       <c r="A1220" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="B1220" t="s">
-        <v>1557</v>
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:2">
+      <c r="A1221" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B1221" t="s">
+        <v>1559</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B1220"/>
+  <autoFilter ref="A1:B1221"/>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
